--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-09-21T23:11:16</t>
+          <t>CreatedAt: 2026-09-22T04:10:26</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -653,70 +653,70 @@
         <v>20.71</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>54.44</v>
+        <v>20.62</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>20.64</v>
+        <v>56.06</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>33.05</v>
+        <v>20.46</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45.5</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>44.9</v>
+        <v>80.13</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>39.63</v>
+        <v>51.22</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>35.24</v>
+        <v>34.58</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>31.28</v>
+        <v>31.53</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>31.28</v>
+        <v>31.61</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>31.56</v>
+        <v>34.04</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>32.27</v>
+        <v>34.04</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>32.24</v>
+        <v>33.97</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>39.67</v>
+        <v>33.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>46.52</v>
+        <v>39.71</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>54.05</v>
+        <v>47.53</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>53.84</v>
+        <v>49.49</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>51.45</v>
+        <v>47.52</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>46.56</v>
+        <v>47.61</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>35.83</v>
+        <v>47.38</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>33.76</v>
+        <v>45.11</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>31.22</v>
+        <v>35.66</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>36.35</v>
+        <v>43.19</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>38.96</v>
@@ -824,70 +824,70 @@
         <v>0.12</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-0.31</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.28</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.52</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.95</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.19</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.47</v>
+        <v>-1.04</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.68</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.39</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="7">
@@ -905,19 +905,19 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>33.82</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>40.86</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>36.47</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>43.32</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>0</v>
@@ -1073,73 +1073,73 @@
         <v>21.39</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>21.55</v>
+        <v>21.57</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>21.44</v>
+        <v>16.03</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>34.15</v>
+        <v>21.61</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>46.42</v>
+        <v>32.59</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>45.76</v>
+        <v>37.64</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>40.47</v>
+        <v>52.53</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>35.8</v>
+        <v>35.46</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>32.14</v>
+        <v>32.3</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>32.3</v>
+        <v>32.98</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.53</v>
+        <v>35.78</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>33.13</v>
+        <v>35.23</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>33.23</v>
+        <v>35.38</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>40.68</v>
+        <v>35.23</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>48.19</v>
+        <v>41.61</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>55.75</v>
+        <v>49.54</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>55.43</v>
+        <v>51.16</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>53.38</v>
+        <v>49.16</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>48.6</v>
+        <v>49.59</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>37.38</v>
+        <v>49.26</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>35.24</v>
+        <v>47.31</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>32.21</v>
+        <v>36.71</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>37.08</v>
+        <v>44.33</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>39.58</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="10">
@@ -1241,70 +1241,70 @@
         <v>0.73</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.32</v>
+        <v>0.75</v>
       </c>
       <c r="I11" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K11" s="3" t="n">
         <v>0.45</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.55</v>
-      </c>
       <c r="L11" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Y11" s="3" t="n">
         <v>0.71</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>0.41</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>0.08</v>
@@ -1424,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>0</v>
@@ -1493,73 +1493,73 @@
         <v>21.39</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>21.55</v>
+        <v>21.57</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>21.44</v>
+        <v>23.61</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>34.15</v>
+        <v>26.52</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>46.42</v>
+        <v>32.59</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>45.76</v>
+        <v>37.64</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>40.51</v>
+        <v>52.58</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>35.8</v>
+        <v>35.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>32.14</v>
+        <v>36.53</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>36.55</v>
+        <v>37.37</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36.9</v>
+        <v>35.78</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>37.33</v>
+        <v>39.91</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>37.45</v>
+        <v>40.1</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>46.25</v>
+        <v>40.03</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>48.24</v>
+        <v>47.31</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>63.79</v>
+        <v>56.63</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>63.48</v>
+        <v>58.48</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>61</v>
+        <v>55.93</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>55.44</v>
+        <v>56.53</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>42.31</v>
+        <v>56.12</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>39.96</v>
+        <v>54.44</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>36.35</v>
+        <v>41.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>37.08</v>
+        <v>50.46</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>39.58</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="15">
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1598,49 +1598,49 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>4.22</v>
+        <v>4.38</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4.22</v>
+        <v>4.68</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>5.58</v>
+        <v>4.8</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>7.99</v>
+        <v>7.04</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>8.06</v>
+        <v>7.33</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>7.57</v>
+        <v>6.78</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>6.79</v>
+        <v>6.93</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>4.93</v>
+        <v>6.86</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>4.73</v>
+        <v>7.13</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1661,70 +1661,70 @@
         <v>0.73</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G16" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.14</v>
-      </c>
       <c r="K16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.74</v>
+        <v>1.09</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.72</v>
+        <v>1.54</v>
       </c>
       <c r="N16" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X16" s="3" t="n">
         <v>0.66</v>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>0.84</v>
-      </c>
       <c r="Y16" s="3" t="n">
-        <v>0.41</v>
+        <v>0.71</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>0.08</v>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0</v>
@@ -1913,73 +1913,73 @@
         <v>63.24</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>60.22</v>
+        <v>60.24</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>20.68</v>
+        <v>57.03</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>33.09</v>
+        <v>59.06</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45.41</v>
+        <v>66.09</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>44.81</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>39.63</v>
+        <v>87.83</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>35.27</v>
+        <v>34.62</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>31.34</v>
+        <v>31.56</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>31.37</v>
+        <v>31.67</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>31.62</v>
+        <v>34.1</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>32.33</v>
+        <v>34.07</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>32.3</v>
+        <v>34.04</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>39.67</v>
+        <v>33.94</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>46.52</v>
+        <v>39.75</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>53.99</v>
+        <v>47.48</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>53.74</v>
+        <v>49.44</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>51.4</v>
+        <v>47.47</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>46.51</v>
+        <v>47.56</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>35.79</v>
+        <v>47.29</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>33.8</v>
+        <v>45.07</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>31.28</v>
+        <v>35.66</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>36.35</v>
+        <v>43.14</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>39.07</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -2081,73 +2081,73 @@
         <v>0.06</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.03</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.11</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.18</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.28</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>-0.22</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O21" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.57</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.74</v>
       </c>
       <c r="T21" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="W21" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.72</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.39</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="22">
@@ -2165,22 +2165,22 @@
         <v>42.51</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>39.54</v>
+        <v>39.58</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0</v>
+        <v>38.54</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>34.42</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>61.57</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>36.65</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>0</v>
@@ -2333,73 +2333,73 @@
         <v>20.73</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>54.5</v>
+        <v>20.66</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>20.68</v>
+        <v>56.09</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>33.09</v>
+        <v>20.52</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45.41</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>44.81</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>39.63</v>
+        <v>51.18</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>35.27</v>
+        <v>34.62</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>31.34</v>
+        <v>31.56</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>31.37</v>
+        <v>31.67</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>31.62</v>
+        <v>34.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>32.33</v>
+        <v>34.07</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>32.3</v>
+        <v>34.04</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>39.67</v>
+        <v>33.94</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>46.52</v>
+        <v>39.75</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>53.99</v>
+        <v>47.48</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>53.74</v>
+        <v>49.44</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>51.4</v>
+        <v>47.47</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>46.51</v>
+        <v>47.56</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>35.79</v>
+        <v>47.29</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>33.8</v>
+        <v>45.07</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>31.28</v>
+        <v>35.66</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>36.35</v>
+        <v>43.14</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>39.07</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
@@ -2501,73 +2501,73 @@
         <v>0.06</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.03</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.11</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.18</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.28</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.28</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>-0.22</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="Q26" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.6</v>
-      </c>
       <c r="R26" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.57</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.74</v>
       </c>
       <c r="T26" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>-1.13</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="W26" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.72</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.39</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.47</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="27">
@@ -2585,19 +2585,19 @@
         <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>33.82</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>40.86</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0</v>
+        <v>36.47</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0</v>
+        <v>43.32</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -2756,70 +2756,70 @@
         <v>60.2</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.68</v>
+        <v>57</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>33.02</v>
+        <v>59</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45.23</v>
+        <v>66</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>44.59</v>
+        <v>98.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>39.51</v>
+        <v>87.61</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>35.2</v>
+        <v>34.55</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>31.31</v>
+        <v>31.5</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>31.31</v>
+        <v>31.58</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>31.59</v>
+        <v>34</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>32.27</v>
+        <v>33.97</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>32.27</v>
+        <v>33.97</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>39.55</v>
+        <v>33.83</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>46.29</v>
+        <v>39.59</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>53.73</v>
+        <v>47.29</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>53.53</v>
+        <v>49.2</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>51.15</v>
+        <v>47.24</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>46.29</v>
+        <v>47.42</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>35.65</v>
+        <v>46.97</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>33.7</v>
+        <v>44.81</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>31.22</v>
+        <v>35.55</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>36.2</v>
+        <v>42.93</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>39.15</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="30">
@@ -2921,73 +2921,73 @@
         <v>0.02</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.13</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.35</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.35</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.27</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.32</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.76</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.98</v>
       </c>
       <c r="T31" s="3" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="U31" s="3" t="n">
         <v>-1.38</v>
       </c>
-      <c r="U31" s="3" t="n">
-        <v>-1.34</v>
-      </c>
       <c r="V31" s="3" t="n">
-        <v>-0.64</v>
+        <v>-1.46</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.99</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="32">
@@ -3005,22 +3005,22 @@
         <v>42.51</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>39.54</v>
+        <v>39.58</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
+        <v>38.54</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>34.42</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>61.57</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>36.65</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>0</v>
@@ -3173,73 +3173,73 @@
         <v>21.85</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>22.11</v>
+        <v>22.13</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>21.92</v>
+        <v>24.08</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>34.91</v>
+        <v>27.17</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>47.28</v>
+        <v>33.24</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>46.65</v>
+        <v>38.38</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>41.26</v>
+        <v>53.49</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>36.24</v>
+        <v>36.05</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>32.7</v>
+        <v>37.17</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>37.16</v>
+        <v>38.24</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>37.48</v>
+        <v>36.86</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>37.85</v>
+        <v>40.69</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>38.11</v>
+        <v>41.04</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>46.97</v>
+        <v>40.96</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>49.35</v>
+        <v>48.52</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>58.05</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>64.69</v>
+        <v>59.71</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>62.4</v>
+        <v>57.06</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>56.82</v>
+        <v>57.93</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>43.34</v>
+        <v>57.52</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>40.87</v>
+        <v>55.95</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>36.99</v>
+        <v>42.48</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>37.73</v>
+        <v>51.42</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>40.19</v>
+        <v>40.39</v>
       </c>
     </row>
     <row r="35">
@@ -3260,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -3278,49 +3278,49 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>4.22</v>
+        <v>4.38</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>4.2</v>
+        <v>4.64</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>4.22</v>
+        <v>4.68</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>5.58</v>
+        <v>4.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>7.99</v>
+        <v>7.04</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>8.06</v>
+        <v>7.33</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>7.57</v>
+        <v>6.78</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>6.79</v>
+        <v>6.93</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>4.93</v>
+        <v>6.86</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>4.73</v>
+        <v>7.13</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>4.14</v>
+        <v>4.89</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3341,73 +3341,73 @@
         <v>1.18</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.24</v>
+        <v>2.13</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.58</v>
+        <v>1.15</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.35</v>
+        <v>1.96</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.29</v>
+        <v>2.62</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.18</v>
+        <v>1.91</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.41</v>
+        <v>2.06</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>2.22</v>
+        <v>2.91</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>2.11</v>
+        <v>2.96</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.24</v>
+        <v>3.03</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.06</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.68</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="37">
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>0</v>
@@ -3593,70 +3593,70 @@
         <v>20.71</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>54.44</v>
+        <v>20.62</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>20.64</v>
+        <v>56.06</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>33.05</v>
+        <v>20.46</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45.5</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>44.9</v>
+        <v>80.13</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>39.63</v>
+        <v>51.22</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>35.24</v>
+        <v>34.58</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>31.28</v>
+        <v>31.53</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>31.28</v>
+        <v>31.61</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>31.56</v>
+        <v>34.04</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>32.27</v>
+        <v>34.04</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>32.24</v>
+        <v>33.97</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>39.67</v>
+        <v>33.9</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>46.52</v>
+        <v>39.71</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>54.05</v>
+        <v>47.53</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>53.84</v>
+        <v>49.49</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>51.45</v>
+        <v>47.52</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>46.56</v>
+        <v>47.61</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>35.83</v>
+        <v>47.38</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>33.76</v>
+        <v>45.11</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>31.22</v>
+        <v>35.66</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>36.35</v>
+        <v>43.19</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>38.96</v>
@@ -3764,70 +3764,70 @@
         <v>0.12</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="K41" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>-0.31</v>
-      </c>
       <c r="L41" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.28</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.52</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.95</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.19</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.47</v>
+        <v>-1.04</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.68</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.39</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="42">
@@ -3845,19 +3845,19 @@
         <v>0</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>33.82</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0</v>
+        <v>40.86</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0</v>
+        <v>36.47</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0</v>
+        <v>43.32</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>0</v>
@@ -4013,73 +4013,73 @@
         <v>20.75</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>20.59</v>
+        <v>20.68</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>20.59</v>
+        <v>15.21</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>33.09</v>
+        <v>20.46</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45.86</v>
+        <v>32</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>45.53</v>
+        <v>37.18</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>39.86</v>
+        <v>51.62</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>35.31</v>
+        <v>34.72</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>31.34</v>
+        <v>31.69</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>31.25</v>
+        <v>31.61</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>31.47</v>
+        <v>34.04</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>32.21</v>
+        <v>34.07</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>32.24</v>
+        <v>34.1</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>39.79</v>
+        <v>34.1</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>46.89</v>
+        <v>40.03</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>55.02</v>
+        <v>48.24</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>54.81</v>
+        <v>50.39</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>52.69</v>
+        <v>48.66</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>47.68</v>
+        <v>48.9</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>36.44</v>
+        <v>48.57</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>34.1</v>
+        <v>45.98</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>31.31</v>
+        <v>35.94</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>36.6</v>
+        <v>43.66</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>39.35</v>
+        <v>39.47</v>
       </c>
     </row>
     <row r="45">
@@ -4181,73 +4181,73 @@
         <v>0.08</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>0.1</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.05</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="47">
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0</v>
@@ -4433,73 +4433,73 @@
         <v>21.31</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>21.06</v>
+        <v>20.93</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>21.04</v>
+        <v>15.51</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>34.08</v>
+        <v>20.81</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>47.77</v>
+        <v>32.89</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>47.63</v>
+        <v>37.45</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>41.35</v>
+        <v>51.8</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>36.46</v>
+        <v>35.04</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>32.23</v>
+        <v>31.91</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>32.73</v>
+        <v>34.83</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>33.4</v>
+        <v>34.66</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>33.23</v>
+        <v>34.55</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>41.18</v>
+        <v>34.48</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>48.43</v>
+        <v>40.6</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>56.38</v>
+        <v>48.49</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>56.34</v>
+        <v>51.16</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>54.1</v>
+        <v>49.56</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>49</v>
+        <v>50.62</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>37.73</v>
+        <v>50.18</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>35.06</v>
+        <v>47.16</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>32.18</v>
+        <v>37.32</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>38.12</v>
+        <v>44.97</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>40.77</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="50">
@@ -4601,73 +4601,73 @@
         <v>0.64</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.57</v>
+        <v>0.44</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.12</v>
+        <v>0.54</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.96</v>
+        <v>1.18</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>2.19</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1.32</v>
+        <v>0.45</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.8</v>
+        <v>0.14</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0.92</v>
+        <v>0.59</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0.76</v>
+        <v>0.45</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.19</v>
+        <v>0.38</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>1.31</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>1.41</v>
+        <v>0.44</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>1.69</v>
+        <v>0.97</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="U51" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W51" s="3" t="n">
         <v>1.37</v>
       </c>
-      <c r="V51" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W51" s="3" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X51" s="3" t="n">
-        <v>0.8</v>
+        <v>1.27</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="52">
@@ -4784,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J53" s="3" t="n">
         <v>0</v>
@@ -4856,70 +4856,70 @@
         <v>21.52</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>21.55</v>
+        <v>15.87</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>34.62</v>
+        <v>21.32</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>48.33</v>
+        <v>33.34</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>47.83</v>
+        <v>38.67</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>40.67</v>
+        <v>51.35</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>36.2</v>
+        <v>34.9</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>31.75</v>
+        <v>31.65</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>31.56</v>
+        <v>32.02</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>31.75</v>
+        <v>34.34</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>32.14</v>
+        <v>33.97</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>31.83</v>
+        <v>33.6</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>38.48</v>
+        <v>32.98</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>45.4</v>
+        <v>38.71</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>52.65</v>
+        <v>46.25</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>51.22</v>
+        <v>47.17</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>49.41</v>
+        <v>45.68</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>44.97</v>
+        <v>46.12</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>34.11</v>
+        <v>45.73</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>32.44</v>
+        <v>44.16</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>31.5</v>
+        <v>36.16</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>37.92</v>
+        <v>45.2</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>40.81</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="55">
@@ -5024,70 +5024,70 @@
         <v>1.03</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.06</v>
+        <v>0.76</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.51</v>
+        <v>1.63</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2.39</v>
+        <v>1.78</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.13</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.1</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.17</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.5</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1.12</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.2</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-2.32</v>
+        <v>-1.8</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-3.43</v>
+        <v>-3.02</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-3.11</v>
+        <v>-2.79</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-2.65</v>
+        <v>-2.68</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-2.18</v>
+        <v>-2.7</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.46</v>
+        <v>-1.63</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="57">
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J58" s="3" t="n">
         <v>0</v>
@@ -5273,73 +5273,73 @@
         <v>21.39</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>21.21</v>
+        <v>21.26</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>21.19</v>
+        <v>15.64</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>34.08</v>
+        <v>21.03</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>47.23</v>
+        <v>32.93</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>46.94</v>
+        <v>38.26</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>41.09</v>
+        <v>52.96</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>36.46</v>
+        <v>35.75</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>32.33</v>
+        <v>32.63</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>32.3</v>
+        <v>32.61</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>32.53</v>
+        <v>35.05</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>33.33</v>
+        <v>35.12</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>33.36</v>
+        <v>35.16</v>
       </c>
       <c r="P59" s="3" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="Q59" s="3" t="n">
         <v>41.18</v>
       </c>
-      <c r="Q59" s="3" t="n">
-        <v>48.53</v>
-      </c>
       <c r="R59" s="3" t="n">
-        <v>56.96</v>
+        <v>49.74</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>56.63</v>
+        <v>51.95</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>54.38</v>
+        <v>50.18</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>49.25</v>
+        <v>50.52</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>37.61</v>
+        <v>50.13</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>35.17</v>
+        <v>47.4</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>32.18</v>
+        <v>36.97</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>37.77</v>
+        <v>44.97</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>40.6</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="60">
@@ -5441,70 +5441,70 @@
         <v>0.73</v>
       </c>
       <c r="D61" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="L61" s="3" t="n">
         <v>0.72</v>
       </c>
-      <c r="E61" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>0.71</v>
-      </c>
       <c r="M61" s="3" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>1.1</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J63" s="3" t="n">
         <v>0</v>
@@ -5693,73 +5693,73 @@
         <v>21.66</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>21.48</v>
+        <v>21.5</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>21.44</v>
+        <v>15.8</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>34.51</v>
+        <v>21.27</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>47.87</v>
+        <v>33.31</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>47.63</v>
+        <v>38.75</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>41.69</v>
+        <v>53.54</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>36.95</v>
+        <v>36.2</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>32.77</v>
+        <v>33</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>32.77</v>
+        <v>33.02</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>33.03</v>
+        <v>35.45</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>33.89</v>
+        <v>35.6</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>33.92</v>
+        <v>35.6</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>41.74</v>
+        <v>35.6</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>49.29</v>
+        <v>41.7</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>57.92</v>
+        <v>50.47</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>57.53</v>
+        <v>52.72</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>55.23</v>
+        <v>50.97</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>50.03</v>
+        <v>51.31</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>38.17</v>
+        <v>50.92</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>35.61</v>
+        <v>48.1</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>32.58</v>
+        <v>37.43</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>38.2</v>
+        <v>45.58</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>41.11</v>
+        <v>41.41</v>
       </c>
     </row>
     <row r="65">
@@ -5861,73 +5861,73 @@
         <v>1</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>1.87</v>
+        <v>2.49</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.71</v>
+        <v>2.31</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="67">
@@ -6044,7 +6044,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J68" s="3" t="n">
         <v>0</v>
@@ -6113,73 +6113,73 @@
         <v>55</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>21.8</v>
+        <v>21.82</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>21.75</v>
+        <v>16.05</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>34.95</v>
+        <v>21.59</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>48.43</v>
+        <v>33.8</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>48.13</v>
+        <v>75.2</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>42.04</v>
+        <v>54.18</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>37.26</v>
+        <v>36.5</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>33.04</v>
+        <v>33.31</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>33.01</v>
+        <v>33.33</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>33.24</v>
+        <v>35.82</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>34.17</v>
+        <v>35.97</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>34.21</v>
+        <v>36.01</v>
       </c>
       <c r="P69" s="3" t="n">
+        <v>35.98</v>
+      </c>
+      <c r="Q69" s="3" t="n">
         <v>42.18</v>
       </c>
-      <c r="Q69" s="3" t="n">
-        <v>49.76</v>
-      </c>
       <c r="R69" s="3" t="n">
-        <v>58.47</v>
+        <v>51.06</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>58.08</v>
+        <v>53.27</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>55.82</v>
+        <v>51.51</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>50.56</v>
+        <v>51.86</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>38.53</v>
+        <v>51.4</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>36.06</v>
+        <v>48.66</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>32.85</v>
+        <v>37.75</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>38.77</v>
+        <v>46.16</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>41.45</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="70">
@@ -6281,73 +6281,73 @@
         <v>1.32</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.26</v>
+        <v>0.95</v>
       </c>
       <c r="F71" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Z71" s="3" t="n">
         <v>1.99</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="S71" s="3" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="T71" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="U71" s="3" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="V71" s="3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="W71" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X71" s="3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Y71" s="3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z71" s="3" t="n">
-        <v>1.95</v>
       </c>
     </row>
     <row r="72">
@@ -6377,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0</v>
+        <v>35.92</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0</v>
@@ -6464,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J73" s="3" t="n">
         <v>0</v>
@@ -6533,70 +6533,70 @@
         <v>21.26</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>21.08</v>
+        <v>21.1</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>21.06</v>
+        <v>15.52</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>33.87</v>
+        <v>20.88</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>47.09</v>
+        <v>32.72</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>46.8</v>
+        <v>38.03</v>
       </c>
       <c r="I74" s="3" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>35.61</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>32.51</v>
+      </c>
+      <c r="M74" s="3" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>34.94</v>
+      </c>
+      <c r="Q74" s="3" t="n">
         <v>40.97</v>
       </c>
-      <c r="J74" s="3" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>32.23</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="M74" s="3" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>33.23</v>
-      </c>
-      <c r="O74" s="3" t="n">
-        <v>33.23</v>
-      </c>
-      <c r="P74" s="3" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="Q74" s="3" t="n">
-        <v>48.38</v>
-      </c>
       <c r="R74" s="3" t="n">
-        <v>56.78</v>
+        <v>49.49</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>56.46</v>
+        <v>51.74</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>54.21</v>
+        <v>50.02</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>49.1</v>
+        <v>50.36</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>37.53</v>
+        <v>49.97</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>35.06</v>
+        <v>47.21</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>32.08</v>
+        <v>36.82</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>37.65</v>
+        <v>44.78</v>
       </c>
       <c r="Z74" s="3" t="n">
         <v>40.52</v>
@@ -6701,73 +6701,73 @@
         <v>0.6</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.37</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.03</v>
+        <v>0.84</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="W76" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="Y76" s="3" t="n">
         <v>1.16</v>
       </c>
-      <c r="X76" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>0.98</v>
-      </c>
       <c r="Z76" s="3" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="77">
@@ -6884,7 +6884,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J78" s="3" t="n">
         <v>0</v>
@@ -6956,70 +6956,70 @@
         <v>20.49</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>20.49</v>
+        <v>15.1</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>32.95</v>
+        <v>20.27</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45.81</v>
+        <v>31.71</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>45.44</v>
+        <v>36.89</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>40.02</v>
+        <v>51.35</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>35.66</v>
+        <v>34.9</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>31.59</v>
+        <v>31.84</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>31.59</v>
+        <v>31.9</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>31.81</v>
+        <v>34.24</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>32.46</v>
+        <v>34.14</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>32.46</v>
+        <v>34.1</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>39.99</v>
+        <v>34.1</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>47.13</v>
+        <v>39.91</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>54.97</v>
+        <v>48.05</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>54.65</v>
+        <v>50.18</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>52.53</v>
+        <v>48.47</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>47.63</v>
+        <v>48.8</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>36.3</v>
+        <v>48.42</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>33.9</v>
+        <v>45.79</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>31.37</v>
+        <v>36.05</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>36.67</v>
+        <v>43.62</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>39.5</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="80">
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0</v>
@@ -7373,73 +7373,73 @@
         <v>21.37</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>21.19</v>
+        <v>21.23</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>21.24</v>
+        <v>15.65</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>33.97</v>
+        <v>21.03</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>47.77</v>
+        <v>33</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>47.73</v>
+        <v>38.54</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>40.84</v>
+        <v>50.44</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>36.35</v>
+        <v>34.01</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>32.01</v>
+        <v>31.13</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>31.75</v>
+        <v>32.35</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>31.81</v>
+        <v>34.62</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>32.08</v>
+        <v>34.14</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>31.83</v>
+        <v>33.9</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>38.78</v>
+        <v>33.63</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>45.71</v>
+        <v>39.47</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>53.06</v>
+        <v>47.34</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>50.55</v>
+        <v>47.08</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>49.23</v>
+        <v>45.81</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>44.97</v>
+        <v>46.52</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>34.05</v>
+        <v>46.25</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>31.95</v>
+        <v>44.24</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>31.4</v>
+        <v>36.82</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>37.65</v>
+        <v>45.53</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>40.48</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="85">
@@ -7541,73 +7541,73 @@
         <v>0.71</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.02</v>
+        <v>0.76</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1.96</v>
+        <v>1.29</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.29</v>
+        <v>1.66</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.82</v>
+        <v>-0.91</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.88</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.42</v>
+        <v>-0.72</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.2</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1.2</v>
+        <v>-0.47</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-1.42</v>
+        <v>-0.43</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.91</v>
+        <v>-0.71</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-4.09</v>
+        <v>-3.11</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.3</v>
+        <v>-2.66</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.65</v>
+        <v>-2.28</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.25</v>
+        <v>-2.17</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.95</v>
+        <v>-1.55</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.03</v>
+        <v>0.77</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>0.98</v>
+        <v>1.91</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.97</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="87">
@@ -7724,7 +7724,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J88" s="3" t="n">
         <v>0</v>
@@ -7796,70 +7796,70 @@
         <v>60.2</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>20.68</v>
+        <v>57</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>33.02</v>
+        <v>59</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>45.23</v>
+        <v>66</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>44.59</v>
+        <v>98.2</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>39.51</v>
+        <v>87.61</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>35.2</v>
+        <v>34.55</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>31.31</v>
+        <v>31.5</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>31.31</v>
+        <v>31.58</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>31.59</v>
+        <v>34</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>32.27</v>
+        <v>33.97</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>32.27</v>
+        <v>33.97</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>39.55</v>
+        <v>33.83</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>46.29</v>
+        <v>39.59</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>53.73</v>
+        <v>47.29</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>53.53</v>
+        <v>49.2</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>51.15</v>
+        <v>47.24</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>46.29</v>
+        <v>47.38</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>35.65</v>
+        <v>46.97</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>33.7</v>
+        <v>44.76</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>31.22</v>
+        <v>35.55</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>36.2</v>
+        <v>42.93</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>39.15</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="90">
@@ -7961,73 +7961,73 @@
         <v>0.02</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.13</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.26</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.35</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.35</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.27</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.32</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.76</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.98</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.23</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.42</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.64</v>
+        <v>-1.46</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.2</v>
+        <v>-1.03</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="92">
@@ -8045,22 +8045,22 @@
         <v>42.51</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>39.54</v>
+        <v>39.58</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>38.54</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>34.42</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>61.57</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>36.65</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -8144,7 +8144,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="J93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-09-23T21:11:34</t>
+          <t>CreatedAt: 2026-09-24T02:10:24</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32.47</v>
+        <v>35.72</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>35.35</v>
+        <v>38.15</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>33.44</v>
+        <v>35.4</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>35.01</v>
+        <v>39.75</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>40.08</v>
+        <v>59.29</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>48.63</v>
+        <v>4.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>43.96</v>
+        <v>45.24</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>40.63</v>
+        <v>43.83</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>34.39</v>
+        <v>37.18</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>32.72</v>
+        <v>34.67</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>32.44</v>
+        <v>34.79</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>32.88</v>
+        <v>37.07</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>32.98</v>
+        <v>34.22</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>38.64</v>
+        <v>35.21</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>35.03</v>
+        <v>38.27</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>35.56</v>
+        <v>44.85</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>35.09</v>
+        <v>45.15</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>47.35</v>
+        <v>49.32</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>62.19</v>
+        <v>62.25</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>61.36</v>
+        <v>61.32</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>45.41</v>
+        <v>48.67</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>48.61</v>
+        <v>48.56</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>35.46</v>
+        <v>42.49</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>45.15</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="5">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.25</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.11</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.23</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.96</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.93</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.83</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="N6" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-0.99</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="T6" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.84</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>-1.37</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.1</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.68</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.59</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="7">
@@ -998,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>32.93</v>
+        <v>36.19</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>36.4</v>
+        <v>38.88</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>34.47</v>
+        <v>36.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>35.72</v>
+        <v>40.15</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.32</v>
+        <v>58.82</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>48.34</v>
+        <v>4.83</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.58</v>
+        <v>45.87</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>41.08</v>
+        <v>44.26</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>34.97</v>
+        <v>37.65</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.11</v>
+        <v>35.01</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.99</v>
+        <v>35.13</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>33.14</v>
+        <v>37.14</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>33.2</v>
+        <v>34.32</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>39.1</v>
+        <v>35.52</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>35.41</v>
+        <v>38.49</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>36.23</v>
+        <v>45.47</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>35.44</v>
+        <v>45.41</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>48.06</v>
+        <v>50.21</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>63.18</v>
+        <v>62.93</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>62.4</v>
+        <v>62.18</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>46.18</v>
+        <v>49.25</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>49.64</v>
+        <v>49.59</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>36.61</v>
+        <v>43.83</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>46.48</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="10">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.08</v>
+        <v>-0.66</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.53</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.45</v>
       </c>
       <c r="L11" s="3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="N11" s="3" t="n">
+      <c r="R11" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>-0.73</v>
       </c>
-      <c r="O11" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-0.46</v>
-      </c>
       <c r="T11" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.05</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.25</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.44</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="12">
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.96</v>
+        <v>36.19</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>36.4</v>
+        <v>38.88</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>34.47</v>
+        <v>36.09</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>35.72</v>
+        <v>40.15</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>40.32</v>
+        <v>58.78</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>48.34</v>
+        <v>4.83</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>44.63</v>
+        <v>45.87</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>41.08</v>
+        <v>44.3</v>
       </c>
       <c r="K14" s="3" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="L14" s="3" t="n">
         <v>35.01</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>33.11</v>
-      </c>
       <c r="M14" s="3" t="n">
-        <v>32.99</v>
+        <v>35.13</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>33.14</v>
+        <v>37.14</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>33.2</v>
+        <v>34.32</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>39.1</v>
+        <v>35.52</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>35.41</v>
+        <v>38.49</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>36.23</v>
+        <v>45.47</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>35.44</v>
+        <v>45.41</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>48.06</v>
+        <v>50.21</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>63.18</v>
+        <v>62.93</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>62.4</v>
+        <v>62.24</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>46.18</v>
+        <v>49.25</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>49.69</v>
+        <v>49.59</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>36.61</v>
+        <v>43.83</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>46.52</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="15">
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.02</v>
+        <v>0.66</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.08</v>
+        <v>-0.71</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.49</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.45</v>
       </c>
       <c r="L16" s="3" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M16" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="N16" s="3" t="n">
+      <c r="R16" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="S16" s="3" t="n">
         <v>-0.73</v>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-0.46</v>
-      </c>
       <c r="T16" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="V16" s="3" t="n">
         <v>-0.19</v>
       </c>
-      <c r="U16" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="W16" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.44</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="17">
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.5</v>
+        <v>35.79</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>35.45</v>
+        <v>38.22</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33.5</v>
+        <v>41.01</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>35.04</v>
+        <v>39.83</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>40.04</v>
+        <v>59.29</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>48.67</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>44.09</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>34.39</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>62.37</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>61.42</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>45.41</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>48.61</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>35.56</v>
+        <v>42.58</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>45.28</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="20">
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I21" s="3" t="n">
         <v>-0.36</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>-0.35</v>
-      </c>
       <c r="J21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.96</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.97</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.87</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.15</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.02</v>
       </c>
       <c r="P21" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>-1.04</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>-1.11</v>
-      </c>
       <c r="W21" s="3" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.51</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="22">
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="F22" s="3" t="n">
         <v>0</v>
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>32.5</v>
+        <v>35.79</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>35.45</v>
+        <v>38.22</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>33.5</v>
+        <v>35.55</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>35.04</v>
+        <v>39.83</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>40.04</v>
+        <v>59.29</v>
       </c>
       <c r="H24" s="3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>45.19</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>48.67</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>44.09</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>34.39</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>32.69</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>32.44</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>35.16</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>47.49</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>62.37</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>61.42</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>45.41</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>48.61</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>35.56</v>
+        <v>42.58</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>45.28</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="25">
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I26" s="3" t="n">
         <v>-0.36</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>-0.35</v>
-      </c>
       <c r="J26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.96</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.97</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.92</v>
+        <v>-0.87</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.15</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.02</v>
       </c>
       <c r="P26" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>-1.04</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>-1.11</v>
-      </c>
       <c r="W26" s="3" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>-0.63</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.51</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="27">
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0</v>
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>32.47</v>
+        <v>35.79</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>35.45</v>
+        <v>38.18</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>33.5</v>
+        <v>41.12</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>34.97</v>
+        <v>39.83</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>39.96</v>
+        <v>59.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>48.63</v>
+        <v>4.55</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>44.23</v>
+        <v>45.42</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>40.52</v>
+        <v>43.74</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>34.29</v>
+        <v>37</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>32.59</v>
+        <v>34.57</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>32.35</v>
+        <v>34.65</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>32.66</v>
+        <v>36.82</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>32.66</v>
+        <v>33.99</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>38.49</v>
+        <v>35.14</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>35.16</v>
+        <v>38.34</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>35.8</v>
+        <v>44.98</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>35.27</v>
+        <v>45.23</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.68</v>
+        <v>49.61</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>62.5</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>61.42</v>
+        <v>61.38</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>45.37</v>
+        <v>48.62</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>48.51</v>
+        <v>48.47</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>35.56</v>
+        <v>42.62</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>45.37</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="30">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.18</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="G31" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>-0.28</v>
       </c>
-      <c r="H31" s="3" t="n">
-        <v>-0.34</v>
-      </c>
       <c r="I31" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.05</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.11</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.93</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.29</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.16</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.65</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.55</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.12</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.04</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.07</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.78</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="32">
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>33.29</v>
+        <v>36.52</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>36.97</v>
+        <v>39.45</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>35.08</v>
+        <v>36.43</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>36.31</v>
+        <v>40.65</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>40.68</v>
+        <v>58.96</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>48.67</v>
+        <v>5.31</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>45.03</v>
+        <v>46.29</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>41.49</v>
+        <v>44.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>35.5</v>
+        <v>38.14</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>33.47</v>
+        <v>35.36</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>33.35</v>
+        <v>35.41</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>33.5</v>
+        <v>37.47</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>33.66</v>
+        <v>34.63</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>39.41</v>
+        <v>35.73</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>35.76</v>
+        <v>38.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>36.6</v>
+        <v>45.88</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>35.62</v>
+        <v>45.64</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>48.4</v>
+        <v>50.66</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>63.88</v>
+        <v>63.56</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>63.29</v>
+        <v>62.99</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>46.78</v>
+        <v>49.74</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>37.33</v>
+        <v>44.65</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>47.39</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="35">
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.45</v>
+        <v>-0.52</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.29</v>
+        <v>0.47</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.25</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.64</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.52</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.21</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.5</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.15</v>
+        <v>0.51</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.32</v>
+        <v>-0.06</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.76</v>
+        <v>0.57</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.37</v>
+        <v>0.05</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="37">
@@ -3518,10 +3518,10 @@
         <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.47</v>
+        <v>35.72</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>35.35</v>
+        <v>38.15</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>33.44</v>
+        <v>35.4</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>35.01</v>
+        <v>39.75</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>40.08</v>
+        <v>59.29</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>48.63</v>
+        <v>4.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>43.96</v>
+        <v>45.24</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>40.63</v>
+        <v>43.83</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>34.39</v>
+        <v>37.18</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>32.72</v>
+        <v>34.67</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>32.44</v>
+        <v>34.79</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>32.88</v>
+        <v>37.07</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>32.98</v>
+        <v>34.22</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>38.64</v>
+        <v>35.21</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>35.03</v>
+        <v>38.27</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>35.56</v>
+        <v>44.85</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>35.09</v>
+        <v>45.15</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>47.35</v>
+        <v>49.32</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>62.19</v>
+        <v>62.25</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>61.36</v>
+        <v>61.32</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>45.41</v>
+        <v>48.67</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>48.61</v>
+        <v>48.56</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>35.46</v>
+        <v>42.49</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>45.15</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="40">
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.25</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.11</v>
+        <v>0.2</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.23</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.96</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.93</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.83</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.87</v>
       </c>
       <c r="N41" s="3" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>-0.99</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>-0.91</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
       <c r="T41" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.84</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>-1.37</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.68</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.59</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="42">
@@ -3938,10 +3938,10 @@
         <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>32.83</v>
+        <v>35.97</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>35.38</v>
+        <v>38.34</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>33.57</v>
+        <v>35.33</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>35.15</v>
+        <v>39.75</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>40.36</v>
+        <v>59.78</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>48.92</v>
+        <v>4.78</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>44.27</v>
+        <v>45.6</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>41.28</v>
+        <v>44.7</v>
       </c>
       <c r="K44" s="3" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>35.19</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>35.34</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="O44" s="3" t="n">
         <v>34.83</v>
       </c>
-      <c r="L44" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="M44" s="3" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>33.56</v>
-      </c>
       <c r="P44" s="3" t="n">
-        <v>39.06</v>
+        <v>35.59</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>35.51</v>
+        <v>38.88</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>35.98</v>
+        <v>45.52</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>35.65</v>
+        <v>45.86</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>48.11</v>
+        <v>50.06</v>
       </c>
       <c r="U44" s="3" t="n">
         <v>63.31</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>62.09</v>
+        <v>62.11</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>46.18</v>
+        <v>49.44</v>
       </c>
       <c r="X44" s="3" t="n">
         <v>49.09</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>35.88</v>
+        <v>43</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>45.78</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>-0.05</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.21</v>
+        <v>-0.09</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.3</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.31</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.36</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.12</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.27</v>
       </c>
       <c r="S46" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>-0.23</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.15</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>33.91</v>
+        <v>37.12</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>36.37</v>
+        <v>39.41</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.58</v>
+        <v>35.95</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>36.23</v>
+        <v>40.44</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>41.87</v>
+        <v>60.97</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>51.33</v>
+        <v>6.54</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>45.31</v>
+        <v>46.11</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>42.38</v>
+        <v>45.06</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>35.82</v>
+        <v>38.07</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>35</v>
+        <v>36.45</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>34.53</v>
+        <v>36.61</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>35.14</v>
+        <v>39</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>35.23</v>
+        <v>35.79</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>41</v>
+        <v>36.6</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>36.86</v>
+        <v>39.35</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>36.97</v>
+        <v>45.93</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>36.63</v>
+        <v>46.46</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>49.39</v>
+        <v>50.46</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>65.12</v>
+        <v>64.27</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>63.8</v>
+        <v>62.74</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>47.21</v>
+        <v>49.89</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>50.35</v>
+        <v>49.89</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>37.03</v>
+        <v>43.88</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>47.54</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.98</v>
+        <v>1.18</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.07</v>
+        <v>0.75</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.12</v>
+        <v>0.89</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.89</v>
+        <v>0.27</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.57</v>
+        <v>-0.04</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1.4</v>
+        <v>0.95</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.21</v>
+        <v>0.95</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1.26</v>
+        <v>0.9</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>1.2</v>
+        <v>0.64</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.35</v>
+        <v>0.66</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0.92</v>
+        <v>0.35</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>0.63</v>
+        <v>0.14</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>0.73</v>
+        <v>0.33</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>1.14</v>
+        <v>0.3</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>1.56</v>
+        <v>0.64</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>1.28</v>
+        <v>0.31</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.11</v>
+        <v>0.65</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="52">
@@ -4778,10 +4778,10 @@
         <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>34.02</v>
+        <v>37.2</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>36.18</v>
+        <v>39.57</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>34.5</v>
+        <v>36.39</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>36.31</v>
+        <v>40.9</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>39.72</v>
+        <v>60.07</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>48.39</v>
+        <v>5.16</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>42.7</v>
+        <v>44.53</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>40.4</v>
+        <v>44.43</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>35.18</v>
+        <v>38.22</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>33.7</v>
+        <v>35.72</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>33.52</v>
+        <v>36.02</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>34.11</v>
+        <v>38.45</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>34</v>
+        <v>35.11</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>38.87</v>
+        <v>35.31</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>34.92</v>
+        <v>38.08</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>34.94</v>
+        <v>44.16</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>34.16</v>
+        <v>43.94</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>45.74</v>
+        <v>47.59</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>60.65</v>
+        <v>60.88</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>59.84</v>
+        <v>59.74</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>46</v>
+        <v>49.29</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>49.99</v>
+        <v>50.04</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>37.18</v>
+        <v>44.88</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>47.54</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="55">
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.8</v>
+        <v>1.35</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>-0.52</v>
+        <v>0.58</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-0.58</v>
+        <v>0.33</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.2</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.36</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.64</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.63</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.2</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-2.52</v>
+        <v>-2.57</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-2.91</v>
+        <v>-2.74</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>-2.69</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="57">
@@ -5198,10 +5198,10 @@
         <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>33.81</v>
+        <v>37.08</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>36.37</v>
+        <v>39.45</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>34.5</v>
+        <v>36.32</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>36.12</v>
+        <v>40.82</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>41.48</v>
+        <v>61.13</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>50.17</v>
+        <v>5.94</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>45.54</v>
+        <v>46.86</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>42.73</v>
+        <v>46.18</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>36.19</v>
+        <v>39.12</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>34.54</v>
+        <v>36.49</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>34.25</v>
+        <v>36.65</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>34.78</v>
+        <v>39.16</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>34.94</v>
+        <v>36.16</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>40.58</v>
+        <v>36.83</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>36.93</v>
+        <v>40.24</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>37.27</v>
+        <v>47.06</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>36.82</v>
+        <v>47.37</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>49.64</v>
+        <v>51.6</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>65.19</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>64.06999999999999</v>
+        <v>63.96</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>47.7</v>
+        <v>51.07</v>
       </c>
       <c r="X59" s="3" t="n">
         <v>50.56</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>37.06</v>
+        <v>44.42</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>47.29</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="O61" s="3" t="n">
         <v>1.01</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>0.91</v>
-      </c>
       <c r="P61" s="3" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.93</v>
+        <v>1.27</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>1.54</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="X61" s="3" t="n">
         <v>1.31</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="62">
@@ -5618,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>34.19</v>
+        <v>37.51</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>36.78</v>
+        <v>39.9</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>34.86</v>
+        <v>36.7</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>36.57</v>
+        <v>41.24</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>41.96</v>
+        <v>61.7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>50.74</v>
+        <v>6.54</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>46.16</v>
+        <v>47.44</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>43.35</v>
+        <v>46.8</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>36.72</v>
+        <v>39.69</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>35</v>
+        <v>36.98</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>34.71</v>
+        <v>37.18</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>35.28</v>
+        <v>39.74</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>35.49</v>
+        <v>36.65</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>41.17</v>
+        <v>37.36</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>37.47</v>
+        <v>40.79</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>37.85</v>
+        <v>47.75</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>37.4</v>
+        <v>48.11</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>50.37</v>
+        <v>52.41</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>66.20999999999999</v>
+        <v>66.34</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>65</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>48.39</v>
+        <v>51.81</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>51.29</v>
+        <v>51.24</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>37.57</v>
+        <v>44.98</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>47.88</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.72</v>
+        <v>2.21</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="I66" s="3" t="n">
         <v>1.71</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="T66" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="W66" s="3" t="n">
         <v>2.12</v>
       </c>
-      <c r="U66" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X66" s="3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="67">
@@ -6038,10 +6038,10 @@
         <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>34.66</v>
+        <v>38.06</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>37.29</v>
+        <v>40.49</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>35.38</v>
+        <v>37.28</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>37.04</v>
+        <v>41.9</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>42.53</v>
+        <v>62.45</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>51.11</v>
+        <v>6.84</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>46.54</v>
+        <v>47.84</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>43.9</v>
+        <v>47.4</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>37.19</v>
+        <v>40.2</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>35.48</v>
+        <v>37.49</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>35.19</v>
+        <v>37.65</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>35.77</v>
+        <v>40.24</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>35.94</v>
+        <v>37.15</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>41.6</v>
+        <v>37.76</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>37.95</v>
+        <v>41.31</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>38.17</v>
+        <v>48.15</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>37.63</v>
+        <v>48.41</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>50.74</v>
+        <v>52.8</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>66.62</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>65.48</v>
+        <v>65.37</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>48.75</v>
+        <v>52.19</v>
       </c>
       <c r="X69" s="3" t="n">
         <v>51.67</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>38.05</v>
+        <v>45.6</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>48.49</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1.9</v>
+        <v>2.27</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="I71" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="K71" s="3" t="n">
         <v>2.09</v>
       </c>
-      <c r="J71" s="3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>1.93</v>
-      </c>
       <c r="L71" s="3" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.83</v>
+        <v>2.36</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="X71" s="3" t="n">
         <v>2.43</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.09</v>
+        <v>2.51</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="72">
@@ -6458,10 +6458,10 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>33.63</v>
+        <v>36.89</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>36.18</v>
+        <v>39.24</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>34.29</v>
+        <v>36.06</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>35.9</v>
+        <v>40.57</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>41.27</v>
+        <v>60.87</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>49.97</v>
+        <v>5.74</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>45.4</v>
+        <v>46.67</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>42.6</v>
+        <v>45.99</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>36.12</v>
+        <v>39.04</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>34.46</v>
+        <v>36.42</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>34.18</v>
+        <v>36.57</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>34.74</v>
+        <v>39.08</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>34.91</v>
+        <v>36.08</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>40.5</v>
+        <v>36.75</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>36.86</v>
+        <v>40.12</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>37.23</v>
+        <v>46.97</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>36.71</v>
+        <v>47.18</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>49.39</v>
+        <v>51.39</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>64.98999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>47.65</v>
+        <v>51.02</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>50.5</v>
+        <v>50.45</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>36.99</v>
+        <v>44.33</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>47.19</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.79</v>
+        <v>1.01</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.92</v>
+        <v>1.12</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="U76" s="3" t="n">
         <v>1.43</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W76" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y76" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="X76" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Z76" s="3" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="77">
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>32.86</v>
+        <v>35.97</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>35.38</v>
+        <v>38.22</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>33.5</v>
+        <v>35.19</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>35.11</v>
+        <v>39.55</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>40.24</v>
+        <v>59.49</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>48.97</v>
+        <v>4.83</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>44.45</v>
+        <v>45.74</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>41.49</v>
+        <v>44.79</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>35.25</v>
+        <v>38.11</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>33.6</v>
+        <v>35.5</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>33.32</v>
+        <v>35.66</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>33.87</v>
+        <v>38.11</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>34.03</v>
+        <v>35.15</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>39.65</v>
+        <v>35.94</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>35.94</v>
+        <v>38.99</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>36.34</v>
+        <v>45.79</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>35.9</v>
+        <v>46.14</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>48.25</v>
+        <v>50.16</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>63.56</v>
+        <v>63.62</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>62.53</v>
+        <v>62.42</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>46.41</v>
+        <v>49.69</v>
       </c>
       <c r="X79" s="3" t="n">
         <v>49.24</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>35.95</v>
+        <v>43.09</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>45.82</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="80">
@@ -7298,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>33.77</v>
+        <v>36.89</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>35.96</v>
+        <v>39.32</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>34.05</v>
+        <v>36.35</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>35.94</v>
+        <v>40.69</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>40.2</v>
+        <v>60.92</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>49.46</v>
+        <v>6.24</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>42.49</v>
+        <v>44.58</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>41.16</v>
+        <v>45.29</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>35.01</v>
+        <v>38.57</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>33.4</v>
+        <v>35.54</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>32.86</v>
+        <v>35.69</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>33.4</v>
+        <v>38.07</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>33.46</v>
+        <v>34.8</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>38.64</v>
+        <v>35.21</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>34.76</v>
+        <v>38.12</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>35.15</v>
+        <v>44.63</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>33.46</v>
+        <v>43.32</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>45.01</v>
+        <v>47.23</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>59.96</v>
+        <v>60.82</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>59.21</v>
+        <v>59.4</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>46.27</v>
+        <v>50.04</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>50.09</v>
+        <v>50.14</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>37.3</v>
+        <v>44.84</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>47.19</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="85">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.58</v>
+        <v>1.1</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="G86" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N86" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="H86" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>-0.47</v>
-      </c>
       <c r="O86" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.35</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1</v>
+        <v>-0.74</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-1.18</v>
+        <v>-0.88</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.16</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.44</v>
+        <v>-2.82</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.24</v>
+        <v>-2.93</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-3.6</v>
+        <v>-2.8</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-3.32</v>
+        <v>-3.03</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.35</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="87">
@@ -7718,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I88" s="3" t="n">
         <v>0</v>
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>32.47</v>
+        <v>35.79</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>35.45</v>
+        <v>38.18</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>33.5</v>
+        <v>41.12</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>34.97</v>
+        <v>39.83</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>39.96</v>
+        <v>59.2</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>48.58</v>
+        <v>4.55</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>44.23</v>
+        <v>45.42</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>40.52</v>
+        <v>43.74</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>34.29</v>
+        <v>37</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>32.59</v>
+        <v>34.57</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>32.35</v>
+        <v>34.65</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>32.66</v>
+        <v>36.82</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>32.66</v>
+        <v>33.99</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>38.49</v>
+        <v>35.14</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>35.16</v>
+        <v>38.34</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>35.8</v>
+        <v>44.98</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>35.27</v>
+        <v>45.23</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>47.68</v>
+        <v>49.61</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>62.5</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>61.42</v>
+        <v>61.38</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>45.37</v>
+        <v>48.62</v>
       </c>
       <c r="X89" s="3" t="n">
         <v>48.47</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>35.56</v>
+        <v>42.62</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>45.37</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="90">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.18</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="G91" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H91" s="3" t="n">
         <v>-0.28</v>
       </c>
-      <c r="H91" s="3" t="n">
-        <v>-0.39</v>
-      </c>
       <c r="I91" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.05</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.11</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.93</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.29</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.16</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.65</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.9</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.55</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.12</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.04</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.07</v>
       </c>
       <c r="X91" s="3" t="n">
         <v>-0.78</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="92">
@@ -8048,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -8138,10 +8138,10 @@
         <v>0</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0</v>
+        <v>11.38</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0</v>
+        <v>-42.19</v>
       </c>
       <c r="I93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-05T20:13:10</t>
+          <t>CreatedAt: 2026-10-06T03:10:34</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>50.9</v>
+        <v>55.57</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46.89</v>
+        <v>52.56</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>42.36</v>
+        <v>47.83</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>35.04</v>
+        <v>48.49</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>95.52</v>
+        <v>81</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>119.88</v>
+        <v>95.27</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>199.65</v>
+        <v>199.77</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>35.28</v>
+        <v>38.48</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>31.41</v>
+        <v>32.26</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>31.28</v>
+        <v>32.55</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>32.05</v>
+        <v>34.44</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>31.38</v>
+        <v>32.25</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>31.31</v>
+        <v>32.23</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>30.64</v>
+        <v>32.16</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>37.86</v>
+        <v>40.14</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>287.26</v>
+        <v>287.31</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>250.33</v>
+        <v>200.24</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>113.56</v>
+        <v>197.76</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>36.84</v>
+        <v>48.1</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>38.69</v>
+        <v>50.68</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>35.03</v>
+        <v>33.4</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>50.86</v>
+        <v>47.47</v>
       </c>
     </row>
     <row r="5">
@@ -791,19 +791,19 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-109.82</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-6.7</v>
+        <v>-19.11</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-19.83</v>
+        <v>-43.96</v>
       </c>
     </row>
     <row r="6">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.39</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="O6" s="3" t="n">
         <v>-1.64</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="L6" s="3" t="n">
+      <c r="P6" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>-1.51</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-1.41</v>
-      </c>
       <c r="R6" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.01</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-2.56</v>
+        <v>-2.13</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.74</v>
+        <v>-3.13</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.75</v>
+        <v>-12</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.78</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.41</v>
+        <v>-2.37</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.9</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="7">
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1028,19 +1028,19 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-139.15</v>
+        <v>-136.21</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>53.85</v>
+        <v>56.11</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>50.14</v>
+        <v>53.18</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>44.97</v>
+        <v>48.77</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>36.97</v>
+        <v>48.78</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>100.24</v>
+        <v>74</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>203.93</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>118.18</v>
+        <v>93.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>201.79</v>
+        <v>199.17</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>36.2</v>
+        <v>39.51</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>31.95</v>
+        <v>32.51</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.05</v>
+        <v>33.12</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>32.81</v>
+        <v>35.11</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>31.8</v>
+        <v>32.75</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>31.92</v>
+        <v>32.96</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>31.35</v>
+        <v>32.89</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>38.32</v>
+        <v>40.72</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>287.75</v>
+        <v>286.21</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>250.22</v>
+        <v>199.28</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>113.23</v>
+        <v>193.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>37.35</v>
+        <v>48.52</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>39.36</v>
+        <v>51.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>36.2</v>
+        <v>34.58</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>52.91</v>
+        <v>50.32</v>
       </c>
     </row>
     <row r="10">
@@ -1211,19 +1211,19 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0</v>
+        <v>-109.82</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-6.7</v>
+        <v>-19.11</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-19.83</v>
+        <v>-43.96</v>
       </c>
     </row>
     <row r="11">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.86</v>
+        <v>-1.85</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.6</v>
+        <v>-1.44</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.26</v>
+        <v>-0.68</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.78</v>
+        <v>-1.56</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.9</v>
+        <v>-4.67</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-3.47</v>
+        <v>-6.51</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-6.62</v>
+        <v>-5.88</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.54</v>
+        <v>-4.82</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.71</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.37</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.61</v>
+        <v>-1.03</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.75</v>
+        <v>-1.05</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.15</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.86</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.79</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.28</v>
+        <v>-1.43</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.13</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-2.07</v>
+        <v>-3.24</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-3.85</v>
+        <v>-4.1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-4.08</v>
+        <v>-16.66</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.6</v>
+        <v>-1.36</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1.35</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="12">
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-6.54</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>-139.46</v>
+        <v>-136.56</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2000</v>
+        <v>56.11</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>114.03</v>
+        <v>53.18</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>112.74</v>
+        <v>48.77</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>114.64</v>
+        <v>48.78</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>100.65</v>
+        <v>74</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>203.93</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>118.18</v>
+        <v>93.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>201.79</v>
+        <v>199.1</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>103.04</v>
+        <v>39.51</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>2000</v>
+        <v>32.51</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>102.11</v>
+        <v>33.12</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>102.22</v>
+        <v>35.11</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>181.18</v>
+        <v>124.33</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>179.73</v>
+        <v>123.83</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>184.72</v>
+        <v>124.12</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>183.29</v>
+        <v>40.72</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>182.91</v>
+        <v>-94.13</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>288.06</v>
+        <v>286.21</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>250.22</v>
+        <v>199.28</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>113.23</v>
+        <v>288.59</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>72.98999999999999</v>
+        <v>48.52</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>73.39</v>
+        <v>70.81</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>184.86</v>
+        <v>124.08</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>74.28</v>
+        <v>94.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1574,19 +1574,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1946.15</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>63.84</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>67.77</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>77.67</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0</v>
@@ -1598,52 +1598,52 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>66.84</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1968.05</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>70.03</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>69.41</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>149.38</v>
+        <v>91.58</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>147.81</v>
+        <v>90.88</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>153.38</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>144.97</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>594.99</v>
+        <v>55.42</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>-14.32</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>35.64</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>27.33</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>148.66</v>
+        <v>89.5</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>1.54</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="16">
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.86</v>
+        <v>-1.85</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.66</v>
+        <v>-1.44</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.26</v>
+        <v>-0.68</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.78</v>
+        <v>-1.56</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1</v>
+        <v>-4.67</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-3.47</v>
+        <v>-6.51</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-6.62</v>
+        <v>-5.88</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-2.54</v>
+        <v>-4.89</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.71</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.37</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.58</v>
+        <v>-1.03</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.75</v>
+        <v>-1.05</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.15</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.86</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.79</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-1.28</v>
+        <v>-1.43</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.13</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-2.07</v>
+        <v>-3.24</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-3.85</v>
+        <v>-4.1</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-4.08</v>
+        <v>-16.66</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.6</v>
+        <v>-1.36</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1.35</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.22</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="17">
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0</v>
+        <v>-6.54</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1868,19 +1868,19 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>-451.53</v>
+        <v>-186.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>50.85</v>
+        <v>55.47</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46.98</v>
+        <v>52.46</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>42.48</v>
+        <v>47.88</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>35.18</v>
+        <v>48.54</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>95.52</v>
+        <v>81.08</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>120</v>
+        <v>95.36</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>199.91</v>
+        <v>199.92</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>35.39</v>
+        <v>38.55</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>31.47</v>
+        <v>32.26</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>31.43</v>
+        <v>32.55</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>32.15</v>
+        <v>34.44</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>31.47</v>
+        <v>32.29</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>31.43</v>
+        <v>32.27</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>30.76</v>
+        <v>32.23</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>37.9</v>
+        <v>40.18</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>287.26</v>
+        <v>287.21</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>250.22</v>
+        <v>200.16</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>113.34</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>36.84</v>
+        <v>48.01</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>31.71</v>
+        <v>30.71</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>35.27</v>
+        <v>33.6</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>30.27</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="20">
@@ -2051,19 +2051,19 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0</v>
+        <v>-224.96</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-13.73</v>
+        <v>-39.14</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-40.63</v>
+        <v>-90.06</v>
       </c>
     </row>
     <row r="21">
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.5</v>
       </c>
       <c r="D21" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>-1.55</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>-4.42</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="L21" s="3" t="n">
+      <c r="Q21" s="3" t="n">
         <v>-1.45</v>
       </c>
-      <c r="M21" s="3" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-1.29</v>
-      </c>
       <c r="R21" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.97</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.48</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.56</v>
+        <v>-2.24</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.85</v>
+        <v>-3.21</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.97</v>
+        <v>-12.88</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.87</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.36</v>
+        <v>-2.31</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="22">
@@ -2267,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2288,19 +2288,19 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>-139.11</v>
+        <v>-136.21</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>50.85</v>
+        <v>55.47</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46.98</v>
+        <v>52.46</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>42.48</v>
+        <v>47.88</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>35.18</v>
+        <v>48.54</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>95.52</v>
+        <v>81.08</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>120</v>
+        <v>95.36</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>199.91</v>
+        <v>199.92</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>35.39</v>
+        <v>38.55</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>31.47</v>
+        <v>32.26</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>31.43</v>
+        <v>32.55</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>32.15</v>
+        <v>34.44</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>31.47</v>
+        <v>32.29</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>31.43</v>
+        <v>32.27</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.76</v>
+        <v>32.23</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>37.9</v>
+        <v>40.18</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>287.26</v>
+        <v>287.21</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>250.22</v>
+        <v>200.16</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>113.34</v>
+        <v>196.88</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>36.84</v>
+        <v>48.01</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>38.73</v>
+        <v>50.74</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>35.27</v>
+        <v>33.6</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>51.06</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="25">
@@ -2471,19 +2471,19 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>-109.82</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-6.7</v>
+        <v>-19.11</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-19.83</v>
+        <v>-43.96</v>
       </c>
     </row>
     <row r="26">
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.14</v>
+        <v>-2.5</v>
       </c>
       <c r="D26" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>-1.55</v>
       </c>
-      <c r="E26" s="3" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>-4.42</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="L26" s="3" t="n">
+      <c r="Q26" s="3" t="n">
         <v>-1.45</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-1.29</v>
-      </c>
       <c r="R26" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.97</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.48</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.56</v>
+        <v>-2.24</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.85</v>
+        <v>-3.21</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.97</v>
+        <v>-12.88</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.87</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.36</v>
+        <v>-2.31</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.71</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="27">
@@ -2687,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2708,19 +2708,19 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>-139.11</v>
+        <v>-136.21</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>0</v>
@@ -2750,52 +2750,52 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>50.56</v>
+        <v>55.31</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46.85</v>
+        <v>52.31</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>42.44</v>
+        <v>47.83</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>35.18</v>
+        <v>48.54</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>95.33</v>
+        <v>81.23</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>199.61</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>120</v>
+        <v>95.45</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>200</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>35.39</v>
+        <v>38.48</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>31.5</v>
+        <v>32.17</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>31.49</v>
+        <v>32.49</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>32.15</v>
+        <v>34.34</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>31.47</v>
+        <v>32.19</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>31.49</v>
+        <v>32.2</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>30.79</v>
+        <v>32.16</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>37.83</v>
+        <v>40.1</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>-100</v>
@@ -2804,22 +2804,22 @@
         <v>287.06</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>112.91</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>36.81</v>
+        <v>47.82</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>31.79</v>
+        <v>30.78</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>35.48</v>
+        <v>33.77</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.55</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="30">
@@ -2891,19 +2891,19 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>0</v>
+        <v>-224.96</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-13.73</v>
+        <v>-39.14</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-40.63</v>
+        <v>-90.06</v>
       </c>
     </row>
     <row r="31">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-2.43</v>
+        <v>-2.65</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-1.69</v>
+        <v>-2.3</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.63</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.8</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-4</v>
+        <v>-3.98</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-7.78</v>
+        <v>-4.28</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-4.8</v>
+        <v>-3.72</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-4.33</v>
+        <v>-3.99</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.74</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.71</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.66</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.82</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.71</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.61</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-1.77</v>
+        <v>-2.05</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.59</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.76</v>
+        <v>-2.39</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.07</v>
+        <v>-3.37</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4.4</v>
+        <v>-14.05</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.14</v>
+        <v>-2.06</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.27</v>
+        <v>-2.24</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="32">
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3128,19 +3128,19 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>-139</v>
+        <v>-136.1</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2000</v>
+        <v>57</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>116.31</v>
+        <v>54.13</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>114.37</v>
+        <v>49.75</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>115.77</v>
+        <v>49.21</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>103.47</v>
+        <v>71.91</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>207.19</v>
+        <v>91.67</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>117.85</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>203.09</v>
+        <v>199.17</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>103.89</v>
+        <v>40.26</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>2000</v>
+        <v>32.67</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>102.52</v>
+        <v>33.47</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>102.67</v>
+        <v>35.52</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>181.42</v>
+        <v>124.71</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>180.2</v>
+        <v>124.46</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>185.17</v>
+        <v>124.71</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>183.83</v>
+        <v>41.24</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>183.38</v>
+        <v>-93.73</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>288.62</v>
+        <v>286.01</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>250.77</v>
+        <v>199.12</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>114.23</v>
+        <v>289.17</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>73.48</v>
+        <v>49.05</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>73.84999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>185.49</v>
+        <v>124.83</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>75.55</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="35">
@@ -3254,19 +3254,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1944.16</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>63.84</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>67.77</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>77.67</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0</v>
@@ -3278,52 +3278,52 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>66.84</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>1967.7</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>70.03</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>69.41</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>149.38</v>
+        <v>91.58</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>147.81</v>
+        <v>90.88</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>153.38</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>144.97</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>594.99</v>
+        <v>55.42</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>-14.32</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>35.64</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>27.33</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>148.66</v>
+        <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1.54</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="36">
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.85</v>
+        <v>-0.97</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>3.94</v>
+        <v>-0.49</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.89</v>
+        <v>0.3</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.91</v>
+        <v>-1.13</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.82</v>
+        <v>-5.35</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.21</v>
+        <v>-7.79</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-6.95</v>
+        <v>-6.75</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-1.24</v>
+        <v>-4.82</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.61</v>
+        <v>-1.21</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.67</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.76</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="R36" s="3" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="S36" s="3" t="n">
         <v>-0.74</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>-0.72</v>
-      </c>
       <c r="T36" s="3" t="n">
-        <v>-1.51</v>
+        <v>-3.44</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-3.3</v>
+        <v>-4.26</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-3.08</v>
+        <v>-16.08</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.83</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.86</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="37">
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>-7.95</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3548,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>-451.53</v>
+        <v>-186.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>50.9</v>
+        <v>55.57</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>46.89</v>
+        <v>52.56</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>42.36</v>
+        <v>47.83</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>35.04</v>
+        <v>48.49</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>95.52</v>
+        <v>81</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>119.88</v>
+        <v>95.27</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>199.65</v>
+        <v>199.77</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>35.28</v>
+        <v>38.48</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>31.41</v>
+        <v>32.26</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>31.28</v>
+        <v>32.55</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>32.05</v>
+        <v>34.44</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>31.38</v>
+        <v>32.25</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>31.31</v>
+        <v>32.23</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.64</v>
+        <v>32.16</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>37.86</v>
+        <v>40.14</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>287.26</v>
+        <v>287.31</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>250.33</v>
+        <v>200.24</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>113.56</v>
+        <v>197.76</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>36.84</v>
+        <v>48.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>38.69</v>
+        <v>50.68</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>35.03</v>
+        <v>33.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>50.86</v>
+        <v>47.47</v>
       </c>
     </row>
     <row r="40">
@@ -3731,19 +3731,19 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>-109.82</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-6.7</v>
+        <v>-19.11</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-19.83</v>
+        <v>-43.96</v>
       </c>
     </row>
     <row r="41">
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.39</v>
       </c>
       <c r="D41" s="3" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>-3.91</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="O41" s="3" t="n">
         <v>-1.64</v>
       </c>
-      <c r="E41" s="3" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>-3.82</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>-4.92</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>-4.68</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="L41" s="3" t="n">
+      <c r="P41" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Q41" s="3" t="n">
         <v>-1.51</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>-1.41</v>
-      </c>
       <c r="R41" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.01</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.48</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-2.56</v>
+        <v>-2.13</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.74</v>
+        <v>-3.13</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.75</v>
+        <v>-12</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.78</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.41</v>
+        <v>-2.37</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.9</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="42">
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -3968,19 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>-139.15</v>
+        <v>-136.21</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>52.83</v>
+        <v>57.79</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>48.29</v>
+        <v>54.45</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>43.32</v>
+        <v>49.31</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>35.7</v>
+        <v>50.19</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>98.94</v>
+        <v>84.7</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>203.53</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>120.58</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>200.53</v>
+        <v>200.84</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>35.04</v>
+        <v>38.19</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>31.23</v>
+        <v>32.17</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>30.92</v>
+        <v>32.4</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>31.75</v>
+        <v>34.31</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>31.14</v>
+        <v>32.13</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>30.95</v>
+        <v>32.05</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>30.37</v>
+        <v>31.92</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>38.21</v>
+        <v>40.49</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>287.96</v>
+        <v>287.88</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>252.23</v>
+        <v>201.65</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>117.19</v>
+        <v>319.58</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>37.69</v>
+        <v>49.53</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>46.66</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>35.24</v>
+        <v>33.7</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>72.45999999999999</v>
+        <v>93.81</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D46" s="3" t="n">
         <v>-0.16</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>-0.24</v>
-      </c>
       <c r="E46" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.15</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.51</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-3.87</v>
+        <v>-2.14</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-4.22</v>
+        <v>-3.35</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-3.8</v>
+        <v>-3.15</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-1.78</v>
+        <v>-2.03</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.71</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.75</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-1.81</v>
+        <v>-1.85</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>-1.77</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.76</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.76</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.39</v>
+        <v>-1.66</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.13</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.56</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.72</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.35</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.14</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4388,19 +4388,19 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>-139.57</v>
+        <v>-136.56</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>53.96</v>
+        <v>59.09</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>49.32</v>
+        <v>55.96</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>44.24</v>
+        <v>50.57</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>36.75</v>
+        <v>51.63</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>102.09</v>
+        <v>87.94</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>201.75</v>
+        <v>103.94</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>126.83</v>
+        <v>101.93</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>206</v>
+        <v>206.23</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>37.63</v>
+        <v>41.51</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>33.41</v>
+        <v>34.85</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>32.99</v>
+        <v>34.98</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>33.93</v>
+        <v>36.9</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>33.21</v>
+        <v>34.63</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>33.05</v>
+        <v>34.43</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>31.95</v>
+        <v>33.91</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>39.94</v>
+        <v>42.92</v>
       </c>
       <c r="S49" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>287.61</v>
+        <v>288.2</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>251.33</v>
+        <v>201.57</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>120.57</v>
+        <v>331.51</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>38.96</v>
+        <v>51.37</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>48.65</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>36.8</v>
+        <v>35.26</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>73.93000000000001</v>
+        <v>96.12</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.97</v>
+        <v>1.12</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.79</v>
+        <v>1.34</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.53</v>
+        <v>1.11</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.55</v>
+        <v>1.29</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>-5.65</v>
+        <v>4.47</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2.03</v>
+        <v>2.75</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.8</v>
+        <v>1.29</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.5</v>
+        <v>0.98</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>0.37</v>
+        <v>0.74</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0.3</v>
+        <v>0.73</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>0.3</v>
+        <v>0.62</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>-0.1</v>
+        <v>0.24</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>0.34</v>
+        <v>0.77</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.41</v>
+        <v>-0.96</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.21</v>
+        <v>-1.25</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.75</v>
+        <v>-1.8</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>3.26</v>
+        <v>11.93</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.85</v>
+        <v>3.08</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="52">
@@ -4787,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4808,19 +4808,19 @@
         <v>0</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R53" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>-139.23</v>
+        <v>-136.74</v>
       </c>
       <c r="T53" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>56.07</v>
+        <v>61.21</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>51.47</v>
+        <v>57.43</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46.31</v>
+        <v>51.79</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>38.38</v>
+        <v>52.65</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>102.94</v>
+        <v>89.41</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>204.13</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>124.05</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>204.52</v>
+        <v>204.07</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>37.36</v>
+        <v>41.26</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>34.11</v>
+        <v>35.07</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>33.88</v>
+        <v>35.38</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>35</v>
+        <v>37.74</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>34.18</v>
+        <v>35.17</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>33.94</v>
+        <v>35.15</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>32.69</v>
+        <v>34.33</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>39.83</v>
+        <v>42.27</v>
       </c>
       <c r="S54" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>288.66</v>
+        <v>286.71</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>249.13</v>
+        <v>198.96</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>112.15</v>
+        <v>286.88</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>36.52</v>
+        <v>49.14</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>47.27</v>
+        <v>73.03</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>37.1</v>
+        <v>35.51</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>76.19</v>
+        <v>98.73999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>0</v>
+        <v>-14.32</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-3.27</v>
+        <v>-0.4</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1.08</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.53</v>
+        <v>1.04</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>1.19</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>1.43</v>
+        <v>1.59</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.7</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-1.16</v>
+        <v>-2.74</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-4.94</v>
+        <v>-4.42</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-5.16</v>
+        <v>-18.37</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.42</v>
+        <v>-0.74</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.47</v>
+        <v>0.88</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>3.66</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="57">
@@ -5207,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>-140.08</v>
+        <v>-136.99</v>
       </c>
       <c r="T58" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>54.69</v>
+        <v>59.76</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>49.88</v>
+        <v>56.3</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>44.6</v>
+        <v>50.93</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>36.71</v>
+        <v>51.84</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>101.99</v>
+        <v>87.58</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>208.86</v>
+        <v>99.97</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>123.44</v>
+        <v>98</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>203.19</v>
+        <v>203</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>35.88</v>
+        <v>39.08</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>31.99</v>
+        <v>32.92</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>31.71</v>
+        <v>33.15</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>32.55</v>
+        <v>35.11</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>31.95</v>
+        <v>32.91</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>31.77</v>
+        <v>32.8</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>31.16</v>
+        <v>32.7</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>39.22</v>
+        <v>41.6</v>
       </c>
       <c r="S59" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>289.53</v>
+        <v>289.12</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>255.14</v>
+        <v>203.9</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>120.94</v>
+        <v>330.14</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>38.84</v>
+        <v>51.05</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>48.2</v>
+        <v>74.39</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>36.27</v>
+        <v>34.69</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>74.77</v>
+        <v>96.81</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.89</v>
+        <v>1.48</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.51</v>
+        <v>1.5</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.46</v>
+        <v>0.5</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.18</v>
       </c>
       <c r="J61" s="3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="K61" s="3" t="n">
         <v>-1.14</v>
       </c>
-      <c r="K61" s="3" t="n">
+      <c r="L61" s="3" t="n">
         <v>-0.95</v>
       </c>
-      <c r="L61" s="3" t="n">
-        <v>-0.93</v>
-      </c>
       <c r="M61" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.99</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>-1.01</v>
+        <v>-1.05</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="P61" s="3" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="Q61" s="3" t="n">
         <v>-0.98</v>
       </c>
-      <c r="Q61" s="3" t="n">
-        <v>-0.89</v>
-      </c>
       <c r="R61" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.54</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.22</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.06</v>
+        <v>0.53</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.63</v>
+        <v>10.56</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>2.24</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="62">
@@ -5627,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5648,19 +5648,19 @@
         <v>0</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>-140.56</v>
+        <v>-137.47</v>
       </c>
       <c r="T63" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>55.37</v>
+        <v>60.51</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>50.5</v>
+        <v>56.95</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>45.16</v>
+        <v>51.52</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>37.16</v>
+        <v>52.49</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>103.48</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>211.85</v>
+        <v>101.29</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>125.05</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>204.52</v>
+        <v>204.07</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>36.38</v>
+        <v>39.58</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>32.43</v>
+        <v>33.34</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>32.11</v>
+        <v>33.54</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>33</v>
+        <v>35.52</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>32.33</v>
+        <v>33.3</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>32.14</v>
+        <v>33.18</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>31.57</v>
+        <v>33.08</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>39.79</v>
+        <v>42.15</v>
       </c>
       <c r="S64" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>290.56</v>
+        <v>289.9</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>256.95</v>
+        <v>205.16</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>122.84</v>
+        <v>333.93</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>39.37</v>
+        <v>51.8</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>48.85</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>36.68</v>
+        <v>35.19</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>75.70999999999999</v>
+        <v>98.12</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1.45</v>
+        <v>2.06</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.97</v>
+        <v>2.15</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>4.14</v>
+        <v>3.55</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>4.45</v>
+        <v>1.82</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.64</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.53</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.6</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.6</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.63</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.6</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.88</v>
+        <v>1.79</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>5.53</v>
+        <v>14.36</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.05</v>
+        <v>3.16</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>3.18</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="67">
@@ -6047,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6068,19 +6068,19 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>-141.13</v>
+        <v>-138</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>56.19</v>
+        <v>61.4</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>51.2</v>
+        <v>57.85</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>45.58</v>
+        <v>52.33</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>37.35</v>
+        <v>53.32</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>104.46</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>211.2</v>
+        <v>101.08</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>123.69</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>203.47</v>
+        <v>203.16</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>35.63</v>
+        <v>38.82</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>31.77</v>
+        <v>32.7</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>31.49</v>
+        <v>32.93</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>32.36</v>
+        <v>34.87</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>31.74</v>
+        <v>32.69</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>31.55</v>
+        <v>32.58</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>30.94</v>
+        <v>32.47</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>39.33</v>
+        <v>41.73</v>
       </c>
       <c r="S69" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>289.6</v>
+        <v>289.23</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>256.34</v>
+        <v>204.8</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>123.75</v>
+        <v>337.82</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>39.61</v>
+        <v>52.12</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>49.42</v>
+        <v>76.28</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>36.83</v>
+        <v>35.26</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>76.51000000000001</v>
+        <v>99.06</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.66</v>
+        <v>3.24</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.16</v>
+        <v>2.99</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>5.12</v>
+        <v>4.58</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.08</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.83</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.4</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.18</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.22</v>
       </c>
       <c r="N71" s="3" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="Q71" s="3" t="n">
         <v>-1.2</v>
       </c>
-      <c r="O71" s="3" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>-1.11</v>
-      </c>
       <c r="R71" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.42</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="T71" s="3" t="n">
         <v>-0.22</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.27</v>
+        <v>1.43</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>6.43</v>
+        <v>18.24</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>1.66</v>
+        <v>2.24</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.62</v>
+        <v>4.12</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>0.99</v>
+        <v>0.95</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>3.98</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="72">
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="T72" s="3" t="n">
         <v>0</v>
@@ -6467,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6488,19 +6488,19 @@
         <v>0</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>-140.68</v>
+        <v>-137.68</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>54.8</v>
+        <v>59.88</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>49.98</v>
+        <v>56.42</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>44.74</v>
+        <v>50.99</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>36.82</v>
+        <v>52</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>102.2</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>209.28</v>
+        <v>100.47</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>124.05</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>204.04</v>
+        <v>203.66</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>36.2</v>
+        <v>39.43</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>32.17</v>
+        <v>33.15</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>31.89</v>
+        <v>33.34</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>32.84</v>
+        <v>35.38</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>32.2</v>
+        <v>33.17</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>31.95</v>
+        <v>32.99</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>31.32</v>
+        <v>32.86</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>39.41</v>
+        <v>41.81</v>
       </c>
       <c r="S74" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>289.82</v>
+        <v>289.39</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>255.62</v>
+        <v>204.26</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>121.44</v>
+        <v>331.85</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>38.96</v>
+        <v>51.32</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>48.4</v>
+        <v>74.77</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>36.38</v>
+        <v>34.83</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>74.93000000000001</v>
+        <v>97.01000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="D76" s="3" t="n">
         <v>1.81</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>1.45</v>
-      </c>
       <c r="E76" s="3" t="n">
-        <v>1.03</v>
+        <v>1.53</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.63</v>
+        <v>1.66</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.86</v>
+        <v>2.54</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.88</v>
+        <v>1</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.79</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.73</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.78</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.82</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.82</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.33</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>1.54</v>
+        <v>0.89</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>4.13</v>
+        <v>12.28</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="77">
@@ -6887,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6908,19 +6908,19 @@
         <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>-140.72</v>
+        <v>-137.65</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>52.99</v>
+        <v>57.96</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>48.53</v>
+        <v>54.61</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>43.71</v>
+        <v>49.46</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>36.2</v>
+        <v>50.34</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>99.34</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>207.4</v>
+        <v>99.47</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>124.8</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>204.33</v>
+        <v>203.99</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>36.83</v>
+        <v>40.22</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>32.91</v>
+        <v>33.88</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>32.66</v>
+        <v>34.14</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>33.56</v>
+        <v>36.16</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>32.91</v>
+        <v>33.9</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>32.75</v>
+        <v>33.81</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>32.05</v>
+        <v>33.68</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>39.6</v>
+        <v>42.15</v>
       </c>
       <c r="S79" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>289.82</v>
+        <v>289.45</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>254.07</v>
+        <v>203.37</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>117.31</v>
+        <v>319.58</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>37.95</v>
+        <v>49.88</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>46.8</v>
+        <v>72.16</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>35.84</v>
+        <v>34.31</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>72.53</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -7307,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7328,19 +7328,19 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>-140.64</v>
+        <v>-137.69</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>56.74</v>
+        <v>61.6</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>52.02</v>
+        <v>57.79</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46.65</v>
+        <v>51.41</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>38.79</v>
+        <v>52.27</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>104.68</v>
+        <v>89.23</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>202.74</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>122.71</v>
+        <v>95.92</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>202.81</v>
+        <v>202.11</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>36.53</v>
+        <v>41.09</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>34.04</v>
+        <v>34.64</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>33.49</v>
+        <v>35.02</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>34.63</v>
+        <v>37.28</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>33.72</v>
+        <v>34.59</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>33.32</v>
+        <v>34.54</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>32.38</v>
+        <v>33.91</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>39.83</v>
+        <v>42.06</v>
       </c>
       <c r="S84" s="3" t="n">
         <v>-100</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>289.82</v>
+        <v>286.11</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>248.07</v>
+        <v>198.17</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>111.2</v>
+        <v>285.46</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>35.97</v>
+        <v>49.83</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>47.51</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>36.95</v>
+        <v>35.77</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>76.67</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>0</v>
+        <v>-14.32</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>3.49</v>
+        <v>3.18</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.94</v>
+        <v>1.95</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.6</v>
+        <v>1.93</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>5.34</v>
+        <v>4.02</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-4.66</v>
+        <v>-2.61</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-2.09</v>
+        <v>-3.26</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.88</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-0.3</v>
+        <v>0.87</v>
       </c>
       <c r="L86" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="N86" s="3" t="n">
         <v>1.12</v>
       </c>
-      <c r="M86" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>1.07</v>
-      </c>
       <c r="O86" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.57</v>
+        <v>0.73</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.33</v>
+        <v>0.24</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.23</v>
+        <v>-0.08</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.12</v>
+        <v>-0.45</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>0</v>
+        <v>-3.34</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6</v>
+        <v>-5.2</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-6.12</v>
+        <v>-19.79</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.98</v>
+        <v>-0.05</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.71</v>
+        <v>1.55</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>4.14</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="87">
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>107.87</v>
+        <v>120.2</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7748,19 +7748,19 @@
         <v>0</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>-140.52</v>
+        <v>-137.25</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V88" s="3" t="n">
         <v>0</v>
@@ -7790,52 +7790,52 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>50.56</v>
+        <v>55.31</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>46.85</v>
+        <v>52.31</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>42.44</v>
+        <v>47.83</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>35.18</v>
+        <v>48.54</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>95.33</v>
+        <v>81.23</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>199.61</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>120</v>
+        <v>95.45</v>
       </c>
       <c r="J89" s="3" t="n">
         <v>200</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>35.39</v>
+        <v>38.48</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>31.5</v>
+        <v>32.17</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>31.49</v>
+        <v>32.49</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>32.15</v>
+        <v>34.34</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>31.47</v>
+        <v>32.19</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>31.49</v>
+        <v>32.2</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>30.79</v>
+        <v>32.16</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>37.83</v>
+        <v>40.1</v>
       </c>
       <c r="S89" s="3" t="n">
         <v>-100</v>
@@ -7844,22 +7844,22 @@
         <v>287.06</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>112.91</v>
+        <v>195.71</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>36.81</v>
+        <v>47.82</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>38.78</v>
+        <v>50.81</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>35.48</v>
+        <v>33.77</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>51.34</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="90">
@@ -7931,19 +7931,19 @@
         <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>0</v>
+        <v>-109.82</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-6.7</v>
+        <v>-19.11</v>
       </c>
       <c r="Y90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-19.83</v>
+        <v>-43.96</v>
       </c>
     </row>
     <row r="91">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-2.43</v>
+        <v>-2.65</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-1.69</v>
+        <v>-2.3</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.63</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.8</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-4</v>
+        <v>-3.98</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-7.78</v>
+        <v>-4.28</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-4.8</v>
+        <v>-3.72</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-4.33</v>
+        <v>-3.99</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.74</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.71</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.66</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.82</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.71</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.61</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-1.77</v>
+        <v>-2.05</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.62</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.76</v>
+        <v>-2.39</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.07</v>
+        <v>-3.37</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4.4</v>
+        <v>-14.05</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.14</v>
+        <v>-2.06</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.24</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="92">
@@ -8147,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>107.87</v>
+        <v>120.19</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>
@@ -8168,19 +8168,19 @@
         <v>0</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>-139</v>
+        <v>-136.07</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>216.26</v>
+        <v>233.96</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>136.88</v>
+        <v>115.64</v>
       </c>
       <c r="V93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-07T00:15:19</t>
+          <t>CreatedAt: 2026-10-07T08:09:16</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -656,70 +656,70 @@
         <v>32</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>32.24</v>
+        <v>31.58</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>31.88</v>
+        <v>34.15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>36.41</v>
+        <v>46.52</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>80.22</v>
+        <v>77</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>113.16</v>
+        <v>88</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>233.27</v>
+        <v>54.34</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-100</v>
+        <v>39.95</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>24.48</v>
+        <v>36.2</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>27.29</v>
+        <v>36.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>42.78</v>
+        <v>36.65</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>37.77</v>
+        <v>39.78</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>53.93</v>
+        <v>36.69</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>54.55</v>
+        <v>56.63</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>64.64</v>
+        <v>62.34</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>57.47</v>
+        <v>54.59</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>94.3</v>
+        <v>66.37</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>294.51</v>
+        <v>159.04</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>161.24</v>
+        <v>104.77</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>75.02</v>
+        <v>64.94</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>70.17</v>
+        <v>43.88</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>58.07</v>
+        <v>43.56</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>63.01</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="5">
@@ -740,70 +740,70 @@
         <v>-0.92</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.95</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-33.04</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-34.82</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-46.25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-23.27</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-23.45</v>
+        <v>-5.07</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-26.43</v>
+        <v>-5.55</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-38.79</v>
+        <v>-6.23</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-28.76</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-28.62</v>
+        <v>-30.76</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-17.1</v>
+        <v>-31.07</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-8.52</v>
+        <v>-6.59</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-63.99</v>
+        <v>-41.04</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-107.2</v>
+        <v>-54.11</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-41.72</v>
+        <v>-32.12</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-41.68</v>
+        <v>-17.21</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-25.91</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-30.9</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="6">
@@ -824,70 +824,70 @@
         <v>-0.26</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.46</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-2.3</v>
+        <v>-1.23</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-3.4</v>
+        <v>-1.68</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.16</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.82</v>
+        <v>-1.44</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.48</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-3.26</v>
+        <v>-1.67</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-4.05</v>
+        <v>-1.47</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-4.08</v>
+        <v>-3.93</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-4.33</v>
+        <v>-4.48</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.17</v>
+        <v>-2.81</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.58</v>
+        <v>-2.79</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-15.77</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-12.35</v>
+        <v>-7.63</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-5.6</v>
+        <v>-4.66</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-4.92</v>
+        <v>-2.63</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-3.19</v>
+        <v>-1.74</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="7">
@@ -1004,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-128.26</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1076,70 +1076,70 @@
         <v>32.23</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>32.44</v>
+        <v>31.88</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>32.34</v>
+        <v>34.39</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>37.19</v>
+        <v>47.04</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>79.77</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>114.08</v>
+        <v>89.34</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>234.94</v>
+        <v>55.47</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>-100</v>
+        <v>40.46</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>25.33</v>
+        <v>35.92</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>28.34</v>
+        <v>36.77</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>44.54</v>
+        <v>37.32</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>37.99</v>
+        <v>40.11</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>55.29</v>
+        <v>260.65</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>56.08</v>
+        <v>58.17</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>65.27</v>
+        <v>63.06</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>57.04</v>
+        <v>54.47</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>95.03</v>
+        <v>355.91</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>294.16</v>
+        <v>509.21</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>162.01</v>
+        <v>284.3</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>76.83</v>
+        <v>67.12</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>71.8</v>
+        <v>44.95</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>60.23</v>
+        <v>44.77</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>65.42</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="10">
@@ -1160,70 +1160,70 @@
         <v>-0.92</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.95</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-33.04</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-34.82</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-46.25</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-23.27</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-23.45</v>
+        <v>-5.07</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-26.43</v>
+        <v>-5.55</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-38.79</v>
+        <v>-6.23</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-28.76</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-28.62</v>
+        <v>-30.76</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-17.1</v>
+        <v>-31.07</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-8.52</v>
+        <v>-6.59</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-63.99</v>
+        <v>-41.04</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-107.2</v>
+        <v>-54.11</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-41.72</v>
+        <v>-32.12</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-41.68</v>
+        <v>-17.21</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-25.91</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-30.9</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="11">
@@ -1244,70 +1244,70 @@
         <v>-0.03</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.54</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.39</v>
+        <v>0.11</v>
       </c>
       <c r="J11" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="L11" s="3" t="n">
         <v>-1.72</v>
       </c>
-      <c r="K11" s="3" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-0.98</v>
-      </c>
       <c r="M11" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.31</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.67</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.69</v>
+        <v>-1.08</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.77</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-3.61</v>
+        <v>-2.93</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3.29</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-16.12</v>
+        <v>-10.89</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-11.58</v>
+        <v>-8.83</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-3.79</v>
+        <v>-2.48</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-3.29</v>
+        <v>-1.55</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.54</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-1.16</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="12">
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>223.56</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -1373,13 +1373,13 @@
         <v>0</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>0</v>
+        <v>290.04</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0</v>
+        <v>352.25</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>0</v>
+        <v>180.73</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>0</v>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-129.07</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1496,70 +1496,70 @@
         <v>33.15</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>33.11</v>
+        <v>32.83</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>67.66</v>
+        <v>34.39</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>67.65000000000001</v>
+        <v>47.04</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>112.81</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>148.89</v>
+        <v>98.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>281.31</v>
+        <v>55.47</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>-100</v>
+        <v>40.46</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>48.77</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>54.77</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>83.34</v>
+        <v>43.55</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>37.99</v>
+        <v>49.08</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>84.05</v>
+        <v>232.7</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>84.78</v>
+        <v>88.92</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>82.37</v>
+        <v>12.8</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>65.56</v>
+        <v>61.06</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>95.03</v>
+        <v>302.6</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>281.36</v>
+        <v>378</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>140.83</v>
+        <v>273.47</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>115.81</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>113.59</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>99.72</v>
+        <v>66.23</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>96.33</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1583,16 +1583,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>34.53</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>30.46</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>32.75</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0</v>
+        <v>31.42</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
@@ -1613,37 +1613,37 @@
         <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
+        <v>-27.94</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>-81.33</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>-53.31</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-76.79000000000001</v>
+        <v>-172.24</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>-128.64</v>
+        <v>-64.93000000000001</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>35.68</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>13.58</v>
+        <v>21.46</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="16">
@@ -1664,70 +1664,70 @@
         <v>-0.03</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.61</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.39</v>
+        <v>0.16</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.55</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.99</v>
+        <v>-0.65</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.98</v>
+        <v>-1.72</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.31</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.67</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.69</v>
+        <v>-1.08</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.77</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-3.61</v>
+        <v>-2.93</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3.29</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-16.12</v>
+        <v>-10.89</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-11.32</v>
+        <v>-8.83</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-3.68</v>
+        <v>-2.48</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-3.18</v>
+        <v>-1.55</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.54</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-1.16</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="17">
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0</v>
+        <v>223.56</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
@@ -1793,13 +1793,13 @@
         <v>0</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>0</v>
+        <v>290.04</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>0</v>
+        <v>352.25</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>0</v>
+        <v>180.73</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>0</v>
@@ -1844,13 +1844,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-152.33</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1919,67 +1919,67 @@
         <v>35</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>31.12</v>
+        <v>35</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>36.52</v>
+        <v>50.86</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>45.47</v>
+        <v>77.23</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>76.89</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>185.11</v>
+        <v>54.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-100</v>
+        <v>39.99</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.01</v>
+        <v>30.88</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-0.37</v>
+        <v>30.82</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>2.33</v>
+        <v>30.2</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>37.8</v>
+        <v>30.52</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>23.92</v>
+        <v>36.8</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.61</v>
+        <v>24.54</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>46.62</v>
+        <v>29.74</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>48.1</v>
+        <v>47.33</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>94.20999999999999</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>226.36</v>
+        <v>115.23</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>47.28</v>
+        <v>47.12</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>30.82</v>
+        <v>30.88</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>26.15</v>
+        <v>25.59</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>30.9</v>
+        <v>43.52</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>30.61</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="20">
@@ -2000,70 +2000,70 @@
         <v>-1.88</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.95</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-67.68000000000001</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-71.31999999999999</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-94.73999999999999</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-47.66</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-48.03</v>
+        <v>-10.39</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-54.14</v>
+        <v>-11.37</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-79.48999999999999</v>
+        <v>-12.77</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0</v>
+        <v>-18.37</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-58.93</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-58.64</v>
+        <v>-63.02</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-35.05</v>
+        <v>-63.67</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-17.46</v>
+        <v>-13.5</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-131.11</v>
+        <v>-84.08</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-219.62</v>
+        <v>-110.86</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-85.47</v>
+        <v>-65.81</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-85.38</v>
+        <v>-35.27</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-53.09</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-63.31</v>
+        <v>-24.79</v>
       </c>
     </row>
     <row r="21">
@@ -2084,70 +2084,70 @@
         <v>-0.23</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.14</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>-1.24</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-2.08</v>
+        <v>-0.91</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-3.07</v>
+        <v>-1.53</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.12</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.44</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-2.15</v>
+        <v>-1.43</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-3.03</v>
+        <v>-1.59</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.86</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-3.89</v>
+        <v>-1.36</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-4</v>
+        <v>-3.76</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-4.41</v>
+        <v>-4.48</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-3.61</v>
+        <v>-3.16</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-3.67</v>
+        <v>-2.91</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-16.8</v>
+        <v>-9.57</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-13.88</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-6.05</v>
+        <v>-5.03</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-5.24</v>
+        <v>-2.86</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-3.19</v>
+        <v>-1.78</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="22">
@@ -2168,13 +2168,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
@@ -2264,13 +2264,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-103.96</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2336,70 +2336,70 @@
         <v>32.03</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>32.27</v>
+        <v>31.58</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>31.94</v>
+        <v>34.29</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>36.52</v>
+        <v>46.66</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>80.11</v>
+        <v>77.23</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>113.39</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>233.6</v>
+        <v>54.5</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-100</v>
+        <v>39.99</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>24.58</v>
+        <v>36.2</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>27.34</v>
+        <v>36.64</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>43.02</v>
+        <v>36.73</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>37.8</v>
+        <v>39.92</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>54.09</v>
+        <v>36.8</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>54.63</v>
+        <v>56.8</v>
       </c>
       <c r="R24" s="3" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>158.27</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>103.86</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>64.56999999999999</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>57.04</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>94.20999999999999</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>293.48</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>159.7</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>74.56999999999999</v>
-      </c>
       <c r="X24" s="3" t="n">
-        <v>69.84999999999999</v>
+        <v>43.64</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>58.07</v>
+        <v>43.52</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>63.01</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="25">
@@ -2420,70 +2420,70 @@
         <v>-0.92</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.95</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-33.04</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-34.82</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-46.25</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-23.27</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-23.45</v>
+        <v>-5.07</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-26.43</v>
+        <v>-5.55</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-38.79</v>
+        <v>-6.23</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-28.76</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-28.62</v>
+        <v>-30.76</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-17.1</v>
+        <v>-31.07</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-8.52</v>
+        <v>-6.59</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-63.99</v>
+        <v>-41.04</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-107.2</v>
+        <v>-54.11</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-41.72</v>
+        <v>-32.12</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-41.68</v>
+        <v>-17.21</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-25.91</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-30.9</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="26">
@@ -2504,70 +2504,70 @@
         <v>-0.23</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.14</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>-1.24</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-2.08</v>
+        <v>-0.91</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-3.07</v>
+        <v>-1.53</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.12</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.44</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-2.15</v>
+        <v>-1.43</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-3.03</v>
+        <v>-1.59</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.86</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-3.89</v>
+        <v>-1.36</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-4</v>
+        <v>-3.76</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-4.41</v>
+        <v>-4.48</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-3.61</v>
+        <v>-3.16</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-3.67</v>
+        <v>-2.91</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-16.8</v>
+        <v>-9.57</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-13.88</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-6.05</v>
+        <v>-5.03</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-5.24</v>
+        <v>-2.86</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-3.19</v>
+        <v>-1.78</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="27">
@@ -2684,13 +2684,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-128.36</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>35</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>31.12</v>
+        <v>35.17</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>36.56</v>
+        <v>51</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>45.36</v>
+        <v>77.53</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>77</v>
+        <v>88.69</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>185.33</v>
+        <v>54.71</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-100</v>
+        <v>40.07</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.08</v>
+        <v>30.88</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.43</v>
+        <v>30.86</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.56</v>
+        <v>30.32</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>37.84</v>
+        <v>30.66</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>23.92</v>
+        <v>36.94</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>24.61</v>
+        <v>24.62</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>46.47</v>
+        <v>29.74</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>47.54</v>
+        <v>46.93</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>94.03</v>
+        <v>66.12</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>225</v>
+        <v>114.66</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>45.26</v>
+        <v>46.07</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>30.16</v>
+        <v>30.34</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>25.73</v>
+        <v>25.3</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>30.66</v>
+        <v>43.44</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.61</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="30">
@@ -2840,70 +2840,70 @@
         <v>-1.88</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.95</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1.62</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-67.68000000000001</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-71.31999999999999</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-94.73999999999999</v>
+        <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-47.66</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-48.03</v>
+        <v>-10.39</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-54.14</v>
+        <v>-11.37</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-79.48999999999999</v>
+        <v>-12.77</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0</v>
+        <v>-18.37</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-58.93</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-58.64</v>
+        <v>-63.02</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-35.05</v>
+        <v>-63.67</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-17.46</v>
+        <v>-13.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-131.11</v>
+        <v>-84.08</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-219.62</v>
+        <v>-110.86</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-85.47</v>
+        <v>-65.81</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-85.38</v>
+        <v>-35.27</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-53.09</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-63.31</v>
+        <v>-24.79</v>
       </c>
     </row>
     <row r="31">
@@ -2924,70 +2924,70 @@
         <v>-0.2</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.31</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-1.36</v>
+        <v>-0.93</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.96</v>
+        <v>-0.54</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-2.85</v>
+        <v>-1.31</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.04</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.44</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.39</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-2.79</v>
+        <v>-1.47</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.72</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-3.89</v>
+        <v>-1.22</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-4</v>
+        <v>-3.68</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-4.56</v>
+        <v>-4.48</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-4.16</v>
+        <v>-3.57</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-3.86</v>
+        <v>-3.04</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-18.16</v>
+        <v>-10.14</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-15.89</v>
+        <v>-9.57</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-6.71</v>
+        <v>-5.58</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-5.67</v>
+        <v>-3.15</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-3.43</v>
+        <v>-1.87</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="32">
@@ -3008,13 +3008,13 @@
         <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
@@ -3104,13 +3104,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-104.06</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3176,70 +3176,70 @@
         <v>33.76</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>33.81</v>
+        <v>33.58</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>68</v>
+        <v>34.68</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>68.22</v>
+        <v>47.79</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>113.48</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>149.58</v>
+        <v>99</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>282.11</v>
+        <v>56.02</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>-100</v>
+        <v>40.7</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>49.16</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>55.47</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>84.33</v>
+        <v>43.94</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>38.1</v>
+        <v>49.13</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>84.54000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>86.04000000000001</v>
+        <v>155</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>83.01000000000001</v>
+        <v>13.26</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>65.93000000000001</v>
+        <v>61.41</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>2000</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>283.78</v>
+        <v>2000</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>143.97</v>
+        <v>227.44</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>118.03</v>
+        <v>101.11</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>115.05</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>101.54</v>
+        <v>67.09</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>98.17</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -3263,16 +3263,16 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>34.53</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>30.46</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -3281,10 +3281,10 @@
         <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>32.75</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>31.42</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3293,37 +3293,37 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>-27.94</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>-81.33</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>-53.31</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-76.79000000000001</v>
+        <v>-172.24</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>-128.64</v>
+        <v>-64.93000000000001</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>0</v>
+        <v>35.68</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>13.58</v>
+        <v>21.46</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>0</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="36">
@@ -3344,70 +3344,70 @@
         <v>0.37</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.13</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.78</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.7</v>
+        <v>0.66</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.41</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.72</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.44</v>
+        <v>-1.23</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.62</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.62</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.08</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.35</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-3.07</v>
+        <v>-3.31</v>
       </c>
       <c r="S36" s="3" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="T36" s="3" t="n">
         <v>-3.23</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>-1.73</v>
-      </c>
       <c r="U36" s="3" t="n">
-        <v>-13.7</v>
+        <v>-11.08</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-8.18</v>
+        <v>-7.78</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-1.45</v>
+        <v>-0.61</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.79</v>
+        <v>0.32</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
@@ -3428,16 +3428,16 @@
         <v>0.21</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>65.03</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0</v>
@@ -3473,13 +3473,13 @@
         <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>0</v>
+        <v>1987.38</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>0</v>
+        <v>1974.44</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>0</v>
+        <v>133.64</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>0</v>
@@ -3524,13 +3524,13 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>-152.75</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3596,70 +3596,70 @@
         <v>32</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>32.24</v>
+        <v>31.58</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>31.88</v>
+        <v>34.15</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>36.41</v>
+        <v>46.52</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>80.22</v>
+        <v>77</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>113.16</v>
+        <v>88</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>233.27</v>
+        <v>54.34</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-100</v>
+        <v>39.95</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>24.48</v>
+        <v>36.2</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>27.29</v>
+        <v>36.6</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>42.78</v>
+        <v>36.65</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>37.77</v>
+        <v>39.78</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>53.93</v>
+        <v>36.69</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>54.55</v>
+        <v>56.63</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>64.64</v>
+        <v>62.34</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>57.47</v>
+        <v>54.59</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>94.3</v>
+        <v>66.37</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>294.51</v>
+        <v>159.04</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>161.24</v>
+        <v>104.77</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>75.02</v>
+        <v>64.94</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>70.17</v>
+        <v>43.88</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>58.07</v>
+        <v>43.56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>63.01</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="40">
@@ -3680,70 +3680,70 @@
         <v>-0.92</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.95</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-33.04</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>-34.82</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-46.25</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-23.27</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-23.45</v>
+        <v>-5.07</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-26.43</v>
+        <v>-5.55</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-38.79</v>
+        <v>-6.23</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-28.76</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-28.62</v>
+        <v>-30.76</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-17.1</v>
+        <v>-31.07</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-8.52</v>
+        <v>-6.59</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-63.99</v>
+        <v>-41.04</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-107.2</v>
+        <v>-54.11</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-41.72</v>
+        <v>-32.12</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-41.68</v>
+        <v>-17.21</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-25.91</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-30.9</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="41">
@@ -3764,70 +3764,70 @@
         <v>-0.26</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.46</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-2.3</v>
+        <v>-1.23</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-3.4</v>
+        <v>-1.68</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.8</v>
+        <v>-1.16</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.82</v>
+        <v>-1.44</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.48</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-3.26</v>
+        <v>-1.67</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-4.05</v>
+        <v>-1.47</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-4.08</v>
+        <v>-3.93</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-4.33</v>
+        <v>-4.48</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-3.17</v>
+        <v>-2.81</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.58</v>
+        <v>-2.79</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-15.77</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-12.35</v>
+        <v>-7.63</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-5.6</v>
+        <v>-4.66</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-4.92</v>
+        <v>-2.63</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-3.19</v>
+        <v>-1.74</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="42">
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>-128.26</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -4016,70 +4016,70 @@
         <v>33.38</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>33.38</v>
+        <v>32.93</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>33.23</v>
+        <v>34.39</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>36.89</v>
+        <v>47.04</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>115.55</v>
+        <v>78.78</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>150.4</v>
+        <v>89.34</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>282.11</v>
+        <v>55.97</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>-100</v>
+        <v>41.02</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>48.63</v>
+        <v>42.46</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>54.61</v>
+        <v>43.2</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>82.69</v>
+        <v>43.64</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>38.47</v>
+        <v>49.61</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>84.54000000000001</v>
+        <v>37.3</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>85.12</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>84.31</v>
+        <v>96.17</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>68.54000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>97.59</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>374.27</v>
+        <v>208.46</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>280.78</v>
+        <v>166</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>121.85</v>
+        <v>101.21</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>116.77</v>
+        <v>63.53</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>86.73999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="45">
@@ -4184,70 +4184,70 @@
         <v>0.2</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.16</v>
+        <v>0.32</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.08</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.25</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-1.31</v>
+        <v>-0.43</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-2.15</v>
+        <v>-0.92</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1</v>
+        <v>-1.14</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-2.2</v>
+        <v>-0.86</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.14</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.77</v>
+        <v>-1.73</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.41</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.51</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.4</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="47">
@@ -4364,13 +4364,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>-152.38</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4436,70 +4436,70 @@
         <v>33.89</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>33.79</v>
+        <v>33.37</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>33.67</v>
+        <v>34.88</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>37.69</v>
+        <v>48.05</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>119.16</v>
+        <v>81.23</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>153.79</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>286.03</v>
+        <v>57.88</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>-99.92</v>
+        <v>42.33</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>50.41</v>
+        <v>43.9</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>57.12</v>
+        <v>44.89</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>86.66</v>
+        <v>46.36</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>40.23</v>
+        <v>52.53</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>88.51000000000001</v>
+        <v>39.46</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>89.3</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>87.48</v>
+        <v>101.87</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>67.47</v>
+        <v>63.17</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>101.01</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>386.64</v>
+        <v>218.04</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>289.16</v>
+        <v>172.54</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>126.64</v>
+        <v>106.62</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>120.63</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>89.31999999999999</v>
+        <v>47</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>99.78</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="50">
@@ -4604,70 +4604,70 @@
         <v>0.71</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>4.77</v>
+        <v>2.76</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>3.51</v>
+        <v>1.51</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>3.11</v>
+        <v>1.85</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.98</v>
+        <v>1.23</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.66</v>
+        <v>1.19</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>0.76</v>
+        <v>1.79</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.05</v>
+        <v>2.82</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>1.4</v>
+        <v>3.97</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.69</v>
+        <v>-0.82</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>12.37</v>
+        <v>9.16</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>8.390000000000001</v>
+        <v>6.04</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>4.31</v>
+        <v>4.9</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>3.86</v>
+        <v>3.07</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.14</v>
+        <v>1.69</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>2.29</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="52">
@@ -4784,13 +4784,13 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>-154.22</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4856,70 +4856,70 @@
         <v>34.89</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>34.78</v>
+        <v>34.14</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>34.59</v>
+        <v>35.65</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>38.64</v>
+        <v>49.01</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>117.69</v>
+        <v>82.25</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>152.8</v>
+        <v>90.86</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>284.94</v>
+        <v>57.76</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>-99.58</v>
+        <v>42.25</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>50.66</v>
+        <v>43.54</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>56.54</v>
+        <v>43.98</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>86.66</v>
+        <v>45.56</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>40.23</v>
+        <v>51.89</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>89.33</v>
+        <v>39.42</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>89.3</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>86.77</v>
+        <v>99.19</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>67.67</v>
+        <v>63.3</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>92.34</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>276.63</v>
+        <v>145.97</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>135.75</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>115.01</v>
+        <v>98.66</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>117.36</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>90.43000000000001</v>
+        <v>47.39</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>102.4</v>
+        <v>63.76</v>
       </c>
     </row>
     <row r="55">
@@ -4988,13 +4988,13 @@
         <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>-76.79000000000001</v>
+        <v>-49.25</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>-128.64</v>
+        <v>-64.93000000000001</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="X55" s="3" t="n">
         <v>0</v>
@@ -5024,70 +5024,70 @@
         <v>1.71</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>2.52</v>
+        <v>1.63</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.62</v>
+        <v>0.35</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>1.82</v>
+        <v>1</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.76</v>
+        <v>1.14</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>2.59</v>
+        <v>1.26</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>2.05</v>
+        <v>2.82</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.29</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.49</v>
+        <v>-0.7</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-5.54</v>
+        <v>-3.42</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-20.85</v>
+        <v>-13.66</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-16.39</v>
+        <v>-11.04</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-4.48</v>
+        <v>-3.06</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.26</v>
+        <v>2.09</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>4.92</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="57">
@@ -5204,13 +5204,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>-154.22</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5276,70 +5276,70 @@
         <v>34.42</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>34.38</v>
+        <v>33.92</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>34.23</v>
+        <v>35.39</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>37.96</v>
+        <v>48.4</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>119.03</v>
+        <v>81.31</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>154.29</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>286.53</v>
+        <v>57.94</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>-99.86</v>
+        <v>42.47</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>50.51</v>
+        <v>44.03</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>56.65</v>
+        <v>44.89</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>85.95</v>
+        <v>45.23</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>39.99</v>
+        <v>51.47</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>87.97</v>
+        <v>38.7</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>88.39</v>
+        <v>92.53</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>87.48</v>
+        <v>99.59</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>70.93000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>100.7</v>
+        <v>71.08</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>386.64</v>
+        <v>215.56</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>290.36</v>
+        <v>171.65</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>125.99</v>
+        <v>104.65</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>120.88</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>89.5</v>
+        <v>46.37</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>100.4</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="60">
@@ -5444,70 +5444,70 @@
         <v>1.24</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>4.64</v>
+        <v>2.85</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>4.01</v>
+        <v>1.98</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>3.61</v>
+        <v>1.91</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.03</v>
+        <v>1.36</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.74</v>
+        <v>1.26</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.12</v>
+        <v>0.68</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.23</v>
+        <v>0.54</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>12.37</v>
+        <v>6.68</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>9.58</v>
+        <v>5.15</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>3.65</v>
+        <v>2.93</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>4.11</v>
+        <v>2.04</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.33</v>
+        <v>1.07</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>2.91</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="62">
@@ -5624,13 +5624,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>-154.22</v>
+        <v>0</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5696,70 +5696,70 @@
         <v>34.89</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>34.78</v>
+        <v>34.32</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>34.63</v>
+        <v>35.8</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>38.44</v>
+        <v>48.96</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>120.28</v>
+        <v>82.33</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>155.95</v>
+        <v>91.98</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>288.16</v>
+        <v>58.79</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>-99.13</v>
+        <v>43.09</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>51.13</v>
+        <v>44.59</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>57.41</v>
+        <v>45.49</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>87.19</v>
+        <v>45.84</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>40.56</v>
+        <v>52.21</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>39.26</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>89.76000000000001</v>
+        <v>93.95</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>88.73999999999999</v>
+        <v>101.13</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>72.04000000000001</v>
+        <v>66.52</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>102.28</v>
+        <v>72.19</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>392.73</v>
+        <v>219.18</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>295.56</v>
+        <v>174.71</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>127.83</v>
+        <v>105.96</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>122.66</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>90.70999999999999</v>
+        <v>47</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>101.76</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="65">
@@ -5864,70 +5864,70 @@
         <v>1.71</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>5.89</v>
+        <v>3.87</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>5.66</v>
+        <v>2.75</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>5.24</v>
+        <v>2.76</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.35</v>
+        <v>1.28</v>
       </c>
       <c r="O66" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P66" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="P66" s="3" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q66" s="3" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="R66" s="3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y66" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z66" s="3" t="n">
         <v>2.66</v>
-      </c>
-      <c r="S66" s="3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X66" s="3" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="Y66" s="3" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="Z66" s="3" t="n">
-        <v>4.27</v>
       </c>
     </row>
     <row r="67">
@@ -6044,13 +6044,13 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>-154.22</v>
+        <v>0</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6116,70 +6116,70 @@
         <v>35.33</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>35.3</v>
+        <v>34.86</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>35.18</v>
+        <v>36.33</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>39.01</v>
+        <v>49.74</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>122.64</v>
+        <v>83.56</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>157.52</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>289.84</v>
+        <v>59.54</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>-98.56</v>
+        <v>43.64</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>51.61</v>
+        <v>45.3</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>57.89</v>
+        <v>46.17</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>87.81999999999999</v>
+        <v>46.22</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>40.86</v>
+        <v>52.59</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>89.89</v>
+        <v>39.54</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>90.22</v>
+        <v>94.44</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>89.2</v>
+        <v>101.45</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>72.42</v>
+        <v>66.87</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>102.93</v>
+        <v>72.64</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>395.63</v>
+        <v>220.57</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>297.75</v>
+        <v>176.01</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>128.91</v>
+        <v>107.19</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>124.09</v>
+        <v>67.5</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>91.67</v>
+        <v>47.49</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>103.27</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="70">
@@ -6284,70 +6284,70 @@
         <v>2.16</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>7.82</v>
+        <v>5.1</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>7.23</v>
+        <v>3.54</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>6.92</v>
+        <v>3.51</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.86</v>
+        <v>2.58</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.97</v>
+        <v>2.54</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.99</v>
+        <v>1.66</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.15</v>
+        <v>1.38</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>3.12</v>
+        <v>3.55</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3.26</v>
+        <v>2.88</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>5.04</v>
+        <v>3.49</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>21.36</v>
+        <v>11.69</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>16.97</v>
+        <v>9.5</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>6.57</v>
+        <v>5.47</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>7.32</v>
+        <v>3.78</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>4.49</v>
+        <v>2.18</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>5.78</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="72">
@@ -6377,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>0</v>
@@ -6464,13 +6464,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>-154.22</v>
+        <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6536,70 +6536,70 @@
         <v>34.42</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>34.38</v>
+        <v>33.92</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>34.23</v>
+        <v>35.35</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>37.92</v>
+        <v>48.35</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>119.03</v>
+        <v>81.39</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>154.55</v>
+        <v>91.27</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>287.15</v>
+        <v>58.24</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>-99.58</v>
+        <v>42.64</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>50.66</v>
+        <v>44.17</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>56.89</v>
+        <v>44.98</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>86.48</v>
+        <v>45.51</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>40.23</v>
+        <v>51.78</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>88.42</v>
+        <v>38.94</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>88.75</v>
+        <v>93</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>87.84</v>
+        <v>100</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>71.15000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>101.22</v>
+        <v>71.44</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>388.65</v>
+        <v>216.68</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>291.87</v>
+        <v>172.72</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>126.64</v>
+        <v>105.3</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>121.38</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>89.87</v>
+        <v>46.61</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>100.71</v>
+        <v>62.71</v>
       </c>
     </row>
     <row r="75">
@@ -6704,70 +6704,70 @@
         <v>1.24</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>4.64</v>
+        <v>2.93</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>4.26</v>
+        <v>2.04</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>4.23</v>
+        <v>2.21</v>
       </c>
       <c r="K76" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y76" s="3" t="n">
         <v>1.31</v>
       </c>
-      <c r="L76" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>14.38</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Z76" s="3" t="n">
-        <v>3.22</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="77">
@@ -6884,13 +6884,13 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>-154.22</v>
+        <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6956,70 +6956,70 @@
         <v>33.18</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>33.11</v>
+        <v>32.67</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>32.93</v>
+        <v>34.15</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>36.63</v>
+        <v>46.76</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>114.39</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>150.29</v>
+        <v>89.23</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>282.92</v>
+        <v>56.02</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>-100</v>
+        <v>41.11</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>49.75</v>
+        <v>42.71</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>55.92</v>
+        <v>43.63</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>84.84</v>
+        <v>44.56</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>39.47</v>
+        <v>50.75</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>86.73999999999999</v>
+        <v>38.16</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>87.23999999999999</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>86.08</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S79" s="3" t="n">
+        <v>63.99</v>
+      </c>
+      <c r="T79" s="3" t="n">
         <v>69.16</v>
       </c>
-      <c r="T79" s="3" t="n">
-        <v>97.88</v>
-      </c>
       <c r="U79" s="3" t="n">
-        <v>374.27</v>
+        <v>208.88</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>280.78</v>
+        <v>166.5</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>122.34</v>
+        <v>101.72</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>116.77</v>
+        <v>63.72</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>87.18000000000001</v>
+        <v>45.3</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>97.48</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="80">
@@ -7304,13 +7304,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>-153.33</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7376,70 +7376,70 @@
         <v>34.82</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>34.71</v>
+        <v>33.99</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>34.52</v>
+        <v>35.54</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>38.76</v>
+        <v>49.17</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>117.2</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>151.11</v>
+        <v>90.17</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>282.8</v>
+        <v>56.99</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>-100</v>
+        <v>41.48</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>49.36</v>
+        <v>42.59</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>55.15</v>
+        <v>43.03</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>84.33</v>
+        <v>44.56</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>39.04</v>
+        <v>50.6</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>38.28</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>86.12</v>
+        <v>91.69</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>84.56</v>
+        <v>97.03</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>66.81999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>89.39</v>
+        <v>63.8</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>270.08</v>
+        <v>140.99</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>130.39</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>111.27</v>
+        <v>95.69</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>115.73</v>
+        <v>63.53</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>90.43000000000001</v>
+        <v>47.74</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>102.29</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="85">
@@ -7508,13 +7508,13 @@
         <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-76.79000000000001</v>
+        <v>-49.25</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>-128.64</v>
+        <v>-64.93000000000001</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>-2.85</v>
+        <v>0</v>
       </c>
       <c r="X85" s="3" t="n">
         <v>0</v>
@@ -7544,70 +7544,70 @@
         <v>1.64</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.81</v>
+        <v>3.18</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-0.12</v>
+        <v>0.97</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.13</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.6</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.15</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-0.35</v>
+        <v>0.11</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-1.12</v>
+        <v>0.37</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.52</v>
+        <v>-0.87</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-2.34</v>
+        <v>-1.19</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-8.49</v>
+        <v>-5.36</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-27.4</v>
+        <v>-18.64</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-21.76</v>
+        <v>-14.86</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.03</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.19</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>4.81</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="87">
@@ -7724,13 +7724,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>-153.65</v>
+        <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7796,70 +7796,70 @@
         <v>32.06</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>35.71</v>
+        <v>36</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>31.94</v>
+        <v>35.17</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>36.56</v>
+        <v>51</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>80</v>
+        <v>77.53</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>113.5</v>
+        <v>88.69</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>233.82</v>
+        <v>54.71</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>-100</v>
+        <v>40.07</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>24.67</v>
+        <v>36.2</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>27.29</v>
+        <v>36.68</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>43.25</v>
+        <v>36.86</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>37.84</v>
+        <v>40.07</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>54.09</v>
+        <v>36.94</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>54.63</v>
+        <v>56.89</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>64.33</v>
+        <v>62.34</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>56.48</v>
+        <v>53.84</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>94.03</v>
+        <v>66.12</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>292.12</v>
+        <v>157.71</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>157.69</v>
+        <v>102.82</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>73.91</v>
+        <v>64.02</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>69.43000000000001</v>
+        <v>43.35</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>57.83</v>
+        <v>43.44</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>63.01</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="90">
@@ -7880,70 +7880,70 @@
         <v>-0.92</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.95</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>-33.04</v>
+        <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-34.82</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>-46.25</v>
+        <v>0</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-23.27</v>
+        <v>0</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-23.45</v>
+        <v>-5.07</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-26.43</v>
+        <v>-5.55</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-38.79</v>
+        <v>-6.23</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-28.76</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-28.62</v>
+        <v>-30.76</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-17.1</v>
+        <v>-31.07</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-8.52</v>
+        <v>-6.59</v>
       </c>
       <c r="T90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>-63.99</v>
+        <v>-41.04</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-107.2</v>
+        <v>-54.11</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-41.72</v>
+        <v>-32.12</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-41.68</v>
+        <v>-17.21</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-25.91</v>
+        <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-30.9</v>
+        <v>-12.1</v>
       </c>
     </row>
     <row r="91">
@@ -7964,70 +7964,70 @@
         <v>-0.2</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.2</v>
+        <v>0.31</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-1.36</v>
+        <v>-0.93</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-1.96</v>
+        <v>-0.54</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-2.85</v>
+        <v>-1.31</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.04</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.44</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-2.2</v>
+        <v>-1.39</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-2.79</v>
+        <v>-1.47</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.72</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-3.89</v>
+        <v>-1.22</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-4</v>
+        <v>-3.68</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-4.64</v>
+        <v>-4.48</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-4.16</v>
+        <v>-3.57</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-3.86</v>
+        <v>-3.04</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-18.16</v>
+        <v>-10.14</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-15.89</v>
+        <v>-9.57</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-6.71</v>
+        <v>-5.58</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-5.67</v>
+        <v>-3.15</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-3.43</v>
+        <v>-1.87</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="92">
@@ -8048,13 +8048,13 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
@@ -8144,13 +8144,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>32.83</v>
+        <v>34.66</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>166.23</v>
+        <v>0</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>-128.46</v>
+        <v>0</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-10T01:12:25</t>
+          <t>CreatedAt: 2026-10-10T08:11:26</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -659,67 +659,67 @@
         <v>48.65</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>48.96</v>
+        <v>48.33</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44.04</v>
+        <v>45.51</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>48.52</v>
+        <v>48.8</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>54.7</v>
+        <v>76.06</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>150.18</v>
+        <v>49.17</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
+        <v>40.39</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>34.22</v>
+        <v>34.62</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>35</v>
+        <v>49.88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>35.39</v>
+        <v>29.74</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>35.32</v>
+        <v>30.61</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>42.27</v>
+        <v>31.54</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>41.64</v>
+        <v>34.95</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>42.15</v>
+        <v>34.88</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>50.12</v>
+        <v>44.01</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.63</v>
+        <v>35.96</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>38.33</v>
+        <v>35.96</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>32.06</v>
+        <v>40.24</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>32.25</v>
+        <v>32.16</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>32.03</v>
+        <v>35.04</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>30.15</v>
+        <v>31.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>29.08</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="5">
@@ -752,28 +752,28 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-5.37</v>
+        <v>-0.83</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>-10.42</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-8.01</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
@@ -794,16 +794,16 @@
         <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.7</v>
+        <v>-3.24</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -827,67 +827,67 @@
         <v>-1.61</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.45</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-1.1</v>
+        <v>-0.96</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-1.16</v>
+        <v>-0.93</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.06</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.73</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.28</v>
+        <v>-1.58</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.12</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.47</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.27</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.3</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.29</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1.33</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.26</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.23</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.9</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.84</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.61</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.88</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="7">
@@ -1004,22 +1004,22 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
@@ -1079,67 +1079,67 @@
         <v>48.56</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>48.82</v>
+        <v>48.05</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44.65</v>
+        <v>45.11</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>48.33</v>
+        <v>48.23</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>54.23</v>
+        <v>75.14</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>150.13</v>
+        <v>49.17</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.63</v>
+        <v>41.24</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.25</v>
+        <v>34.56</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>34.94</v>
+        <v>49.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>36.05</v>
+        <v>30.32</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>35.73</v>
+        <v>30.94</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>43.06</v>
+        <v>32</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>41.6</v>
+        <v>34.92</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>41.51</v>
+        <v>34.38</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>49.4</v>
+        <v>43.22</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>42.18</v>
+        <v>35.44</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>38.11</v>
+        <v>35.57</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>32.44</v>
+        <v>32.28</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>31.48</v>
+        <v>34.33</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>30.03</v>
+        <v>31.56</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>28.88</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="10">
@@ -1172,28 +1172,28 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-5.37</v>
+        <v>-0.83</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>-10.42</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-8.01</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
@@ -1214,16 +1214,16 @@
         <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.7</v>
+        <v>-3.24</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1247,67 +1247,67 @@
         <v>-1.7</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.73</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.49</v>
+        <v>-1.35</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.91</v>
+        <v>-1.98</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.73</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.65</v>
+        <v>-0.72</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.19</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.85</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.17</v>
+        <v>-0.83</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.36</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.99</v>
+        <v>-1.75</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.03</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.42</v>
       </c>
       <c r="U11" s="3" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Y11" s="3" t="n">
         <v>-1.18</v>
       </c>
-      <c r="V11" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-0.92</v>
-      </c>
       <c r="Z11" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="12">
@@ -1424,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>0</v>
@@ -1502,64 +1502,64 @@
         <v>37.88</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44.65</v>
+        <v>37.88</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>48.33</v>
+        <v>37.88</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>59.6</v>
+        <v>75.97</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>150.13</v>
+        <v>54.14</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2000</v>
+        <v>51.66</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>34.25</v>
+        <v>34.94</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>34.94</v>
+        <v>42.48</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2000</v>
+        <v>30.66</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>2000</v>
+        <v>31.28</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>51.12</v>
+        <v>32</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>41.6</v>
+        <v>34.92</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>41.51</v>
+        <v>34.38</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>10.98</v>
+        <v>10.39</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>42.18</v>
+        <v>35.44</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>38.11</v>
+        <v>35.57</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>32.44</v>
+        <v>32.28</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>9.17</v>
+        <v>9.44</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>8.720000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>7.98</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="15">
@@ -1583,13 +1583,13 @@
         <v>-40.23</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-10.94</v>
+        <v>-10.17</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>-7.23</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>-10.35</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0</v>
@@ -1598,19 +1598,19 @@
         <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1963.81</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0</v>
+        <v>-7.02</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1963.92</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>1964.27</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-38.42</v>
+        <v>-32.83</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>0</v>
@@ -1634,16 +1634,16 @@
         <v>0</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>-22.31</v>
+        <v>-24.89</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>-22.02</v>
+        <v>-25.55</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>-21.93</v>
+        <v>-20.55</v>
       </c>
     </row>
     <row r="16">
@@ -1667,67 +1667,67 @@
         <v>-1.7</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.56</v>
+        <v>-1.73</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.49</v>
+        <v>-1.35</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.91</v>
+        <v>-1.98</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.73</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.72</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.4</v>
+        <v>-1.19</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.85</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.83</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.36</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-1.99</v>
+        <v>-1.75</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.03</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.42</v>
       </c>
       <c r="U16" s="3" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="Y16" s="3" t="n">
         <v>-1.18</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>-0.92</v>
-      </c>
       <c r="Z16" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="17">
@@ -1844,10 +1844,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1856,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>0</v>
@@ -1919,67 +1919,67 @@
         <v>48.51</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>48.86</v>
+        <v>48.24</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>44.04</v>
+        <v>45.37</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>48.43</v>
+        <v>48.61</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>48.77</v>
+        <v>74.89</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>150</v>
+        <v>43.8</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>29.31</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>34.06</v>
+        <v>34.12</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>34.84</v>
+        <v>49.8</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>35.29</v>
+        <v>29.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>35.18</v>
+        <v>30.16</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>33.72</v>
+        <v>31.48</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>41.44</v>
+        <v>34.82</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>41.83</v>
+        <v>34.68</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>49.88</v>
+        <v>43.8</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>42.59</v>
+        <v>35.92</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>38.26</v>
+        <v>35.89</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>31.97</v>
+        <v>40.16</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>32.19</v>
+        <v>32.08</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>31.97</v>
+        <v>34.94</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>29.35</v>
+        <v>28.33</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>28.03</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="20">
@@ -2012,28 +2012,28 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-11.01</v>
+        <v>-1.71</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>-10.18</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>-21.35</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-16.42</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
@@ -2054,16 +2054,16 @@
         <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-1.44</v>
+        <v>-6.64</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2087,67 +2087,67 @@
         <v>-1.75</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.54</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.09</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.12</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.36</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.89</v>
       </c>
       <c r="K21" s="3" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>-1.35</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-2.11</v>
-      </c>
       <c r="Q21" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.46</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.46</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.45</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.93</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.97</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.92</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.67</v>
       </c>
       <c r="X21" s="3" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>-0.83</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>-0.87</v>
       </c>
     </row>
     <row r="22">
@@ -2264,22 +2264,22 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>0</v>
@@ -2339,67 +2339,67 @@
         <v>48.51</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>48.86</v>
+        <v>48.24</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>44.04</v>
+        <v>45.37</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>48.43</v>
+        <v>48.61</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>54.4</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>150</v>
+        <v>49.02</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>40.24</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>34.06</v>
+        <v>34.52</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>34.84</v>
+        <v>49.8</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>35.29</v>
+        <v>29.65</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>35.18</v>
+        <v>30.52</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>42.12</v>
+        <v>31.48</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>41.44</v>
+        <v>34.82</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>41.83</v>
+        <v>34.68</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>49.88</v>
+        <v>43.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>42.59</v>
+        <v>35.92</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>38.26</v>
+        <v>35.89</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>31.97</v>
+        <v>40.16</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>32.19</v>
+        <v>32.09</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>31.97</v>
+        <v>34.94</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>30.09</v>
+        <v>31.73</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>29.11</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="25">
@@ -2432,28 +2432,28 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-5.37</v>
+        <v>-0.83</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>-10.42</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-8.01</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>0</v>
@@ -2474,16 +2474,16 @@
         <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0.7</v>
+        <v>-3.24</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2507,67 +2507,67 @@
         <v>-1.75</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-1.51</v>
+        <v>-1.54</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.09</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.12</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.36</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.89</v>
       </c>
       <c r="K26" s="3" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>-1.35</v>
       </c>
-      <c r="L26" s="3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-2.11</v>
-      </c>
       <c r="Q26" s="3" t="n">
-        <v>-1.7</v>
+        <v>-1.46</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.46</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.85</v>
+        <v>-1.45</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.93</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.97</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.92</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.67</v>
       </c>
       <c r="X26" s="3" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>-0.83</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>-0.87</v>
       </c>
     </row>
     <row r="27">
@@ -2684,22 +2684,22 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>48.28</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>48.77</v>
+        <v>48.14</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>44</v>
+        <v>45.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>48.24</v>
+        <v>48.37</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>48.36</v>
+        <v>74.55</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>149.78</v>
+        <v>43.49</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.24</v>
+        <v>29.11</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>33.83</v>
+        <v>33.98</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>34.61</v>
+        <v>49.69</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>35.08</v>
+        <v>29.15</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>35.02</v>
+        <v>29.99</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>33.43</v>
+        <v>31.33</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>41.2</v>
+        <v>34.62</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>41.35</v>
+        <v>34.41</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>49.59</v>
+        <v>43.59</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>42.63</v>
+        <v>35.92</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>38.22</v>
+        <v>35.82</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>31.87</v>
+        <v>40.04</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>32.09</v>
+        <v>31.98</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>31.91</v>
+        <v>34.87</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>29.26</v>
+        <v>28.23</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>28.12</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="30">
@@ -2852,28 +2852,28 @@
         <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-11.01</v>
+        <v>-1.71</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0</v>
+        <v>-10.18</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>-21.35</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-16.42</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>0</v>
@@ -2894,16 +2894,16 @@
         <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-1.44</v>
+        <v>-6.64</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2927,67 +2927,67 @@
         <v>-1.98</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.64</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.27</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.35</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-2.14</v>
+        <v>-1.7</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.92</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.36</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-1.94</v>
+        <v>-1.66</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.51</v>
       </c>
       <c r="O31" s="3" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>-1.72</v>
       </c>
-      <c r="P31" s="3" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-2.15</v>
-      </c>
       <c r="S31" s="3" t="n">
-        <v>-2.13</v>
+        <v>-1.66</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.93</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.04</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.04</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.77</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.05</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.12</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="32">
@@ -3104,22 +3104,22 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
@@ -3179,67 +3179,67 @@
         <v>13.16</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>39.55</v>
+        <v>39.41</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45.42</v>
+        <v>39.22</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>48.9</v>
+        <v>39.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>60.07</v>
+        <v>75.78</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>150.62</v>
+        <v>54.89</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2000</v>
+        <v>52.44</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>34.58</v>
+        <v>35.38</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>35.38</v>
+        <v>43.18</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>2000</v>
+        <v>31.16</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>2000</v>
+        <v>31.62</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>51.83</v>
+        <v>32.41</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>42.16</v>
+        <v>35.32</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>41.71</v>
+        <v>34.51</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>15.2</v>
+        <v>13.84</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>42.34</v>
+        <v>35.54</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>38.3</v>
+        <v>35.68</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>32.31</v>
+        <v>40.24</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>32.83</v>
+        <v>32.63</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>11.37</v>
+        <v>11.87</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>11.25</v>
+        <v>12.15</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>10.35</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3263,13 +3263,13 @@
         <v>-36.2</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-9.84</v>
+        <v>-9.15</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>-6.51</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>-9.31</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0</v>
@@ -3278,19 +3278,19 @@
         <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>1963.27</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>-6.32</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1963.3</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1963.85</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-34.58</v>
+        <v>-29.55</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>0</v>
@@ -3314,16 +3314,16 @@
         <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>-20.08</v>
+        <v>-22.4</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>-19.81</v>
+        <v>-22.99</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>-19.73</v>
+        <v>-18.49</v>
       </c>
     </row>
     <row r="36">
@@ -3347,67 +3347,67 @@
         <v>-0.89</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.21</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.27</v>
+        <v>-0.91</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.78</v>
+        <v>-1.02</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-1.44</v>
+        <v>-2.17</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>-1.15</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-1.07</v>
+        <v>-0.95</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.85</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.63</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.95</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.62</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-1.94</v>
+        <v>-1.87</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.32</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-1</v>
+        <v>-1.18</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.84</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.64</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.84</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="37">
@@ -3434,22 +3434,22 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3536,10 +3536,10 @@
         <v>0</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>0</v>
@@ -3599,67 +3599,67 @@
         <v>48.65</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>48.96</v>
+        <v>48.33</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>44.04</v>
+        <v>45.51</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>48.52</v>
+        <v>48.8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>54.7</v>
+        <v>76.06</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>150.18</v>
+        <v>49.17</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
+        <v>40.39</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>34.22</v>
+        <v>34.62</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>35</v>
+        <v>49.88</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>35.39</v>
+        <v>29.74</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>35.32</v>
+        <v>30.61</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>42.27</v>
+        <v>31.54</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>41.64</v>
+        <v>34.95</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>42.15</v>
+        <v>34.88</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>50.12</v>
+        <v>44.01</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>42.63</v>
+        <v>35.96</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>38.33</v>
+        <v>35.96</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>32.06</v>
+        <v>40.24</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>32.25</v>
+        <v>32.16</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>32.03</v>
+        <v>35.04</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>30.15</v>
+        <v>31.8</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>29.08</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="40">
@@ -3692,28 +3692,28 @@
         <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>-5.37</v>
+        <v>-0.83</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>-10.42</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-8.01</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>0</v>
@@ -3734,16 +3734,16 @@
         <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-0.7</v>
+        <v>-3.24</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3767,67 +3767,67 @@
         <v>-1.61</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.45</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-1.1</v>
+        <v>-0.96</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-1.16</v>
+        <v>-0.93</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.06</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.73</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.28</v>
+        <v>-1.58</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.12</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.47</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-1.38</v>
+        <v>-1.27</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.3</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.29</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1.33</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.26</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.6</v>
+        <v>-1.23</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.9</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.9</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.84</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.61</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.88</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-0.8</v>
+        <v>-0.95</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="42">
@@ -3944,22 +3944,22 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>0</v>
@@ -4019,67 +4019,67 @@
         <v>50.11</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>50.28</v>
+        <v>49.73</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45.1</v>
+        <v>46.56</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>49.74</v>
+        <v>49.92</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>61.63</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>151.4</v>
+        <v>55.88</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.77</v>
+        <v>52.23</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>35.2</v>
+        <v>35.92</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>35.97</v>
+        <v>50.86</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>36.23</v>
+        <v>30.88</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>36.19</v>
+        <v>31.81</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>51.52</v>
+        <v>32.41</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>42.67</v>
+        <v>35.85</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>43.33</v>
+        <v>35.95</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>52.04</v>
+        <v>45.52</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>44.09</v>
+        <v>37.19</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>39.61</v>
+        <v>37.11</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>33.16</v>
+        <v>41.41</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>33.13</v>
+        <v>32.98</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>33</v>
+        <v>36.09</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>31.72</v>
+        <v>36.02</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>31.17</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="45">
@@ -4187,67 +4187,67 @@
         <v>-0.15</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.16</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.22</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.49</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.48</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.45</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.42</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.44</v>
+        <v>0.33</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>0.33</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="47">
@@ -4364,22 +4364,22 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -4439,67 +4439,67 @@
         <v>51.44</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>51.88</v>
+        <v>51.06</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>46.59</v>
+        <v>47.75</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>51.38</v>
+        <v>51.32</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>63.41</v>
+        <v>79.17</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>153.09</v>
+        <v>57.43</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>2.18</v>
+        <v>53.89</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>36.46</v>
+        <v>37.06</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>37.79</v>
+        <v>52.8</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>38.02</v>
+        <v>32.45</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>37.99</v>
+        <v>33.42</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>54.02</v>
+        <v>33.99</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>44.7</v>
+        <v>37.59</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>45.31</v>
+        <v>37.68</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>54.39</v>
+        <v>47.63</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>42.97</v>
+        <v>36.28</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>40.68</v>
+        <v>38.15</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>33.95</v>
+        <v>42.48</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>34.13</v>
+        <v>34.11</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>33.82</v>
+        <v>37.02</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>32.47</v>
+        <v>36.95</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>31.78</v>
+        <v>30.03</v>
       </c>
     </row>
     <row r="50">
@@ -4607,67 +4607,67 @@
         <v>1.18</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1.9</v>
+        <v>1.21</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.91</v>
+        <v>1.51</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.78</v>
+        <v>1.16</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>2.67</v>
+        <v>2.38</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>1.33</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="52">
@@ -4784,22 +4784,22 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O53" s="3" t="n">
         <v>0</v>
@@ -4859,67 +4859,67 @@
         <v>52.96</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>52.92</v>
+        <v>52.24</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>47.37</v>
+        <v>48.65</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52.25</v>
+        <v>52.12</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>64.34</v>
+        <v>80.38</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>154.11</v>
+        <v>58.63</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2.85</v>
+        <v>54.68</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>36.95</v>
+        <v>37.52</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>37.83</v>
+        <v>52.75</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>38.06</v>
+        <v>32.45</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>38.06</v>
+        <v>33.39</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>53.86</v>
+        <v>33.78</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>44.15</v>
+        <v>37.13</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>43.54</v>
+        <v>36.2</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>49.78</v>
+        <v>42.61</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>40.68</v>
+        <v>34.32</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>36.62</v>
+        <v>34.35</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>30.6</v>
+        <v>38.32</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>31.42</v>
+        <v>32.12</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>33.4</v>
+        <v>36.68</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>33.11</v>
+        <v>37.72</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>32.37</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="55">
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="X55" s="3" t="n">
         <v>0</v>
@@ -5027,67 +5027,67 @@
         <v>2.7</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>2.33</v>
+        <v>2.76</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="L56" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N56" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="Y56" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z56" s="3" t="n">
         <v>1.29</v>
-      </c>
-      <c r="M56" s="3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="O56" s="3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P56" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q56" s="3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="R56" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="S56" s="3" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="T56" s="3" t="n">
-        <v>-2.97</v>
-      </c>
-      <c r="U56" s="3" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="V56" s="3" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="W56" s="3" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="X56" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Y56" s="3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z56" s="3" t="n">
-        <v>1.36</v>
       </c>
     </row>
     <row r="57">
@@ -5204,22 +5204,22 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O58" s="3" t="n">
         <v>0</v>
@@ -5279,67 +5279,67 @@
         <v>51.86</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>52.04</v>
+        <v>51.43</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>46.59</v>
+        <v>48.1</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>51.38</v>
+        <v>51.53</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>63.74</v>
+        <v>79.94</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>153.14</v>
+        <v>57.9</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>2.11</v>
+        <v>54.17</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>36.57</v>
+        <v>37.33</v>
       </c>
       <c r="M59" s="3" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>33.71</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>37.33</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>47.18</v>
+      </c>
+      <c r="T59" s="3" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="W59" s="3" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="X59" s="3" t="n">
         <v>37.37</v>
       </c>
-      <c r="N59" s="3" t="n">
-        <v>37.67</v>
-      </c>
-      <c r="O59" s="3" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="P59" s="3" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="Q59" s="3" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="R59" s="3" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="S59" s="3" t="n">
-        <v>53.88</v>
-      </c>
-      <c r="T59" s="3" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="U59" s="3" t="n">
-        <v>40.97</v>
-      </c>
-      <c r="V59" s="3" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="W59" s="3" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="X59" s="3" t="n">
-        <v>34.13</v>
-      </c>
       <c r="Y59" s="3" t="n">
-        <v>32.84</v>
+        <v>37.33</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>32.31</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="60">
@@ -5447,67 +5447,67 @@
         <v>1.61</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.36</v>
+        <v>2.03</v>
       </c>
       <c r="K61" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N61" s="3" t="n">
         <v>0.83</v>
       </c>
-      <c r="L61" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O61" s="3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="P61" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Y61" s="3" t="n">
         <v>1.34</v>
       </c>
-      <c r="Q61" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X61" s="3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Y61" s="3" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="62">
@@ -5624,22 +5624,22 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O63" s="3" t="n">
         <v>0</v>
@@ -5699,67 +5699,67 @@
         <v>52.57</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>52.7</v>
+        <v>52.13</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>47.17</v>
+        <v>48.7</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>52.03</v>
+        <v>52.23</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>64.68000000000001</v>
+        <v>80.67</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>153.9</v>
+        <v>58.76</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>2.65</v>
+        <v>54.91</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>37.1</v>
+        <v>37.87</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>37.95</v>
+        <v>53.2</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>38.3</v>
+        <v>32.73</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>38.26</v>
+        <v>33.63</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>54.47</v>
+        <v>34.31</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>45.07</v>
+        <v>37.91</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>45.69</v>
+        <v>37.99</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>54.79</v>
+        <v>47.93</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>46.34</v>
+        <v>39.09</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>41.62</v>
+        <v>39.04</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>34.81</v>
+        <v>43.47</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>34.78</v>
+        <v>34.73</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>34.68</v>
+        <v>37.84</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>33.32</v>
+        <v>37.8</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>32.75</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="65">
@@ -5867,67 +5867,67 @@
         <v>2.31</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.37</v>
+        <v>2.53</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="P66" s="3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T66" s="3" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q66" s="3" t="n">
+      <c r="U66" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="W66" s="3" t="n">
         <v>1.94</v>
       </c>
-      <c r="R66" s="3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S66" s="3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X66" s="3" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="67">
@@ -6044,22 +6044,22 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0</v>
@@ -6119,67 +6119,67 @@
         <v>53.35</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>53.48</v>
+        <v>52.9</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>47.87</v>
+        <v>49.43</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>52.8</v>
+        <v>53.01</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>65.58</v>
+        <v>81.42</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>154.53</v>
+        <v>59.57</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>3.13</v>
+        <v>55.73</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>37.57</v>
+        <v>38.44</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>38.39</v>
+        <v>53.79</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>38.66</v>
+        <v>33.09</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>38.62</v>
+        <v>33.99</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>54.99</v>
+        <v>34.63</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>45.5</v>
+        <v>38.27</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>46.13</v>
+        <v>38.36</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>55.44</v>
+        <v>48.5</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>46.89</v>
+        <v>39.55</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>42.11</v>
+        <v>39.5</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>35.22</v>
+        <v>43.94</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>35.19</v>
+        <v>35.06</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>35.12</v>
+        <v>38.41</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>33.78</v>
+        <v>38.41</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>33.17</v>
+        <v>31.24</v>
       </c>
     </row>
     <row r="70">
@@ -6287,67 +6287,67 @@
         <v>3.09</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.73</v>
+        <v>2.97</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>3.12</v>
+        <v>3.29</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>4.07</v>
+        <v>3.47</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.75</v>
+        <v>3.69</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.86</v>
+        <v>3.34</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.92</v>
+        <v>2.31</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.84</v>
+        <v>2.44</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.63</v>
+        <v>2.22</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.24</v>
+        <v>2.69</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.4</v>
+        <v>2.86</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="72">
@@ -6464,22 +6464,22 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O73" s="3" t="n">
         <v>0</v>
@@ -6539,67 +6539,67 @@
         <v>51.97</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>52.15</v>
+        <v>51.53</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>46.69</v>
+        <v>48.15</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>51.49</v>
+        <v>51.64</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>63.94</v>
+        <v>80.05</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>153.24</v>
+        <v>57.96</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>2.22</v>
+        <v>54.28</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>36.76</v>
+        <v>37.52</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>37.6</v>
+        <v>52.75</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>37.87</v>
+        <v>32.35</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>37.83</v>
+        <v>33.28</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>53.86</v>
+        <v>33.88</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>44.42</v>
+        <v>37.4</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>45.08</v>
+        <v>37.44</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>54.16</v>
+        <v>47.38</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>45.71</v>
+        <v>38.55</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>41.14</v>
+        <v>38.55</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>34.41</v>
+        <v>42.97</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>34.34</v>
+        <v>34.22</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>34.24</v>
+        <v>37.49</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>32.94</v>
+        <v>37.45</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>32.34</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="75">
@@ -6707,67 +6707,67 @@
         <v>1.72</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="J76" s="3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Y76" s="3" t="n">
         <v>1.46</v>
       </c>
-      <c r="K76" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z76" s="3" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="77">
@@ -6884,22 +6884,22 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O78" s="3" t="n">
         <v>0</v>
@@ -6959,67 +6959,67 @@
         <v>50.26</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>50.38</v>
+        <v>49.78</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45.14</v>
+        <v>46.46</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>49.69</v>
+        <v>49.73</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>61.51</v>
+        <v>77.95</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>151.78</v>
+        <v>55.88</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1.28</v>
+        <v>52.38</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>35.66</v>
+        <v>36.13</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>36.54</v>
+        <v>51.35</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>36.77</v>
+        <v>31.35</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>36.73</v>
+        <v>32.25</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>52.24</v>
+        <v>32.83</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>43.13</v>
+        <v>36.28</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>43.5</v>
+        <v>36.13</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>51.72</v>
+        <v>45.25</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>43.65</v>
+        <v>36.86</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>39.29</v>
+        <v>36.86</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>32.83</v>
+        <v>41.08</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>32.8</v>
+        <v>32.78</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>32.8</v>
+        <v>35.91</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>31.65</v>
+        <v>35.99</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>31.01</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="80">
@@ -7304,22 +7304,22 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O83" s="3" t="n">
         <v>0</v>
@@ -7379,67 +7379,67 @@
         <v>53.18</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>53.09</v>
+        <v>52.13</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>47.57</v>
+        <v>48.6</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>52.47</v>
+        <v>52.18</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>64.20999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>153.95</v>
+        <v>58.51</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>2.38</v>
+        <v>54.12</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>36.42</v>
+        <v>36.87</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>37.21</v>
+        <v>52.02</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>37.4</v>
+        <v>31.81</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>37.48</v>
+        <v>32.81</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>53.2</v>
+        <v>33.36</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>43.7</v>
+        <v>36.72</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>43.5</v>
+        <v>36.17</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>50.36</v>
+        <v>41.9</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>40.46</v>
+        <v>34.1</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>36.35</v>
+        <v>34.09</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>30.51</v>
+        <v>38.18</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>31.06</v>
+        <v>32.7</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>33.51</v>
+        <v>36.83</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>33.08</v>
+        <v>37.72</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>32.2</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="85">
@@ -7514,7 +7514,7 @@
         <v>0</v>
       </c>
       <c r="W85" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="X85" s="3" t="n">
         <v>0</v>
@@ -7547,67 +7547,67 @@
         <v>2.92</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.71</v>
+        <v>2.35</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.1</v>
+        <v>1.73</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="M86" s="3" t="n">
         <v>0.67</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.96</v>
+        <v>0.53</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.57</v>
+        <v>0.44</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-1.36</v>
+        <v>-3.35</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-3.2</v>
+        <v>-2.76</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.76</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.9</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.74</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="87">
@@ -7724,22 +7724,22 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O88" s="3" t="n">
         <v>0</v>
@@ -7799,67 +7799,67 @@
         <v>48.28</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>48.77</v>
+        <v>48.14</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>44</v>
+        <v>45.15</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>48.19</v>
+        <v>48.37</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>54</v>
+        <v>75.42</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>149.78</v>
+        <v>48.7</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>-0.24</v>
+        <v>40.04</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>33.83</v>
+        <v>34.39</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>34.61</v>
+        <v>49.69</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>35.08</v>
+        <v>29.51</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>35.02</v>
+        <v>30.35</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>41.84</v>
+        <v>31.33</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>41.2</v>
+        <v>34.62</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>41.35</v>
+        <v>34.41</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>49.54</v>
+        <v>43.59</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>42.63</v>
+        <v>35.92</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>38.22</v>
+        <v>35.82</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>31.87</v>
+        <v>40.04</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>32.09</v>
+        <v>32</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>31.91</v>
+        <v>34.87</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>30</v>
+        <v>31.63</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>29.2</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="90">
@@ -7892,28 +7892,28 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-5.37</v>
+        <v>-0.83</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0</v>
+        <v>-4.97</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0</v>
+        <v>-10.42</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0</v>
+        <v>-0.39</v>
       </c>
       <c r="M90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-8.01</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
         <v>0</v>
@@ -7934,16 +7934,16 @@
         <v>0</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="X90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-0.7</v>
+        <v>-3.24</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7967,67 +7967,67 @@
         <v>-1.98</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.64</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.31</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.35</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-2.14</v>
+        <v>-1.7</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.2</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.92</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.83</v>
+        <v>-1.36</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-1.94</v>
+        <v>-1.66</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.51</v>
       </c>
       <c r="O91" s="3" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="R91" s="3" t="n">
         <v>-1.72</v>
       </c>
-      <c r="P91" s="3" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>-2.15</v>
-      </c>
       <c r="S91" s="3" t="n">
-        <v>-2.18</v>
+        <v>-1.66</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.93</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.07</v>
+        <v>-1.04</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.04</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.77</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.05</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.12</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="92">
@@ -8144,22 +8144,22 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>26.38</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>104.45</v>
+        <v>0</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>-35.53</v>
+        <v>0</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M93" s="3" t="n">
-        <v>0</v>
+        <v>10.19</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-10T19:09:45</t>
+          <t>CreatedAt: 2026-10-11T01:12:20</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>48.96</v>
+        <v>33.12</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>48.7</v>
+        <v>32.93</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>48.65</v>
+        <v>33.78</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>48.33</v>
+        <v>40.3</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45.51</v>
+        <v>28.48</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>48.8</v>
+        <v>33.09</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>76.06</v>
+        <v>33.84</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>49.17</v>
+        <v>62.72</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>40.39</v>
+        <v>-0.19</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>34.62</v>
+        <v>33.49</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>41.46</v>
+        <v>33.88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>40.19</v>
+        <v>50.44</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>33.96</v>
+        <v>64.56</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>34.31</v>
+        <v>64.73</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>35.44</v>
+        <v>74.91</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>42.81</v>
+        <v>70.66</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>50</v>
+        <v>69.47</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>62.63</v>
+        <v>74</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>60.6</v>
+        <v>80.72</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>55.34</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>52.42</v>
+        <v>71.62</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>41.75</v>
+        <v>50.58</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>40.22</v>
+        <v>50.53</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>28.83</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="5">
@@ -752,31 +752,31 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-10.42</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-10.44</v>
+        <v>-3.82</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-4.48</v>
+        <v>-12.41</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-5.37</v>
+        <v>-12.26</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-10.78</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-1.91</v>
+        <v>-0.33</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.13</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-1.45</v>
+        <v>-0.33</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.41</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.43</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.51</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.74</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.58</v>
+        <v>-0.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.34</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.46</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.39</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-1.38</v>
+        <v>-3.46</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-1.39</v>
+        <v>-3.46</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-1.24</v>
+        <v>-3.38</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-1.33</v>
+        <v>-3.11</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.15</v>
+        <v>-2.71</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.37</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-1.21</v>
+        <v>-2.5</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-1.16</v>
+        <v>-2.73</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1</v>
+        <v>-2.72</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.04</v>
+        <v>-2.07</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.07</v>
+        <v>-2.02</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="7">
@@ -995,22 +995,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>48.73</v>
+        <v>32.48</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>48.46</v>
+        <v>33.07</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>48.56</v>
+        <v>33.98</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>48.05</v>
+        <v>39.94</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45.11</v>
+        <v>28.89</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>48.23</v>
+        <v>33.72</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>75.14</v>
+        <v>34.14</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>49.17</v>
+        <v>62.69</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>41.24</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>34.56</v>
+        <v>33.52</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>41.42</v>
+        <v>34.61</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>41.03</v>
+        <v>51.34</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>34.3</v>
+        <v>65.23</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>34.78</v>
+        <v>65.78</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>35.4</v>
+        <v>75.28</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>42.11</v>
+        <v>69.53</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>49.71</v>
+        <v>68.55</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>62.32</v>
+        <v>75.31</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>60.07</v>
+        <v>81.75</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>55.02</v>
+        <v>73.02</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>52.83</v>
+        <v>71.34</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>41.66</v>
+        <v>50.87</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>40.77</v>
+        <v>50.92</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>28.81</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="10">
@@ -1172,31 +1172,31 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-10.42</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-10.44</v>
+        <v>-3.82</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-4.48</v>
+        <v>-12.41</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-5.37</v>
+        <v>-12.26</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-10.78</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>0</v>
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.14</v>
+        <v>-0.97</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.7</v>
+        <v>0.03</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.5</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.98</v>
+        <v>-0.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.77</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.79</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.31</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.45</v>
+        <v>-0.73</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-1.08</v>
+        <v>-1.49</v>
       </c>
       <c r="O11" s="3" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="T11" s="3" t="n">
         <v>-1.05</v>
       </c>
-      <c r="P11" s="3" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-1.62</v>
-      </c>
       <c r="U11" s="3" t="n">
-        <v>-1.74</v>
+        <v>-1.47</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.53</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.58</v>
+        <v>-3</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.78</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.52</v>
+        <v>-1.63</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="12">
@@ -1415,22 +1415,22 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>37.88</v>
+        <v>32.48</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>37.88</v>
+        <v>33.07</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8.33</v>
+        <v>33.98</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>37.88</v>
+        <v>39.94</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>37.88</v>
+        <v>28.89</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>37.88</v>
+        <v>55.17</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>75.97</v>
+        <v>55.6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>54.14</v>
+        <v>62.69</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>51.66</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>34.94</v>
+        <v>33.52</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>41.42</v>
+        <v>34.61</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>38.62</v>
+        <v>55.16</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>38.62</v>
+        <v>77.64</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>38.62</v>
+        <v>78.11</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>35.4</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>42.11</v>
+        <v>55.1</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>49.71</v>
+        <v>68.55</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>62.32</v>
+        <v>188.03</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>60.07</v>
+        <v>190.89</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>55.02</v>
+        <v>186.46</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>86.31</v>
+        <v>71.34</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>41.66</v>
+        <v>50.87</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>51.55</v>
+        <v>50.92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>28.81</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="15">
@@ -1574,25 +1574,25 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>-10.85</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-10.58</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-40.23</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>-10.17</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>-7.23</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-10.35</v>
+        <v>21.45</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>21.46</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1607,34 +1607,34 @@
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-12.85</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-1.57</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>-14.42</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>112.72</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>109.14</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>113.44</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>33.48</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.14</v>
+        <v>-0.97</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-1.7</v>
+        <v>0.03</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.5</v>
+        <v>0.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.98</v>
+        <v>-0.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.77</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.79</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.31</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.45</v>
+        <v>-0.73</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-1.08</v>
+        <v>-1.49</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="T16" s="3" t="n">
         <v>-1.05</v>
       </c>
-      <c r="P16" s="3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>-1.62</v>
-      </c>
       <c r="U16" s="3" t="n">
-        <v>-1.74</v>
+        <v>-1.47</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.53</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.58</v>
+        <v>-3</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.78</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.52</v>
+        <v>-1.63</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.89</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1835,22 +1835,22 @@
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>48.73</v>
+        <v>33.03</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>48.51</v>
+        <v>32.9</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>48.51</v>
+        <v>33.71</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>48.24</v>
+        <v>40.26</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45.37</v>
+        <v>28.53</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>48.61</v>
+        <v>33.16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>74.89</v>
+        <v>33.84</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>43.8</v>
+        <v>62.69</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>29.31</v>
+        <v>-0.26</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>34.12</v>
+        <v>33.36</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>41.42</v>
+        <v>33.75</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>29.14</v>
+        <v>46.12</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>29.14</v>
+        <v>50.97</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>28.56</v>
+        <v>51.29</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>35.33</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>42.52</v>
+        <v>70.06</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>49.8</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>62.57</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>60.36</v>
+        <v>80.72</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>55.13</v>
+        <v>71.61</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>52.16</v>
+        <v>71.41</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>41.54</v>
+        <v>50.44</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>28.81</v>
+        <v>50.34</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>28.81</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="20">
@@ -2012,31 +2012,31 @@
         <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-1.71</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-10.18</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-21.35</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-21.39</v>
+        <v>-7.83</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-9.19</v>
+        <v>-25.42</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-11.01</v>
+        <v>-25.11</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0</v>
+        <v>-4.08</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-22.08</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>0</v>
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-2.14</v>
+        <v>-0.43</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-1.79</v>
+        <v>-0.16</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-1.75</v>
+        <v>-0.24</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-1.54</v>
+        <v>-0.36</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.36</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.36</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-1.36</v>
+        <v>-0.51</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1.89</v>
+        <v>-0.77</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.05</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.47</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.59</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-2.02</v>
+        <v>-2.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-1.49</v>
+        <v>-4.05</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-1.5</v>
+        <v>-4.05</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-1.34</v>
+        <v>-3.97</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-1.62</v>
+        <v>-3.71</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-1.34</v>
+        <v>-3.17</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.3</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-1.45</v>
+        <v>-2.5</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.94</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.25</v>
+        <v>-2.93</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.25</v>
+        <v>-2.22</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.17</v>
+        <v>-2.21</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="22">
@@ -2255,22 +2255,22 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>48.73</v>
+        <v>33.03</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>48.51</v>
+        <v>32.9</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>48.51</v>
+        <v>33.71</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>48.24</v>
+        <v>40.26</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45.37</v>
+        <v>28.53</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>48.61</v>
+        <v>33.16</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>33.84</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>49.02</v>
+        <v>62.69</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>40.24</v>
+        <v>-0.26</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>34.52</v>
+        <v>33.36</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>41.42</v>
+        <v>33.75</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>40.09</v>
+        <v>50.13</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>33.85</v>
+        <v>63.98</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>34.2</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>35.33</v>
+        <v>74.33</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>42.52</v>
+        <v>70.06</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>49.8</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>62.57</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>60.36</v>
+        <v>80.72</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>55.13</v>
+        <v>71.61</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>52.16</v>
+        <v>71.41</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>41.54</v>
+        <v>50.44</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>40.12</v>
+        <v>50.34</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>28.81</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="25">
@@ -2432,31 +2432,31 @@
         <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-10.42</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-10.44</v>
+        <v>-3.82</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-4.48</v>
+        <v>-12.41</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-5.37</v>
+        <v>-12.26</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-10.78</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-2.14</v>
+        <v>-0.43</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-1.79</v>
+        <v>-0.16</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-1.75</v>
+        <v>-0.24</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-1.54</v>
+        <v>-0.36</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.36</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.36</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-1.36</v>
+        <v>-0.51</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-1.89</v>
+        <v>-0.77</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.72</v>
+        <v>-1.05</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.47</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.59</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-2.02</v>
+        <v>-2.7</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-1.49</v>
+        <v>-4.05</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-1.5</v>
+        <v>-4.05</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-1.34</v>
+        <v>-3.97</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-1.62</v>
+        <v>-3.71</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-1.34</v>
+        <v>-3.17</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.3</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-1.45</v>
+        <v>-2.5</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.94</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.25</v>
+        <v>-2.93</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.25</v>
+        <v>-2.22</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.17</v>
+        <v>-2.21</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="27">
@@ -2675,22 +2675,22 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>48.36</v>
+        <v>32.86</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>48.28</v>
+        <v>32.84</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>48.28</v>
+        <v>33.55</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>48.14</v>
+        <v>40.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45.2</v>
+        <v>28.53</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>48.37</v>
+        <v>33.16</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>74.55</v>
+        <v>33.81</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>43.49</v>
+        <v>62.59</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>29.11</v>
+        <v>-0.41</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>33.98</v>
+        <v>33.17</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>41.34</v>
+        <v>33.52</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>28.9</v>
+        <v>45.51</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>28.96</v>
+        <v>50.04</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>28.41</v>
+        <v>50.36</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>35.2</v>
+        <v>71.31</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>42.19</v>
+        <v>69.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>49.56</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>62.51</v>
+        <v>74.14</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>60.07</v>
+        <v>80.72</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>54.81</v>
+        <v>71.27</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>51.76</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>41.34</v>
+        <v>50.29</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>28.67</v>
+        <v>50</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>28.81</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="30">
@@ -2852,31 +2852,31 @@
         <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-1.71</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-10.18</v>
+        <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-21.35</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-0.79</v>
+        <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-21.39</v>
+        <v>-7.83</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-9.19</v>
+        <v>-25.42</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-11.01</v>
+        <v>-25.11</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0</v>
+        <v>-4.08</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-22.08</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>0</v>
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-2.51</v>
+        <v>-0.59</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-2.03</v>
+        <v>-0.23</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-1.98</v>
+        <v>-0.4</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.64</v>
+        <v>-0.43</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-1.27</v>
+        <v>-0.36</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-1.35</v>
+        <v>-0.36</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.7</v>
+        <v>-0.54</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-2.2</v>
+        <v>-0.87</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1.92</v>
+        <v>-1.21</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.66</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.81</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-2.26</v>
+        <v>-3.31</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-1.68</v>
+        <v>-4.98</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-1.66</v>
+        <v>-4.98</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-1.48</v>
+        <v>-4.9</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-1.94</v>
+        <v>-4.57</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-1.59</v>
+        <v>-3.89</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.44</v>
+        <v>-2.22</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.5</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-1.7</v>
+        <v>-3.28</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.66</v>
+        <v>-3.27</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.45</v>
+        <v>-2.36</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.55</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="32">
@@ -3095,22 +3095,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>39.82</v>
+        <v>32.48</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>39.7</v>
+        <v>33.33</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>13.16</v>
+        <v>34.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>39.41</v>
+        <v>40.04</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>39.22</v>
+        <v>29.19</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>39.7</v>
+        <v>55.72</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>75.78</v>
+        <v>55.98</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>54.89</v>
+        <v>62.92</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>52.44</v>
+        <v>0.46</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>35.38</v>
+        <v>33.98</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>42.09</v>
+        <v>35.48</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>40.84</v>
+        <v>56.54</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>39.21</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>39.52</v>
+        <v>79.97</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>35.9</v>
+        <v>78.95</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>42.3</v>
+        <v>57.27</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>50.57</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>213.09</v>
+        <v>189.31</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>105.4</v>
+        <v>192.03</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>55.56</v>
+        <v>187.7</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>87.16</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>41.95</v>
+        <v>51.78</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>52.33</v>
+        <v>52.24</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>29.09</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="35">
@@ -3254,25 +3254,25 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-9.76</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-9.52</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-36.2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-9.15</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>-6.51</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-9.31</v>
+        <v>21.45</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>21.46</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -3287,34 +3287,34 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-11.56</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>-12.98</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>112.72</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>0</v>
+        <v>109.14</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>113.44</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>33.48</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-1.29</v>
+        <v>-0.97</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-1.08</v>
+        <v>0.27</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.89</v>
+        <v>0.45</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-1.21</v>
+        <v>-0.59</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-0.91</v>
+        <v>0.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-1.02</v>
+        <v>0.75</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-2.17</v>
+        <v>0.17</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.54</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.34</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.85</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
       <c r="N36" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="Y36" s="3" t="n">
         <v>-0.31</v>
       </c>
-      <c r="O36" s="3" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>0.26</v>
-      </c>
       <c r="Z36" s="3" t="n">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3434,49 +3434,49 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>150.64</v>
+        <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>44.86</v>
+        <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>0</v>
@@ -3515,22 +3515,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>48.96</v>
+        <v>33.12</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>48.7</v>
+        <v>32.93</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>48.65</v>
+        <v>33.78</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>48.33</v>
+        <v>40.3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45.51</v>
+        <v>28.48</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>48.8</v>
+        <v>33.09</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>76.06</v>
+        <v>33.84</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>49.17</v>
+        <v>62.72</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>40.39</v>
+        <v>-0.19</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>34.62</v>
+        <v>33.49</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>41.46</v>
+        <v>33.88</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>40.19</v>
+        <v>50.44</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>33.96</v>
+        <v>64.56</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>34.31</v>
+        <v>64.73</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>35.44</v>
+        <v>74.91</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>42.81</v>
+        <v>70.66</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>50</v>
+        <v>69.47</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>62.63</v>
+        <v>74</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>60.6</v>
+        <v>80.72</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>55.34</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>52.42</v>
+        <v>71.62</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>41.75</v>
+        <v>50.58</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>40.22</v>
+        <v>50.53</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>28.83</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="40">
@@ -3692,31 +3692,31 @@
         <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-10.42</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-10.44</v>
+        <v>-3.82</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-4.48</v>
+        <v>-12.41</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-5.37</v>
+        <v>-12.26</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-10.78</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>0</v>
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-1.91</v>
+        <v>-0.33</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.13</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.17</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-1.45</v>
+        <v>-0.33</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.41</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.43</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.51</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.74</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.58</v>
+        <v>-0.99</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.34</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.46</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.39</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-1.38</v>
+        <v>-3.46</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-1.39</v>
+        <v>-3.46</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-1.24</v>
+        <v>-3.38</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-1.33</v>
+        <v>-3.11</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.15</v>
+        <v>-2.71</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.37</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-1.21</v>
+        <v>-2.5</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-1.16</v>
+        <v>-2.73</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1</v>
+        <v>-2.72</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.04</v>
+        <v>-2.07</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.07</v>
+        <v>-2.02</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="42">
@@ -3935,22 +3935,22 @@
         <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>50.57</v>
+        <v>33.52</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>50.1</v>
+        <v>33.23</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>50.11</v>
+        <v>34.02</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>49.73</v>
+        <v>40.7</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>46.56</v>
+        <v>28.8</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>49.92</v>
+        <v>33.52</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>78.20999999999999</v>
+        <v>34.38</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>55.88</v>
+        <v>63.32</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>52.23</v>
+        <v>0.39</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>35.92</v>
+        <v>34.24</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>42.49</v>
+        <v>34.71</v>
       </c>
       <c r="N44" s="3" t="n">
+        <v>55.76</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>79.09</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>79.03</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>79.42</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>82.64</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>73.95999999999999</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="X44" s="3" t="n">
         <v>52.03</v>
       </c>
-      <c r="O44" s="3" t="n">
-        <v>39.47</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>36.35</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>43.91</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>64.39</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>62.25</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>57.02</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>53.79</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>42.92</v>
-      </c>
       <c r="Y44" s="3" t="n">
-        <v>52.07</v>
+        <v>51.98</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>29.61</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="Z46" s="3" t="n">
         <v>-0.3</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>-0.37</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>-0.09</v>
       </c>
     </row>
     <row r="47">
@@ -4355,22 +4355,22 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>51.91</v>
+        <v>34.1</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>51.28</v>
+        <v>33.74</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>51.44</v>
+        <v>34.4</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>51.06</v>
+        <v>41.17</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>47.75</v>
+        <v>29.38</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>51.32</v>
+        <v>34.24</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>79.17</v>
+        <v>34.87</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>57.43</v>
+        <v>63.95</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>53.89</v>
+        <v>1.27</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>37.06</v>
+        <v>35.25</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>44.56</v>
+        <v>36.13</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>54.4</v>
+        <v>58.65</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>41.14</v>
+        <v>83.7</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>42.43</v>
+        <v>83.11</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>37.81</v>
+        <v>83.03</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>45.83</v>
+        <v>76.68000000000001</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>53.5</v>
+        <v>71.75</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>62.81</v>
+        <v>78.73</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>63.92</v>
+        <v>85.53</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>58.37</v>
+        <v>76.62</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>55.52</v>
+        <v>76.95</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>44.11</v>
+        <v>54.06</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>53.35</v>
+        <v>53.68</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>30.37</v>
+        <v>44.76</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1.04</v>
+        <v>0.65</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.18</v>
+        <v>0.45</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.28</v>
+        <v>0.54</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.29</v>
+        <v>0.49</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.59</v>
+        <v>0.72</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1.21</v>
+        <v>0.52</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1.55</v>
+        <v>0.49</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>1.51</v>
+        <v>0.48</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.69</v>
+        <v>0.79</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>1.32</v>
+        <v>3.26</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.36</v>
+        <v>2.66</v>
       </c>
       <c r="Q51" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Y51" s="3" t="n">
         <v>1.13</v>
       </c>
-      <c r="R51" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S51" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T51" s="3" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="U51" s="3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="V51" s="3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W51" s="3" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="X51" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Y51" s="3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="Z51" s="3" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="52">
@@ -4775,22 +4775,22 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>53.49</v>
+        <v>34.96</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>52.89</v>
+        <v>34.48</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>52.96</v>
+        <v>35.47</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>52.24</v>
+        <v>42.13</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>48.65</v>
+        <v>30.31</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>52.12</v>
+        <v>35.1</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>80.38</v>
+        <v>36.08</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>58.63</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>54.68</v>
+        <v>2.54</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>37.52</v>
+        <v>36.7</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>44.47</v>
+        <v>37.19</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>54.51</v>
+        <v>58.05</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>41.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>42.34</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>37.46</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>44.13</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>48.12</v>
+        <v>69.95</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>59.59</v>
+        <v>71.5</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>57.71</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>52.76</v>
+        <v>71.75</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>53.09</v>
+        <v>73.02</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>44.02</v>
+        <v>54.06</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>54.58</v>
+        <v>55.09</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>31</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="55">
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>2.59</v>
+        <v>1.41</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2.7</v>
+        <v>1.53</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2.46</v>
+        <v>1.5</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.19</v>
+        <v>1.42</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>2.43</v>
+        <v>1.73</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>2.76</v>
+        <v>1.69</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="L56" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N56" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="M56" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N56" s="3" t="n">
-        <v>1.96</v>
-      </c>
       <c r="O56" s="3" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.79</v>
+        <v>1.47</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-3.03</v>
+        <v>-2.24</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-4.35</v>
+        <v>-4.86</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-4.1</v>
+        <v>-5.15</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-3.75</v>
+        <v>-2.8</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.32</v>
+        <v>-1.31</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.3</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="57">
@@ -5195,22 +5195,22 @@
         <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>52.45</v>
+        <v>34.63</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>51.91</v>
+        <v>34.3</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>51.86</v>
+        <v>35.07</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>51.43</v>
+        <v>41.77</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>48.1</v>
+        <v>29.76</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>51.53</v>
+        <v>34.63</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>79.94</v>
+        <v>35.52</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>57.9</v>
+        <v>64.52</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>54.17</v>
+        <v>1.59</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>37.33</v>
+        <v>35.54</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>44.2</v>
+        <v>36.02</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>54.17</v>
+        <v>57.87</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>41.1</v>
+        <v>82.16</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>42.34</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>37.81</v>
+        <v>82.27</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>45.64</v>
+        <v>75.66</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>53.23</v>
+        <v>74.34</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>66.75</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>64.39</v>
+        <v>85.36</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>58.98</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>55.64</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>44.43</v>
+        <v>53.89</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>53.9</v>
+        <v>53.85</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>30.71</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.61</v>
+        <v>1.23</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.65</v>
+        <v>1.14</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.64</v>
+        <v>0.87</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="I61" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W61" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="J61" s="3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>2.23</v>
-      </c>
       <c r="X61" s="3" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="62">
@@ -5615,22 +5615,22 @@
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>53.16</v>
+        <v>35.07</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>52.62</v>
+        <v>34.73</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>52.57</v>
+        <v>35.51</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>52.13</v>
+        <v>42.21</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>48.7</v>
+        <v>30.14</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>52.23</v>
+        <v>35.14</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>80.67</v>
+        <v>36.04</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>58.76</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>54.91</v>
+        <v>2.09</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>37.87</v>
+        <v>36.09</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>44.89</v>
+        <v>36.62</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>55.02</v>
+        <v>58.89</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>41.7</v>
+        <v>83.52</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>43.01</v>
+        <v>83.63</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>38.41</v>
+        <v>83.64</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>46.41</v>
+        <v>77.08</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>54.13</v>
+        <v>75.67</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>67.81</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>65.41</v>
+        <v>86.78</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>59.92</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>56.52</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>45.14</v>
+        <v>54.68</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>54.69</v>
+        <v>54.63</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>30.97</v>
+        <v>45.74</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.35</v>
+        <v>1.58</v>
       </c>
       <c r="G66" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N66" s="3" t="n">
         <v>2.24</v>
       </c>
-      <c r="H66" s="3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="M66" s="3" t="n">
+      <c r="O66" s="3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="X66" s="3" t="n">
         <v>2.02</v>
       </c>
-      <c r="N66" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O66" s="3" t="n">
+      <c r="Y66" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z66" s="3" t="n">
         <v>1.88</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q66" s="3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R66" s="3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S66" s="3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="X66" s="3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y66" s="3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z66" s="3" t="n">
-        <v>1.27</v>
       </c>
     </row>
     <row r="67">
@@ -6035,22 +6035,22 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>53.95</v>
+        <v>35.59</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>53.4</v>
+        <v>35.25</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>53.35</v>
+        <v>36.04</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>52.9</v>
+        <v>42.73</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>49.43</v>
+        <v>30.54</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>53.01</v>
+        <v>35.59</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>81.42</v>
+        <v>36.5</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>59.57</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>55.73</v>
+        <v>2.43</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>38.44</v>
+        <v>36.43</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>45.51</v>
+        <v>36.84</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>55.78</v>
+        <v>59.2</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>42.32</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>43.6</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>38.94</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>47</v>
+        <v>77.41</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>54.76</v>
+        <v>75.98</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>68.61</v>
+        <v>80.05</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>66.18000000000001</v>
+        <v>87.14</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>60.63</v>
+        <v>78.23</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>57.25</v>
+        <v>78.09</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>45.71</v>
+        <v>55.08</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>55.39</v>
+        <v>55.2</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>31.53</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3.08</v>
+        <v>2.14</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>3.09</v>
+        <v>2.09</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.97</v>
+        <v>1.65</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>3.29</v>
+        <v>2.06</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>3.47</v>
+        <v>2.15</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>3.69</v>
+        <v>2.03</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>3.34</v>
+        <v>1.63</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>3.24</v>
+        <v>2.55</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>2.5</v>
+        <v>3.61</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.53</v>
+        <v>3.61</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.26</v>
+        <v>3.78</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>2.87</v>
+        <v>3.64</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3.61</v>
+        <v>3.8</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>4.67</v>
+        <v>3.68</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>4.37</v>
+        <v>3.92</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>4.12</v>
+        <v>3.68</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.93</v>
+        <v>2.42</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>3.32</v>
+        <v>2.65</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="72">
@@ -6455,22 +6455,22 @@
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>52.61</v>
+        <v>34.63</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>52.02</v>
+        <v>34.3</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>51.97</v>
+        <v>35.07</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>51.53</v>
+        <v>41.77</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>48.15</v>
+        <v>29.79</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>51.64</v>
+        <v>34.67</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>80.05</v>
+        <v>35.59</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>57.96</v>
+        <v>64.56</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>54.28</v>
+        <v>1.63</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>37.52</v>
+        <v>35.65</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>44.43</v>
+        <v>36.24</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>54.45</v>
+        <v>58.23</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>41.27</v>
+        <v>82.75</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>42.56</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>37.89</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>45.78</v>
+        <v>76.05</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>53.5</v>
+        <v>74.73</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>66.89</v>
+        <v>78.81</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>64.59</v>
+        <v>85.88</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>59.23</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>55.87</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>44.62</v>
+        <v>54.17</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>54.07</v>
+        <v>54.12</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>30.78</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1.74</v>
+        <v>1.18</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.72</v>
+        <v>1.23</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.69</v>
+        <v>0.9</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.91</v>
+        <v>1.14</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.09</v>
+        <v>1.25</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.09</v>
+        <v>1.1</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.9</v>
+        <v>0.83</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.39</v>
+        <v>0.82</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>1.55</v>
+        <v>0.91</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1.44</v>
+        <v>2.32</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>1.21</v>
+        <v>2.31</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.94</v>
+        <v>2.44</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>2.46</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="77">
@@ -6875,22 +6875,22 @@
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>50.87</v>
+        <v>33.46</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>50.3</v>
+        <v>33.07</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>50.26</v>
+        <v>33.95</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>49.78</v>
+        <v>40.63</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>46.46</v>
+        <v>28.89</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>49.73</v>
+        <v>33.52</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>77.95</v>
+        <v>34.35</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>55.88</v>
+        <v>63.46</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>52.38</v>
+        <v>0.79</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>36.13</v>
+        <v>34.83</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>42.87</v>
+        <v>35.33</v>
       </c>
       <c r="N79" s="3" t="n">
+        <v>56.65</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>80.29000000000001</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>73.77</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>83.22</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>52.66</v>
+      </c>
+      <c r="Y79" s="3" t="n">
         <v>52.55</v>
       </c>
-      <c r="O79" s="3" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="P79" s="3" t="n">
-        <v>41.07</v>
-      </c>
-      <c r="Q79" s="3" t="n">
-        <v>36.68</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="T79" s="3" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>61.81</v>
-      </c>
-      <c r="V79" s="3" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="W79" s="3" t="n">
-        <v>53.41</v>
-      </c>
-      <c r="X79" s="3" t="n">
-        <v>42.79</v>
-      </c>
-      <c r="Y79" s="3" t="n">
-        <v>52.07</v>
-      </c>
       <c r="Z79" s="3" t="n">
-        <v>29.7</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="80">
@@ -7295,22 +7295,22 @@
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>53.27</v>
+        <v>34.81</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>52.84</v>
+        <v>34.27</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>53.18</v>
+        <v>35.47</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>52.13</v>
+        <v>42.1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>48.6</v>
+        <v>30.47</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>52.18</v>
+        <v>35.21</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>80.27</v>
+        <v>36.23</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>58.51</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>54.12</v>
+        <v>2.39</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>36.87</v>
+        <v>36.54</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>43.79</v>
+        <v>37</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>53.62</v>
+        <v>58.23</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>40.6</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>41.83</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>36.97</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>44</v>
+        <v>74.36</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>47.4</v>
+        <v>71.12</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>59.15</v>
+        <v>71.17</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>57.23</v>
+        <v>77.92</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>52.47</v>
+        <v>73.67</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>51.91</v>
+        <v>74.56</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>44.16</v>
+        <v>54.45</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>54.63</v>
+        <v>55.44</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>30.87</v>
+        <v>45.84</v>
       </c>
     </row>
     <row r="85">
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.54</v>
+        <v>1.2</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.35</v>
+        <v>1.47</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.14</v>
+        <v>1.58</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>2.63</v>
+        <v>1.69</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.74</v>
+        <v>1.72</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.92</v>
+        <v>1.66</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.77</v>
+        <v>1.39</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.75</v>
+        <v>1.47</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.3</v>
+        <v>1.06</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.13</v>
+        <v>0.59</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-3.74</v>
+        <v>-1.07</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-4.79</v>
+        <v>-5.2</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-4.58</v>
+        <v>-5.3</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-4.04</v>
+        <v>-0.88</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.51</v>
+        <v>0.22</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.17</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="87">
@@ -7715,22 +7715,22 @@
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>48.36</v>
+        <v>32.86</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>48.28</v>
+        <v>32.84</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>48.28</v>
+        <v>33.55</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>48.14</v>
+        <v>40.2</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>45.15</v>
+        <v>28.53</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>48.37</v>
+        <v>33.16</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>75.42</v>
+        <v>33.81</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>48.7</v>
+        <v>62.59</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>40.04</v>
+        <v>-0.41</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>34.39</v>
+        <v>33.17</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>41.34</v>
+        <v>33.52</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>39.8</v>
+        <v>49.52</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>33.66</v>
+        <v>63.05</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>34.05</v>
+        <v>63.21</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>35.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>42.19</v>
+        <v>69.2</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>49.56</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>62.51</v>
+        <v>74.14</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>60.07</v>
+        <v>80.72</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>54.81</v>
+        <v>71.27</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>51.76</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>41.34</v>
+        <v>50.29</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>39.97</v>
+        <v>50</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>28.81</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="90">
@@ -7892,31 +7892,31 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.83</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>-4.97</v>
+        <v>0</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-10.42</v>
+        <v>0</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-10.44</v>
+        <v>-3.82</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-4.48</v>
+        <v>-12.41</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-5.37</v>
+        <v>-12.26</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0</v>
+        <v>-1.99</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0</v>
@@ -7940,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-10.78</v>
+        <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
         <v>0</v>
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-2.51</v>
+        <v>-0.59</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-2.03</v>
+        <v>-0.23</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-1.98</v>
+        <v>-0.4</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-1.64</v>
+        <v>-0.43</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-1.31</v>
+        <v>-0.36</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-1.35</v>
+        <v>-0.36</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-1.7</v>
+        <v>-0.54</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-2.2</v>
+        <v>-0.87</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1.92</v>
+        <v>-1.21</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.66</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.81</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-2.31</v>
+        <v>-3.31</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-1.68</v>
+        <v>-4.98</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-1.66</v>
+        <v>-4.98</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-1.48</v>
+        <v>-4.9</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-1.94</v>
+        <v>-4.57</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-1.59</v>
+        <v>-3.89</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.44</v>
+        <v>-2.22</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.5</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-1.7</v>
+        <v>-3.28</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.66</v>
+        <v>-3.27</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-1.45</v>
+        <v>-2.36</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.55</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="92">
@@ -8135,22 +8135,22 @@
         <v>0</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0</v>
+        <v>29.21</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0</v>
+        <v>-33.06</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-11T01:12:20</t>
+          <t>CreatedAt: 2026-10-11T08:10:07</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -659,67 +659,67 @@
         <v>33.78</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>40.3</v>
+        <v>33.35</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>28.48</v>
+        <v>34.08</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>33.09</v>
+        <v>39.83</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>33.84</v>
+        <v>58.78</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>62.72</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>-0.19</v>
+        <v>45.64</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>33.49</v>
+        <v>45.81</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>33.88</v>
+        <v>57.37</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>50.44</v>
+        <v>57.38</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>64.56</v>
+        <v>63.65</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>64.73</v>
+        <v>62.48</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>74.91</v>
+        <v>64.5</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>70.66</v>
+        <v>59.11</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>69.47</v>
+        <v>57.96</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>74</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>80.72</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>71.81999999999999</v>
+        <v>58.74</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>71.62</v>
+        <v>50.85</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>50.58</v>
+        <v>50.06</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>50.53</v>
+        <v>50.71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>42.38</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="5">
@@ -764,19 +764,19 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0</v>
+        <v>-21.83</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-3.82</v>
+        <v>-13.47</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-12.41</v>
+        <v>-12.11</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-12.26</v>
+        <v>-10.55</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-1.99</v>
+        <v>-8.74</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
@@ -827,67 +827,67 @@
         <v>-0.17</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.27</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.28</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.37</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.79</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-1.46</v>
+        <v>-3.41</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-2.39</v>
+        <v>-3.05</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.33</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.21</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-3.38</v>
+        <v>-3.15</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-3.11</v>
+        <v>-2.48</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-2.71</v>
+        <v>-2.09</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.31</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.49</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.73</v>
+        <v>-2.06</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.72</v>
+        <v>-1.88</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.02</v>
+        <v>-2.08</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="7">
@@ -995,22 +995,22 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1079,67 +1079,67 @@
         <v>33.98</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>39.94</v>
+        <v>33.25</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>28.89</v>
+        <v>34.32</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>33.72</v>
+        <v>39.75</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>34.14</v>
+        <v>57.73</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>62.69</v>
+        <v>66.88</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>45.82</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>33.52</v>
+        <v>45.98</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>34.61</v>
+        <v>58.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>51.34</v>
+        <v>59.05</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>65.23</v>
+        <v>64.98</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>65.78</v>
+        <v>64.2</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>75.28</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>69.53</v>
+        <v>58.71</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>68.55</v>
+        <v>57.85</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>75.31</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>81.75</v>
+        <v>90.48</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>73.02</v>
+        <v>60.14</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>71.34</v>
+        <v>50.94</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>50.87</v>
+        <v>50.45</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>50.92</v>
+        <v>51.25</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>42.96</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="10">
@@ -1184,19 +1184,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>-21.83</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-3.82</v>
+        <v>-13.47</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-12.41</v>
+        <v>-12.11</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-12.26</v>
+        <v>-10.55</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-1.99</v>
+        <v>-8.74</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1247,67 +1247,67 @@
         <v>0.03</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.33</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.2</v>
+        <v>-0.36</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.62</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.79</v>
+        <v>-1.19</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.61</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.73</v>
+        <v>-2.17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.38</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.42</v>
+        <v>-1.5</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.01</v>
+        <v>-2.23</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-4.24</v>
+        <v>-2.88</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-3.63</v>
+        <v>-2.2</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.47</v>
+        <v>-1</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.53</v>
+        <v>-0.66</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-3</v>
+        <v>-1.78</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1415,22 +1415,22 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1499,67 +1499,67 @@
         <v>33.98</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>39.94</v>
+        <v>33.25</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>28.89</v>
+        <v>34.32</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>55.17</v>
+        <v>39.75</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>55.6</v>
+        <v>47.68</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>62.69</v>
+        <v>38.62</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0</v>
+        <v>38.62</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>33.52</v>
+        <v>38.62</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>34.61</v>
+        <v>38.62</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>55.16</v>
+        <v>72.52</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>77.64</v>
+        <v>77.08</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>78.11</v>
+        <v>74.75</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>77.34999999999999</v>
+        <v>74.17</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>55.1</v>
+        <v>52.74</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>68.55</v>
+        <v>53.19</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>188.03</v>
+        <v>196.83</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>190.89</v>
+        <v>196.13</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>186.46</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>71.34</v>
+        <v>50.94</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>50.87</v>
+        <v>50.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>50.92</v>
+        <v>51.25</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>42.96</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="15">
@@ -1589,22 +1589,22 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>21.45</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>21.46</v>
+        <v>-10.05</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>-28.25</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>-7.2</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>-7.36</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0</v>
+        <v>-41.81</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0</v>
@@ -1619,19 +1619,19 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-14.42</v>
+        <v>-5.98</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0</v>
+        <v>-4.66</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>112.72</v>
+        <v>109.09</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>109.14</v>
+        <v>105.64</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>113.44</v>
+        <v>126.32</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1667,67 +1667,67 @@
         <v>0.03</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.33</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.2</v>
+        <v>-0.36</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.2</v>
+        <v>-1.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.62</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.79</v>
+        <v>-1.19</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.61</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-0.73</v>
+        <v>-2.17</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.38</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.34</v>
+        <v>-1.5</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.23</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-4.24</v>
+        <v>-2.88</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-3.63</v>
+        <v>-2.2</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.05</v>
+        <v>0</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.47</v>
+        <v>-1</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.53</v>
+        <v>-0.66</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-3</v>
+        <v>-1.78</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.78</v>
+        <v>-1.57</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-1.63</v>
+        <v>-1.54</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="17">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>0</v>
@@ -1835,22 +1835,22 @@
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1919,67 +1919,67 @@
         <v>33.71</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>40.26</v>
+        <v>33.35</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>28.53</v>
+        <v>34.12</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>33.16</v>
+        <v>46.16</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>33.84</v>
+        <v>58.74</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>62.69</v>
+        <v>66.83</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>-0.26</v>
+        <v>45.51</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>33.36</v>
+        <v>45.59</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>33.75</v>
+        <v>34.17</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.12</v>
+        <v>42.85</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>50.97</v>
+        <v>50.45</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>51.29</v>
+        <v>50.93</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>72.23999999999999</v>
+        <v>54.77</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>70.06</v>
+        <v>58.66</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>57.63</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>74.06999999999999</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>80.72</v>
+        <v>89.16</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>71.61</v>
+        <v>58.69</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>71.41</v>
+        <v>50.7</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>50.44</v>
+        <v>49.96</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>50.34</v>
+        <v>50.52</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>42.34</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="20">
@@ -2024,19 +2024,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0</v>
+        <v>-44.72</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-7.83</v>
+        <v>-27.59</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-25.42</v>
+        <v>-24.8</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-25.11</v>
+        <v>-21.62</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-4.08</v>
+        <v>-17.91</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0</v>
@@ -2087,67 +2087,67 @@
         <v>-0.24</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.61</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.66</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.5</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-1.47</v>
+        <v>-2.01</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-1.59</v>
+        <v>-3.71</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-2.7</v>
+        <v>-3.45</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-4.05</v>
+        <v>-3.84</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-4.05</v>
+        <v>-3.7</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-3.97</v>
+        <v>-3.71</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-3.71</v>
+        <v>-2.93</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-3.17</v>
+        <v>-2.42</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.06</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.32</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.11</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.93</v>
+        <v>-2.03</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.22</v>
+        <v>-2.1</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.27</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="22">
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -2255,22 +2255,22 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2339,67 +2339,67 @@
         <v>33.71</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>40.26</v>
+        <v>33.35</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>28.53</v>
+        <v>34.12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>33.16</v>
+        <v>39.87</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>33.84</v>
+        <v>58.74</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>62.69</v>
+        <v>66.83</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>-0.26</v>
+        <v>45.51</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>33.36</v>
+        <v>45.59</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>33.75</v>
+        <v>57.07</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>50.13</v>
+        <v>56.98</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>63.98</v>
+        <v>63.14</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>64.15000000000001</v>
+        <v>62</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>74.33</v>
+        <v>63.94</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>70.06</v>
+        <v>58.66</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>57.63</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>74.06999999999999</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>80.72</v>
+        <v>89.16</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>71.61</v>
+        <v>58.69</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>71.41</v>
+        <v>50.7</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>50.44</v>
+        <v>49.96</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>50.34</v>
+        <v>50.52</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>42.34</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="25">
@@ -2444,19 +2444,19 @@
         <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>0</v>
+        <v>-21.83</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-3.82</v>
+        <v>-13.47</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-12.41</v>
+        <v>-12.11</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-12.26</v>
+        <v>-10.55</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-1.99</v>
+        <v>-8.74</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2507,67 +2507,67 @@
         <v>-0.24</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.24</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.61</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.66</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-1.47</v>
+        <v>-2.01</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-1.59</v>
+        <v>-3.71</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-2.7</v>
+        <v>-3.45</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-4.05</v>
+        <v>-3.84</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-4.05</v>
+        <v>-3.7</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-3.97</v>
+        <v>-3.71</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-3.71</v>
+        <v>-2.93</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-3.17</v>
+        <v>-2.42</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.3</v>
+        <v>-2.06</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.32</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.11</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.93</v>
+        <v>-2.03</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.22</v>
+        <v>-2.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.21</v>
+        <v>-2.27</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="27">
@@ -2675,22 +2675,22 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>33.55</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>40.2</v>
+        <v>33.32</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>28.53</v>
+        <v>34.05</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>33.16</v>
+        <v>46.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>33.81</v>
+        <v>58.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>62.59</v>
+        <v>66.83</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.41</v>
+        <v>45.25</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>33.17</v>
+        <v>45.28</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>33.52</v>
+        <v>33.65</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>45.51</v>
+        <v>42.19</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>50.04</v>
+        <v>49.53</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50.36</v>
+        <v>50.11</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>71.31</v>
+        <v>53.89</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>69.2</v>
+        <v>58</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>57.19</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>74.14</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>80.72</v>
+        <v>89.25</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>71.27</v>
+        <v>58.46</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>71.06999999999999</v>
+        <v>50.46</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>50.29</v>
+        <v>49.82</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>50</v>
+        <v>50.18</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>42.26</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="30">
@@ -2864,19 +2864,19 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>0</v>
+        <v>-44.72</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-7.83</v>
+        <v>-27.59</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-25.42</v>
+        <v>-24.8</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-25.11</v>
+        <v>-21.62</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-4.08</v>
+        <v>-17.91</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
@@ -2927,67 +2927,67 @@
         <v>-0.4</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.27</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.65</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.66</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.76</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-1.66</v>
+        <v>-2.31</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-1.81</v>
+        <v>-4.23</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-3.31</v>
+        <v>-4.12</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-4.98</v>
+        <v>-4.76</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-4.98</v>
+        <v>-4.52</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-4.9</v>
+        <v>-4.6</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-4.57</v>
+        <v>-3.6</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-3.89</v>
+        <v>-2.86</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.22</v>
+        <v>-1.8</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.23</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-3.28</v>
+        <v>-2.34</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.27</v>
+        <v>-2.27</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.24</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.55</v>
+        <v>-2.61</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="32">
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3179,67 +3179,67 @@
         <v>34.4</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>40.04</v>
+        <v>33.39</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>29.19</v>
+        <v>34.7</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>55.72</v>
+        <v>40.03</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>55.98</v>
+        <v>49.23</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>62.92</v>
+        <v>41.85</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.46</v>
+        <v>40.11</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>33.98</v>
+        <v>40.26</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>35.48</v>
+        <v>44.81</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>56.54</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>79.23999999999999</v>
+        <v>79.09</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>79.97</v>
+        <v>77.02</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>78.95</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>57.27</v>
+        <v>54.19</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>69.54000000000001</v>
+        <v>54.85</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>189.31</v>
+        <v>198.71</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>192.03</v>
+        <v>197.4</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>187.7</v>
+        <v>187.74</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>51.74</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>51.78</v>
+        <v>51.44</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>52.24</v>
+        <v>52.84</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>43.87</v>
+        <v>46.05</v>
       </c>
     </row>
     <row r="35">
@@ -3269,22 +3269,22 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>21.45</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>21.46</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>-25.43</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>-6.48</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>-6.63</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>-37.63</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3299,19 +3299,19 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-12.98</v>
+        <v>-5.38</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0</v>
+        <v>-4.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>112.72</v>
+        <v>109.09</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>109.14</v>
+        <v>105.64</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>113.44</v>
+        <v>126.32</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3347,67 +3347,67 @@
         <v>0.45</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.08</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.17</v>
+        <v>-1.07</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.42</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.11</v>
+        <v>0.67</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-1.19</v>
+        <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.48</v>
+        <v>0.77</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-1.34</v>
+        <v>-0.38</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-3.51</v>
+        <v>-2.03</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-2.64</v>
+        <v>-1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.23</v>
+        <v>1.88</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.33</v>
+        <v>0.28</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-0.3</v>
+        <v>0.61</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-2.24</v>
+        <v>-0.98</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.62</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>-0.31</v>
+        <v>0.05</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="37">
@@ -3515,22 +3515,22 @@
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3599,67 +3599,67 @@
         <v>33.78</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>40.3</v>
+        <v>33.35</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>28.48</v>
+        <v>34.08</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>33.09</v>
+        <v>39.83</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>33.84</v>
+        <v>58.78</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>62.72</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>-0.19</v>
+        <v>45.64</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>33.49</v>
+        <v>45.81</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>33.88</v>
+        <v>57.37</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>50.44</v>
+        <v>57.38</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>64.56</v>
+        <v>63.65</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>64.73</v>
+        <v>62.48</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>74.91</v>
+        <v>64.5</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>70.66</v>
+        <v>59.11</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>69.47</v>
+        <v>57.96</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>74</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>80.72</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>71.81999999999999</v>
+        <v>58.74</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>71.62</v>
+        <v>50.85</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>50.58</v>
+        <v>50.06</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>50.53</v>
+        <v>50.71</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>42.38</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="40">
@@ -3704,19 +3704,19 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>-21.83</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-3.82</v>
+        <v>-13.47</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-12.41</v>
+        <v>-12.11</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-12.26</v>
+        <v>-10.55</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-1.99</v>
+        <v>-8.74</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3767,67 +3767,67 @@
         <v>-0.17</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.23</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.27</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.28</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.37</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.79</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-1.46</v>
+        <v>-3.41</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-2.39</v>
+        <v>-3.05</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.33</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.21</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-3.38</v>
+        <v>-3.15</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-3.11</v>
+        <v>-2.48</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-2.71</v>
+        <v>-2.09</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.31</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.49</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.73</v>
+        <v>-2.06</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.72</v>
+        <v>-1.88</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.02</v>
+        <v>-2.08</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="42">
@@ -3935,22 +3935,22 @@
         <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -4019,67 +4019,67 @@
         <v>34.02</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>40.7</v>
+        <v>33.62</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>28.8</v>
+        <v>34.39</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>33.52</v>
+        <v>40.19</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>34.38</v>
+        <v>59.43</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>63.32</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.39</v>
+        <v>46.83</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>34.24</v>
+        <v>47.17</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>34.71</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>55.76</v>
+        <v>72.66</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>79.09</v>
+        <v>77.69</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>79.03</v>
+        <v>74.97</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>79.42</v>
+        <v>75.56</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>73.11</v>
+        <v>61.04</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>59.69</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>75.83</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>82.64</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>73.95999999999999</v>
+        <v>60.32</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>73.75</v>
+        <v>52.31</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>52.03</v>
+        <v>51.44</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>51.98</v>
+        <v>52.17</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>43.56</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="45">
@@ -4187,67 +4187,67 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.14</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.19</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.42</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.9</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.24</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1.34</v>
+        <v>-1.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.27</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.83</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.55</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.55</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.48</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.42</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.62</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.57</v>
+        <v>-0.63</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="47">
@@ -4355,22 +4355,22 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4439,67 +4439,67 @@
         <v>34.4</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>41.17</v>
+        <v>34.1</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>29.38</v>
+        <v>34.88</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>34.24</v>
+        <v>40.93</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>34.87</v>
+        <v>59.92</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>63.95</v>
+        <v>68.08</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>1.27</v>
+        <v>47.97</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>35.25</v>
+        <v>48.66</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>36.13</v>
+        <v>84.81</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>58.65</v>
+        <v>76.5</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>83.7</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>83.11</v>
+        <v>78.77</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>83.03</v>
+        <v>79</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>76.68000000000001</v>
+        <v>64.02</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>71.75</v>
+        <v>59.63</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>78.73</v>
+        <v>90.45</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>85.53</v>
+        <v>94.12</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>76.62</v>
+        <v>62.49</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>76.95</v>
+        <v>54.58</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>54.06</v>
+        <v>53.45</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>53.68</v>
+        <v>53.92</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>44.76</v>
+        <v>46.15</v>
       </c>
     </row>
     <row r="50">
@@ -4607,67 +4607,67 @@
         <v>0.45</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.42</v>
+        <v>1.07</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>0.79</v>
+        <v>2.21</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>2.91</v>
+        <v>2.43</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.42</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.07</v>
+        <v>1.69</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>2.62</v>
+        <v>1.86</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Y51" s="3" t="n">
         <v>1.13</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="52">
@@ -4775,22 +4775,22 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4859,67 +4859,67 @@
         <v>35.47</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>42.13</v>
+        <v>35.02</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>30.31</v>
+        <v>35.98</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>35.1</v>
+        <v>41.96</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>36.08</v>
+        <v>61.46</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>69.41</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2.54</v>
+        <v>49.33</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>36.7</v>
+        <v>50.15</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>37.19</v>
+        <v>84.38</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>58.05</v>
+        <v>75.56</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>79.72</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>82.01000000000001</v>
+        <v>77.41</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>81.76000000000001</v>
+        <v>78.03</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>74.51000000000001</v>
+        <v>61.53</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>69.95</v>
+        <v>58.7</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>71.5</v>
+        <v>82.23</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>78.06999999999999</v>
+        <v>85.42</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>71.75</v>
+        <v>58.46</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>73.02</v>
+        <v>51.59</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>54.06</v>
+        <v>53.01</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>55.09</v>
+        <v>55.4</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>46.03</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="55">
@@ -5027,67 +5027,67 @@
         <v>1.53</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>1.87</v>
+        <v>2.56</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>1.39</v>
+        <v>0.64</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.75</v>
+        <v>-0.06</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-2.24</v>
+        <v>-1.35</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-4.86</v>
+        <v>-5.51</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-5.15</v>
+        <v>-6.06</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-2.8</v>
+        <v>-2.34</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.31</v>
+        <v>-1.14</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.41</v>
+        <v>0.95</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="57">
@@ -5195,22 +5195,22 @@
         <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5279,67 +5279,67 @@
         <v>35.07</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>41.77</v>
+        <v>34.66</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>29.76</v>
+        <v>35.49</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>34.63</v>
+        <v>41.48</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>35.52</v>
+        <v>60.89</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>64.52</v>
+        <v>68.92</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>1.59</v>
+        <v>48.57</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>35.54</v>
+        <v>49.06</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>36.02</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>57.87</v>
+        <v>75.48</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>82.16</v>
+        <v>80.78</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>82.27</v>
+        <v>78.27</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>75.66</v>
+        <v>63.17</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>74.34</v>
+        <v>61.71</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>78.31999999999999</v>
+        <v>90.08</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>85.36</v>
+        <v>93.92</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>76.54000000000001</v>
+        <v>62.42</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>76.31999999999999</v>
+        <v>54.14</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>53.89</v>
+        <v>53.29</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>53.85</v>
+        <v>54.09</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>45.13</v>
+        <v>46.53</v>
       </c>
     </row>
     <row r="60">
@@ -5447,67 +5447,67 @@
         <v>1.12</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G61" s="3" t="n">
         <v>1.14</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>0.87</v>
-      </c>
       <c r="H61" s="3" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.8</v>
+        <v>1.55</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.71</v>
+        <v>1.47</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.68</v>
+        <v>2.47</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>2.13</v>
+        <v>2.44</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="62">
@@ -5615,22 +5615,22 @@
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5699,67 +5699,67 @@
         <v>35.51</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>42.21</v>
+        <v>35.1</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>30.14</v>
+        <v>35.94</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>35.14</v>
+        <v>42.04</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>36.04</v>
+        <v>61.56</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>65.04000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>2.09</v>
+        <v>49.33</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>36.09</v>
+        <v>49.83</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>36.62</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>58.89</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>83.52</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>83.63</v>
+        <v>79.34</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>83.64</v>
+        <v>79.58</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>77.08</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>75.67</v>
+        <v>62.88</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>79.70999999999999</v>
+        <v>91.68000000000001</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>86.78</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>77.81999999999999</v>
+        <v>63.47</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>77.59999999999999</v>
+        <v>55.04</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>54.68</v>
+        <v>54.12</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>54.63</v>
+        <v>54.88</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>45.74</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="65">
@@ -5867,67 +5867,67 @@
         <v>1.56</v>
       </c>
       <c r="F66" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G66" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="H66" s="3" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>1.69</v>
+        <v>2.21</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>1.58</v>
+        <v>2.06</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>1.3</v>
+        <v>2.32</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>1.28</v>
+        <v>4.07</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="O66" s="3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P66" s="3" t="n">
         <v>3.09</v>
       </c>
-      <c r="P66" s="3" t="n">
+      <c r="Q66" s="3" t="n">
         <v>3.18</v>
       </c>
-      <c r="Q66" s="3" t="n">
-        <v>3.35</v>
-      </c>
       <c r="R66" s="3" t="n">
-        <v>3.31</v>
+        <v>2.7</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>3.48</v>
+        <v>2.83</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.56</v>
+        <v>4.01</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.27</v>
+        <v>2.67</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>3.26</v>
+        <v>2.31</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="67">
@@ -6035,22 +6035,22 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6119,67 +6119,67 @@
         <v>36.04</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>42.73</v>
+        <v>35.66</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>30.54</v>
+        <v>36.47</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>35.59</v>
+        <v>42.62</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>36.5</v>
+        <v>62.2</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>65.48999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>2.43</v>
+        <v>49.96</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>36.43</v>
+        <v>50.52</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>36.84</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>59.2</v>
+        <v>77.22</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>84.04000000000001</v>
+        <v>82.64</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>84.06999999999999</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>84.06999999999999</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>77.41</v>
+        <v>64.63</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>75.98</v>
+        <v>63.01</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>80.05</v>
+        <v>91.97</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>87.14</v>
+        <v>95.89</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>78.23</v>
+        <v>63.8</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>78.09</v>
+        <v>55.39</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>55.08</v>
+        <v>54.51</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>55.2</v>
+        <v>55.45</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>46.32</v>
+        <v>47.81</v>
       </c>
     </row>
     <row r="70">
@@ -6287,67 +6287,67 @@
         <v>2.09</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.06</v>
+        <v>2.51</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.03</v>
+        <v>2.66</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>1.63</v>
+        <v>2.95</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.6</v>
+        <v>2.93</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.51</v>
+        <v>4.99</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>2.55</v>
+        <v>3.32</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>3.64</v>
+        <v>3.04</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.68</v>
+        <v>4.23</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.92</v>
+        <v>4.41</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.75</v>
+        <v>2.66</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="72">
@@ -6455,22 +6455,22 @@
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6539,67 +6539,67 @@
         <v>35.07</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>41.77</v>
+        <v>34.7</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>29.79</v>
+        <v>35.49</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>34.67</v>
+        <v>41.52</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>35.59</v>
+        <v>60.98</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>64.56</v>
+        <v>68.92</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>1.63</v>
+        <v>48.62</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>35.65</v>
+        <v>49.32</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>36.24</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>58.23</v>
+        <v>75.95</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>82.75</v>
+        <v>81.36</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>78.28</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>78.59</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>76.05</v>
+        <v>63.43</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>74.73</v>
+        <v>62.03</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>78.81</v>
+        <v>90.64</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>85.88</v>
+        <v>94.41</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>77.01000000000001</v>
+        <v>62.81</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>76.79000000000001</v>
+        <v>54.47</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>54.17</v>
+        <v>53.56</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>54.12</v>
+        <v>54.37</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>45.27</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="75">
@@ -6707,67 +6707,67 @@
         <v>1.12</v>
       </c>
       <c r="F76" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G76" s="3" t="n">
         <v>1.14</v>
       </c>
-      <c r="G76" s="3" t="n">
-        <v>0.9</v>
-      </c>
       <c r="H76" s="3" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.83</v>
+        <v>1.6</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.82</v>
+        <v>1.73</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>0.91</v>
+        <v>3</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.54</v>
+        <v>1.99</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.46</v>
+        <v>2.01</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>2.46</v>
+        <v>1.74</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="77">
@@ -6875,22 +6875,22 @@
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6959,67 +6959,67 @@
         <v>33.95</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>40.63</v>
+        <v>33.59</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>28.89</v>
+        <v>34.36</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>33.52</v>
+        <v>40.11</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>34.35</v>
+        <v>59.35</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>63.46</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.79</v>
+        <v>47.01</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>34.83</v>
+        <v>47.59</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>35.33</v>
+        <v>82.61</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>56.65</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>79.09</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>80.45</v>
+        <v>76.25</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>80.29000000000001</v>
+        <v>76.39</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>73.77</v>
+        <v>61.59</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>72.18000000000001</v>
+        <v>60.05</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>76.37</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>83.22</v>
+        <v>91.48</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>74.55</v>
+        <v>60.8</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>74.34</v>
+        <v>52.73</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>52.66</v>
+        <v>52.06</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>52.55</v>
+        <v>52.79</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>43.87</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="80">
@@ -7295,22 +7295,22 @@
         <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7379,67 +7379,67 @@
         <v>35.47</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>42.1</v>
+        <v>34.91</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>30.47</v>
+        <v>36.09</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>35.21</v>
+        <v>41.96</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>36.23</v>
+        <v>61.51</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>2.39</v>
+        <v>49.08</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>36.54</v>
+        <v>49.99</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>37</v>
+        <v>82.11</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>58.23</v>
+        <v>73.75</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>81.81999999999999</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>81.93000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>81.34999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>74.36</v>
+        <v>59.85</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>71.12</v>
+        <v>59.63</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>71.17</v>
+        <v>81.92</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>77.92</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>73.67</v>
+        <v>59.96</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>74.56</v>
+        <v>52.67</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>54.45</v>
+        <v>53.45</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>55.44</v>
+        <v>55.69</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>45.84</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="85">
@@ -7547,67 +7547,67 @@
         <v>1.53</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>1.66</v>
+        <v>-0.49</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>1.57</v>
+        <v>-0.15</v>
       </c>
       <c r="O86" s="3" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>-1.74</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>-6.22</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X86" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="P86" s="3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="U86" s="3" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="V86" s="3" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="W86" s="3" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="X86" s="3" t="n">
-        <v>1.8</v>
-      </c>
       <c r="Y86" s="3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="87">
@@ -7715,22 +7715,22 @@
         <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7799,67 +7799,67 @@
         <v>33.55</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>40.2</v>
+        <v>33.32</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>28.53</v>
+        <v>34.05</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>33.16</v>
+        <v>46.2</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>33.81</v>
+        <v>58.7</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>62.59</v>
+        <v>66.83</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>-0.41</v>
+        <v>45.25</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>33.17</v>
+        <v>45.28</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>33.52</v>
+        <v>56.54</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>49.52</v>
+        <v>56.31</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>63.05</v>
+        <v>62.22</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>63.21</v>
+        <v>61.11</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>63.06</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>69.2</v>
+        <v>58</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>57.19</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>74.14</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>80.72</v>
+        <v>89.25</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>71.27</v>
+        <v>58.46</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>71.06999999999999</v>
+        <v>50.46</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>50.29</v>
+        <v>49.82</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>50</v>
+        <v>50.18</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>42.26</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="90">
@@ -7904,19 +7904,19 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>0</v>
+        <v>-21.83</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-3.82</v>
+        <v>-13.47</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-12.41</v>
+        <v>-12.11</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-12.26</v>
+        <v>-10.55</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-1.99</v>
+        <v>-8.74</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0</v>
@@ -7967,67 +7967,67 @@
         <v>-0.4</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.27</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.65</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.66</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.76</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-1.66</v>
+        <v>-2.31</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-1.81</v>
+        <v>-4.23</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-3.31</v>
+        <v>-4.12</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-4.98</v>
+        <v>-4.76</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-4.98</v>
+        <v>-4.59</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-4.9</v>
+        <v>-4.6</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-4.57</v>
+        <v>-3.6</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-3.89</v>
+        <v>-2.86</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.22</v>
+        <v>-1.8</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.23</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-3.28</v>
+        <v>-2.34</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.27</v>
+        <v>-2.27</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.24</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.55</v>
+        <v>-2.61</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="92">
@@ -8057,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -8135,22 +8135,22 @@
         <v>0</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="H93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>15.45</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>29.21</v>
+        <v>25.77</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>-33.06</v>
+        <v>0</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-11T08:10:07</t>
+          <t>CreatedAt: 2026-10-11T13:08:38</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -680,46 +680,46 @@
         <v>45.81</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>57.37</v>
+        <v>58.41</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>57.38</v>
+        <v>65</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>63.65</v>
+        <v>71.83</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>62.48</v>
+        <v>87.28</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>64.5</v>
+        <v>90.66</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>59.11</v>
+        <v>92.73</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>57.96</v>
+        <v>19.88</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>85.43000000000001</v>
+        <v>193.51</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>88.98999999999999</v>
+        <v>118.01</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>58.74</v>
+        <v>105.18</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>50.85</v>
+        <v>85.88</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>50.06</v>
+        <v>58.3</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>50.71</v>
+        <v>58.25</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>43.74</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="5">
@@ -764,19 +764,19 @@
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-21.83</v>
+        <v>-11.8</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-13.47</v>
+        <v>-15.56</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-12.11</v>
+        <v>-4.85</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-10.55</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
@@ -848,43 +848,43 @@
         <v>-1.79</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-3.41</v>
+        <v>-3.09</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-3.05</v>
+        <v>-3.38</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-3.33</v>
+        <v>-3.3</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.84</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-3.15</v>
+        <v>-4.17</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-2.48</v>
+        <v>-4.36</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.79</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-2.31</v>
+        <v>-3.13</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.49</v>
+        <v>-3.3</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.06</v>
+        <v>-3.58</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.88</v>
+        <v>-3.09</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-2</v>
+        <v>-2.39</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.08</v>
+        <v>-2.45</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-1.49</v>
@@ -1034,10 +1034,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1100,46 +1100,46 @@
         <v>45.98</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>58.6</v>
+        <v>59.51</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>59.05</v>
+        <v>66.02</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>64.98</v>
+        <v>72.34</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>64.2</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>65.43000000000001</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>58.71</v>
+        <v>92.73</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>57.85</v>
+        <v>20.1</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>196.41</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>90.48</v>
+        <v>120.11</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>60.14</v>
+        <v>107.89</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>50.94</v>
+        <v>86.38</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>50.45</v>
+        <v>58.87</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>51.25</v>
+        <v>59.15</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>44.82</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="10">
@@ -1184,19 +1184,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-21.83</v>
+        <v>-11.8</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-13.47</v>
+        <v>-15.56</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-12.11</v>
+        <v>-4.85</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-10.55</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1268,46 +1268,46 @@
         <v>-1.61</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-2.17</v>
+        <v>-2</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.37</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-2</v>
+        <v>-2.78</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.5</v>
+        <v>-2.83</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-2.88</v>
+        <v>-4.36</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.2</v>
+        <v>-2.57</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.86</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-1.78</v>
+        <v>-2.59</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.82</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>-1.54</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>0</v>
@@ -1523,43 +1523,43 @@
         <v>38.62</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>72.52</v>
+        <v>38.62</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>77.08</v>
+        <v>38.62</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>74.75</v>
+        <v>38.62</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>74.17</v>
+        <v>54.32</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>52.74</v>
+        <v>16.48</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>53.19</v>
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>196.83</v>
+        <v>196.41</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>196.13</v>
+        <v>195.47</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>186.46</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>50.94</v>
+        <v>75</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>50.5</v>
+        <v>58.87</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>51.25</v>
+        <v>59.21</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>44.87</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="15">
@@ -1604,37 +1604,37 @@
         <v>-7.36</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-41.81</v>
+        <v>-32.76</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0</v>
+        <v>-42.96</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0</v>
+        <v>-38.57</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
+        <v>-49.67</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0</v>
+        <v>-37.22</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-5.98</v>
+        <v>-76.26000000000001</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-4.66</v>
+        <v>-20.1</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>109.09</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>105.64</v>
+        <v>75.36</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>126.32</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>0</v>
+        <v>-11.38</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>0</v>
@@ -1688,46 +1688,46 @@
         <v>-1.61</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-2.17</v>
+        <v>-1.93</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.37</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-2</v>
+        <v>-2.78</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-1.5</v>
+        <v>-2.83</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.3</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-2.88</v>
+        <v>-4.36</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-2.2</v>
+        <v>-2.57</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.76</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-1.78</v>
+        <v>-2.59</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.82</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.48</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
@@ -1874,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
@@ -1940,46 +1940,46 @@
         <v>45.59</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>34.17</v>
+        <v>45.77</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>42.85</v>
+        <v>48.3</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>50.45</v>
+        <v>66.16</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>50.93</v>
+        <v>86.7</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>54.77</v>
+        <v>90.14</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>58.66</v>
+        <v>92.03</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>57.63</v>
+        <v>19.52</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>85.68000000000001</v>
+        <v>193.85</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>89.16</v>
+        <v>118.24</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>58.69</v>
+        <v>105.08</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>50.7</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>49.96</v>
+        <v>58.19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>50.52</v>
+        <v>58.02</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>43.74</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="20">
@@ -2024,19 +2024,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-44.72</v>
+        <v>-24.18</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-27.59</v>
+        <v>-31.87</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-24.8</v>
+        <v>-9.93</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-21.62</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-17.91</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0</v>
@@ -2108,43 +2108,43 @@
         <v>-2.01</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.36</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-3.45</v>
+        <v>-3.77</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-3.84</v>
+        <v>-3.88</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-3.7</v>
+        <v>-4.42</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-3.71</v>
+        <v>-4.69</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-2.93</v>
+        <v>-5.06</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-2.42</v>
+        <v>-3.15</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.79</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-2.32</v>
+        <v>-3.07</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.11</v>
+        <v>-3.68</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.03</v>
+        <v>-3.26</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.67</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>-1.49</v>
@@ -2294,10 +2294,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>0</v>
@@ -2360,46 +2360,46 @@
         <v>45.59</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>57.07</v>
+        <v>58.14</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>56.98</v>
+        <v>64.62</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>63.14</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>62</v>
+        <v>86.7</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>63.94</v>
+        <v>90.14</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>58.66</v>
+        <v>92.03</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>57.63</v>
+        <v>19.52</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>85.68000000000001</v>
+        <v>193.85</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>89.16</v>
+        <v>118.24</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>58.69</v>
+        <v>105.08</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>50.7</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>49.96</v>
+        <v>58.19</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>50.52</v>
+        <v>58.02</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>43.74</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="25">
@@ -2444,19 +2444,19 @@
         <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-21.83</v>
+        <v>-11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-13.47</v>
+        <v>-15.56</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-12.11</v>
+        <v>-4.85</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-10.55</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2528,43 +2528,43 @@
         <v>-2.01</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.36</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-3.45</v>
+        <v>-3.77</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-3.84</v>
+        <v>-3.88</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-3.7</v>
+        <v>-4.42</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-3.71</v>
+        <v>-4.69</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-2.93</v>
+        <v>-5.06</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-2.42</v>
+        <v>-3.15</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.79</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-2.32</v>
+        <v>-3.07</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.11</v>
+        <v>-3.68</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.03</v>
+        <v>-3.26</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.67</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>-1.49</v>
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0</v>
@@ -2780,46 +2780,46 @@
         <v>45.28</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>33.65</v>
+        <v>45.24</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>42.19</v>
+        <v>47.62</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>49.53</v>
+        <v>65.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50.11</v>
+        <v>85.8</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>53.89</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>58</v>
+        <v>91.08</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>57.19</v>
+        <v>18.88</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>85.93000000000001</v>
+        <v>194.08</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>89.25</v>
+        <v>118.35</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>58.46</v>
+        <v>104.77</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>50.46</v>
+        <v>85.38</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>49.82</v>
+        <v>58.02</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>50.18</v>
+        <v>57.64</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>43.65</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="30">
@@ -2864,19 +2864,19 @@
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-44.72</v>
+        <v>-24.18</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-27.59</v>
+        <v>-31.87</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-24.8</v>
+        <v>-9.93</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-21.62</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-17.91</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
@@ -2948,46 +2948,46 @@
         <v>-2.31</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-4.23</v>
+        <v>-3.89</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-4.12</v>
+        <v>-4.45</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-4.76</v>
+        <v>-4.74</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-4.52</v>
+        <v>-5.32</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-4.6</v>
+        <v>-5.62</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-3.6</v>
+        <v>-6.01</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-2.86</v>
+        <v>-3.79</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1.8</v>
+        <v>-2.57</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.23</v>
+        <v>-2.96</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.34</v>
+        <v>-3.98</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-2.27</v>
+        <v>-3.59</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.24</v>
+        <v>-2.67</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.61</v>
+        <v>-3.05</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="32">
@@ -3134,10 +3134,10 @@
         <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>0</v>
@@ -3200,25 +3200,25 @@
         <v>40.26</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>44.81</v>
+        <v>43.82</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>74.56999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>79.09</v>
+        <v>44.46</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>77.02</v>
+        <v>46.14</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>76.01000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>54.19</v>
+        <v>26</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>54.85</v>
+        <v>3.8</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>198.71</v>
@@ -3227,19 +3227,19 @@
         <v>197.4</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>187.74</v>
+        <v>188.87</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>51.74</v>
+        <v>77.67</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>51.44</v>
+        <v>60.15</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>52.84</v>
+        <v>61.18</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>46.05</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="35">
@@ -3284,37 +3284,37 @@
         <v>-6.63</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-37.63</v>
+        <v>-29.48</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>-38.66</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0</v>
+        <v>-34.71</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>-44.7</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>-33.49</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-5.38</v>
+        <v>-68.63</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-4.2</v>
+        <v>-18.09</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>109.09</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>105.64</v>
+        <v>75.36</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>126.32</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>-10.24</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
@@ -3368,46 +3368,46 @@
         <v>-0.7</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.67</v>
+        <v>-0.58</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.77</v>
+        <v>-0.27</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-2.03</v>
+        <v>-2.46</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-1</v>
+        <v>-0.77</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.61</v>
+        <v>1.66</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.98</v>
+        <v>-1.05</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.54</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.83</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="37">
@@ -3554,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>0</v>
@@ -3620,46 +3620,46 @@
         <v>45.81</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>57.37</v>
+        <v>58.41</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>57.38</v>
+        <v>65</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>63.65</v>
+        <v>71.83</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>62.48</v>
+        <v>87.28</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>64.5</v>
+        <v>90.66</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>59.11</v>
+        <v>92.73</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>57.96</v>
+        <v>19.88</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>85.43000000000001</v>
+        <v>193.51</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>88.98999999999999</v>
+        <v>118.01</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>58.74</v>
+        <v>105.18</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>50.85</v>
+        <v>85.88</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>50.06</v>
+        <v>58.3</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>50.71</v>
+        <v>58.25</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>43.74</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="40">
@@ -3704,19 +3704,19 @@
         <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-21.83</v>
+        <v>-11.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-13.47</v>
+        <v>-15.56</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-12.11</v>
+        <v>-4.85</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-10.55</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3788,43 +3788,43 @@
         <v>-1.79</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-3.41</v>
+        <v>-3.09</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-3.05</v>
+        <v>-3.38</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-3.33</v>
+        <v>-3.3</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.84</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-3.15</v>
+        <v>-4.17</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-2.48</v>
+        <v>-4.36</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-2.09</v>
+        <v>-2.79</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-2.31</v>
+        <v>-3.13</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.49</v>
+        <v>-3.3</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.06</v>
+        <v>-3.58</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.88</v>
+        <v>-3.09</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-2</v>
+        <v>-2.39</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.08</v>
+        <v>-2.45</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-1.49</v>
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>0</v>
@@ -4040,46 +4040,46 @@
         <v>47.17</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>81.70999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>72.66</v>
+        <v>83.19</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>77.69</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>74.97</v>
+        <v>89.95</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>75.56</v>
+        <v>93.62</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>61.04</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>59.69</v>
+        <v>22.2</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>87.20999999999999</v>
+        <v>196.05</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>90.93000000000001</v>
+        <v>120.59</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>60.32</v>
+        <v>107.89</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>52.31</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>51.44</v>
+        <v>59.97</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>52.17</v>
+        <v>59.97</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>44.91</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="45">
@@ -4208,43 +4208,43 @@
         <v>-0.42</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.58</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.75</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1.4</v>
+        <v>-0.79</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.17</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.22</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.77</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.47</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.59</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.72</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.86</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.71</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.72</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.63</v>
+        <v>-0.72</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>-0.31</v>
@@ -4394,10 +4394,10 @@
         <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U48" s="3" t="n">
         <v>0</v>
@@ -4460,46 +4460,46 @@
         <v>48.66</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>84.81</v>
+        <v>75.5</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>76.5</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>82.20999999999999</v>
+        <v>83.39</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>78.77</v>
+        <v>94.42</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>79</v>
+        <v>98.37</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>64.02</v>
+        <v>101.14</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>59.63</v>
+        <v>21.82</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>90.45</v>
+        <v>200.33</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>94.12</v>
+        <v>124.8</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>62.49</v>
+        <v>111.77</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>54.58</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>53.45</v>
+        <v>62.38</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>53.92</v>
+        <v>61.99</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>46.15</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="50">
@@ -4628,43 +4628,43 @@
         <v>1.07</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>2.6</v>
+        <v>3.41</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.61</v>
+        <v>3.54</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>2.43</v>
+        <v>4.05</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.85</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>2.71</v>
+        <v>3.69</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>2.64</v>
+        <v>3.49</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>1.69</v>
+        <v>3.02</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.86</v>
+        <v>3.13</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>0.92</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T53" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U53" s="3" t="n">
         <v>0</v>
@@ -4880,46 +4880,46 @@
         <v>50.15</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>84.38</v>
+        <v>74.95</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>75.56</v>
+        <v>83.94</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>79.72</v>
+        <v>79.73</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>77.41</v>
+        <v>90.67</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>78.03</v>
+        <v>94.08</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>61.53</v>
+        <v>98.67</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>58.7</v>
+        <v>21.51</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>82.23</v>
+        <v>188.13</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>85.42</v>
+        <v>112.74</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>58.46</v>
+        <v>105.38</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>51.59</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>53.01</v>
+        <v>61.99</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>55.4</v>
+        <v>64.02</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>47.6</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="55">
@@ -5048,43 +5048,43 @@
         <v>2.56</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>0.64</v>
+        <v>-0.24</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>1.16</v>
+        <v>-0.45</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>1.64</v>
+        <v>-0.75</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.06</v>
+        <v>1.58</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.35</v>
+        <v>-1.15</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-5.51</v>
+        <v>-8.52</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-6.06</v>
+        <v>-8.57</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-2.34</v>
+        <v>-3.37</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.57</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.95</v>
+        <v>1.3</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="Z56" s="3" t="n">
         <v>2.38</v>
@@ -5234,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T58" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U58" s="3" t="n">
         <v>0</v>
@@ -5300,46 +5300,46 @@
         <v>49.06</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>85.06999999999999</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>75.48</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>80.78</v>
+        <v>82.53</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>77.95999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>78.27</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>63.17</v>
+        <v>99.89</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>61.71</v>
+        <v>24.83</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>90.08</v>
+        <v>199.83</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>93.92</v>
+        <v>124.55</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>62.42</v>
+        <v>111.66</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>54.14</v>
+        <v>91.44</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>53.29</v>
+        <v>62.12</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>54.09</v>
+        <v>62.18</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>46.53</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="60">
@@ -5468,43 +5468,43 @@
         <v>1.47</v>
       </c>
       <c r="M61" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W61" s="3" t="n">
         <v>2.47</v>
       </c>
-      <c r="N61" s="3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="Z61" s="3" t="n">
         <v>1.3</v>
@@ -5654,10 +5654,10 @@
         <v>0</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T63" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U63" s="3" t="n">
         <v>0</v>
@@ -5720,46 +5720,46 @@
         <v>49.83</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>86.68000000000001</v>
+        <v>77</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>76.73999999999999</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>82.04000000000001</v>
+        <v>83.91</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>79.34</v>
+        <v>95.41</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>79.58</v>
+        <v>98.89</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>64.29000000000001</v>
+        <v>101.67</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>62.88</v>
+        <v>26.34</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>91.68000000000001</v>
+        <v>202</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>95.48999999999999</v>
+        <v>126.63</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>63.47</v>
+        <v>113.52</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>55.04</v>
+        <v>92.87</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>54.12</v>
+        <v>63.09</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>54.88</v>
+        <v>63.09</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>47.16</v>
+        <v>47.21</v>
       </c>
     </row>
     <row r="65">
@@ -5888,46 +5888,46 @@
         <v>2.24</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>4.07</v>
+        <v>3.7</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.84</v>
+        <v>4.05</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>3.09</v>
+        <v>4.29</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>3.18</v>
+        <v>4.05</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>2.7</v>
+        <v>4.58</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.83</v>
+        <v>3.68</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.94</v>
+        <v>5.36</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>4.01</v>
+        <v>5.32</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.67</v>
+        <v>4.77</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.31</v>
+        <v>3.9</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.09</v>
+        <v>2.4</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="67">
@@ -6074,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U68" s="3" t="n">
         <v>0</v>
@@ -6140,46 +6140,46 @@
         <v>50.52</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>87.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>77.22</v>
+        <v>89.02</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>82.64</v>
+        <v>84.98</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>79.76000000000001</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>64.63</v>
+        <v>102.31</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>63.01</v>
+        <v>26.52</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>91.97</v>
+        <v>202.39</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>95.89</v>
+        <v>127.16</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>63.8</v>
+        <v>114.12</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>55.39</v>
+        <v>93.45</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>54.51</v>
+        <v>63.48</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>55.45</v>
+        <v>63.68</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>47.81</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="70">
@@ -6308,46 +6308,46 @@
         <v>2.93</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4.99</v>
+        <v>4.6</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>3.32</v>
+        <v>5.07</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.55</v>
+        <v>5.01</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.51</v>
+        <v>5.2</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>3.6</v>
+        <v>4.68</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>3.04</v>
+        <v>5.22</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>4.23</v>
+        <v>5.75</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>4.41</v>
+        <v>5.85</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3</v>
+        <v>5.36</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.66</v>
+        <v>4.49</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.66</v>
+        <v>2.99</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="72">
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U73" s="3" t="n">
         <v>0</v>
@@ -6560,46 +6560,46 @@
         <v>49.32</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>76.12</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>75.95</v>
+        <v>87.08</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>81.36</v>
+        <v>83.13</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>78.28</v>
+        <v>94.42</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>78.59</v>
+        <v>97.87</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>63.43</v>
+        <v>100.61</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>62.03</v>
+        <v>25.25</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>90.64</v>
+        <v>200.59</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>94.41</v>
+        <v>125.32</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>62.81</v>
+        <v>112.35</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>54.47</v>
+        <v>91.91</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>53.56</v>
+        <v>62.44</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>54.37</v>
+        <v>62.44</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>46.67</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="75">
@@ -6728,43 +6728,43 @@
         <v>1.73</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.05</v>
+        <v>3.13</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>2.28</v>
+        <v>3.16</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.2</v>
+        <v>3.03</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.84</v>
+        <v>3.52</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.99</v>
+        <v>2.58</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.9</v>
+        <v>3.94</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.93</v>
+        <v>4.01</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.01</v>
+        <v>3.6</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.74</v>
+        <v>2.94</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="Z76" s="3" t="n">
         <v>1.45</v>
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U78" s="3" t="n">
         <v>0</v>
@@ -6980,46 +6980,46 @@
         <v>47.59</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>82.61</v>
+        <v>73.31</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>83.94</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>79.09</v>
+        <v>79.97</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>76.25</v>
+        <v>91.12</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>76.39</v>
+        <v>94.83</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>61.59</v>
+        <v>97.09</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>60.05</v>
+        <v>22.67</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>196.65</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>91.48</v>
+        <v>121.31</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>60.8</v>
+        <v>108.75</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>52.73</v>
+        <v>88.97</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>52.06</v>
+        <v>60.69</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>52.79</v>
+        <v>60.69</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>45.22</v>
+        <v>45.27</v>
       </c>
     </row>
     <row r="80">
@@ -7334,10 +7334,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U83" s="3" t="n">
         <v>0</v>
@@ -7400,46 +7400,46 @@
         <v>49.99</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>82.11</v>
+        <v>72.87</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>73.75</v>
+        <v>81.42</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>77.45999999999999</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>75.19</v>
+        <v>87.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>77.70999999999999</v>
+        <v>90.92</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>59.85</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>59.63</v>
+        <v>22.43</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>81.92</v>
+        <v>187.51</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>85.26000000000001</v>
+        <v>112.22</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>59.96</v>
+        <v>107.78</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>52.67</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>53.45</v>
+        <v>62.44</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>55.69</v>
+        <v>64.22</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>47.5</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="85">
@@ -7568,43 +7568,43 @@
         <v>2.4</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-0.49</v>
+        <v>-0.44</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.15</v>
+        <v>-2.52</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-1.63</v>
+        <v>-2.7</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1.05</v>
+        <v>-3.42</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>1.32</v>
+        <v>-3.91</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.23</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-5.82</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.22</v>
+        <v>-9.09</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.97</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.27</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.9</v>
+        <v>3.53</v>
       </c>
       <c r="Z86" s="3" t="n">
         <v>2.28</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U88" s="3" t="n">
         <v>0</v>
@@ -7820,46 +7820,46 @@
         <v>45.28</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>56.54</v>
+        <v>57.61</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>56.31</v>
+        <v>63.93</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>62.22</v>
+        <v>70.38</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>61.11</v>
+        <v>85.8</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>63.06</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>58</v>
+        <v>91.08</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>57.19</v>
+        <v>18.88</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>85.93000000000001</v>
+        <v>194.08</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>89.25</v>
+        <v>118.24</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>58.46</v>
+        <v>104.77</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>50.46</v>
+        <v>85.3</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>49.82</v>
+        <v>58.02</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>50.18</v>
+        <v>57.64</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>43.65</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="90">
@@ -7904,19 +7904,19 @@
         <v>0</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-21.83</v>
+        <v>-11.8</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-13.47</v>
+        <v>-15.56</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-12.11</v>
+        <v>-4.85</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-10.55</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-8.74</v>
+        <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0</v>
@@ -7988,46 +7988,46 @@
         <v>-2.31</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-4.23</v>
+        <v>-3.89</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-4.12</v>
+        <v>-4.45</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-4.76</v>
+        <v>-4.74</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-4.59</v>
+        <v>-5.32</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-4.6</v>
+        <v>-5.62</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-3.6</v>
+        <v>-6.01</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-2.86</v>
+        <v>-3.79</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-1.8</v>
+        <v>-2.57</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.07</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.34</v>
+        <v>-3.98</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-2.27</v>
+        <v>-3.67</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.24</v>
+        <v>-2.67</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.61</v>
+        <v>-3.05</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="92">
@@ -8174,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>0</v>
+        <v>-55.4</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>0</v>
+        <v>77.47</v>
       </c>
       <c r="U93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-11T13:08:38</t>
+          <t>CreatedAt: 2026-10-11T17:09:36</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -695,31 +695,31 @@
         <v>90.66</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>92.73</v>
+        <v>100.51</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>19.88</v>
+        <v>99</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>193.51</v>
+        <v>119.02</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>118.01</v>
+        <v>113.55</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>105.18</v>
+        <v>91.37</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>85.88</v>
+        <v>73.39</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>58.3</v>
+        <v>50.06</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>58.25</v>
+        <v>49.72</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>43.78</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="5">
@@ -863,31 +863,31 @@
         <v>-4.17</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.62</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-2.79</v>
+        <v>-3.86</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.45</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3.29</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.58</v>
+        <v>-3.47</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-3.09</v>
+        <v>-2.64</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-2.39</v>
+        <v>-2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.45</v>
+        <v>-1.89</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="7">
@@ -1034,10 +1034,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
         <v>91.54000000000001</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>92.73</v>
+        <v>100.6</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>20.1</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>196.41</v>
+        <v>121.74</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>120.11</v>
+        <v>115</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>107.89</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>86.38</v>
+        <v>73.67</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>58.87</v>
+        <v>50.45</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>59.15</v>
+        <v>50.59</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>45.04</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="10">
@@ -1283,31 +1283,31 @@
         <v>-3.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.53</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.57</v>
+        <v>-3.57</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.73</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.84</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.86</v>
+        <v>-2.49</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.82</v>
+        <v>-1.61</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.01</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="12">
@@ -1454,10 +1454,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>0</v>
@@ -1535,31 +1535,31 @@
         <v>54.32</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>16.48</v>
+        <v>25.42</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>0</v>
+        <v>10.66</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>196.41</v>
+        <v>121.74</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>195.47</v>
+        <v>115</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>186.46</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>75</v>
+        <v>9.32</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>58.87</v>
+        <v>50.45</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>59.21</v>
+        <v>50.59</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>45.04</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="15">
@@ -1619,22 +1619,22 @@
         <v>-37.22</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-76.26000000000001</v>
+        <v>-75.18000000000001</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-20.1</v>
+        <v>-88.62</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>75.36</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>78.45999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-11.38</v>
+        <v>-64.34999999999999</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>0</v>
@@ -1703,31 +1703,31 @@
         <v>-3.3</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.53</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-2.57</v>
+        <v>-3.57</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.73</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.84</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.76</v>
+        <v>-2.49</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.82</v>
+        <v>-1.61</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-1.48</v>
+        <v>-1.01</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="17">
@@ -1874,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
@@ -1955,31 +1955,31 @@
         <v>90.14</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>92.03</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>19.52</v>
+        <v>98.62</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>193.85</v>
+        <v>119.48</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>118.24</v>
+        <v>113.77</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>105.08</v>
+        <v>91.19</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>58.19</v>
+        <v>49.96</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>58.02</v>
+        <v>49.57</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>43.78</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="20">
@@ -2123,31 +2123,31 @@
         <v>-4.69</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-5.06</v>
+        <v>-5.2</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-3.15</v>
+        <v>-4.24</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.99</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>-3.07</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.68</v>
+        <v>-3.65</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-3.26</v>
+        <v>-2.85</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.67</v>
+        <v>-2.03</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="22">
@@ -2294,10 +2294,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>0</v>
@@ -2375,31 +2375,31 @@
         <v>90.14</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>92.03</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>19.52</v>
+        <v>98.62</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>193.85</v>
+        <v>119.48</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>118.24</v>
+        <v>113.77</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>105.08</v>
+        <v>91.19</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>58.19</v>
+        <v>49.96</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>58.02</v>
+        <v>49.57</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>43.78</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="25">
@@ -2543,31 +2543,31 @@
         <v>-4.69</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-5.06</v>
+        <v>-5.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-3.15</v>
+        <v>-4.24</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.99</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>-3.07</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.68</v>
+        <v>-3.65</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-3.26</v>
+        <v>-2.85</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.67</v>
+        <v>-2.03</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="27">
@@ -2714,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>0</v>
@@ -2795,31 +2795,31 @@
         <v>89.20999999999999</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>91.08</v>
+        <v>99.08</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>18.88</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>194.08</v>
+        <v>120.07</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>118.35</v>
+        <v>114.1</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>104.77</v>
+        <v>90.84</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>85.38</v>
+        <v>72.97</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>58.02</v>
+        <v>49.82</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>57.64</v>
+        <v>49.24</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>43.74</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="30">
@@ -2963,31 +2963,31 @@
         <v>-5.62</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.01</v>
+        <v>-6.04</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-3.79</v>
+        <v>-4.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.4</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.96</v>
+        <v>-2.74</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-3.98</v>
+        <v>-4</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.59</v>
+        <v>-3.06</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.67</v>
+        <v>-2.24</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-3.05</v>
+        <v>-2.36</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="32">
@@ -3134,10 +3134,10 @@
         <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>0</v>
@@ -3215,31 +3215,31 @@
         <v>60.4</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>26</v>
+        <v>34.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>3.8</v>
+        <v>21.78</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>198.71</v>
+        <v>144.76</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>197.4</v>
+        <v>147.71</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>188.87</v>
+        <v>93.53</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>77.67</v>
+        <v>16.99</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>60.15</v>
+        <v>51.44</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>61.18</v>
+        <v>52.18</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>46.43</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="35">
@@ -3299,22 +3299,22 @@
         <v>-33.49</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-68.63</v>
+        <v>-67.66</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-18.09</v>
+        <v>-79.76000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>75.36</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>78.45999999999999</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-10.24</v>
+        <v>-57.92</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
@@ -3383,31 +3383,31 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2.56</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.77</v>
+        <v>-1.32</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.73</v>
+        <v>-0.23</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.66</v>
+        <v>-1.31</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.12</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.62</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.49</v>
+        <v>0.57</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.16</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="37">
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>0</v>
+        <v>20.55</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>0</v>
@@ -3554,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>0</v>
@@ -3635,31 +3635,31 @@
         <v>90.66</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>92.73</v>
+        <v>100.51</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>19.88</v>
+        <v>99</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>193.51</v>
+        <v>119.02</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>118.01</v>
+        <v>113.55</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>105.18</v>
+        <v>91.37</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>85.88</v>
+        <v>73.39</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>58.3</v>
+        <v>50.06</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>58.25</v>
+        <v>49.72</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>43.78</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="40">
@@ -3803,31 +3803,31 @@
         <v>-4.17</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.62</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-2.79</v>
+        <v>-3.86</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.45</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3.29</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.58</v>
+        <v>-3.47</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-3.09</v>
+        <v>-2.64</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-2.39</v>
+        <v>-2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.45</v>
+        <v>-1.89</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="42">
@@ -3974,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>0</v>
@@ -4055,31 +4055,31 @@
         <v>93.62</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>96.31999999999999</v>
+        <v>103.68</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>22.2</v>
+        <v>101.94</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>196.05</v>
+        <v>120.66</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>120.59</v>
+        <v>116.03</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>107.89</v>
+        <v>94.56</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>88.26000000000001</v>
+        <v>75.28</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>59.97</v>
+        <v>51.44</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>59.97</v>
+        <v>51.04</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>44.96</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="45">
@@ -4223,31 +4223,31 @@
         <v>-1.22</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.77</v>
+        <v>-1.45</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.47</v>
+        <v>-0.92</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.81</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.28</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.71</v>
+        <v>-0.75</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.62</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="47">
@@ -4394,10 +4394,10 @@
         <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
         <v>0</v>
@@ -4475,31 +4475,31 @@
         <v>98.37</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>101.14</v>
+        <v>109.05</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>21.82</v>
+        <v>101.74</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>200.33</v>
+        <v>125.48</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>124.8</v>
+        <v>119.72</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>111.77</v>
+        <v>97.47</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>62.38</v>
+        <v>53.4</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>61.99</v>
+        <v>52.66</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>46.19</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="50">
@@ -4643,31 +4643,31 @@
         <v>3.54</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>4.05</v>
+        <v>3.93</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.12</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>3.69</v>
+        <v>3.01</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>3.49</v>
+        <v>2.87</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>3.02</v>
+        <v>2.63</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>3.13</v>
+        <v>2.43</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="52">
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T53" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U53" s="3" t="n">
         <v>0</v>
@@ -4895,31 +4895,31 @@
         <v>94.08</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>98.67</v>
+        <v>105.98</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>21.51</v>
+        <v>101.54</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>188.13</v>
+        <v>119.25</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>112.74</v>
+        <v>112.13</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>105.38</v>
+        <v>93.16</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>61.99</v>
+        <v>53.51</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>64.02</v>
+        <v>54.32</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>47.65</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="55">
@@ -5063,31 +5063,31 @@
         <v>-0.75</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>1.58</v>
+        <v>0.85</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.15</v>
+        <v>-1.32</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-8.52</v>
+        <v>-3.22</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-8.57</v>
+        <v>-4.71</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-3.37</v>
+        <v>-1.68</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.57</v>
+        <v>0.54</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.33</v>
+        <v>2.72</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="57">
@@ -5234,10 +5234,10 @@
         <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
         <v>0</v>
@@ -5315,31 +5315,31 @@
         <v>97.26000000000001</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>99.89</v>
+        <v>107.6</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>24.83</v>
+        <v>105.5</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>199.83</v>
+        <v>124.21</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>124.55</v>
+        <v>119.84</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>111.66</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>91.44</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>62.12</v>
+        <v>53.23</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>62.18</v>
+        <v>52.88</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>46.57</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="60">
@@ -5483,31 +5483,31 @@
         <v>2.43</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>2.17</v>
+        <v>2.64</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>3.18</v>
+        <v>1.74</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>2.47</v>
+        <v>1.87</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="62">
@@ -5654,10 +5654,10 @@
         <v>0</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T63" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
         <v>0</v>
@@ -5735,31 +5735,31 @@
         <v>98.89</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>101.67</v>
+        <v>109.51</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>26.34</v>
+        <v>107.37</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>202</v>
+        <v>126.52</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>126.63</v>
+        <v>121.84</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>113.52</v>
+        <v>99.52</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>92.87</v>
+        <v>79.03</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>63.09</v>
+        <v>54.06</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>63.09</v>
+        <v>53.64</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>47.21</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="65">
@@ -5903,31 +5903,31 @@
         <v>4.05</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>3.68</v>
+        <v>4.51</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>5.36</v>
+        <v>4.05</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.77</v>
+        <v>4.68</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="67">
@@ -6074,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
         <v>0</v>
@@ -6155,31 +6155,31 @@
         <v>99.51000000000001</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>102.31</v>
+        <v>109.85</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>26.52</v>
+        <v>107.82</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>202.39</v>
+        <v>126</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>127.16</v>
+        <v>122.35</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>114.12</v>
+        <v>101</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>93.45</v>
+        <v>79.61</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>63.48</v>
+        <v>54.46</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>63.68</v>
+        <v>54.15</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>47.8</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="70">
@@ -6323,31 +6323,31 @@
         <v>4.68</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>5.22</v>
+        <v>4.72</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>3.85</v>
+        <v>4.96</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>5.75</v>
+        <v>3.53</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>5.85</v>
+        <v>5.51</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>5.36</v>
+        <v>6.16</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>4.49</v>
+        <v>3.58</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="72">
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
         <v>0</v>
@@ -6575,31 +6575,31 @@
         <v>97.87</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>100.61</v>
+        <v>108.38</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>25.25</v>
+        <v>106.04</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>200.59</v>
+        <v>125.1</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>125.32</v>
+        <v>120.46</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>112.35</v>
+        <v>98.69</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>91.91</v>
+        <v>78.3</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>62.44</v>
+        <v>53.51</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>62.44</v>
+        <v>53.09</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>46.72</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="75">
@@ -6743,31 +6743,31 @@
         <v>3.03</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.58</v>
+        <v>3.18</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>3.94</v>
+        <v>2.63</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>4.01</v>
+        <v>3.61</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>2.94</v>
+        <v>2.27</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="77">
@@ -6914,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T78" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
         <v>0</v>
@@ -6995,31 +6995,31 @@
         <v>94.83</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>97.09</v>
+        <v>105.13</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>22.67</v>
+        <v>102.86</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>196.65</v>
+        <v>122.47</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>121.31</v>
+        <v>116.84</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>108.75</v>
+        <v>94.84</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>88.97</v>
+        <v>76.03</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>60.69</v>
+        <v>52.06</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>60.69</v>
+        <v>51.61</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>45.27</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="80">
@@ -7334,10 +7334,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
         <v>0</v>
@@ -7415,31 +7415,31 @@
         <v>90.92</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>98.56999999999999</v>
+        <v>105.98</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>22.43</v>
+        <v>102.55</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>187.51</v>
+        <v>121.14</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>112.22</v>
+        <v>114.33</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>107.78</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>89.23999999999999</v>
+        <v>77.58</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>62.44</v>
+        <v>53.84</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>64.22</v>
+        <v>54.49</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>47.55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85">
@@ -7583,31 +7583,31 @@
         <v>-3.91</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>1.48</v>
+        <v>0.85</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-9.130000000000001</v>
+        <v>-1.33</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-9.09</v>
+        <v>-2.52</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-0.97</v>
+        <v>0.09</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>0.27</v>
+        <v>1.55</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>3.53</v>
+        <v>2.89</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="87">
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U88" s="3" t="n">
         <v>0</v>
@@ -7835,31 +7835,31 @@
         <v>89.20999999999999</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>91.08</v>
+        <v>99.08</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>18.88</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>194.08</v>
+        <v>120.07</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>118.24</v>
+        <v>114.1</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>104.77</v>
+        <v>90.84</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>85.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>58.02</v>
+        <v>49.82</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>57.64</v>
+        <v>49.24</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>43.74</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="90">
@@ -8003,31 +8003,31 @@
         <v>-5.62</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.01</v>
+        <v>-6.04</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-3.79</v>
+        <v>-4.9</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.4</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-3.07</v>
+        <v>-2.74</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-3.98</v>
+        <v>-4</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.67</v>
+        <v>-3.13</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.67</v>
+        <v>-2.24</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-3.05</v>
+        <v>-2.36</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
@@ -8174,10 +8174,10 @@
         <v>0</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>-55.4</v>
+        <v>0</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>77.47</v>
+        <v>0</v>
       </c>
       <c r="U93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-11T17:09:36</t>
+          <t>CreatedAt: 2026-10-11T20:14:20</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>33.12</v>
+        <v>43.32</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>32.93</v>
+        <v>49.79</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>33.78</v>
+        <v>43.81</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>33.35</v>
+        <v>47.98</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>34.08</v>
+        <v>49</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>39.83</v>
+        <v>47</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>58.78</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>68.06</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>45.64</v>
+        <v>55.97</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>45.81</v>
+        <v>59.4</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>58.41</v>
+        <v>60.1</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>65</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>71.83</v>
+        <v>58.37</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>87.28</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>90.66</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>100.51</v>
+        <v>77.53</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>99</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>119.02</v>
+        <v>98.63</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>113.55</v>
+        <v>96.75</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>91.37</v>
+        <v>87.44</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>73.39</v>
+        <v>73.56</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>50.06</v>
+        <v>59.62</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>49.72</v>
+        <v>68.78</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>36.05</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="5">
@@ -758,52 +758,52 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>-4.92</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0</v>
+        <v>-12.6</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-11.8</v>
+        <v>-13.53</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-15.56</v>
+        <v>-26.83</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-4.85</v>
+        <v>-14.46</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
+        <v>-31.76</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>-34.58</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>-30.51</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0</v>
+        <v>-47.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0</v>
+        <v>-48.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0</v>
+        <v>-48.79</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-51.05</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0</v>
+        <v>-38.06</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0</v>
+        <v>-18.86</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-36.45</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="6">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.95</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.66</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.62</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.59</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0.7</v>
+        <v>-1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-1.37</v>
+        <v>-2.07</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-1.79</v>
+        <v>-2.59</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-3.09</v>
+        <v>-2.72</v>
       </c>
       <c r="N6" s="3" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>-3.38</v>
       </c>
-      <c r="O6" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-4.17</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>-3.45</v>
-      </c>
       <c r="U6" s="3" t="n">
-        <v>-3.29</v>
+        <v>-3.93</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.47</v>
+        <v>-3.6</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.64</v>
+        <v>-3.01</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-2</v>
+        <v>-1.96</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.89</v>
+        <v>-2.53</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="7">
@@ -1004,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>32.48</v>
+        <v>44.63</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>33.07</v>
+        <v>51.56</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>33.98</v>
+        <v>45.56</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>33.25</v>
+        <v>49.55</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>34.32</v>
+        <v>50.55</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>39.75</v>
+        <v>48.63</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>57.73</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>66.88</v>
+        <v>69.34</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>45.82</v>
+        <v>57.05</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>45.98</v>
+        <v>60.03</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>59.51</v>
+        <v>61.55</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>66.02</v>
+        <v>72.92</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>72.34</v>
+        <v>59.87</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>88.29000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>91.54000000000001</v>
+        <v>81.64</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>100.6</v>
+        <v>79.88</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>99.29000000000001</v>
+        <v>100.74</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>121.74</v>
+        <v>101.56</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>115</v>
+        <v>98.47</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>92.34999999999999</v>
+        <v>90.19</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>73.67</v>
+        <v>75.89</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>50.45</v>
+        <v>61.1</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>50.59</v>
+        <v>72.28</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>36.98</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="10">
@@ -1178,52 +1178,52 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>-4.92</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>-12.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-11.8</v>
+        <v>-13.53</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-15.56</v>
+        <v>-26.83</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-4.85</v>
+        <v>-14.46</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>-31.76</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>-34.58</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>-30.51</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>-47.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>-48.2</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0</v>
+        <v>-48.79</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0</v>
+        <v>-51.05</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0</v>
+        <v>-38.06</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0</v>
+        <v>-18.86</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-36.45</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>0</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="11">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.97</v>
+        <v>0.36</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.03</v>
+        <v>1.09</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.96</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.36</v>
+        <v>0.83</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.2</v>
+        <v>0.86</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.42</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-1.19</v>
+        <v>-0.99</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.96</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-2</v>
+        <v>-1.28</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-2.37</v>
+        <v>-0.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-2.78</v>
+        <v>-1.41</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.83</v>
+        <v>0.22</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-4.53</v>
+        <v>-1.32</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-3.57</v>
+        <v>-0.89</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.45</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.21</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2.49</v>
+        <v>-0.85</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-2.36</v>
+        <v>-0.68</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.48</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-1.01</v>
+        <v>0.98</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="12">
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>32.48</v>
+        <v>110.89</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>33.07</v>
+        <v>110.69</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>33.98</v>
+        <v>2000</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>33.25</v>
+        <v>49.55</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>34.32</v>
+        <v>50.55</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>39.75</v>
+        <v>48.63</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>47.68</v>
+        <v>75.28</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>38.62</v>
+        <v>69.34</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>38.62</v>
+        <v>61.97</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>38.62</v>
+        <v>72.62</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>38.62</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>38.62</v>
+        <v>114.34</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>38.62</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>38.62</v>
+        <v>111.08</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>54.32</v>
+        <v>116.22</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>25.42</v>
+        <v>110.83</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>10.66</v>
+        <v>495.9</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>121.74</v>
+        <v>1700</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>115</v>
+        <v>1796.73</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>92.34999999999999</v>
+        <v>1700</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>9.32</v>
+        <v>113.98</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>50.45</v>
+        <v>116.88</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>50.59</v>
+        <v>2000</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>36.98</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="15">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>66.25</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>59.13</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>1954.4</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0</v>
@@ -1592,55 +1592,55 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-10.05</v>
+        <v>3.68</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-28.25</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-7.2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>-7.36</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-32.76</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-42.96</v>
+        <v>14.49</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-38.57</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-49.67</v>
+        <v>1.08</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>-37.22</v>
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-75.18000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-88.62</v>
+        <v>347.31</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>1550.24</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>1649.48</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>1558.76</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>-64.34999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>36.91</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>1891.16</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.97</v>
+        <v>0.36</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.03</v>
+        <v>1.14</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.03</v>
+        <v>0.96</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.36</v>
+        <v>0.83</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.2</v>
+        <v>0.86</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.42</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-1.19</v>
+        <v>-0.99</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.61</v>
+        <v>-1.96</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.93</v>
+        <v>-1.28</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-2.37</v>
+        <v>0</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-2.78</v>
+        <v>-1.41</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.83</v>
+        <v>0.22</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-3.3</v>
+        <v>0</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-4.53</v>
+        <v>-1.32</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-3.57</v>
+        <v>-0.74</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.73</v>
+        <v>-0.45</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.84</v>
+        <v>-2.21</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-2.49</v>
+        <v>-0.85</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-2.36</v>
+        <v>-0.68</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.61</v>
+        <v>-0.48</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="17">
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.42</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>33.03</v>
+        <v>43.37</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>32.9</v>
+        <v>49.89</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33.71</v>
+        <v>43.94</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>33.35</v>
+        <v>48.08</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>34.12</v>
+        <v>49.05</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46.16</v>
+        <v>47</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>58.74</v>
+        <v>69.42</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>66.83</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>45.51</v>
+        <v>50.51</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>45.59</v>
+        <v>45.77</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>45.77</v>
+        <v>45.63</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>48.3</v>
+        <v>41.13</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>66.16</v>
+        <v>43.06</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>86.7</v>
+        <v>40.69</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>90.14</v>
+        <v>41</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>99.93000000000001</v>
+        <v>45.21</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>98.62</v>
+        <v>46.97</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>119.48</v>
+        <v>47.35</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>113.77</v>
+        <v>44.59</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>91.19</v>
+        <v>33.21</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>73.18000000000001</v>
+        <v>33.09</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>49.96</v>
+        <v>39.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>49.57</v>
+        <v>30.55</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>36.08</v>
+        <v>33.24</v>
       </c>
     </row>
     <row r="20">
@@ -2018,52 +2018,52 @@
         <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
+        <v>-10.09</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0</v>
+        <v>-25.81</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-24.18</v>
+        <v>-27.71</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-31.87</v>
+        <v>-54.97</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-9.93</v>
+        <v>-29.62</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0</v>
+        <v>-70.86</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0</v>
+        <v>-62.52</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0</v>
+        <v>-97.73999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0</v>
+        <v>-98.78</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0</v>
+        <v>-99.95999999999999</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0</v>
+        <v>-104.6</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>0</v>
+        <v>-77.98</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0</v>
+        <v>-38.65</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0</v>
+        <v>-74.68000000000001</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>0</v>
+        <v>-12.78</v>
       </c>
     </row>
     <row r="21">
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.91</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.53</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.53</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.54</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.61</v>
+        <v>-1.32</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0.66</v>
+        <v>-1.97</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-1.5</v>
+        <v>-2.36</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-2.01</v>
+        <v>-3.01</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-3.36</v>
+        <v>-3.01</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-3.77</v>
+        <v>-3.75</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-3.88</v>
+        <v>-3.05</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-4.42</v>
+        <v>-4.02</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-4.69</v>
+        <v>-4.36</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-5.2</v>
+        <v>-3.99</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-4.24</v>
+        <v>-4.63</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-2.99</v>
+        <v>-4.09</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.07</v>
+        <v>-4.91</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.27</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3.55</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.19</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.03</v>
+        <v>-2.53</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="22">
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>33.03</v>
+        <v>43.37</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>32.9</v>
+        <v>49.89</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>33.71</v>
+        <v>43.94</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>33.35</v>
+        <v>48.08</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>34.12</v>
+        <v>49.05</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>39.87</v>
+        <v>47</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>58.74</v>
+        <v>69.42</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>66.83</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>45.51</v>
+        <v>55.67</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>45.59</v>
+        <v>58.98</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>58.14</v>
+        <v>59.82</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>64.62</v>
+        <v>69.28</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>71.23999999999999</v>
+        <v>58.23</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>86.7</v>
+        <v>74</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>90.14</v>
+        <v>77.28</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>99.93000000000001</v>
+        <v>77.22</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>98.62</v>
+        <v>97</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>119.48</v>
+        <v>97.92</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>113.77</v>
+        <v>95.77</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>91.19</v>
+        <v>86.77</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>73.18000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>49.96</v>
+        <v>59.39</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>49.57</v>
+        <v>68.78</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>36.08</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="25">
@@ -2438,52 +2438,52 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0</v>
+        <v>-4.92</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0</v>
+        <v>-12.6</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-11.8</v>
+        <v>-13.53</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-15.56</v>
+        <v>-26.83</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-4.85</v>
+        <v>-14.46</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
+        <v>-31.76</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0</v>
+        <v>-34.58</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0</v>
+        <v>-30.51</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0</v>
+        <v>-47.7</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0</v>
+        <v>-48.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0</v>
+        <v>-48.79</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>-51.05</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0</v>
+        <v>-38.06</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>0</v>
+        <v>-18.86</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-36.45</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="26">
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.91</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.8</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.53</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.53</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.54</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.8</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.61</v>
+        <v>-1.32</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.66</v>
+        <v>-1.97</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-1.5</v>
+        <v>-2.36</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-2.01</v>
+        <v>-3.01</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-3.36</v>
+        <v>-3.01</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-3.77</v>
+        <v>-3.75</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-3.88</v>
+        <v>-3.05</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-4.42</v>
+        <v>-4.02</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-4.69</v>
+        <v>-4.36</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-5.2</v>
+        <v>-3.99</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-4.24</v>
+        <v>-4.63</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-2.99</v>
+        <v>-4.09</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.07</v>
+        <v>-4.91</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.27</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3.55</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.19</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.03</v>
+        <v>-2.53</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="27">
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>32.86</v>
+        <v>43.24</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>32.84</v>
+        <v>49.89</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>33.55</v>
+        <v>43.94</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>33.32</v>
+        <v>48.03</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>34.05</v>
+        <v>48.95</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>46.2</v>
+        <v>46.91</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>58.7</v>
+        <v>69.09</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>66.83</v>
+        <v>67.33</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>45.25</v>
+        <v>49.93</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>45.28</v>
+        <v>45.22</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>45.24</v>
+        <v>45.21</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>47.62</v>
+        <v>40.58</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>65.3</v>
+        <v>42.79</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>85.8</v>
+        <v>40.38</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>89.20999999999999</v>
+        <v>40.46</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>99.08</v>
+        <v>44.59</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>97.95999999999999</v>
+        <v>45.85</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>120.07</v>
+        <v>46.36</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>114.1</v>
+        <v>43.21</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>90.84</v>
+        <v>32.02</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>72.97</v>
+        <v>32.34</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>49.82</v>
+        <v>39.15</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>49.24</v>
+        <v>30.24</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>36.08</v>
+        <v>33.24</v>
       </c>
     </row>
     <row r="30">
@@ -2858,52 +2858,52 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>-10.09</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0</v>
+        <v>-25.81</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-24.18</v>
+        <v>-27.71</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-31.87</v>
+        <v>-54.97</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-9.93</v>
+        <v>-29.62</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0</v>
+        <v>-70.86</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0</v>
+        <v>-62.52</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0</v>
+        <v>-97.73999999999999</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>0</v>
+        <v>-98.78</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>0</v>
+        <v>-99.95999999999999</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>0</v>
+        <v>-104.6</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>0</v>
+        <v>-77.98</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0</v>
+        <v>-38.65</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>-74.68000000000001</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0</v>
+        <v>-12.78</v>
       </c>
     </row>
     <row r="31">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.04</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.8</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.53</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.58</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.64</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.89</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0.65</v>
+        <v>-1.66</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0.66</v>
+        <v>-2.42</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-1.76</v>
+        <v>-2.94</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-2.31</v>
+        <v>-3.55</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-3.89</v>
+        <v>-3.43</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-4.45</v>
+        <v>-4.3</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-4.74</v>
+        <v>-3.33</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-5.32</v>
+        <v>-4.32</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-5.62</v>
+        <v>-4.9</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.04</v>
+        <v>-4.61</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-4.9</v>
+        <v>-5.74</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.4</v>
+        <v>-5.08</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-2.74</v>
+        <v>-6.3</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4</v>
+        <v>-5.46</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.06</v>
+        <v>-4.3</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.24</v>
+        <v>-2.65</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.83</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="32">
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>0</v>
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>32.48</v>
+        <v>111.99</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>33.33</v>
+        <v>112.09</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>34.4</v>
+        <v>2000</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>33.39</v>
+        <v>50.79</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>34.7</v>
+        <v>51.98</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>40.03</v>
+        <v>50.26</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>49.23</v>
+        <v>77.44</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>41.85</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>40.11</v>
+        <v>63.86</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>40.26</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>43.82</v>
+        <v>77.28</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>44.7</v>
+        <v>117.75</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>44.46</v>
+        <v>76.19</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>46.14</v>
+        <v>114.72</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>60.4</v>
+        <v>119.94</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>34.9</v>
+        <v>113.51</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.78</v>
+        <v>500</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>144.76</v>
+        <v>1703.99</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>147.71</v>
+        <v>1800</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>93.53</v>
+        <v>1703.75</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>16.99</v>
+        <v>117</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>51.44</v>
+        <v>118.67</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>52.18</v>
+        <v>2000</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>37.96</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="35">
@@ -3254,13 +3254,13 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>66.25</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>59.13</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>1953.05</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -3272,55 +3272,55 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-9.039999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-25.43</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-6.48</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-6.63</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-29.48</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-38.66</v>
+        <v>14.49</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-34.71</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-44.7</v>
+        <v>1.08</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>-33.49</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-67.66</v>
+        <v>0.44</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-79.76000000000001</v>
+        <v>347.31</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>1550.24</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>0</v>
+        <v>1649.48</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>1558.76</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>-57.92</v>
+        <v>0.03</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>0</v>
+        <v>36.91</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>1888.11</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-0.97</v>
+        <v>1.46</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.27</v>
+        <v>2.28</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.45</v>
+        <v>2.49</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-0.2</v>
+        <v>2.18</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.35</v>
+        <v>2.39</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.08</v>
+        <v>2.46</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-1.07</v>
+        <v>3.02</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.21</v>
+        <v>1.64</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.42</v>
+        <v>0.89</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.58</v>
+        <v>3.41</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.79</v>
+        <v>0.46</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.27</v>
+        <v>3.86</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.72</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-2.56</v>
+        <v>1.36</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-1.32</v>
+        <v>3.36</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.74</v>
+        <v>3.54</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.23</v>
+        <v>1.05</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>-1.31</v>
+        <v>2.9</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-1.12</v>
+        <v>2.34</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.62</v>
+        <v>1.31</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.57</v>
+        <v>4.14</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.84</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="37">
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>20.55</v>
+        <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>33.12</v>
+        <v>43.32</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>32.93</v>
+        <v>49.79</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>33.78</v>
+        <v>43.81</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>33.35</v>
+        <v>47.98</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>34.08</v>
+        <v>49</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>39.83</v>
+        <v>47</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>58.78</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>68.06</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>45.64</v>
+        <v>55.97</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>45.81</v>
+        <v>59.4</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>58.41</v>
+        <v>60.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>65</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>71.83</v>
+        <v>58.37</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>87.28</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>90.66</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>100.51</v>
+        <v>77.53</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>99</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>119.02</v>
+        <v>98.63</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>113.55</v>
+        <v>96.75</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>91.37</v>
+        <v>87.44</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>73.39</v>
+        <v>73.56</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>50.06</v>
+        <v>59.62</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>49.72</v>
+        <v>68.78</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>36.05</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="40">
@@ -3698,52 +3698,52 @@
         <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>-4.92</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>-12.6</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-11.8</v>
+        <v>-13.53</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-15.56</v>
+        <v>-26.83</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-4.85</v>
+        <v>-14.46</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>-31.76</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>-34.58</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>-30.51</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>-47.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>-48.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>0</v>
+        <v>-48.79</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>-51.05</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>0</v>
+        <v>-38.06</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>0</v>
+        <v>-18.86</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-36.45</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="41">
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-0.33</v>
+        <v>-0.95</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.9</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.66</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.62</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.59</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.8</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.7</v>
+        <v>-1.7</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.37</v>
+        <v>-2.07</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-1.79</v>
+        <v>-2.59</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-3.09</v>
+        <v>-2.72</v>
       </c>
       <c r="N41" s="3" t="n">
+        <v>-3.56</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="T41" s="3" t="n">
         <v>-3.38</v>
       </c>
-      <c r="O41" s="3" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>-4.17</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>-4.62</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>-3.86</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>-3.45</v>
-      </c>
       <c r="U41" s="3" t="n">
-        <v>-3.29</v>
+        <v>-3.93</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.47</v>
+        <v>-3.6</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.64</v>
+        <v>-3.01</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-2</v>
+        <v>-1.96</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.89</v>
+        <v>-2.53</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="42">
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>33.52</v>
+        <v>44.23</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>33.23</v>
+        <v>50.53</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>34.02</v>
+        <v>44.38</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>33.62</v>
+        <v>48.61</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>34.39</v>
+        <v>49.44</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>40.19</v>
+        <v>47.75</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>59.43</v>
+        <v>70.81</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>69.34</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>46.83</v>
+        <v>62.4</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>47.17</v>
+        <v>73.92</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>72.72</v>
+        <v>75.3</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>83.19</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>79.18000000000001</v>
+        <v>74.91</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>89.95</v>
+        <v>109.23</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>93.62</v>
+        <v>115.87</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>103.68</v>
+        <v>112.28</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>101.94</v>
+        <v>150.54</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>120.66</v>
+        <v>152.04</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>116.03</v>
+        <v>150.83</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>94.56</v>
+        <v>143.23</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>75.28</v>
+        <v>115.09</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>51.44</v>
+        <v>80.69</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>51.04</v>
+        <v>107.86</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>36.91</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0.09</v>
-      </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.67</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-0.58</v>
+        <v>-1.05</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.75</v>
+        <v>-1.28</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.82</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.17</v>
+        <v>-0.55</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.22</v>
+        <v>-0.35</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.92</v>
+        <v>1.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.28</v>
+        <v>1.15</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.75</v>
+        <v>0.46</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.62</v>
+        <v>0.24</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.22</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="47">
@@ -4364,10 +4364,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>34.1</v>
+        <v>45.09</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>33.74</v>
+        <v>51.51</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.4</v>
+        <v>45.14</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>34.1</v>
+        <v>49.45</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>34.88</v>
+        <v>50.44</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>40.93</v>
+        <v>48.82</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>59.92</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>68.08</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>47.97</v>
+        <v>64.45</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>48.66</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>75.5</v>
+        <v>78.31</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>87.34999999999999</v>
+        <v>103.37</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>83.39</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>94.42</v>
+        <v>113.53</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>98.37</v>
+        <v>120.31</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>109.05</v>
+        <v>110.07</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>101.74</v>
+        <v>146.26</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>125.48</v>
+        <v>150.82</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>119.72</v>
+        <v>145.82</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>97.47</v>
+        <v>146.48</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>78.45999999999999</v>
+        <v>119.03</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>53.4</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>52.66</v>
+        <v>110.51</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>37.85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.45</v>
+        <v>0.68</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.51</v>
+        <v>0.84</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.58</v>
+        <v>2.26</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.59</v>
+        <v>1.42</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.96</v>
+        <v>1.48</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1.07</v>
+        <v>1.68</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>2.19</v>
+        <v>1.96</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.41</v>
+        <v>3.51</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.42</v>
+        <v>2.67</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>3.54</v>
+        <v>4.09</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>3.93</v>
+        <v>-1.65</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.12</v>
+        <v>-3.07</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>3.01</v>
+        <v>0.6</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>2.87</v>
+        <v>-3.65</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.63</v>
+        <v>4.39</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>2.43</v>
+        <v>4.4</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.33</v>
+        <v>2.49</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.05</v>
+        <v>2.76</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.72</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="52">
@@ -4784,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>34.96</v>
+        <v>46.46</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>34.48</v>
+        <v>53.3</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>35.47</v>
+        <v>46.76</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>35.02</v>
+        <v>51.16</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>35.98</v>
+        <v>52.25</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>41.96</v>
+        <v>50.37</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>61.46</v>
+        <v>74.47</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>69.41</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>49.33</v>
+        <v>66.42</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>50.15</v>
+        <v>77.37</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>74.95</v>
+        <v>79.78</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>83.94</v>
+        <v>102.42</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>79.73</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>90.67</v>
+        <v>111.79</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>94.08</v>
+        <v>117.87</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>105.98</v>
+        <v>110.28</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>101.54</v>
+        <v>106.17</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>119.25</v>
+        <v>82.28</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>112.13</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>93.16</v>
+        <v>72.03</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>76.56999999999999</v>
+        <v>110.86</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>53.51</v>
+        <v>82.42</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>54.32</v>
+        <v>112.12</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>39.08</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="55">
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>0</v>
+        <v>-36.6</v>
       </c>
       <c r="T55" s="3" t="n">
-        <v>0</v>
+        <v>-57.84</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>0</v>
+        <v>-58.54</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>0</v>
+        <v>-61.26</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.41</v>
+        <v>2.61</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.44</v>
+        <v>2.56</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.62</v>
+        <v>2.66</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>2.12</v>
+        <v>3.72</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1.92</v>
+        <v>3.98</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>2.32</v>
+        <v>3.45</v>
       </c>
       <c r="L56" s="3" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M56" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="N56" s="3" t="n">
         <v>2.56</v>
       </c>
-      <c r="M56" s="3" t="n">
+      <c r="O56" s="3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q56" s="3" t="n">
         <v>1.65</v>
       </c>
-      <c r="N56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="3" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="P56" s="3" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="Q56" s="3" t="n">
-        <v>-0.75</v>
-      </c>
       <c r="R56" s="3" t="n">
-        <v>0.85</v>
+        <v>-1.43</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-1.32</v>
+        <v>-6.57</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-3.22</v>
+        <v>-10.09</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-4.71</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.68</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>0.54</v>
+        <v>-3.77</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>2.72</v>
+        <v>4.37</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="57">
@@ -5204,10 +5204,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>34.63</v>
+        <v>45.79</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>34.3</v>
+        <v>52.25</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>35.07</v>
+        <v>45.89</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>34.66</v>
+        <v>50.16</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>35.49</v>
+        <v>50.91</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>41.48</v>
+        <v>49.28</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>60.89</v>
+        <v>73.16</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>68.92</v>
+        <v>71.69</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>48.57</v>
+        <v>64.64</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>49.06</v>
+        <v>76.58</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>75.65000000000001</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>86.54000000000001</v>
+        <v>102.21</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>82.53</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>93.73999999999999</v>
+        <v>113.41</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>97.26000000000001</v>
+        <v>120.06</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>107.6</v>
+        <v>116.25</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>105.5</v>
+        <v>155.56</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>124.21</v>
+        <v>156.96</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>119.84</v>
+        <v>155.86</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>98.18000000000001</v>
+        <v>148.32</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>119.16</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>53.23</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>52.88</v>
+        <v>111.54</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>38.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.55</v>
+        <v>2.41</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.42</v>
+        <v>1.94</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="M61" s="3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N61" s="3" t="n">
         <v>2.35</v>
       </c>
-      <c r="N61" s="3" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O61" s="3" t="n">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2.62</v>
+        <v>3.63</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>2.43</v>
+        <v>3.84</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2.47</v>
+        <v>4.53</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>2.64</v>
+        <v>6.22</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.74</v>
+        <v>6.75</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>3</v>
+        <v>6.39</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.34</v>
+        <v>6.23</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.87</v>
+        <v>4.53</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.17</v>
+        <v>3.09</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.27</v>
+        <v>3.79</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.07</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="62">
@@ -5624,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>35.07</v>
+        <v>46.41</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>34.73</v>
+        <v>52.91</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>35.51</v>
+        <v>46.46</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>35.1</v>
+        <v>50.79</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>35.94</v>
+        <v>51.54</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>42.04</v>
+        <v>49.95</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>61.56</v>
+        <v>74.23</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>69.55</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>49.33</v>
+        <v>65.59</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>49.83</v>
+        <v>77.69</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>77</v>
+        <v>79.28</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>87.98999999999999</v>
+        <v>103.8</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>83.91</v>
+        <v>79.06</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>95.41</v>
+        <v>115.19</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>98.89</v>
+        <v>122.21</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>109.51</v>
+        <v>118.22</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>107.37</v>
+        <v>158.19</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>126.52</v>
+        <v>159.29</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>121.84</v>
+        <v>158.33</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>99.52</v>
+        <v>150.68</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>79.03</v>
+        <v>120.92</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>54.06</v>
+        <v>84.77</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>53.64</v>
+        <v>113.18</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>38.76</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1.61</v>
+        <v>2.13</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.51</v>
+        <v>2.18</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.21</v>
+        <v>3.49</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.06</v>
+        <v>2.98</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>2.24</v>
+        <v>3.11</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>3.7</v>
+        <v>2.93</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.94</v>
+        <v>3.32</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>4.29</v>
+        <v>5.41</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>4.05</v>
+        <v>5.99</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>4.38</v>
+        <v>6.5</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>4.51</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>4.05</v>
+        <v>9.08</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.68</v>
+        <v>8.59</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>3</v>
+        <v>6.29</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2</v>
+        <v>4.32</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.04</v>
+        <v>5.43</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.63</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="67">
@@ -6044,10 +6044,10 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>35.59</v>
+        <v>47.1</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>35.25</v>
+        <v>53.75</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>36.04</v>
+        <v>47.15</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>35.66</v>
+        <v>51.6</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>36.47</v>
+        <v>52.14</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>42.62</v>
+        <v>50.58</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>62.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>70.15000000000001</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>49.96</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>50.52</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>89.02</v>
+        <v>104.56</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>84.98</v>
+        <v>79.72</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>96.31999999999999</v>
+        <v>116.41</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>99.51000000000001</v>
+        <v>123.24</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>109.85</v>
+        <v>119.48</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>107.82</v>
+        <v>160.23</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>126</v>
+        <v>161.62</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>122.35</v>
+        <v>160.93</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>101</v>
+        <v>152.62</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>79.61</v>
+        <v>122.57</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>54.46</v>
+        <v>86.31</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>54.15</v>
+        <v>114.75</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>39.25</v>
+        <v>49.79</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.14</v>
+        <v>2.83</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.19</v>
+        <v>3.06</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.09</v>
+        <v>2.69</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.07</v>
+        <v>2.99</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.85</v>
+        <v>4.36</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>2.66</v>
+        <v>3.67</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>2.93</v>
+        <v>3.84</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4.6</v>
+        <v>3.51</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>5.07</v>
+        <v>4.71</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>5.01</v>
+        <v>3.99</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>5.2</v>
+        <v>6.64</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>4.68</v>
+        <v>7.02</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>4.72</v>
+        <v>7.77</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>4.96</v>
+        <v>10.55</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.53</v>
+        <v>11.13</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>5.51</v>
+        <v>10.73</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>6.16</v>
+        <v>10.37</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.58</v>
+        <v>7.84</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.4</v>
+        <v>5.41</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.55</v>
+        <v>7</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.12</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="72">
@@ -6410,22 +6410,22 @@
         <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="Y72" s="3" t="n">
         <v>0</v>
@@ -6464,10 +6464,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>34.63</v>
+        <v>45.84</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>34.3</v>
+        <v>52.31</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>35.07</v>
+        <v>45.93</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>34.7</v>
+        <v>50.21</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>35.49</v>
+        <v>50.96</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>41.52</v>
+        <v>49.38</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>60.98</v>
+        <v>73.39</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>68.92</v>
+        <v>71.77</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>48.62</v>
+        <v>64.78</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>49.32</v>
+        <v>76.73</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>76.12</v>
+        <v>78.47</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>87.08</v>
+        <v>102.84</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>83.13</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>94.42</v>
+        <v>113.76</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>97.87</v>
+        <v>120.44</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>108.38</v>
+        <v>116.49</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>106.04</v>
+        <v>156.04</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>125.1</v>
+        <v>157.46</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>120.46</v>
+        <v>156.35</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>98.69</v>
+        <v>148.94</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>78.3</v>
+        <v>119.66</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>53.51</v>
+        <v>83.8</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>53.09</v>
+        <v>111.89</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>38.32</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>1.64</v>
+        <v>2.64</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>1.42</v>
+        <v>2.01</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.82</v>
+        <v>2.12</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>3.13</v>
+        <v>2.98</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.16</v>
+        <v>2.5</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>3.03</v>
+        <v>4.22</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>3.25</v>
+        <v>4.78</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>3.18</v>
+        <v>6.71</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.63</v>
+        <v>7.24</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>3.61</v>
+        <v>6.88</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.85</v>
+        <v>6.85</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>2.27</v>
+        <v>5.03</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.44</v>
+        <v>3.35</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.49</v>
+        <v>4.14</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.19</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="77">
@@ -6884,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>33.46</v>
+        <v>44.28</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>33.07</v>
+        <v>50.68</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>33.95</v>
+        <v>44.46</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>33.59</v>
+        <v>48.61</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>34.36</v>
+        <v>49.58</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>40.11</v>
+        <v>47.8</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>59.35</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>67.48999999999999</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>47.01</v>
+        <v>62.96</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>47.59</v>
+        <v>74.59</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>73.31</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>83.94</v>
+        <v>99.86</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>79.97</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>91.12</v>
+        <v>109.78</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>94.83</v>
+        <v>116.22</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>105.13</v>
+        <v>111.72</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>102.86</v>
+        <v>149.33</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>122.47</v>
+        <v>150.21</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>116.84</v>
+        <v>149.47</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>94.84</v>
+        <v>142.09</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>76.03</v>
+        <v>114.63</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>52.06</v>
+        <v>80.44</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>51.61</v>
+        <v>107.75</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>37.13</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="80">
@@ -7304,10 +7304,10 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>34.81</v>
+        <v>46.31</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>34.27</v>
+        <v>53.35</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>35.47</v>
+        <v>46.66</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>34.91</v>
+        <v>51.22</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>36.09</v>
+        <v>52.42</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>41.96</v>
+        <v>50.63</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>61.51</v>
+        <v>74.55</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>69.28</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>49.08</v>
+        <v>66.42</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>49.99</v>
+        <v>77.37</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>72.87</v>
+        <v>79.37</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>81.42</v>
+        <v>102.31</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>77.26000000000001</v>
+        <v>78.16</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>87.7</v>
+        <v>111.45</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>90.92</v>
+        <v>118.23</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>105.98</v>
+        <v>111.38</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>102.55</v>
+        <v>104.41</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>121.14</v>
+        <v>81.37</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>114.33</v>
+        <v>80.63</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>94.93000000000001</v>
+        <v>71.53</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>77.58</v>
+        <v>110.22</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>53.84</v>
+        <v>83.36</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>54.49</v>
+        <v>113.18</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>39</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="85">
@@ -7502,16 +7502,16 @@
         <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>0</v>
+        <v>-36.6</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>0</v>
+        <v>-57.84</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>0</v>
+        <v>-58.54</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>0</v>
+        <v>-61.26</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1.2</v>
+        <v>2.67</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.33</v>
+        <v>2.61</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1.73</v>
+        <v>2.83</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>1.78</v>
+        <v>4.06</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>2.06</v>
+        <v>3.45</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-0.44</v>
+        <v>3.02</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-2.7</v>
+        <v>2.42</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-3.42</v>
+        <v>1.67</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-3.91</v>
+        <v>2.01</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.85</v>
+        <v>-0.33</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-0.31</v>
+        <v>-8.32</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-1.33</v>
+        <v>-11</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-2.52</v>
+        <v>-10.3</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>0.09</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>1.55</v>
+        <v>-4.41</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.78</v>
+        <v>2.92</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.89</v>
+        <v>5.43</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.87</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="87">
@@ -7724,10 +7724,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>0</v>
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>32.86</v>
+        <v>43.24</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>32.84</v>
+        <v>49.89</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>33.55</v>
+        <v>43.94</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>33.32</v>
+        <v>48.03</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>34.05</v>
+        <v>48.95</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>46.2</v>
+        <v>46.86</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>58.7</v>
+        <v>69.09</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>66.83</v>
+        <v>67.33</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>45.25</v>
+        <v>55.1</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>45.28</v>
+        <v>58.44</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>57.61</v>
+        <v>59.4</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>63.93</v>
+        <v>68.72</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>70.38</v>
+        <v>57.95</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>85.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>89.20999999999999</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>99.08</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>97.95999999999999</v>
+        <v>95.89</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>120.07</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>114.1</v>
+        <v>94.38</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>90.84</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>72.90000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>49.82</v>
+        <v>58.94</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>49.24</v>
+        <v>68.47</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>36.08</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="90">
@@ -7898,52 +7898,52 @@
         <v>0</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0</v>
+        <v>-4.92</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0</v>
+        <v>-12.6</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-11.8</v>
+        <v>-13.53</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-15.56</v>
+        <v>-26.83</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-4.85</v>
+        <v>-14.46</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>0</v>
+        <v>-31.76</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0</v>
+        <v>-34.58</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>0</v>
+        <v>-30.51</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>0</v>
+        <v>-47.7</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>0</v>
+        <v>-48.2</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>0</v>
+        <v>-48.79</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>0</v>
+        <v>-51.05</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>0</v>
+        <v>-38.06</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>0</v>
+        <v>-18.86</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>0</v>
+        <v>-36.45</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>0</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="91">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.04</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.8</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.53</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.58</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.64</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.65</v>
+        <v>-1.66</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-0.66</v>
+        <v>-2.42</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-1.76</v>
+        <v>-2.94</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-2.31</v>
+        <v>-3.55</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-3.89</v>
+        <v>-3.43</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-4.45</v>
+        <v>-4.3</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-4.74</v>
+        <v>-3.33</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-5.32</v>
+        <v>-4.42</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-5.62</v>
+        <v>-4.9</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.04</v>
+        <v>-4.61</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-4.9</v>
+        <v>-5.74</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.4</v>
+        <v>-5.08</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-2.74</v>
+        <v>-6.3</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4</v>
+        <v>-5.46</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.24</v>
+        <v>-2.65</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.36</v>
+        <v>-2.83</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.05</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="92">
@@ -8057,7 +8057,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -8144,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>15.45</v>
+        <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>25.77</v>
+        <v>0</v>
       </c>
       <c r="K93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-11T20:14:20</t>
+          <t>CreatedAt: 2026-10-12T03:12:23</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>43.32</v>
+        <v>51.44</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>49.79</v>
+        <v>53.3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>43.81</v>
+        <v>45.38</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>47.98</v>
+        <v>46.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>49</v>
+        <v>55.13</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>47</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>69.48999999999999</v>
+        <v>98.62</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>68.06</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>55.97</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>59.4</v>
+        <v>68.47</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>60.1</v>
+        <v>85.77</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>58.37</v>
+        <v>74.52</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>74.20999999999999</v>
+        <v>90.12</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>77.48999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>77.53</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>97.70999999999999</v>
+        <v>135.01</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>98.63</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>96.75</v>
+        <v>70.91</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>87.44</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>73.56</v>
+        <v>76.52</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>59.62</v>
+        <v>41.26</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>68.78</v>
+        <v>75.94</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>39.69</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="5">
@@ -758,52 +758,52 @@
         <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-4.92</v>
+        <v>-17.05</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-12.6</v>
+        <v>-22.96</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-13.53</v>
+        <v>-49.64</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-26.83</v>
+        <v>-45.28</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-14.46</v>
+        <v>-28.42</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-31.76</v>
+        <v>-44.76</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-34.58</v>
+        <v>-44.97</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-30.51</v>
+        <v>-46.84</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-47.7</v>
+        <v>-14.41</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-48.2</v>
+        <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-48.79</v>
+        <v>-18.96</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-51.05</v>
+        <v>-19.42</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-38.06</v>
+        <v>-29.72</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-18.86</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-36.45</v>
+        <v>-14.85</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-6.24</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="6">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.23</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.33</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.66</v>
+        <v>-1.09</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.97</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-1.25</v>
+        <v>-2.17</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-1.7</v>
+        <v>-2.31</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-2.59</v>
+        <v>-3.66</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-2.72</v>
+        <v>-5.55</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-3.56</v>
+        <v>-5.67</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-2.91</v>
+        <v>-4.94</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-3.81</v>
+        <v>-5.66</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-4.15</v>
+        <v>-5.82</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-3.67</v>
+        <v>-5.98</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.93</v>
+        <v>-4.93</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.38</v>
+        <v>-2.68</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.93</v>
+        <v>-2.79</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.6</v>
+        <v>-2.64</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-3.01</v>
+        <v>-3.29</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.11</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.53</v>
+        <v>-1.93</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="7">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="9">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>44.63</v>
+        <v>52.36</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>51.56</v>
+        <v>55.4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>45.56</v>
+        <v>47.23</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>49.55</v>
+        <v>48</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>50.55</v>
+        <v>56.29</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>48.63</v>
+        <v>73.36</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>100.89</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>69.34</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>57.05</v>
+        <v>68.67</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>60.03</v>
+        <v>68.47</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>61.55</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>72.92</v>
+        <v>90.23</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>59.87</v>
+        <v>75.91</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>78.23999999999999</v>
+        <v>94.39</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>81.64</v>
+        <v>94.92</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>79.88</v>
+        <v>98.39</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>100.74</v>
+        <v>138.11</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>101.56</v>
+        <v>100.93</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>98.47</v>
+        <v>72.05</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>90.19</v>
+        <v>67.28</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>75.89</v>
+        <v>78.84</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>61.1</v>
+        <v>42.04</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>72.28</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.28</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="10">
@@ -1178,52 +1178,52 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-4.92</v>
+        <v>-17.05</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-12.6</v>
+        <v>-22.96</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-13.53</v>
+        <v>-49.64</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-26.83</v>
+        <v>-45.28</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-14.46</v>
+        <v>-28.42</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-31.76</v>
+        <v>-44.76</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-34.58</v>
+        <v>-44.97</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-30.51</v>
+        <v>-46.84</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-47.7</v>
+        <v>-14.41</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>-48.2</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-48.79</v>
+        <v>-18.96</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-51.05</v>
+        <v>-19.42</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-38.06</v>
+        <v>-29.72</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-18.86</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-36.45</v>
+        <v>-14.85</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-6.24</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="11">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.09</v>
+        <v>0.76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.96</v>
+        <v>0.06</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.83</v>
+        <v>-0.29</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.86</v>
+        <v>0.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.42</v>
+        <v>-1.17</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.99</v>
+        <v>-2.49</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.96</v>
+        <v>-3.66</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.28</v>
+        <v>-3.97</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.1</v>
+        <v>-2.03</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.41</v>
+        <v>-3.55</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.22</v>
+        <v>-1.39</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.32</v>
+        <v>-3.05</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.83</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.45</v>
+        <v>-1.01</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-2.21</v>
+        <v>-1.64</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.04</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.98</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.34</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.67</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="12">
@@ -1472,10 +1472,10 @@
         <v>0</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="14">
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>110.89</v>
+        <v>52.36</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>110.69</v>
+        <v>59.42</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2000</v>
+        <v>60.09</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>49.55</v>
+        <v>267.17</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>50.55</v>
+        <v>56.29</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>48.63</v>
+        <v>73.36</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>75.28</v>
+        <v>100.89</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>69.34</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>61.97</v>
+        <v>85.72</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>72.62</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>75.06999999999999</v>
+        <v>137</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>114.34</v>
+        <v>135.52</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>74.31999999999999</v>
+        <v>104.34</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>111.08</v>
+        <v>139.15</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>116.22</v>
+        <v>139.89</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>110.83</v>
+        <v>871.65</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>495.9</v>
+        <v>495.65</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1700</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1796.73</v>
+        <v>1700</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>1700</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>113.98</v>
+        <v>108.56</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>116.88</v>
+        <v>129.49</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>2000</v>
+        <v>119.42</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>47.56</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="15">
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>66.25</v>
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>59.13</v>
+        <v>3.96</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1954.4</v>
+        <v>12.86</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>219.12</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1607,40 +1607,40 @@
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>14.49</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0.44</v>
+        <v>726.4299999999999</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>347.31</v>
+        <v>342.99</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>1550.24</v>
+        <v>1598.97</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>1649.48</v>
+        <v>1608.99</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>1558.76</v>
+        <v>1613.22</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>36.91</v>
+        <v>87.45</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1891.16</v>
+        <v>26.03</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.36</v>
+        <v>-0.31</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.14</v>
+        <v>0.76</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.96</v>
+        <v>0.06</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.83</v>
+        <v>-0.29</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.86</v>
+        <v>0.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0.42</v>
+        <v>-1.17</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-0.99</v>
+        <v>-2.49</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.96</v>
+        <v>-3.66</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.28</v>
+        <v>-3.97</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-1.41</v>
+        <v>-3.55</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.22</v>
+        <v>-1.39</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-1.32</v>
+        <v>-3.05</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.74</v>
+        <v>-1.68</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.91</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-2.21</v>
+        <v>-1.64</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.95</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.68</v>
+        <v>-0.98</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.34</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1.09</v>
+        <v>0.67</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.71</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="17">
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="19">
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>43.37</v>
+        <v>51.34</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>49.89</v>
+        <v>53.3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>43.94</v>
+        <v>45.47</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>48.08</v>
+        <v>46.45</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>49.05</v>
+        <v>55.03</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>47</v>
+        <v>72.14</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>69.42</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>50.51</v>
+        <v>49.8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>45.77</v>
+        <v>43.87</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>45.63</v>
+        <v>33.06</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>41.13</v>
+        <v>38.59</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>43.06</v>
+        <v>44.22</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>40.69</v>
+        <v>42.91</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>41</v>
+        <v>42.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>45.21</v>
+        <v>45.64</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>46.97</v>
+        <v>119.03</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>47.35</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>44.59</v>
+        <v>50.33</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>33.21</v>
+        <v>44.82</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>33.09</v>
+        <v>44.73</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>39.6</v>
+        <v>41.06</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>30.55</v>
+        <v>60.23</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>33.24</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="20">
@@ -2018,52 +2018,52 @@
         <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-10.09</v>
+        <v>-34.93</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-25.81</v>
+        <v>-47.03</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-27.71</v>
+        <v>-101.71</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-54.97</v>
+        <v>-92.78</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-29.62</v>
+        <v>-58.24</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-65.06999999999999</v>
+        <v>-91.70999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-70.86</v>
+        <v>-92.14</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-62.52</v>
+        <v>-95.98</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-97.73999999999999</v>
+        <v>-29.52</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>-98.78</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-99.95999999999999</v>
+        <v>-38.85</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-104.6</v>
+        <v>-39.79</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-77.98</v>
+        <v>-60.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-38.65</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-74.68000000000001</v>
+        <v>-30.43</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-12.78</v>
+        <v>-45.36</v>
       </c>
     </row>
     <row r="21">
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.33</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.33</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.53</v>
+        <v>-1</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.93</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.54</v>
+        <v>-1.21</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.51</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.36</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-1.97</v>
+        <v>-2.61</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-2.36</v>
+        <v>-3.47</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-3.01</v>
+        <v>-4.18</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-3.01</v>
+        <v>-6.2</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-3.75</v>
+        <v>-6.17</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-3.05</v>
+        <v>-5.43</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-4.02</v>
+        <v>-5.92</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-4.36</v>
+        <v>-6.34</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-3.99</v>
+        <v>-6.66</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-4.63</v>
+        <v>-5.79</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-4.09</v>
+        <v>-3.26</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-4.91</v>
+        <v>-3.48</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-4.27</v>
+        <v>-3.13</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-3.55</v>
+        <v>-3.91</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.19</v>
+        <v>-1.31</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.07</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="22">
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="24">
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>43.37</v>
+        <v>51.34</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>49.89</v>
+        <v>53.3</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>43.94</v>
+        <v>45.47</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>48.08</v>
+        <v>46.45</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>49.05</v>
+        <v>55.03</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>47</v>
+        <v>72.14</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>69.42</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>67.79000000000001</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>55.67</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>58.98</v>
+        <v>67.94</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>59.82</v>
+        <v>85.12</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>69.28</v>
+        <v>86.09</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>58.23</v>
+        <v>74.03</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>74</v>
+        <v>89.86</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>77.28</v>
+        <v>89.98</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>77.22</v>
+        <v>94.78</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>97</v>
+        <v>134.14</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>97.92</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>95.77</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>86.77</v>
+        <v>65.19</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>73.02</v>
+        <v>75.91</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>59.39</v>
+        <v>41.06</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.78</v>
+        <v>75.8</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>39.78</v>
+        <v>43.06</v>
       </c>
     </row>
     <row r="25">
@@ -2438,52 +2438,52 @@
         <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-4.92</v>
+        <v>-17.05</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-12.6</v>
+        <v>-22.96</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-13.53</v>
+        <v>-49.64</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-26.83</v>
+        <v>-45.28</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-14.46</v>
+        <v>-28.42</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-31.76</v>
+        <v>-44.76</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-34.58</v>
+        <v>-44.97</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-30.51</v>
+        <v>-46.84</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-47.7</v>
+        <v>-14.41</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-48.2</v>
+        <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-48.79</v>
+        <v>-18.96</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-51.05</v>
+        <v>-19.42</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-38.06</v>
+        <v>-29.72</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-18.86</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-36.45</v>
+        <v>-14.85</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-6.24</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="26">
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.91</v>
+        <v>-1.33</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.33</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-1</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.93</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.54</v>
+        <v>-1.21</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.51</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-1.32</v>
+        <v>-2.36</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-1.97</v>
+        <v>-2.61</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-2.36</v>
+        <v>-3.47</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-3.01</v>
+        <v>-4.18</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-3.01</v>
+        <v>-6.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-3.75</v>
+        <v>-6.17</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-3.05</v>
+        <v>-5.43</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-4.02</v>
+        <v>-5.92</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-4.36</v>
+        <v>-6.34</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-3.99</v>
+        <v>-6.66</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-4.63</v>
+        <v>-5.79</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-4.09</v>
+        <v>-3.26</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-4.91</v>
+        <v>-3.48</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-4.27</v>
+        <v>-3.13</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-3.55</v>
+        <v>-3.91</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.19</v>
+        <v>-1.31</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.07</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="27">
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="29">
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>43.24</v>
+        <v>51.09</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>49.89</v>
+        <v>53.14</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>43.94</v>
+        <v>45.43</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>48.03</v>
+        <v>46.35</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>48.95</v>
+        <v>54.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>46.91</v>
+        <v>71.72</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>69.09</v>
+        <v>97.95</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>67.33</v>
+        <v>76.33</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>49.93</v>
+        <v>48.92</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>45.22</v>
+        <v>43.01</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>45.21</v>
+        <v>32.16</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>40.58</v>
+        <v>37.72</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>42.79</v>
+        <v>43.45</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>40.38</v>
+        <v>42.27</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>40.46</v>
+        <v>41.91</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>44.59</v>
+        <v>44.57</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>45.85</v>
+        <v>117.61</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>46.36</v>
+        <v>97.92</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>43.21</v>
+        <v>49.48</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>32.02</v>
+        <v>43.93</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>32.34</v>
+        <v>43.82</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>39.15</v>
+        <v>40.75</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>30.24</v>
+        <v>59.81</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>33.24</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="30">
@@ -2858,52 +2858,52 @@
         <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-10.09</v>
+        <v>-34.93</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-25.81</v>
+        <v>-47.03</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-27.71</v>
+        <v>-101.71</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-54.97</v>
+        <v>-92.78</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-29.62</v>
+        <v>-58.24</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-65.06999999999999</v>
+        <v>-91.70999999999999</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-70.86</v>
+        <v>-92.14</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-62.52</v>
+        <v>-95.98</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-97.73999999999999</v>
+        <v>-29.52</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-98.78</v>
+        <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-99.95999999999999</v>
+        <v>-38.85</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-104.6</v>
+        <v>-39.79</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-77.98</v>
+        <v>-60.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-38.65</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-74.68000000000001</v>
+        <v>-30.43</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-12.78</v>
+        <v>-45.36</v>
       </c>
     </row>
     <row r="31">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>-1.04</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>-0.53</v>
-      </c>
       <c r="F31" s="3" t="n">
-        <v>-0.58</v>
+        <v>-1.02</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.64</v>
+        <v>-1.53</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.94</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-1.66</v>
+        <v>-2.84</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-2.42</v>
+        <v>-3.13</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-2.94</v>
+        <v>-4.36</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-3.55</v>
+        <v>-5.04</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-3.43</v>
+        <v>-7.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-4.3</v>
+        <v>-7.05</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-3.33</v>
+        <v>-6.2</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-4.32</v>
+        <v>-6.56</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-4.9</v>
+        <v>-7.24</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-4.61</v>
+        <v>-7.73</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-5.74</v>
+        <v>-7.21</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-5.08</v>
+        <v>-4.01</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-6.3</v>
+        <v>-4.33</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-5.46</v>
+        <v>-4.02</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-4.3</v>
+        <v>-4.82</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.65</v>
+        <v>-1.63</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.83</v>
+        <v>-2.48</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="32">
@@ -3152,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="34">
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>111.99</v>
+        <v>53.59</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>112.09</v>
+        <v>61.22</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2000</v>
+        <v>61.52</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>50.79</v>
+        <v>268.47</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>51.98</v>
+        <v>57.74</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>50.26</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>77.44</v>
+        <v>103.17</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>80.27</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>63.86</v>
+        <v>87.94</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>74.51000000000001</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>77.28</v>
+        <v>140.41</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>117.75</v>
+        <v>139.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>76.19</v>
+        <v>106.82</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>114.72</v>
+        <v>143.7</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>119.94</v>
+        <v>144.17</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>113.51</v>
+        <v>875.45</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>500</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>1703.99</v>
+        <v>1702.46</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1800</v>
+        <v>1702.11</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>1703.75</v>
+        <v>1702.2</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>117</v>
+        <v>111.43</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>118.67</v>
+        <v>130.47</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>2000</v>
+        <v>121.89</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>48.9</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="35">
@@ -3254,16 +3254,16 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>66.25</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>59.13</v>
+        <v>3.96</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1953.05</v>
+        <v>12.86</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>219.12</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -3272,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -3287,40 +3287,40 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>14.49</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0.44</v>
+        <v>726.4299999999999</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>347.31</v>
+        <v>342.99</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1550.24</v>
+        <v>1598.97</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1649.48</v>
+        <v>1608.99</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>1558.76</v>
+        <v>1613.22</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>36.91</v>
+        <v>87.45</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1888.11</v>
+        <v>26.03</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.46</v>
+        <v>0.91</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.39</v>
+        <v>1.5</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.46</v>
+        <v>1.58</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.02</v>
+        <v>2.37</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.64</v>
+        <v>0.8</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.89</v>
+        <v>-0.26</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.68</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.93</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>3.41</v>
+        <v>1.95</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.46</v>
+        <v>-1.07</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>3.86</v>
+        <v>3.16</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.36</v>
+        <v>0.75</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>3.36</v>
+        <v>2.67</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>3.54</v>
+        <v>1.55</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.05</v>
+        <v>0.47</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.31</v>
+        <v>0.65</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>4.14</v>
+        <v>3.14</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.05</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="37">
@@ -3572,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="39">
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>43.32</v>
+        <v>51.44</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>49.79</v>
+        <v>53.3</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>43.81</v>
+        <v>45.38</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>47.98</v>
+        <v>46.4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>49</v>
+        <v>55.13</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>47</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>69.48999999999999</v>
+        <v>98.62</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>68.06</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>55.97</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>59.4</v>
+        <v>68.47</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>60.1</v>
+        <v>85.77</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>69.45999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>58.37</v>
+        <v>74.52</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>74.20999999999999</v>
+        <v>90.12</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>77.48999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>77.53</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>97.70999999999999</v>
+        <v>135.01</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>98.63</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>96.75</v>
+        <v>70.91</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>87.44</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>73.56</v>
+        <v>76.52</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>59.62</v>
+        <v>41.26</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>68.78</v>
+        <v>75.94</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>39.69</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="40">
@@ -3698,52 +3698,52 @@
         <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-4.92</v>
+        <v>-17.05</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-12.6</v>
+        <v>-22.96</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-13.53</v>
+        <v>-49.64</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-26.83</v>
+        <v>-45.28</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-14.46</v>
+        <v>-28.42</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-31.76</v>
+        <v>-44.76</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-34.58</v>
+        <v>-44.97</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-30.51</v>
+        <v>-46.84</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-47.7</v>
+        <v>-14.41</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>-48.2</v>
+        <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-48.79</v>
+        <v>-18.96</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-51.05</v>
+        <v>-19.42</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-38.06</v>
+        <v>-29.72</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-18.86</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-36.45</v>
+        <v>-14.85</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-6.24</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="41">
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.23</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.33</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.66</v>
+        <v>-1.09</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.97</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.59</v>
+        <v>-1.1</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.3</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-1.25</v>
+        <v>-2.17</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-1.7</v>
+        <v>-2.31</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.9</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-2.59</v>
+        <v>-3.66</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-2.72</v>
+        <v>-5.55</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-3.56</v>
+        <v>-5.67</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-2.91</v>
+        <v>-4.94</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-3.81</v>
+        <v>-5.66</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-4.15</v>
+        <v>-5.82</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-3.67</v>
+        <v>-5.98</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-3.93</v>
+        <v>-4.93</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.38</v>
+        <v>-2.68</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.93</v>
+        <v>-2.79</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.6</v>
+        <v>-2.64</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-3.01</v>
+        <v>-3.29</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.96</v>
+        <v>-1.11</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.53</v>
+        <v>-1.93</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="42">
@@ -3992,10 +3992,10 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="44">
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>44.23</v>
+        <v>52.52</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>50.53</v>
+        <v>54.52</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>44.38</v>
+        <v>46.29</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>48.61</v>
+        <v>47.28</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>49.44</v>
+        <v>56.18</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>47.75</v>
+        <v>73.66</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>70.81</v>
+        <v>100.49</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>69.34</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>62.4</v>
+        <v>87.33</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>73.92</v>
+        <v>93.86</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>75.3</v>
+        <v>138.48</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>98.56999999999999</v>
+        <v>134.99</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>74.91</v>
+        <v>105.98</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>109.23</v>
+        <v>138.33</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>115.87</v>
+        <v>139.48</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>112.28</v>
+        <v>147.24</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>150.54</v>
+        <v>154.65</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>152.04</v>
+        <v>102.76</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>150.83</v>
+        <v>93.02</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>143.23</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>115.09</v>
+        <v>109.87</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>80.69</v>
+        <v>42.46</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>107.86</v>
+        <v>92.58</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>47.04</v>
+        <v>66.83</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-2.21</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>-0.15</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>0.11</v>
-      </c>
       <c r="Z46" s="3" t="n">
-        <v>0.19</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="47">
@@ -4412,10 +4412,10 @@
         <v>0</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="49">
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>45.09</v>
+        <v>53.59</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>51.51</v>
+        <v>55.74</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>45.14</v>
+        <v>47.08</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>49.45</v>
+        <v>48.05</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>50.44</v>
+        <v>57.21</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>48.82</v>
+        <v>75.47</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>73.01000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>71.18000000000001</v>
+        <v>81.67</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>64.45</v>
+        <v>86.14</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>76.26000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>78.31</v>
+        <v>142.68</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>103.37</v>
+        <v>133.42</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>107.56</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>113.53</v>
+        <v>144.59</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>120.31</v>
+        <v>145.36</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>110.07</v>
+        <v>145.37</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>146.26</v>
+        <v>151.02</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>150.82</v>
+        <v>105.64</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>145.82</v>
+        <v>96.11</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>146.48</v>
+        <v>90.45</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>119.03</v>
+        <v>113.75</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>43.82</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>110.51</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>48</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.68</v>
+        <v>0.61</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2.26</v>
+        <v>-2.84</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1.42</v>
+        <v>2.21</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>1.48</v>
+        <v>-2.07</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.51</v>
+        <v>-4.14</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>2.67</v>
+        <v>-0.32</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-1.65</v>
+        <v>-2.91</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.07</v>
+        <v>-3.32</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.65</v>
+        <v>3.46</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>4.39</v>
+        <v>2.71</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>4.4</v>
+        <v>4.21</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.49</v>
+        <v>1.45</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.76</v>
+        <v>2.04</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="52">
@@ -4832,10 +4832,10 @@
         <v>0</v>
       </c>
       <c r="Y53" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="54">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>46.46</v>
+        <v>55.28</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>53.3</v>
+        <v>57.75</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>46.76</v>
+        <v>49.02</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>51.16</v>
+        <v>50.03</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>52.25</v>
+        <v>59.32</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>50.37</v>
+        <v>77.7</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>74.47</v>
+        <v>105.76</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>73.73999999999999</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>66.42</v>
+        <v>92.56</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>77.37</v>
+        <v>96.53</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>79.78</v>
+        <v>141.82</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>102.42</v>
+        <v>139.65</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>78.31999999999999</v>
+        <v>109.08</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>111.79</v>
+        <v>140.82</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>117.87</v>
+        <v>137.84</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>110.28</v>
+        <v>148.42</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>106.17</v>
+        <v>147.41</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>82.28</v>
+        <v>95.09</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>81.15000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>72.03</v>
+        <v>59.16</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>110.86</v>
+        <v>107.92</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>82.42</v>
+        <v>43.64</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>112.12</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>49.21</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4982,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>-36.6</v>
+        <v>0</v>
       </c>
       <c r="T55" s="3" t="n">
-        <v>-57.84</v>
+        <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>-58.54</v>
+        <v>-22.75</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>-61.26</v>
+        <v>-23.3</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>2.61</v>
+        <v>3.12</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>2.66</v>
+        <v>3.08</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>2.57</v>
+        <v>4.04</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>3.72</v>
+        <v>4.97</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>3.98</v>
+        <v>4.36</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>3.45</v>
+        <v>4.35</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>2.79</v>
+        <v>1.45</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>3.43</v>
+        <v>0.85</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>2.56</v>
+        <v>2.09</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>2.58</v>
+        <v>1.2</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>2.01</v>
+        <v>0.28</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>1.65</v>
+        <v>-3.45</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.43</v>
+        <v>0.15</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-6.57</v>
+        <v>-6.93</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-10.09</v>
+        <v>-6.85</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-9.779999999999999</v>
+        <v>-5.74</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-8.800000000000001</v>
+        <v>-5.28</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-3.77</v>
+        <v>-1.62</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.98</v>
+        <v>1.27</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>4.37</v>
+        <v>3.54</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.36</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="57">
@@ -5252,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z58" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="59">
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>45.79</v>
+        <v>54.36</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>52.25</v>
+        <v>56.43</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>45.89</v>
+        <v>47.96</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>50.16</v>
+        <v>48.89</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>50.91</v>
+        <v>58.1</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>49.28</v>
+        <v>76.17</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>73.16</v>
+        <v>103.91</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>71.69</v>
+        <v>81.34</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>64.64</v>
+        <v>90.38</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>76.58</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>78.06999999999999</v>
+        <v>143.7</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>102.21</v>
+        <v>140.22</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>77.76000000000001</v>
+        <v>110.2</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>113.41</v>
+        <v>143.85</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>120.06</v>
+        <v>144.91</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>116.25</v>
+        <v>153.02</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>155.56</v>
+        <v>160.44</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>156.96</v>
+        <v>106.41</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>155.86</v>
+        <v>96.41</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>148.32</v>
+        <v>91.39</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>119.16</v>
+        <v>113.75</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>83.54000000000001</v>
+        <v>43.91</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>111.54</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>48.6</v>
+        <v>69.63</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.32</v>
+        <v>1.86</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>1.48</v>
+        <v>2.51</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2.41</v>
+        <v>3.12</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>1.68</v>
+        <v>2.17</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.72</v>
+        <v>2.73</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>3.63</v>
+        <v>3.31</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>4.53</v>
+        <v>4.74</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>6.22</v>
+        <v>6.1</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>6.75</v>
+        <v>4.47</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>6.39</v>
+        <v>3.76</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>6.23</v>
+        <v>3.66</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>3.09</v>
+        <v>1.54</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>3.79</v>
+        <v>2.43</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.75</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="62">
@@ -5672,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="64">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>46.41</v>
+        <v>55.1</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>52.91</v>
+        <v>57.2</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>46.46</v>
+        <v>48.56</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>50.79</v>
+        <v>49.55</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>51.54</v>
+        <v>58.89</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>49.95</v>
+        <v>77.13</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>74.23</v>
+        <v>105.32</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>72.73999999999999</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>65.59</v>
+        <v>91.69</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>77.69</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>79.28</v>
+        <v>146.08</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>103.8</v>
+        <v>141.95</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>79.06</v>
+        <v>112.03</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>115.19</v>
+        <v>145.94</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>122.21</v>
+        <v>147.18</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>118.22</v>
+        <v>156.24</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>158.19</v>
+        <v>163.15</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>159.29</v>
+        <v>108.21</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>158.33</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>150.68</v>
+        <v>92.94</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>120.92</v>
+        <v>115.55</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>84.77</v>
+        <v>44.56</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>113.18</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>49.26</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>2.18</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>2.15</v>
+        <v>3.47</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3.49</v>
+        <v>4.53</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>2.62</v>
+        <v>3.48</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>3.11</v>
+        <v>3.65</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>2.93</v>
+        <v>5.11</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.32</v>
+        <v>4.15</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>5.41</v>
+        <v>5.4</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>5.99</v>
+        <v>5.89</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>6.5</v>
+        <v>7.97</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>9.08</v>
+        <v>6.28</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>8.869999999999999</v>
+        <v>5.39</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>8.59</v>
+        <v>5.2</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>6.29</v>
+        <v>6.01</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>4.32</v>
+        <v>2.18</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>5.43</v>
+        <v>3.46</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.41</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="67">
@@ -6092,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="69">
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>47.1</v>
+        <v>55.92</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>53.75</v>
+        <v>58.05</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>47.15</v>
+        <v>49.33</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>51.6</v>
+        <v>50.29</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>52.14</v>
+        <v>59.76</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>50.58</v>
+        <v>90</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>106.66</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>73.43000000000001</v>
+        <v>83.38</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>66.20999999999999</v>
+        <v>92.66</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>78.43000000000001</v>
+        <v>99.77</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>79.87</v>
+        <v>147</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>104.56</v>
+        <v>143.43</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>79.72</v>
+        <v>113.09</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>116.41</v>
+        <v>147.78</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>123.24</v>
+        <v>148.88</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>119.48</v>
+        <v>157.57</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>160.23</v>
+        <v>165.36</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>161.62</v>
+        <v>109.63</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>160.93</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>152.62</v>
+        <v>94.38</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>122.57</v>
+        <v>117.29</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>86.31</v>
+        <v>45.26</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>114.75</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>49.79</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.83</v>
+        <v>3.24</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.06</v>
+        <v>3.43</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.99</v>
+        <v>2.92</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.55</v>
+        <v>3.53</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>2.78</v>
+        <v>4.62</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>4.36</v>
+        <v>5.87</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>3.67</v>
+        <v>3.92</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>3.24</v>
+        <v>4.45</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>3.84</v>
+        <v>4.69</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>3.51</v>
+        <v>6.03</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.71</v>
+        <v>5.88</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.99</v>
+        <v>5.2</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>6.64</v>
+        <v>7.24</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>7.02</v>
+        <v>7.59</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>7.77</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S71" s="3" t="n">
         <v>10.55</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>11.13</v>
+        <v>7.44</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>10.73</v>
+        <v>6.44</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>10.37</v>
+        <v>6.3</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>7.84</v>
+        <v>7.36</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>5.41</v>
+        <v>2.8</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>7</v>
+        <v>4.52</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.94</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="72">
@@ -6377,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0</v>
+        <v>11.72</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0</v>
@@ -6410,22 +6410,22 @@
         <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="V72" s="3" t="n">
         <v>0.34</v>
       </c>
-      <c r="T72" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="U72" s="3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="V72" s="3" t="n">
-        <v>0.16</v>
-      </c>
       <c r="W72" s="3" t="n">
-        <v>0.1</v>
+        <v>0.38</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="Y72" s="3" t="n">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="74">
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>45.84</v>
+        <v>54.48</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>52.31</v>
+        <v>56.55</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>45.93</v>
+        <v>48.01</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>50.21</v>
+        <v>48.99</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>50.96</v>
+        <v>58.22</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>49.38</v>
+        <v>76.25</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>73.39</v>
+        <v>103.91</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>71.77</v>
+        <v>81.5</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>64.78</v>
+        <v>90.47</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>76.73</v>
+        <v>97.52</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>78.47</v>
+        <v>144.44</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>102.84</v>
+        <v>140.79</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>78.23999999999999</v>
+        <v>110.88</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>113.76</v>
+        <v>144.44</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>120.44</v>
+        <v>145.36</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>116.49</v>
+        <v>153.49</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>156.04</v>
+        <v>160.94</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>157.46</v>
+        <v>106.97</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>156.35</v>
+        <v>96.92</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>148.94</v>
+        <v>91.87</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>119.66</v>
+        <v>114.22</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>83.8</v>
+        <v>44.1</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>111.89</v>
+        <v>95.39</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>48.7</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="D76" s="3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F76" s="3" t="n">
         <v>1.62</v>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="G76" s="3" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1.58</v>
+        <v>2.59</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.64</v>
+        <v>3.12</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.12</v>
+        <v>3.47</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>4.22</v>
+        <v>4.07</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>4.78</v>
+        <v>5.22</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>6.71</v>
+        <v>6.6</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>7.24</v>
+        <v>5.03</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>6.88</v>
+        <v>4.26</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>6.85</v>
+        <v>4.13</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>5.03</v>
+        <v>4.68</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>3.35</v>
+        <v>1.72</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>4.14</v>
+        <v>2.66</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.85</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="77">
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="79">
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>44.28</v>
+        <v>52.68</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>50.68</v>
+        <v>54.63</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>44.46</v>
+        <v>46.47</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>48.61</v>
+        <v>47.37</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>49.58</v>
+        <v>56.24</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>47.8</v>
+        <v>73.66</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>70.73999999999999</v>
+        <v>100.79</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>69.76000000000001</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>62.96</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>74.59</v>
+        <v>95.08</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>76.34999999999999</v>
+        <v>140.97</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>99.86</v>
+        <v>137.55</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>75.73999999999999</v>
+        <v>107.88</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>109.78</v>
+        <v>140.54</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>116.22</v>
+        <v>141.29</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>111.72</v>
+        <v>148.27</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>149.33</v>
+        <v>154.34</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>150.21</v>
+        <v>101.94</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>149.47</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>142.09</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>114.63</v>
+        <v>109.54</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>80.44</v>
+        <v>42.38</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>107.75</v>
+        <v>92.72</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>46.85</v>
+        <v>66.98999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="84">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>46.31</v>
+        <v>54.99</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>53.35</v>
+        <v>58.12</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>46.66</v>
+        <v>49.28</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>51.22</v>
+        <v>50.4</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>52.42</v>
+        <v>59.89</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>50.63</v>
+        <v>78.19</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>74.55</v>
+        <v>106.55</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>73.81999999999999</v>
+        <v>84.36</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>66.42</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>77.37</v>
+        <v>94.42</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>79.37</v>
+        <v>138.75</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>102.31</v>
+        <v>141.37</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>78.16</v>
+        <v>106.71</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>111.45</v>
+        <v>136.45</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>118.23</v>
+        <v>134.05</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>111.38</v>
+        <v>148.42</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>104.41</v>
+        <v>145.19</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>81.37</v>
+        <v>93.78</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>80.63</v>
+        <v>63.36</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>71.53</v>
+        <v>58.31</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>110.22</v>
+        <v>108.89</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>83.36</v>
+        <v>44.01</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>113.18</v>
+        <v>96.51000000000001</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>49.21</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -7502,16 +7502,16 @@
         <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>-36.6</v>
+        <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>-57.84</v>
+        <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-58.54</v>
+        <v>-22.75</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>-61.26</v>
+        <v>-23.3</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.67</v>
+        <v>3.49</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.61</v>
+        <v>3.02</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>2.83</v>
+        <v>3.65</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>2.84</v>
+        <v>4.54</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>4.06</v>
+        <v>4.89</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>3.45</v>
+        <v>5.04</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>2.79</v>
+        <v>-0.66</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>3.02</v>
+        <v>-2.22</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>2.46</v>
+        <v>3.82</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>2.42</v>
+        <v>-1.17</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>1.67</v>
+        <v>-4.09</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>2.01</v>
+        <v>-7.24</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-0.33</v>
+        <v>0.15</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-8.32</v>
+        <v>-9.15</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-11</v>
+        <v>-8.16</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-10.3</v>
+        <v>-6.54</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.12</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-4.41</v>
+        <v>-0.65</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>5.43</v>
+        <v>3.78</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.36</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="87">
@@ -7772,10 +7772,10 @@
         <v>0</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
     <row r="89">
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>43.24</v>
+        <v>51.09</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>49.89</v>
+        <v>53.14</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>43.94</v>
+        <v>45.43</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>48.03</v>
+        <v>46.35</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>48.95</v>
+        <v>54.7</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>46.86</v>
+        <v>71.72</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>69.09</v>
+        <v>97.95</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>67.33</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>55.1</v>
+        <v>66.8</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>58.44</v>
+        <v>67.08</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>59.4</v>
+        <v>84.23</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>68.72</v>
+        <v>85.22</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>57.95</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>89.22</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>76.73999999999999</v>
+        <v>89.08</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>95.89</v>
+        <v>132.73</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>96.93000000000001</v>
+        <v>97.92</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>94.38</v>
+        <v>69.36</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>85.56999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>72.27</v>
+        <v>75</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>58.94</v>
+        <v>40.75</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>68.47</v>
+        <v>75.39</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>39.78</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="90">
@@ -7898,52 +7898,52 @@
         <v>0</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-4.92</v>
+        <v>-17.05</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-12.6</v>
+        <v>-22.96</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-13.53</v>
+        <v>-49.64</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-26.83</v>
+        <v>-45.28</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-14.46</v>
+        <v>-28.42</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-31.76</v>
+        <v>-44.76</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-34.58</v>
+        <v>-44.97</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-30.51</v>
+        <v>-46.84</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-47.7</v>
+        <v>-14.41</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>-48.2</v>
+        <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>-48.79</v>
+        <v>-18.96</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-51.05</v>
+        <v>-19.42</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-38.06</v>
+        <v>-29.72</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-18.86</v>
+        <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-36.45</v>
+        <v>-14.85</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-6.24</v>
+        <v>-22.14</v>
       </c>
     </row>
     <row r="91">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="E91" s="3" t="n">
         <v>-1.04</v>
       </c>
-      <c r="D91" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.53</v>
-      </c>
       <c r="F91" s="3" t="n">
-        <v>-0.58</v>
+        <v>-1.02</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.64</v>
+        <v>-1.53</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.94</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-1.66</v>
+        <v>-2.84</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-2.42</v>
+        <v>-3.2</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-2.94</v>
+        <v>-4.36</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-3.55</v>
+        <v>-5.04</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-3.43</v>
+        <v>-7.1</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-4.3</v>
+        <v>-7.05</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-3.33</v>
+        <v>-6.2</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-4.42</v>
+        <v>-6.56</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-4.9</v>
+        <v>-7.24</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-4.61</v>
+        <v>-7.73</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-5.74</v>
+        <v>-7.21</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-5.08</v>
+        <v>-4.01</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-6.3</v>
+        <v>-4.33</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-5.46</v>
+        <v>-4.02</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-4.3</v>
+        <v>-4.82</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.65</v>
+        <v>-1.63</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.83</v>
+        <v>-2.48</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="92">
@@ -8192,10 +8192,10 @@
         <v>0</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>0</v>
+        <v>19.32</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>0</v>
+        <v>-12.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-12T03:12:23</t>
+          <t>CreatedAt: 2026-10-12T12:09:16</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -665,61 +665,61 @@
         <v>55.13</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>72.34999999999999</v>
+        <v>72.13</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>98.62</v>
+        <v>77.44</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>77.15000000000001</v>
+        <v>76.73</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>68.26000000000001</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>68.47</v>
+        <v>67.5</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>85.77</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>74.52</v>
+        <v>75.05</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>90.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>90.5</v>
+        <v>68.94</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>95.45999999999999</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>135.01</v>
+        <v>72.94</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>99.26000000000001</v>
+        <v>73.41</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>70.91</v>
+        <v>76.17</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>65.68000000000001</v>
+        <v>63.37</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>76.52</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>41.26</v>
+        <v>76.38</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>75.94</v>
+        <v>56.91</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>42.98</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="5">
@@ -755,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-17.05</v>
+        <v>-21.15</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-22.96</v>
+        <v>-29.33</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-49.64</v>
+        <v>-33.36</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-45.28</v>
+        <v>-34.03</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-28.42</v>
+        <v>-31.98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-44.76</v>
+        <v>-30.9</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-44.97</v>
+        <v>-25.89</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-46.84</v>
+        <v>-12.64</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-14.41</v>
+        <v>0</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-18.96</v>
+        <v>-13.84</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-19.42</v>
+        <v>-12.32</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-29.72</v>
+        <v>-18.68</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0</v>
+        <v>-38.04</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-14.85</v>
+        <v>-19.52</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-22.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -836,58 +836,58 @@
         <v>-1.3</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-2.17</v>
+        <v>-1.16</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-2.31</v>
+        <v>-2.34</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-3.66</v>
+        <v>-3.87</v>
       </c>
       <c r="M6" s="3" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>-5.55</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>-5.67</v>
-      </c>
       <c r="O6" s="3" t="n">
-        <v>-4.94</v>
+        <v>-5.78</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-5.66</v>
+        <v>-4.23</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-5.82</v>
+        <v>-4.08</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.98</v>
+        <v>-3.3</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-4.93</v>
+        <v>-2.04</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-2.68</v>
+        <v>-1.92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.61</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.64</v>
+        <v>-2.5</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-3.29</v>
+        <v>-2.65</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.11</v>
+        <v>-3.2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.93</v>
+        <v>-2.06</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.87</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="7">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1085,61 +1085,61 @@
         <v>56.29</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>73.36</v>
+        <v>73.06</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>100.89</v>
+        <v>79.08</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>78.29000000000001</v>
+        <v>77.34</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>68.67</v>
+        <v>67</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>68.47</v>
+        <v>67.59</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>87.34999999999999</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>90.23</v>
+        <v>77.59</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>75.91</v>
+        <v>73.45</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>94.39</v>
+        <v>68.91</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>94.92</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>98.39</v>
+        <v>75.78</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>138.11</v>
+        <v>74.38</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>100.93</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>72.05</v>
+        <v>77.06</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>67.28</v>
+        <v>64.64</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>78.84</v>
+        <v>68.34</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>42.04</v>
+        <v>78.53</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>78.54000000000001</v>
+        <v>59.44</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>45.98</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="10">
@@ -1175,55 +1175,55 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-17.05</v>
+        <v>-21.15</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-22.96</v>
+        <v>-29.33</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-49.64</v>
+        <v>-33.36</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-45.28</v>
+        <v>-34.03</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-28.42</v>
+        <v>-31.98</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-44.76</v>
+        <v>-30.9</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-44.97</v>
+        <v>-25.89</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-46.84</v>
+        <v>-12.64</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-14.41</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-18.96</v>
+        <v>-13.84</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-19.42</v>
+        <v>-12.32</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-29.72</v>
+        <v>-18.68</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0</v>
+        <v>-38.04</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-14.85</v>
+        <v>-19.52</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-22.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1253,61 +1253,61 @@
         <v>0.06</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.37</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.1</v>
+        <v>0.47</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.73</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.29</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-3.66</v>
+        <v>-3.78</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-3.97</v>
+        <v>-3.41</v>
       </c>
       <c r="N11" s="3" t="n">
+        <v>-4.91</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>-2.03</v>
       </c>
-      <c r="O11" s="3" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="R11" s="3" t="n">
-        <v>-3.05</v>
+        <v>-1.77</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-1.83</v>
+        <v>-0.6</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.01</v>
+        <v>-0.9</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.73</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.23</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.96</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.34</v>
+        <v>-1.05</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.67</v>
+        <v>0.47</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1472,10 +1472,10 @@
         <v>0</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1505,61 +1505,61 @@
         <v>56.29</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>73.36</v>
+        <v>73.06</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>100.89</v>
+        <v>79.08</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>78.29000000000001</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>85.72</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>91.43000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>137</v>
+        <v>79.78</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>135.52</v>
+        <v>95.66</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>104.34</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>139.15</v>
+        <v>87.72</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>139.89</v>
+        <v>96.88</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>871.65</v>
+        <v>88.41</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>495.65</v>
+        <v>140.66</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>1700</v>
+        <v>200.74</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1700</v>
+        <v>1049.97</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>1700</v>
+        <v>727.35</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>108.56</v>
+        <v>124.59</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>129.49</v>
+        <v>126.47</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>119.42</v>
+        <v>137.07</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>68.12</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="15">
@@ -1601,46 +1601,46 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>-18.69</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0</v>
+        <v>-23.57</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0</v>
+        <v>-16.07</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0</v>
+        <v>-17.03</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
+        <v>-12.09</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>726.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>342.99</v>
+        <v>66.28</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>1598.97</v>
+        <v>126.03</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>1608.99</v>
+        <v>959.0700000000001</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>1613.22</v>
+        <v>650.39</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>0</v>
+        <v>37.57</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>87.45</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>26.03</v>
+        <v>58.03</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1673,61 +1673,61 @@
         <v>0.06</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.29</v>
+        <v>-0.37</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1</v>
+        <v>0.47</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.17</v>
+        <v>-1.73</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.29</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-3.66</v>
+        <v>-3.78</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.97</v>
+        <v>-3.41</v>
       </c>
       <c r="N16" s="3" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>-7.38</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>-2.03</v>
       </c>
-      <c r="O16" s="3" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="R16" s="3" t="n">
-        <v>-3.05</v>
+        <v>-1.77</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-1.68</v>
+        <v>-0.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.9</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.73</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.23</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.96</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.93</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1925,61 +1925,61 @@
         <v>55.03</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>72.14</v>
+        <v>71.92</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>79.42</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>76.84999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>49.8</v>
+        <v>43.8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>43.87</v>
+        <v>36.19</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>33.06</v>
+        <v>33.92</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>38.59</v>
+        <v>40.73</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>44.22</v>
+        <v>40.8</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>42.91</v>
+        <v>34.78</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>42.8</v>
+        <v>41.51</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>45.64</v>
+        <v>60.65</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>119.03</v>
+        <v>72.58</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>98.68000000000001</v>
+        <v>72.69</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>50.33</v>
+        <v>61.04</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>44.82</v>
+        <v>49.93</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>44.73</v>
+        <v>46.56</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>41.06</v>
+        <v>36.03</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>60.23</v>
+        <v>36.29</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>19.83</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="20">
@@ -2015,55 +2015,55 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>-2.46</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-34.93</v>
+        <v>-43.33</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-47.03</v>
+        <v>-60.09</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-101.71</v>
+        <v>-68.34</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-92.78</v>
+        <v>-69.72</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-58.24</v>
+        <v>-65.52</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-91.70999999999999</v>
+        <v>-63.31</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-92.14</v>
+        <v>-53.05</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-95.98</v>
+        <v>-25.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-29.52</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-38.85</v>
+        <v>-28.37</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-39.79</v>
+        <v>-25.25</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-60.9</v>
+        <v>-38.28</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0</v>
+        <v>-77.95</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-30.43</v>
+        <v>-39.99</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-45.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2096,58 +2096,58 @@
         <v>-1.51</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-2.36</v>
+        <v>-1.24</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.71</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-3.47</v>
+        <v>-3.31</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-4.18</v>
+        <v>-4.43</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-6.2</v>
+        <v>-4.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-6.17</v>
+        <v>-6.07</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-5.43</v>
+        <v>-6.49</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-5.92</v>
+        <v>-4.61</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-6.34</v>
+        <v>-4.35</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-6.66</v>
+        <v>-3.63</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-5.79</v>
+        <v>-2.4</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-3.26</v>
+        <v>-2.34</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.48</v>
+        <v>-3.22</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.01</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-3.91</v>
+        <v>-3.14</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.31</v>
+        <v>-3.65</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.21</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="22">
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2312,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2345,61 +2345,61 @@
         <v>55.03</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>72.14</v>
+        <v>71.92</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>77.36</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>76.84999999999999</v>
+        <v>76.36</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>67.68000000000001</v>
+        <v>65.98</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>67.94</v>
+        <v>66.94</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>85.12</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>86.09</v>
+        <v>76.42</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>74.03</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>89.86</v>
+        <v>67.19</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>89.98</v>
+        <v>68.67</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>94.78</v>
+        <v>73.91</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>134.14</v>
+        <v>72.58</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>98.68000000000001</v>
+        <v>72.98</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>70.20999999999999</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>65.19</v>
+        <v>62.86</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>75.91</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>41.06</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>75.8</v>
+        <v>56.76</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>43.06</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="25">
@@ -2435,55 +2435,55 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-17.05</v>
+        <v>-21.15</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-22.96</v>
+        <v>-29.33</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-49.64</v>
+        <v>-33.36</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-45.28</v>
+        <v>-34.03</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-28.42</v>
+        <v>-31.98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-44.76</v>
+        <v>-30.9</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-44.97</v>
+        <v>-25.89</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-46.84</v>
+        <v>-12.64</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-14.41</v>
+        <v>0</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-18.96</v>
+        <v>-13.84</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-19.42</v>
+        <v>-12.32</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-29.72</v>
+        <v>-18.68</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>0</v>
+        <v>-38.04</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-14.85</v>
+        <v>-19.52</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-22.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2516,58 +2516,58 @@
         <v>-1.51</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-2.36</v>
+        <v>-1.24</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.71</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-3.47</v>
+        <v>-3.31</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-4.18</v>
+        <v>-4.43</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-6.2</v>
+        <v>-4.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-6.17</v>
+        <v>-6.07</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-5.43</v>
+        <v>-6.49</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-5.92</v>
+        <v>-4.61</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-6.34</v>
+        <v>-4.35</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-6.66</v>
+        <v>-3.63</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-5.79</v>
+        <v>-2.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-3.26</v>
+        <v>-2.34</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.48</v>
+        <v>-3.22</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.01</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-3.91</v>
+        <v>-3.14</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.31</v>
+        <v>-3.65</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.21</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.79</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="27">
@@ -2732,10 +2732,10 @@
         <v>0</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2765,61 +2765,61 @@
         <v>54.7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>71.72</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>97.95</v>
+        <v>79.12</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>76.33</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>48.92</v>
+        <v>43.05</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>43.01</v>
+        <v>35.45</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>32.16</v>
+        <v>33.33</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>37.72</v>
+        <v>40.11</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>43.45</v>
+        <v>40.11</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>42.27</v>
+        <v>34.41</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>41.91</v>
+        <v>41.24</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>44.57</v>
+        <v>60.07</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>117.61</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>97.92</v>
+        <v>72.05</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>49.48</v>
+        <v>60.19</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>43.93</v>
+        <v>49.22</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>43.82</v>
+        <v>45.83</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>40.75</v>
+        <v>35.26</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>59.81</v>
+        <v>35.85</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>19.68</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="30">
@@ -2855,55 +2855,55 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0</v>
+        <v>-2.46</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-34.93</v>
+        <v>-43.33</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-47.03</v>
+        <v>-60.09</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-101.71</v>
+        <v>-68.34</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-92.78</v>
+        <v>-69.72</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-58.24</v>
+        <v>-65.52</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-91.70999999999999</v>
+        <v>-63.31</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-92.14</v>
+        <v>-53.05</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-95.98</v>
+        <v>-25.9</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-29.52</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-38.85</v>
+        <v>-28.37</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-39.79</v>
+        <v>-25.25</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-60.9</v>
+        <v>-38.28</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0</v>
+        <v>-77.95</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-30.43</v>
+        <v>-39.99</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-45.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2933,61 +2933,61 @@
         <v>-1.53</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-1.94</v>
+        <v>-1.86</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-2.84</v>
+        <v>-1.54</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.31</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.06</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-5.04</v>
+        <v>-5.16</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-7.1</v>
+        <v>-5.08</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-7.05</v>
+        <v>-6.7</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-6.2</v>
+        <v>-7.18</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-6.56</v>
+        <v>-4.98</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-7.24</v>
+        <v>-4.62</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-7.73</v>
+        <v>-4.21</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-7.21</v>
+        <v>-2.88</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-4.01</v>
+        <v>-2.98</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.33</v>
+        <v>-4.07</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4.02</v>
+        <v>-3.72</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-4.82</v>
+        <v>-3.87</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.63</v>
+        <v>-4.42</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.48</v>
+        <v>-2.65</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.95</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="32">
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3152,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3185,61 +3185,61 @@
         <v>57.74</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>75.23999999999999</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>103.17</v>
+        <v>80.53</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>80.27</v>
+        <v>80.19</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>87.94</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>140.41</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>139.5</v>
+        <v>97.91</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>106.82</v>
+        <v>89.91</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>143.7</v>
+        <v>89.91</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>144.17</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>875.45</v>
+        <v>90.27</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>500</v>
+        <v>142.55</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>1702.46</v>
+        <v>202.48</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1702.11</v>
+        <v>1051.79</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>1702.2</v>
+        <v>729.29</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>111.43</v>
+        <v>126.79</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>130.47</v>
+        <v>129.08</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>121.89</v>
+        <v>139.45</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>70.75</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="35">
@@ -3281,46 +3281,46 @@
         <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>-16.82</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>-21.22</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>-14.46</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0</v>
+        <v>-15.32</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>-10.88</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>726.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>342.99</v>
+        <v>66.28</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1598.97</v>
+        <v>126.03</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1608.99</v>
+        <v>959.0700000000001</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>1613.22</v>
+        <v>650.39</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>37.57</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>87.45</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>26.03</v>
+        <v>58.03</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3353,61 +3353,61 @@
         <v>1.5</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.8</v>
+        <v>-0.08</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.45</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.88</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.47</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.95</v>
+        <v>-4.16</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-1.07</v>
+        <v>-7.58</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>3.16</v>
+        <v>-1.91</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>2.88</v>
+        <v>-0.59</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.75</v>
+        <v>0.09</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>2.67</v>
+        <v>1.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.55</v>
+        <v>0.84</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.47</v>
+        <v>0.09</v>
       </c>
       <c r="V36" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>1.89</v>
-      </c>
       <c r="X36" s="3" t="n">
-        <v>0.65</v>
+        <v>1.67</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>3.76</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="37">
@@ -3572,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3605,61 +3605,61 @@
         <v>55.13</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>72.34999999999999</v>
+        <v>72.13</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>98.62</v>
+        <v>77.44</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>77.15000000000001</v>
+        <v>76.73</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>68.26000000000001</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>68.47</v>
+        <v>67.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>85.77</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>74.52</v>
+        <v>75.05</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>90.12</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>90.5</v>
+        <v>68.94</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>95.45999999999999</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>135.01</v>
+        <v>72.94</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>99.26000000000001</v>
+        <v>73.41</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>70.91</v>
+        <v>76.17</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>65.68000000000001</v>
+        <v>63.37</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>76.52</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>41.26</v>
+        <v>76.38</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>75.94</v>
+        <v>56.91</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>42.98</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="40">
@@ -3695,55 +3695,55 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-17.05</v>
+        <v>-21.15</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-22.96</v>
+        <v>-29.33</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-49.64</v>
+        <v>-33.36</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-45.28</v>
+        <v>-34.03</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-28.42</v>
+        <v>-31.98</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-44.76</v>
+        <v>-30.9</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-44.97</v>
+        <v>-25.89</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-46.84</v>
+        <v>-12.64</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-14.41</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-18.96</v>
+        <v>-13.84</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-19.42</v>
+        <v>-12.32</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-29.72</v>
+        <v>-18.68</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>0</v>
+        <v>-38.04</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-14.85</v>
+        <v>-19.52</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-22.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3776,58 +3776,58 @@
         <v>-1.3</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-2.17</v>
+        <v>-1.16</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-2.31</v>
+        <v>-2.34</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-2.9</v>
+        <v>-2.8</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-3.66</v>
+        <v>-3.87</v>
       </c>
       <c r="M41" s="3" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="N41" s="3" t="n">
         <v>-5.55</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>-5.67</v>
-      </c>
       <c r="O41" s="3" t="n">
-        <v>-4.94</v>
+        <v>-5.78</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-5.66</v>
+        <v>-4.23</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-5.82</v>
+        <v>-4.08</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.98</v>
+        <v>-3.3</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-4.93</v>
+        <v>-2.04</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-2.68</v>
+        <v>-1.92</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.79</v>
+        <v>-2.61</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.64</v>
+        <v>-2.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-3.29</v>
+        <v>-2.65</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.11</v>
+        <v>-3.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.93</v>
+        <v>-2.06</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.87</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="42">
@@ -3992,10 +3992,10 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4025,61 +4025,61 @@
         <v>56.18</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>73.66</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>100.49</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>80.03</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>87.33</v>
+        <v>90.17</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>93.86</v>
+        <v>99.7</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>138.48</v>
+        <v>105.49</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>134.99</v>
+        <v>114.36</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>105.98</v>
+        <v>111.25</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>138.33</v>
+        <v>101.59</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>139.48</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>147.24</v>
+        <v>89.91</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>154.65</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>102.76</v>
+        <v>76.22</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>93.02</v>
+        <v>93.09</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>88.18000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>109.87</v>
+        <v>87.97</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>42.46</v>
+        <v>117.63</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>92.58</v>
+        <v>78.33</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>66.83</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="45">
@@ -4196,55 +4196,55 @@
         <v>0</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-0.3</v>
+        <v>0.16</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.24</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.27</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-2.49</v>
+        <v>-1.27</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-2.56</v>
+        <v>-2.17</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1.91</v>
+        <v>-1.56</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-2.21</v>
+        <v>-1.12</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.81</v>
+        <v>-0.98</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.03</v>
+        <v>-0.27</v>
       </c>
       <c r="S46" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="V46" s="3" t="n">
         <v>0.31</v>
       </c>
-      <c r="T46" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>0.44</v>
-      </c>
       <c r="W46" s="3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>-0.16</v>
@@ -4412,10 +4412,10 @@
         <v>0</v>
       </c>
       <c r="Y48" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4445,61 +4445,61 @@
         <v>57.21</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>75.47</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>97.95</v>
+        <v>80.53</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>81.67</v>
+        <v>82.58</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>86.14</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>96.43000000000001</v>
+        <v>102.54</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>142.68</v>
+        <v>108.61</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>133.42</v>
+        <v>120.26</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>107.56</v>
+        <v>116.78</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>144.59</v>
+        <v>105.99</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>145.36</v>
+        <v>101.76</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>145.37</v>
+        <v>93.55</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>151.02</v>
+        <v>73.44</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>105.64</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>96.11</v>
+        <v>96.09</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>90.45</v>
+        <v>80.61</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>113.75</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>43.82</v>
+        <v>121.51</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>94.76000000000001</v>
+        <v>80.66</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>68.53</v>
+        <v>41.02</v>
       </c>
     </row>
     <row r="50">
@@ -4613,61 +4613,61 @@
         <v>0.97</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-2.84</v>
+        <v>1.93</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>-4.14</v>
+        <v>3.73</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>-0.32</v>
+        <v>3.97</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>4.05</v>
+        <v>3.29</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>4.07</v>
+        <v>2.85</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-2.91</v>
+        <v>3.37</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.32</v>
+        <v>-1.54</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>3.7</v>
+        <v>2.74</v>
       </c>
       <c r="U51" s="3" t="n">
         <v>3.46</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>4.21</v>
+        <v>3.38</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.45</v>
+        <v>3.89</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.54</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="52">
@@ -4832,10 +4832,10 @@
         <v>0</v>
       </c>
       <c r="Y53" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z53" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4865,61 +4865,61 @@
         <v>59.32</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>77.7</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>105.76</v>
+        <v>82.13</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>83.81999999999999</v>
+        <v>84.14</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>92.56</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>96.53</v>
+        <v>105.33</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>141.82</v>
+        <v>110.98</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>139.65</v>
+        <v>120.76</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>109.08</v>
+        <v>116.18</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>140.82</v>
+        <v>105.44</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>137.84</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>148.42</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>147.41</v>
+        <v>71.27</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>95.09</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>64.16</v>
+        <v>70.77</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>59.16</v>
+        <v>61.35</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>107.92</v>
+        <v>87.89</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>43.64</v>
+        <v>119.78</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>96.26000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>71.01000000000001</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="55">
@@ -4985,13 +4985,13 @@
         <v>0</v>
       </c>
       <c r="T55" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>-22.75</v>
+        <v>-16.61</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>-23.3</v>
+        <v>-14.79</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5033,61 +5033,61 @@
         <v>3.08</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>4.04</v>
+        <v>3.86</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>4.97</v>
+        <v>3.53</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>4.36</v>
+        <v>3.87</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>4.35</v>
+        <v>4.26</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>1.45</v>
+        <v>4.63</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.85</v>
+        <v>4.22</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>2.09</v>
+        <v>4.23</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>1.2</v>
+        <v>3.37</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.28</v>
+        <v>2.74</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-3.45</v>
+        <v>0.8</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.15</v>
+        <v>-1.42</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-6.93</v>
+        <v>-3.71</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-6.85</v>
+        <v>-4.48</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-5.74</v>
+        <v>-5.24</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-5.28</v>
+        <v>-2.06</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.62</v>
+        <v>-0.09</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.27</v>
+        <v>2.16</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.54</v>
+        <v>3.87</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>4.02</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="57">
@@ -5252,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5285,61 +5285,61 @@
         <v>58.1</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>76.17</v>
+        <v>75.86</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>103.91</v>
+        <v>81.37</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>81.34</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>90.38</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>97.31999999999999</v>
+        <v>103.39</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>143.7</v>
+        <v>109.39</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>140.22</v>
+        <v>118.66</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>110.2</v>
+        <v>115.94</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>143.85</v>
+        <v>105.77</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>144.91</v>
+        <v>101.97</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>153.02</v>
+        <v>93.45</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>160.44</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>106.41</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>96.41</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>91.39</v>
+        <v>81.36</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>113.75</v>
+        <v>90.98</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>43.91</v>
+        <v>121.77</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>95.15000000000001</v>
+        <v>81.08</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>69.63</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="60">
@@ -5453,61 +5453,61 @@
         <v>1.86</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="I61" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="S61" s="3" t="n">
         <v>3.12</v>
       </c>
-      <c r="J61" s="3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="P61" s="3" t="n">
+      <c r="T61" s="3" t="n">
         <v>3.31</v>
       </c>
-      <c r="Q61" s="3" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>4.47</v>
-      </c>
       <c r="U61" s="3" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.66</v>
+        <v>3.17</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>4.21</v>
+        <v>3</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.54</v>
+        <v>4.14</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>2.64</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="62">
@@ -5672,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="Y63" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z63" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5705,61 +5705,61 @@
         <v>58.89</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>77.13</v>
+        <v>76.89</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>105.32</v>
+        <v>82.48</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>82.43000000000001</v>
+        <v>84.05</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>91.69</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>98.73999999999999</v>
+        <v>104.68</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>146.08</v>
+        <v>110.75</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>141.95</v>
+        <v>120.01</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>112.03</v>
+        <v>116.66</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>145.94</v>
+        <v>106.87</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>147.18</v>
+        <v>102.82</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>156.24</v>
+        <v>95.03</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>163.15</v>
+        <v>79.34</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>108.21</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>98.04000000000001</v>
+        <v>97.92</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>92.94</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>115.55</v>
+        <v>92.41</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>44.56</v>
+        <v>123.56</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>96.18000000000001</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>70.75</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="65">
@@ -5873,61 +5873,61 @@
         <v>2.65</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>4.53</v>
+        <v>3.88</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="K66" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N66" s="3" t="n">
         <v>3.48</v>
       </c>
-      <c r="L66" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>4.4</v>
-      </c>
       <c r="O66" s="3" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>5.4</v>
+        <v>4.17</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>5.89</v>
+        <v>3.91</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>7.97</v>
+        <v>4.85</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>8.81</v>
+        <v>4.36</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>6.28</v>
+        <v>4.57</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>5.2</v>
+        <v>4.55</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>6.01</v>
+        <v>4.44</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>2.18</v>
+        <v>5.93</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>3.76</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="67">
@@ -6092,10 +6092,10 @@
         <v>0</v>
       </c>
       <c r="Y68" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z68" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6128,58 +6128,58 @@
         <v>90</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>106.66</v>
+        <v>90</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>83.38</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>92.66</v>
+        <v>96.12</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>99.77</v>
+        <v>106</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>147</v>
+        <v>112.03</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>143.43</v>
+        <v>121.13</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>113.09</v>
+        <v>119</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>147.78</v>
+        <v>108.91</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>148.88</v>
+        <v>105</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>157.57</v>
+        <v>96.14</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>165.36</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>109.63</v>
+        <v>81.5</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>99.45999999999999</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>94.38</v>
+        <v>84</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>117.29</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>45.26</v>
+        <v>125.13</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>97.23999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>71.72</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="70">
@@ -6293,61 +6293,61 @@
         <v>3.53</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>5.87</v>
+        <v>5.11</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>3.92</v>
+        <v>5.12</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>4.45</v>
+        <v>5.67</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4.69</v>
+        <v>5.3</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>6.03</v>
+        <v>5.27</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>5.88</v>
+        <v>4.6</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>5.2</v>
+        <v>6.19</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>7.24</v>
+        <v>6.21</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>7.59</v>
+        <v>6.09</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>5.96</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>10.55</v>
+        <v>5.3</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>7.44</v>
+        <v>5.52</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>6.44</v>
+        <v>6.33</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>6.3</v>
+        <v>5.53</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>7.36</v>
+        <v>5.32</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.8</v>
+        <v>7.51</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>4.52</v>
+        <v>4.83</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>4.73</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="72">
@@ -6377,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.72</v>
+        <v>11.97</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>0</v>
@@ -6410,22 +6410,22 @@
         <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="n">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Y73" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z73" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6545,61 +6545,61 @@
         <v>58.22</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>76.25</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>103.91</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>81.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>90.47</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>97.52</v>
+        <v>103.71</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>144.44</v>
+        <v>109.95</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>140.79</v>
+        <v>119.52</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>110.88</v>
+        <v>116.78</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>144.44</v>
+        <v>106.21</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>145.36</v>
+        <v>102.29</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>153.49</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>160.94</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>106.97</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>96.92</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>91.87</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>114.22</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>44.1</v>
+        <v>122.14</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>95.39</v>
+        <v>81.33</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>69.8</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="75">
@@ -6713,61 +6713,61 @@
         <v>1.98</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.04</v>
+        <v>2.83</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>2.26</v>
+        <v>2.99</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>2.44</v>
+        <v>3.01</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>3.47</v>
+        <v>3.19</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>2.99</v>
+        <v>3.97</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>4.07</v>
+        <v>3.38</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>5.22</v>
+        <v>3.56</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>6.6</v>
+        <v>3.37</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>5.03</v>
+        <v>3.65</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>4.13</v>
+        <v>3.6</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>4.68</v>
+        <v>3.38</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.72</v>
+        <v>4.52</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>2.81</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="77">
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="Y78" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z78" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6965,61 +6965,61 @@
         <v>56.24</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>73.66</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>100.79</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>79.45999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>88.20999999999999</v>
+        <v>90.44</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>95.08</v>
+        <v>100.7</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>140.97</v>
+        <v>106.76</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>137.55</v>
+        <v>116.53</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>107.88</v>
+        <v>112.81</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>140.54</v>
+        <v>102.7</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>141.29</v>
+        <v>98.91</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>148.27</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>154.34</v>
+        <v>74.98</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>101.94</v>
+        <v>75.61</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>92.65000000000001</v>
+        <v>92.63</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>78.19</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>109.54</v>
+        <v>87.97</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>42.38</v>
+        <v>117.63</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>92.72</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>66.98999999999999</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="80">
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="Y83" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -7385,61 +7385,61 @@
         <v>59.89</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>78.19</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>106.55</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>84.36</v>
+        <v>84.67</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>93.23999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>94.42</v>
+        <v>105.89</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>138.75</v>
+        <v>111.79</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>141.37</v>
+        <v>121.89</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>106.71</v>
+        <v>116.78</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>136.45</v>
+        <v>105.23</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>134.05</v>
+        <v>99.31</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>148.42</v>
+        <v>85.97</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>145.19</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>93.78</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>63.36</v>
+        <v>69.31</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>58.31</v>
+        <v>62.32</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>108.89</v>
+        <v>88.33</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>44.01</v>
+        <v>116.23</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>96.51000000000001</v>
+        <v>81.42</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>71.01000000000001</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="85">
@@ -7505,13 +7505,13 @@
         <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-22.75</v>
+        <v>-16.61</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>-23.3</v>
+        <v>-14.79</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7553,61 +7553,61 @@
         <v>3.65</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>4.54</v>
+        <v>4.36</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>5.75</v>
+        <v>4.05</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>5.04</v>
+        <v>4.86</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-0.66</v>
+        <v>5.19</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-2.22</v>
+        <v>5.03</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>3.82</v>
+        <v>5.36</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-1.17</v>
+        <v>3.97</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-4.09</v>
+        <v>2.53</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-7.24</v>
+        <v>0.4</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.15</v>
+        <v>-4.21</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-9.15</v>
+        <v>-4.97</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-8.16</v>
+        <v>-5.54</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.54</v>
+        <v>-6.7</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-6.12</v>
+        <v>-1.08</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-0.65</v>
+        <v>0.35</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.63</v>
+        <v>-1.39</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>3.78</v>
+        <v>2.93</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>4.02</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="87">
@@ -7772,10 +7772,10 @@
         <v>0</v>
       </c>
       <c r="Y88" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z88" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7805,61 +7805,61 @@
         <v>54.7</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>71.72</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>97.95</v>
+        <v>79.12</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>76.26000000000001</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>66.8</v>
+        <v>65.23</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>67.08</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>84.23</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>85.22</v>
+        <v>75.8</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>73.26000000000001</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>89.22</v>
+        <v>66.73</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>89.08</v>
+        <v>68.31</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>93.70999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>132.73</v>
+        <v>72.03</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>97.92</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>69.36</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>64.3</v>
+        <v>62.14</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>75</v>
+        <v>65.42</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>40.75</v>
+        <v>75.17</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>75.39</v>
+        <v>56.32</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>42.9</v>
+        <v>39.14</v>
       </c>
     </row>
     <row r="90">
@@ -7895,55 +7895,55 @@
         <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-17.05</v>
+        <v>-21.15</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-22.96</v>
+        <v>-29.33</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-49.64</v>
+        <v>-33.36</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-45.28</v>
+        <v>-34.03</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-28.42</v>
+        <v>-31.98</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-44.76</v>
+        <v>-30.9</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-44.97</v>
+        <v>-25.89</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-46.84</v>
+        <v>-12.64</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-14.41</v>
+        <v>0</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>-18.96</v>
+        <v>-13.84</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-19.42</v>
+        <v>-12.32</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-29.72</v>
+        <v>-18.68</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>0</v>
+        <v>-38.04</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-14.85</v>
+        <v>-19.52</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-22.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7973,61 +7973,61 @@
         <v>-1.53</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-1.94</v>
+        <v>-1.86</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-2.84</v>
+        <v>-1.54</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-3.2</v>
+        <v>-3.31</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.06</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-5.04</v>
+        <v>-5.16</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-7.1</v>
+        <v>-5.08</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-7.05</v>
+        <v>-6.7</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-6.2</v>
+        <v>-7.18</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-6.56</v>
+        <v>-5.08</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-7.24</v>
+        <v>-4.71</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-7.73</v>
+        <v>-4.21</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-7.21</v>
+        <v>-2.95</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-4.01</v>
+        <v>-2.98</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.33</v>
+        <v>-4.07</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4.02</v>
+        <v>-3.72</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-4.82</v>
+        <v>-3.87</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-1.63</v>
+        <v>-4.42</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.48</v>
+        <v>-2.65</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.95</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="92">
@@ -8060,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -8192,10 +8192,10 @@
         <v>0</v>
       </c>
       <c r="Y93" s="3" t="n">
-        <v>19.32</v>
+        <v>0</v>
       </c>
       <c r="Z93" s="3" t="n">
-        <v>-12.77</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-12T12:09:16</t>
+          <t>CreatedAt: 2026-10-12T19:07:59</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -692,34 +692,34 @@
         <v>67.56999999999999</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>68.94</v>
+        <v>68</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>59.53</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>72.94</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>73.41</v>
+        <v>118.37</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>76.17</v>
+        <v>134.13</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>63.37</v>
+        <v>117.66</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>66.65000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>76.38</v>
+        <v>83.08</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>56.91</v>
+        <v>86.08</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>39.22</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="5">
@@ -776,34 +776,34 @@
         <v>-30.9</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-25.89</v>
+        <v>-27.23</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-12.64</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-13.84</v>
+        <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-12.32</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-18.68</v>
+        <v>-23.52</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-38.04</v>
+        <v>-32.31</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-19.52</v>
+        <v>-40.56</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-17.85</v>
       </c>
     </row>
     <row r="6">
@@ -860,34 +860,34 @@
         <v>-4.23</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-4.08</v>
+        <v>-4.12</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-3.3</v>
+        <v>-2.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-2.04</v>
+        <v>-1.67</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.84</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.82</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.5</v>
+        <v>-3.18</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.65</v>
+        <v>-3.4</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.2</v>
+        <v>-3.81</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.06</v>
+        <v>-3.29</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="7">
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
@@ -1112,34 +1112,34 @@
         <v>68.91</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>70.98999999999999</v>
+        <v>70.31</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>75.78</v>
+        <v>60.76</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>74.38</v>
+        <v>70.86</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>74.43000000000001</v>
+        <v>119.54</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>77.06</v>
+        <v>136</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>64.64</v>
+        <v>120.47</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>68.34</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>78.53</v>
+        <v>85.59</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>59.44</v>
+        <v>90.16</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>40.28</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="10">
@@ -1196,34 +1196,34 @@
         <v>-30.9</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-25.89</v>
+        <v>-27.23</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-12.64</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-13.84</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-12.32</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-18.68</v>
+        <v>-23.52</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-38.04</v>
+        <v>-32.31</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-19.52</v>
+        <v>-40.56</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>0</v>
+        <v>-17.85</v>
       </c>
     </row>
     <row r="11">
@@ -1280,34 +1280,34 @@
         <v>-2.89</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-2.03</v>
+        <v>-1.81</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-1.77</v>
+        <v>-0.97</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.21</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.67</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.95</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.23</v>
+        <v>-0.36</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.05</v>
+        <v>-1.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.47</v>
+        <v>0.78</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="12">
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0</v>
@@ -1532,34 +1532,34 @@
         <v>87.72</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>96.88</v>
+        <v>97.55</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>88.41</v>
+        <v>112.22</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>140.66</v>
+        <v>138.82</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>200.74</v>
+        <v>119.54</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1049.97</v>
+        <v>406.66</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>727.35</v>
+        <v>333</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>124.59</v>
+        <v>137.29</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>126.47</v>
+        <v>117.9</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>137.07</v>
+        <v>130.72</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>40.28</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1619,28 +1619,28 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>51.46</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>66.28</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>126.03</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>959.0700000000001</v>
+        <v>270.53</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>650.39</v>
+        <v>212.53</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>37.57</v>
+        <v>16.71</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>58.03</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1700,34 +1700,34 @@
         <v>-2.89</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.03</v>
+        <v>-1.81</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-1.77</v>
+        <v>-0.97</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.21</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.67</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.73</v>
+        <v>-0.82</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.23</v>
+        <v>-0.36</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.96</v>
+        <v>0</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.93</v>
+        <v>-1.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="17">
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
@@ -1952,34 +1952,34 @@
         <v>34.78</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>41.51</v>
+        <v>39.15</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>60.65</v>
+        <v>60.31</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>72.58</v>
+        <v>88.47</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>72.69</v>
+        <v>199.04</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>61.04</v>
+        <v>222.65</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>49.93</v>
+        <v>222.34</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>46.56</v>
+        <v>68.77</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>36.03</v>
+        <v>48.86</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>36.29</v>
+        <v>43.17</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>39.22</v>
+        <v>32.48</v>
       </c>
     </row>
     <row r="20">
@@ -2036,34 +2036,34 @@
         <v>-63.31</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-53.05</v>
+        <v>-55.8</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-25.9</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-28.37</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-25.25</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-38.28</v>
+        <v>-48.19</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-77.95</v>
+        <v>-66.19</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-39.99</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>0</v>
+        <v>-36.56</v>
       </c>
     </row>
     <row r="21">
@@ -2120,34 +2120,34 @@
         <v>-4.61</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-4.35</v>
+        <v>-4.4</v>
       </c>
       <c r="R21" s="3" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="W21" s="3" t="n">
         <v>-3.63</v>
       </c>
-      <c r="S21" s="3" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>-3.14</v>
-      </c>
       <c r="X21" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.14</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.21</v>
+        <v>-3.66</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="22">
@@ -2207,19 +2207,19 @@
         <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0</v>
+        <v>19.33</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0</v>
+        <v>81.13</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0</v>
+        <v>88.78</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>0</v>
+        <v>104.91</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
@@ -2372,34 +2372,34 @@
         <v>67.19</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>68.67</v>
+        <v>67.72</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>73.91</v>
+        <v>59.3</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>72.58</v>
+        <v>69.13</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>72.98</v>
+        <v>117.91</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>75.56999999999999</v>
+        <v>133.87</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>62.86</v>
+        <v>117.43</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>66.15000000000001</v>
+        <v>93.44</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>75.93000000000001</v>
+        <v>82.75</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>56.76</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>39.22</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="25">
@@ -2456,34 +2456,34 @@
         <v>-30.9</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-25.89</v>
+        <v>-27.23</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-12.64</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-13.84</v>
+        <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-12.32</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-18.68</v>
+        <v>-23.52</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-38.04</v>
+        <v>-32.31</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-19.52</v>
+        <v>-40.56</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-17.85</v>
       </c>
     </row>
     <row r="26">
@@ -2540,34 +2540,34 @@
         <v>-4.61</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-4.35</v>
+        <v>-4.4</v>
       </c>
       <c r="R26" s="3" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="W26" s="3" t="n">
         <v>-3.63</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>-3.14</v>
-      </c>
       <c r="X26" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.14</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.21</v>
+        <v>-3.66</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="27">
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2792,34 +2792,34 @@
         <v>34.41</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>41.24</v>
+        <v>38.69</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>60.07</v>
+        <v>60.03</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>72.05</v>
+        <v>198.24</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>60.19</v>
+        <v>222</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>49.22</v>
+        <v>222</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>45.83</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>35.26</v>
+        <v>48.42</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>35.85</v>
+        <v>42.44</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>39.14</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="30">
@@ -2876,34 +2876,34 @@
         <v>-63.31</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-53.05</v>
+        <v>-55.8</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-25.9</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-28.37</v>
+        <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-25.25</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-38.28</v>
+        <v>-48.19</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-77.95</v>
+        <v>-66.19</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-39.99</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0</v>
+        <v>-36.56</v>
       </c>
     </row>
     <row r="31">
@@ -2960,34 +2960,34 @@
         <v>-4.98</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-4.62</v>
+        <v>-4.87</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-4.21</v>
+        <v>-2.71</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-2.88</v>
+        <v>-2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-2.98</v>
+        <v>-4.1</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.07</v>
+        <v>-3.73</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.75</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.87</v>
+        <v>-4.08</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-4.42</v>
+        <v>-4.58</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.65</v>
+        <v>-4.39</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="32">
@@ -3047,19 +3047,19 @@
         <v>0</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0</v>
+        <v>19.33</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>0</v>
+        <v>81.13</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>0</v>
+        <v>88.78</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>0</v>
+        <v>104.91</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
@@ -3212,34 +3212,34 @@
         <v>89.91</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>98.31999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>90.27</v>
+        <v>113.63</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>142.55</v>
+        <v>140.81</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>202.48</v>
+        <v>356</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1051.79</v>
+        <v>409</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>729.29</v>
+        <v>335.58</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>126.79</v>
+        <v>140</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>129.08</v>
+        <v>118.84</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>139.45</v>
+        <v>134.79</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>41.4</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="35">
@@ -3299,28 +3299,28 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>51.46</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>66.28</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>126.03</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>959.0700000000001</v>
+        <v>270.53</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>650.39</v>
+        <v>212.53</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>37.57</v>
+        <v>16.71</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>9.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>58.03</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3380,34 +3380,34 @@
         <v>-1.91</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.2</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.84</v>
+        <v>1.22</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.09</v>
+        <v>1.52</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.71</v>
+        <v>2.21</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.25</v>
+        <v>2.71</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.67</v>
+        <v>-0.36</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.93</v>
+        <v>4.85</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -3470,10 +3470,10 @@
         <v>0</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>0</v>
+        <v>233.56</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
@@ -3632,34 +3632,34 @@
         <v>67.56999999999999</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>68.94</v>
+        <v>68</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>74.23999999999999</v>
+        <v>59.53</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>72.94</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>73.41</v>
+        <v>118.37</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>76.17</v>
+        <v>134.13</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>63.37</v>
+        <v>117.66</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>66.65000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>76.38</v>
+        <v>83.08</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>56.91</v>
+        <v>86.08</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>39.22</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="40">
@@ -3716,34 +3716,34 @@
         <v>-30.9</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-25.89</v>
+        <v>-27.23</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-12.64</v>
+        <v>0</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-13.84</v>
+        <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-12.32</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-18.68</v>
+        <v>-23.52</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-38.04</v>
+        <v>-32.31</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-19.52</v>
+        <v>-40.56</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>-17.85</v>
       </c>
     </row>
     <row r="41">
@@ -3800,34 +3800,34 @@
         <v>-4.23</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-4.08</v>
+        <v>-4.12</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-3.3</v>
+        <v>-2.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-2.04</v>
+        <v>-1.67</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.84</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.61</v>
+        <v>-2.82</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.5</v>
+        <v>-3.18</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.65</v>
+        <v>-3.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.2</v>
+        <v>-3.81</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.06</v>
+        <v>-3.29</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="42">
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
@@ -4052,34 +4052,34 @@
         <v>101.59</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>97.93000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>89.91</v>
+        <v>61.67</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>75.43000000000001</v>
+        <v>71.36</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>76.22</v>
+        <v>120.73</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>93.09</v>
+        <v>135.73</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>78.5</v>
+        <v>120.23</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>87.97</v>
+        <v>119.98</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>117.63</v>
+        <v>118.84</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>78.33</v>
+        <v>129.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>40.12</v>
+        <v>70.22</v>
       </c>
     </row>
     <row r="45">
@@ -4220,34 +4220,34 @@
         <v>-1.12</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.51</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.27</v>
+        <v>-0.06</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>0.61</v>
+        <v>-0.48</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.47</v>
+        <v>-1.22</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.6</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -4472,34 +4472,34 @@
         <v>105.99</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>101.76</v>
+        <v>102.95</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>93.55</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>73.44</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>124.83</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>96.09</v>
+        <v>141.04</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>80.61</v>
+        <v>124.19</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>91.34999999999999</v>
+        <v>124.96</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>121.51</v>
+        <v>123.14</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>80.66</v>
+        <v>133.54</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>41.02</v>
+        <v>71.58</v>
       </c>
     </row>
     <row r="50">
@@ -4640,34 +4640,34 @@
         <v>3.29</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>3.37</v>
+        <v>2.37</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.54</v>
+        <v>-1.53</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>2.74</v>
+        <v>3.62</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>3.46</v>
+        <v>4.09</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>3.38</v>
+        <v>4.37</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.18</v>
+        <v>3.61</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.74</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="52">
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0</v>
@@ -4892,34 +4892,34 @@
         <v>105.44</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>99.70999999999999</v>
+        <v>100.18</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>88.76000000000001</v>
+        <v>62.11</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>71.27</v>
+        <v>67.69</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>70.79000000000001</v>
+        <v>114.24</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>70.77</v>
+        <v>128.95</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>61.35</v>
+        <v>118.35</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>87.89</v>
+        <v>121.92</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>119.78</v>
+        <v>123.65</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>82.36</v>
+        <v>136.2</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>42.31</v>
+        <v>73.84</v>
       </c>
     </row>
     <row r="55">
@@ -4985,13 +4985,13 @@
         <v>0</v>
       </c>
       <c r="T55" s="3" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>-16.61</v>
+        <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>-14.79</v>
+        <v>0</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5060,34 +5060,34 @@
         <v>2.74</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.42</v>
+        <v>0.37</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.38</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-4.48</v>
+        <v>-6.97</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-5.24</v>
+        <v>-8</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-2.06</v>
+        <v>-2.49</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-0.09</v>
+        <v>1.34</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>2.16</v>
+        <v>4.45</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.87</v>
+        <v>6.27</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.03</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="57">
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
@@ -5312,34 +5312,34 @@
         <v>105.77</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>101.97</v>
+        <v>102.95</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>93.45</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>78.93000000000001</v>
+        <v>124.19</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>96.29000000000001</v>
+        <v>139.17</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>81.36</v>
+        <v>123.93</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>90.98</v>
+        <v>123.67</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>121.77</v>
+        <v>122.88</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>81.08</v>
+        <v>134.37</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>41.57</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="60">
@@ -5480,34 +5480,34 @@
         <v>3.07</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>3.27</v>
+        <v>2.37</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>3.31</v>
+        <v>2.98</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>3.66</v>
+        <v>2.23</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>4.14</v>
+        <v>3.69</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.59</v>
+        <v>4.43</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="62">
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
@@ -5732,34 +5732,34 @@
         <v>106.87</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>102.82</v>
+        <v>104.06</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>95.03</v>
+        <v>65.19</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>79.34</v>
+        <v>75.05</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>80.18000000000001</v>
+        <v>127.46</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>97.92</v>
+        <v>141.33</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>126.26</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>92.41</v>
+        <v>125.22</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>123.56</v>
+        <v>123.9</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>136.2</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>42.18</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="65">
@@ -5900,34 +5900,34 @@
         <v>4.17</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>3.91</v>
+        <v>4.71</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>4.36</v>
+        <v>3.98</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>4.57</v>
+        <v>6.25</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5.29</v>
+        <v>4.38</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.55</v>
+        <v>5.43</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>4.44</v>
+        <v>4.63</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>5.93</v>
+        <v>4.71</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>3.7</v>
+        <v>6.27</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.9</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="67">
@@ -6068,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
@@ -6152,34 +6152,34 @@
         <v>108.91</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>96.14</v>
+        <v>65.95</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>80.45999999999999</v>
+        <v>75.61</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>81.5</v>
+        <v>126</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>98.95999999999999</v>
+        <v>140.46</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>93.29000000000001</v>
+        <v>126</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>125.13</v>
+        <v>126</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>83.31999999999999</v>
+        <v>138.08</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>42.62</v>
+        <v>74.47</v>
       </c>
     </row>
     <row r="70">
@@ -6320,34 +6320,34 @@
         <v>6.21</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>6.09</v>
+        <v>6.64</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>5.96</v>
+        <v>4.22</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>5.3</v>
+        <v>4.54</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>5.52</v>
+        <v>4.79</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>6.33</v>
+        <v>3.51</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>5.53</v>
+        <v>5.17</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>5.32</v>
+        <v>5.42</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>7.51</v>
+        <v>6.8</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>4.83</v>
+        <v>8.15</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.34</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="72">
@@ -6410,16 +6410,16 @@
         <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>0</v>
@@ -6572,34 +6572,34 @@
         <v>106.21</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>102.29</v>
+        <v>103.28</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>93.73999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>73.95</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>79.26000000000001</v>
+        <v>124.7</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>96.79000000000001</v>
+        <v>139.89</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>81.79000000000001</v>
+        <v>124.57</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>91.34999999999999</v>
+        <v>124.31</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>122.14</v>
+        <v>123.39</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>81.33</v>
+        <v>134.65</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>41.7</v>
+        <v>72.77</v>
       </c>
     </row>
     <row r="75">
@@ -6740,34 +6740,34 @@
         <v>3.5</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>3.38</v>
+        <v>3.93</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>3.56</v>
+        <v>2.57</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>3.65</v>
+        <v>3.49</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>4.16</v>
+        <v>2.94</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>3.38</v>
+        <v>3.73</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>4.52</v>
+        <v>4.2</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.85</v>
+        <v>4.71</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.42</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="77">
@@ -6908,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         <v>102.7</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>98.91</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>90.18000000000001</v>
+        <v>61.73</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>74.98</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>75.61</v>
+        <v>121.21</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>92.63</v>
+        <v>136.95</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>78.19</v>
+        <v>120.83</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>87.97</v>
+        <v>120.58</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>117.63</v>
+        <v>119.2</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>78.48999999999999</v>
+        <v>129.93</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>40.28</v>
+        <v>70.22</v>
       </c>
     </row>
     <row r="80">
@@ -7328,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
@@ -7412,34 +7412,34 @@
         <v>105.23</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>99.31</v>
+        <v>99.87</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>85.97</v>
+        <v>61.98</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>70.01000000000001</v>
+        <v>66.86</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>69.73999999999999</v>
+        <v>112.44</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>69.31</v>
+        <v>126.69</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>62.32</v>
+        <v>119.05</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>88.33</v>
+        <v>121.92</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>116.23</v>
+        <v>122.88</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>81.42</v>
+        <v>134.51</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>42.36</v>
+        <v>73.84</v>
       </c>
     </row>
     <row r="85">
@@ -7505,13 +7505,13 @@
         <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-16.61</v>
+        <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>-14.79</v>
+        <v>0</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7580,34 +7580,34 @@
         <v>2.53</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="R86" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S86" s="3" t="n">
         <v>-4.21</v>
       </c>
-      <c r="S86" s="3" t="n">
-        <v>-4.97</v>
-      </c>
       <c r="T86" s="3" t="n">
-        <v>-5.54</v>
+        <v>-8.77</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-6.7</v>
+        <v>-10.26</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.08</v>
+        <v>-1.79</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>0.35</v>
+        <v>1.34</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.39</v>
+        <v>3.69</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.93</v>
+        <v>4.57</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.08</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="87">
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>0</v>
@@ -7832,34 +7832,34 @@
         <v>66.73</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>68.31</v>
+        <v>67.25</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>73.33</v>
+        <v>60.03</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>72.03</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>72.34999999999999</v>
+        <v>198.24</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>74.70999999999999</v>
+        <v>222</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>62.14</v>
+        <v>222</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>65.42</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>75.17</v>
+        <v>82.31</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>56.32</v>
+        <v>84.98</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>39.14</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="90">
@@ -7916,34 +7916,34 @@
         <v>-30.9</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-25.89</v>
+        <v>-27.23</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-12.64</v>
+        <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>-13.84</v>
+        <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-12.32</v>
+        <v>0</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-18.68</v>
+        <v>-23.52</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-38.04</v>
+        <v>-32.31</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-19.52</v>
+        <v>-40.56</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>0</v>
+        <v>-17.85</v>
       </c>
     </row>
     <row r="91">
@@ -8000,34 +8000,34 @@
         <v>-5.08</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-4.71</v>
+        <v>-4.87</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-4.21</v>
+        <v>-2.71</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-2.95</v>
+        <v>-2.47</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-2.98</v>
+        <v>-4.1</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.07</v>
+        <v>-3.73</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.75</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.87</v>
+        <v>-4.08</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-4.42</v>
+        <v>-4.58</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.65</v>
+        <v>-4.39</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.14</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="92">
@@ -8087,19 +8087,19 @@
         <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>19.33</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>81.13</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>0</v>
+        <v>88.78</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>0</v>
+        <v>104.91</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>0</v>
+        <v>-2.93</v>
       </c>
       <c r="R93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-12T19:07:59</t>
+          <t>CreatedAt: 2026-10-13T01:12:37</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>51.44</v>
+        <v>32.8</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>53.3</v>
+        <v>33.11</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>45.38</v>
+        <v>33.62</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>46.4</v>
+        <v>32.85</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>55.13</v>
+        <v>37.85</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>72.13</v>
+        <v>71.75</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>77.44</v>
+        <v>49.52</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>76.73</v>
+        <v>110.85</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>66.48999999999999</v>
+        <v>80.22</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>67.5</v>
+        <v>63.68</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>69.29000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>76.95</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>75.05</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>67.56999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>68</v>
+        <v>84.55</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>59.53</v>
+        <v>84.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>79.39</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>118.37</v>
+        <v>81.09</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>134.13</v>
+        <v>106.84</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>117.66</v>
+        <v>76.3</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>93.67</v>
+        <v>48.9</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>83.08</v>
+        <v>59.83</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>86.08</v>
+        <v>38.21</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>51.07</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="5">
@@ -749,61 +749,61 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0</v>
+        <v>-21.74</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-1.2</v>
+        <v>-28.47</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-21.15</v>
+        <v>-48.79</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-29.33</v>
+        <v>-29.88</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-33.36</v>
+        <v>-52.94</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-34.03</v>
+        <v>-50.3</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-31.98</v>
+        <v>-50.43</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-30.9</v>
+        <v>-50.41</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-27.23</v>
+        <v>-50.18</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>-47.71</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0</v>
+        <v>-15.74</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0</v>
+        <v>-3.69</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0</v>
+        <v>-46.13</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-23.52</v>
+        <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-32.31</v>
+        <v>-17.44</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-40.56</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-17.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-1.23</v>
+        <v>-0.52</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.43</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.54</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.62</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-1.1</v>
+        <v>-0.87</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-1.3</v>
+        <v>-2.71</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.44</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-2.34</v>
+        <v>-3.08</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-2.8</v>
+        <v>-4.89</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-3.87</v>
+        <v>-3.56</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-4.11</v>
+        <v>-5.14</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.02</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-5.78</v>
+        <v>-5.15</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-4.23</v>
+        <v>-5.54</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-4.12</v>
+        <v>-5.66</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-2.2</v>
+        <v>-5.56</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-1.67</v>
+        <v>-3.42</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-2.84</v>
+        <v>-2.97</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.82</v>
+        <v>-6.58</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>-3.18</v>
       </c>
       <c r="W6" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="X6" s="3" t="n">
         <v>-3.4</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>-3.81</v>
-      </c>
       <c r="Y6" s="3" t="n">
-        <v>-3.29</v>
+        <v>-1.53</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.31</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>52.36</v>
+        <v>33.39</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>55.4</v>
+        <v>33.99</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>47.23</v>
+        <v>33.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>48</v>
+        <v>32.92</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>56.29</v>
+        <v>38.41</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>73.06</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>79.08</v>
+        <v>49.62</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>77.34</v>
+        <v>112.67</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>67</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>67.59</v>
+        <v>65.89</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>69.98999999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>77.59</v>
+        <v>89.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>73.45</v>
+        <v>88.06</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>68.91</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>70.31</v>
+        <v>88.13</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>60.76</v>
+        <v>87.03</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>70.86</v>
+        <v>81.17</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>119.54</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>136</v>
+        <v>109.68</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>120.47</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>97.06999999999999</v>
+        <v>49.91</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>85.59</v>
+        <v>61.27</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>90.16</v>
+        <v>39.34</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>53.3</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="10">
@@ -1169,61 +1169,61 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>-21.74</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-1.2</v>
+        <v>-28.47</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-21.15</v>
+        <v>-48.79</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-29.33</v>
+        <v>-29.88</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-33.36</v>
+        <v>-52.94</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-34.03</v>
+        <v>-50.3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-31.98</v>
+        <v>-50.43</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-30.9</v>
+        <v>-50.41</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-27.23</v>
+        <v>-50.18</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>-47.71</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>-15.74</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>-3.69</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0</v>
+        <v>-46.13</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-23.52</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-32.31</v>
+        <v>-17.44</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-40.56</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-17.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>-0.31</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.06</v>
-      </c>
       <c r="H11" s="3" t="n">
-        <v>-0.37</v>
+        <v>-1.89</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.47</v>
+        <v>-1.34</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.25</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.69</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-3.78</v>
+        <v>-1.34</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-3.41</v>
+        <v>-1.09</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-4.91</v>
+        <v>-0.98</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-7.38</v>
+        <v>-2.08</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.89</v>
+        <v>-1.12</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-1.81</v>
+        <v>-2.07</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.97</v>
+        <v>-3.23</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.21</v>
+        <v>-1.65</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.13</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-0.95</v>
+        <v>-3.74</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.36</v>
+        <v>-1.66</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.97</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.78</v>
+        <v>-0.39</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="12">
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>52.36</v>
+        <v>33.42</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>59.42</v>
+        <v>33.99</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>60.09</v>
+        <v>33.86</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>267.17</v>
+        <v>32.95</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>56.29</v>
+        <v>38.41</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>73.06</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>79.08</v>
+        <v>49.62</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>78.54000000000001</v>
+        <v>133.14</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>88.15000000000001</v>
+        <v>97.59</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>78.23</v>
+        <v>95.78</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>79.78</v>
+        <v>135.76</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>95.66</v>
+        <v>139.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>131.68</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>87.72</v>
+        <v>139.48</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>97.55</v>
+        <v>131.85</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>112.22</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>138.82</v>
+        <v>96.91</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>119.54</v>
+        <v>134.77</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>406.66</v>
+        <v>100.45</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>333</v>
+        <v>98.03</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>137.29</v>
+        <v>49.91</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>117.9</v>
+        <v>78.7</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>130.72</v>
+        <v>53.9</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>71.15000000000001</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="15">
@@ -1577,13 +1577,13 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>12.86</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>219.12</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1595,52 +1595,52 @@
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>-33.63</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>-18.69</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>-23.57</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>-16.07</v>
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-17.03</v>
+        <v>-6.81</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>-12.09</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0</v>
+        <v>-6.47</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>51.46</v>
+        <v>-37.78</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>67.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>48.16</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>270.53</v>
+        <v>-55.36</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>212.53</v>
+        <v>18.86</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>14.56</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>-0.31</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0.06</v>
-      </c>
       <c r="H16" s="3" t="n">
-        <v>-0.37</v>
+        <v>-1.79</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.47</v>
+        <v>-1.34</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.25</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.69</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-3.78</v>
+        <v>-1.34</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.41</v>
+        <v>-1.09</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-4.8</v>
+        <v>-0.98</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-7.38</v>
+        <v>-2.08</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.89</v>
+        <v>-1.12</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-1.81</v>
+        <v>-2.07</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-0.97</v>
+        <v>-3.23</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-0.21</v>
+        <v>-1.65</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.67</v>
+        <v>-1.13</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-0.82</v>
+        <v>-3.74</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.36</v>
+        <v>-1.66</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>0</v>
+        <v>-1.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.97</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.78</v>
+        <v>-0.39</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.92</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="17">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>51.34</v>
+        <v>32.7</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>53.3</v>
+        <v>33.19</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>45.47</v>
+        <v>33.49</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>46.45</v>
+        <v>32.79</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>55.03</v>
+        <v>37.7</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>71.92</v>
+        <v>48.41</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>79.42</v>
+        <v>49.23</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>80.69</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>43.8</v>
+        <v>28.66</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>36.19</v>
+        <v>32.24</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>33.92</v>
+        <v>23.37</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>40.73</v>
+        <v>32.35</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>40.8</v>
+        <v>31.81</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>34.78</v>
+        <v>31.62</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>39.15</v>
+        <v>31.63</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>60.31</v>
+        <v>34.12</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>88.47</v>
+        <v>62.41</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>199.04</v>
+        <v>76.89</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>222.65</v>
+        <v>57.71</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>222.34</v>
+        <v>74.44</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>68.77</v>
+        <v>48.62</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>48.86</v>
+        <v>41.25</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>43.17</v>
+        <v>38.1</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.48</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="20">
@@ -2009,61 +2009,61 @@
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0</v>
+        <v>-44.53</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-2.46</v>
+        <v>-58.33</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-43.33</v>
+        <v>-99.97</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-60.09</v>
+        <v>-61.23</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-68.34</v>
+        <v>-108.47</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-69.72</v>
+        <v>-103.08</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-65.52</v>
+        <v>-103.35</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-63.31</v>
+        <v>-103.31</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-55.8</v>
+        <v>-102.85</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0</v>
+        <v>-97.78</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0</v>
+        <v>-32.27</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0</v>
+        <v>-7.55</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0</v>
+        <v>-94.53</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0</v>
+        <v>-2.76</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-48.19</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-66.19</v>
+        <v>-35.72</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-83.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-36.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.62</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.5</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.02</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-1.51</v>
+        <v>-3.25</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.72</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-2.71</v>
+        <v>-3.38</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-3.31</v>
+        <v>-5.28</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-4.43</v>
+        <v>-3.65</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-4.5</v>
+        <v>-5.01</v>
       </c>
       <c r="N21" s="3" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="R21" s="3" t="n">
         <v>-6.07</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>-6.49</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-2.43</v>
-      </c>
       <c r="S21" s="3" t="n">
-        <v>-1.94</v>
+        <v>-3.88</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3.29</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.08</v>
+        <v>-7.31</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.41</v>
+        <v>-3.63</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-3.63</v>
+        <v>-2.38</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-4.14</v>
+        <v>-3.69</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-3.66</v>
+        <v>-1.64</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.17</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="22">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2207,19 +2207,19 @@
         <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19.33</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>81.13</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>88.78</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>104.91</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2267,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>51.34</v>
+        <v>32.7</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>53.3</v>
+        <v>33.05</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>45.47</v>
+        <v>33.49</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>46.45</v>
+        <v>32.79</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>55.03</v>
+        <v>37.7</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>71.92</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>77.36</v>
+        <v>49.23</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>76.36</v>
+        <v>110.55</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>65.98</v>
+        <v>79.84</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>66.94</v>
+        <v>63.59</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>76.42</v>
+        <v>85.13</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>74.34999999999999</v>
+        <v>84.73</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>67.19</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>67.72</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>59.3</v>
+        <v>84.19</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>69.13</v>
+        <v>78.94</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>117.91</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>133.87</v>
+        <v>106.11</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>117.43</v>
+        <v>75.86</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>93.44</v>
+        <v>48.62</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>82.75</v>
+        <v>59.54</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>85.70999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>51.2</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="25">
@@ -2429,61 +2429,61 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>-21.74</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-1.2</v>
+        <v>-28.47</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-21.15</v>
+        <v>-48.79</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-29.33</v>
+        <v>-29.88</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-33.36</v>
+        <v>-52.94</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-34.03</v>
+        <v>-50.3</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-31.98</v>
+        <v>-50.43</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-30.9</v>
+        <v>-50.41</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-27.23</v>
+        <v>-50.18</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0</v>
+        <v>-47.71</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0</v>
+        <v>-15.74</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0</v>
+        <v>-3.69</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0</v>
+        <v>-46.13</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-23.52</v>
+        <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-32.31</v>
+        <v>-17.44</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-40.56</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-17.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.62</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.5</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-1.21</v>
+        <v>-1.02</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-1.51</v>
+        <v>-3.25</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-1.24</v>
+        <v>-1.72</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-2.71</v>
+        <v>-3.38</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-3.31</v>
+        <v>-5.28</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-4.43</v>
+        <v>-3.65</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-4.5</v>
+        <v>-5.01</v>
       </c>
       <c r="N26" s="3" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>-6.07</v>
       </c>
-      <c r="O26" s="3" t="n">
-        <v>-6.49</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-4.61</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-2.43</v>
-      </c>
       <c r="S26" s="3" t="n">
-        <v>-1.94</v>
+        <v>-3.88</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3.29</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.08</v>
+        <v>-7.31</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.41</v>
+        <v>-3.63</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-3.63</v>
+        <v>-2.38</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-4.14</v>
+        <v>-3.69</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-3.66</v>
+        <v>-1.64</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.17</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="27">
@@ -2687,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>51.09</v>
+        <v>32.51</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>53.14</v>
+        <v>33</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>45.43</v>
+        <v>33.33</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>46.35</v>
+        <v>32.69</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>54.7</v>
+        <v>37.48</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>71.56999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>79.12</v>
+        <v>48.81</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>74.51000000000001</v>
+        <v>80</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>43.05</v>
+        <v>28.03</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>35.45</v>
+        <v>31.79</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>33.33</v>
+        <v>22.99</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>40.11</v>
+        <v>31.83</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>40.11</v>
+        <v>31.29</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>34.41</v>
+        <v>30.97</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>38.69</v>
+        <v>30.98</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>60.03</v>
+        <v>33.24</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>88</v>
+        <v>61.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>198.24</v>
+        <v>76.25</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>222</v>
+        <v>56.7</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>222</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>68.31999999999999</v>
+        <v>48.25</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>48.42</v>
+        <v>40.88</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>42.44</v>
+        <v>37.88</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.62</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="30">
@@ -2849,61 +2849,61 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0</v>
+        <v>-44.53</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-2.46</v>
+        <v>-58.33</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-43.33</v>
+        <v>-99.97</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-60.09</v>
+        <v>-61.23</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-68.34</v>
+        <v>-108.47</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-69.72</v>
+        <v>-103.08</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-65.52</v>
+        <v>-103.35</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-63.31</v>
+        <v>-103.31</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-55.8</v>
+        <v>-102.85</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0</v>
+        <v>-97.78</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0</v>
+        <v>-32.27</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>0</v>
+        <v>-7.55</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>0</v>
+        <v>-94.53</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>0</v>
+        <v>-2.76</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-48.19</v>
+        <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-66.19</v>
+        <v>-35.72</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-83.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-36.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-1.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-1.49</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.83</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.78</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.24</v>
       </c>
       <c r="H31" s="3" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>-6.94</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>-1.86</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>-5.08</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>-7.18</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>-4.39</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="32">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3047,19 +3047,19 @@
         <v>0</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>19.33</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>81.13</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>88.78</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>104.91</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>53.59</v>
+        <v>34.28</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61.22</v>
+        <v>35.01</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>61.52</v>
+        <v>34.51</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>268.47</v>
+        <v>33.34</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>57.74</v>
+        <v>39.23</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>74.93000000000001</v>
+        <v>96.39</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>80.53</v>
+        <v>50.21</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>80.19</v>
+        <v>135.14</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>89.98999999999999</v>
+        <v>100.15</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>82</v>
+        <v>97.8</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>84.06999999999999</v>
+        <v>139.07</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>97.91</v>
+        <v>143.3</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>89.91</v>
+        <v>134.46</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>89.91</v>
+        <v>143.31</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>99.15000000000001</v>
+        <v>135.63</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>113.63</v>
+        <v>99.64</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>140.81</v>
+        <v>99.36</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>356</v>
+        <v>136.87</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>409</v>
+        <v>103.88</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>335.58</v>
+        <v>100.01</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>140</v>
+        <v>51.05</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>118.84</v>
+        <v>80.27</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>134.79</v>
+        <v>54.86</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>73.22</v>
+        <v>33.12</v>
       </c>
     </row>
     <row r="35">
@@ -3257,13 +3257,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>12.86</v>
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>219.12</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0</v>
@@ -3275,52 +3275,52 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>-33.63</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-16.82</v>
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>-21.22</v>
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-14.46</v>
+        <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-15.32</v>
+        <v>-6.81</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>-10.88</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>-6.47</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>51.46</v>
+        <v>-37.78</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>67.95999999999999</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>48.16</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>270.53</v>
+        <v>-55.36</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>212.53</v>
+        <v>18.86</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>14.56</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.19</v>
+        <v>0.35</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.97</v>
+        <v>-0.13</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.5</v>
+        <v>0.51</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.5</v>
+        <v>0.19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.93</v>
+        <v>-0.75</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.08</v>
+        <v>0.75</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.14</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-1.88</v>
+        <v>0.68</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-1.47</v>
+        <v>2.23</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-4.16</v>
+        <v>2.72</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-7.58</v>
+        <v>0.71</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-1.91</v>
+        <v>2.72</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.2</v>
+        <v>1.71</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.44</v>
+        <v>-0.55</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.6</v>
+        <v>0.79</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.22</v>
+        <v>0.98</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.52</v>
+        <v>-0.32</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.21</v>
+        <v>0.32</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.71</v>
+        <v>0.05</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.4</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>4.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>3</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="37">
@@ -3470,10 +3470,10 @@
         <v>0</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>233.56</v>
+        <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>51.44</v>
+        <v>32.8</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>53.3</v>
+        <v>33.11</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>45.38</v>
+        <v>33.62</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>46.4</v>
+        <v>32.85</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>55.13</v>
+        <v>37.85</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>72.13</v>
+        <v>71.75</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>77.44</v>
+        <v>49.52</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>76.73</v>
+        <v>110.85</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>66.48999999999999</v>
+        <v>80.22</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>67.5</v>
+        <v>63.68</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>69.29000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>76.95</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>75.05</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>67.56999999999999</v>
+        <v>84.64</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>68</v>
+        <v>84.55</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>59.53</v>
+        <v>84.7</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>79.39</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>118.37</v>
+        <v>81.09</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>134.13</v>
+        <v>106.84</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>117.66</v>
+        <v>76.3</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>93.67</v>
+        <v>48.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>83.08</v>
+        <v>59.83</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>86.08</v>
+        <v>38.21</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>51.07</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="40">
@@ -3689,61 +3689,61 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>-21.74</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-1.2</v>
+        <v>-28.47</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-21.15</v>
+        <v>-48.79</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-29.33</v>
+        <v>-29.88</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-33.36</v>
+        <v>-52.94</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-34.03</v>
+        <v>-50.3</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-31.98</v>
+        <v>-50.43</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-30.9</v>
+        <v>-50.41</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-27.23</v>
+        <v>-50.18</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>-47.71</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>-15.74</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>-3.69</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>0</v>
+        <v>-46.13</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-23.52</v>
+        <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-32.31</v>
+        <v>-17.44</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-40.56</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-17.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-1.23</v>
+        <v>-0.52</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.43</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-1.09</v>
+        <v>-0.54</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.62</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-1.1</v>
+        <v>-0.87</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-1.3</v>
+        <v>-2.71</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.44</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-2.34</v>
+        <v>-3.08</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-2.8</v>
+        <v>-4.89</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-3.87</v>
+        <v>-3.56</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-4.11</v>
+        <v>-5.14</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.02</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-5.78</v>
+        <v>-5.15</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-4.23</v>
+        <v>-5.54</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-4.12</v>
+        <v>-5.66</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-2.2</v>
+        <v>-5.56</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-1.67</v>
+        <v>-3.42</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-2.84</v>
+        <v>-2.97</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.82</v>
+        <v>-6.58</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>-3.18</v>
       </c>
       <c r="W41" s="3" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>-3.4</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>-3.81</v>
-      </c>
       <c r="Y41" s="3" t="n">
-        <v>-3.29</v>
+        <v>-1.53</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.31</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>52.52</v>
+        <v>33.49</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>54.52</v>
+        <v>33.68</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>46.29</v>
+        <v>34.33</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>47.28</v>
+        <v>33.65</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>56.18</v>
+        <v>38.84</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>73.43000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>78.76000000000001</v>
+        <v>50.91</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>80.03</v>
+        <v>141.66</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>90.17</v>
+        <v>132.28</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>99.7</v>
+        <v>94.75</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>105.49</v>
+        <v>133.51</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>114.36</v>
+        <v>137.82</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>111.25</v>
+        <v>137.81</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>101.59</v>
+        <v>137.03</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>98.84999999999999</v>
+        <v>136.7</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>61.67</v>
+        <v>135</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>71.36</v>
+        <v>97.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>120.73</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>135.73</v>
+        <v>158.44</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>120.23</v>
+        <v>80.11</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>119.98</v>
+        <v>50.55</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>118.84</v>
+        <v>80.11</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>129.8</v>
+        <v>39.54</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>70.22</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>-0.16</v>
+        <v>0.17</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.19</v>
+        <v>0.17</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>-0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.16</v>
+        <v>-0.05</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.74</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.27</v>
+        <v>-1.63</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1</v>
+        <v>-2.37</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-1.27</v>
+        <v>-3.34</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-2.17</v>
+        <v>-2.76</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1.56</v>
+        <v>-2.76</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.12</v>
+        <v>-3.56</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-3.69</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.06</v>
+        <v>-2.97</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0.29</v>
+        <v>-1.26</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.78</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.11</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.72</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.45</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>53.59</v>
+        <v>33.93</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>55.74</v>
+        <v>34.12</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>47.08</v>
+        <v>34.82</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>48.05</v>
+        <v>34.27</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>57.21</v>
+        <v>39.92</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>74.93000000000001</v>
+        <v>100.21</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>80.53</v>
+        <v>52.59</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>82.58</v>
+        <v>145.44</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>88.15000000000001</v>
+        <v>137.43</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>102.54</v>
+        <v>100.12</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>108.61</v>
+        <v>140.5</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>120.26</v>
+        <v>144.33</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>116.78</v>
+        <v>144.02</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>105.99</v>
+        <v>144.05</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>102.95</v>
+        <v>144.14</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>134.74</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>69.54000000000001</v>
+        <v>97.59</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>124.83</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>141.04</v>
+        <v>156.27</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>124.19</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>124.96</v>
+        <v>52.04</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>123.14</v>
+        <v>83.16</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>133.54</v>
+        <v>40.8</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>71.58</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.91</v>
+        <v>0.61</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1.11</v>
+        <v>0.58</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.97</v>
+        <v>1.2</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.5</v>
+        <v>4.01</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2.31</v>
+        <v>3.05</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>-2.29</v>
+        <v>3.52</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>1.85</v>
+        <v>3.65</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.97</v>
+        <v>3.46</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>3.29</v>
+        <v>3.46</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>2.37</v>
+        <v>-3.23</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.53</v>
+        <v>-0.98</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>3.62</v>
+        <v>-0.7</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>4.09</v>
+        <v>-3.28</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>3.35</v>
+        <v>2.16</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>4.37</v>
+        <v>1.04</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>3.94</v>
+        <v>2.49</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>3.61</v>
+        <v>1.06</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.36</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="52">
@@ -4787,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>55.28</v>
+        <v>34.71</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>57.75</v>
+        <v>35.09</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>49.02</v>
+        <v>35.59</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>50.03</v>
+        <v>35.02</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>59.32</v>
+        <v>40.59</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>77.29000000000001</v>
+        <v>100.41</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>82.13</v>
+        <v>51.37</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>84.14</v>
+        <v>132.22</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>94.70999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>105.33</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>110.98</v>
+        <v>137.54</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>120.76</v>
+        <v>137.15</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>116.18</v>
+        <v>131.27</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>105.44</v>
+        <v>137.56</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>100.18</v>
+        <v>134.06</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>62.11</v>
+        <v>95.91</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>67.69</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>114.24</v>
+        <v>77.5</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>128.95</v>
+        <v>93.06</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>118.35</v>
+        <v>74.84</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>121.92</v>
+        <v>47.85</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>123.65</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>136.2</v>
+        <v>41.61</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>73.84</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="55">
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0</v>
+        <v>-33.63</v>
       </c>
       <c r="L55" s="3" t="n">
         <v>0</v>
@@ -4970,25 +4970,25 @@
         <v>0</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>0</v>
+        <v>-6.81</v>
       </c>
       <c r="P55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>0</v>
+        <v>-6.47</v>
       </c>
       <c r="R55" s="3" t="n">
-        <v>0</v>
+        <v>-37.78</v>
       </c>
       <c r="S55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="3" t="n">
-        <v>0</v>
+        <v>-4.42</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>0</v>
+        <v>-55.36</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>0</v>
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>3.12</v>
+        <v>1.54</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2.55</v>
+        <v>1.42</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>2.65</v>
+        <v>1.54</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3.08</v>
+        <v>1.87</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>3.86</v>
+        <v>4.22</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>3.53</v>
+        <v>0.41</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>3.87</v>
+        <v>-2.18</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>4.26</v>
+        <v>-4.38</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>4.63</v>
+        <v>0.78</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>4.22</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>4.23</v>
+        <v>-3.43</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>3.37</v>
+        <v>-2.49</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>2.74</v>
+        <v>-3.03</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.82</v>
+        <v>0.14</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0.37</v>
+        <v>-4.28</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-3.38</v>
+        <v>-5.49</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-6.97</v>
+        <v>-5.82</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-8</v>
+        <v>-11.13</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-2.49</v>
+        <v>-5.99</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>1.34</v>
+        <v>-3.16</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>4.45</v>
+        <v>0.65</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>6.27</v>
+        <v>1.87</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>3.62</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="57">
@@ -5207,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>54.36</v>
+        <v>34.6</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>56.43</v>
+        <v>34.8</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>47.96</v>
+        <v>35.44</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>48.89</v>
+        <v>34.73</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>58.1</v>
+        <v>40.12</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>75.86</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>81.37</v>
+        <v>52.53</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>83.01000000000001</v>
+        <v>145.22</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>93.43000000000001</v>
+        <v>137.14</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>103.39</v>
+        <v>97.8</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>109.39</v>
+        <v>137.81</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>118.66</v>
+        <v>141.86</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>115.94</v>
+        <v>141.7</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>105.77</v>
+        <v>141.58</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>102.95</v>
+        <v>141.1</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>64.09999999999999</v>
+        <v>139.23</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>73.8</v>
+        <v>99.86</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>124.19</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>139.17</v>
+        <v>163.14</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>123.93</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>123.67</v>
+        <v>52.2</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>122.88</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>134.37</v>
+        <v>40.84</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>72.62</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.69</v>
+        <v>1.28</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T61" s="3" t="n">
         <v>1.52</v>
       </c>
-      <c r="G61" s="3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>2.98</v>
-      </c>
       <c r="U61" s="3" t="n">
-        <v>2.23</v>
+        <v>3.59</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>3.09</v>
+        <v>1.2</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>3.69</v>
+        <v>2.07</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>4.43</v>
+        <v>1.1</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>2.4</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="62">
@@ -5627,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>55.1</v>
+        <v>35.04</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>57.2</v>
+        <v>35.2</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>48.56</v>
+        <v>35.88</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>49.55</v>
+        <v>35.17</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>58.89</v>
+        <v>40.63</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>76.89</v>
+        <v>100.52</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>82.48</v>
+        <v>53.25</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>84.05</v>
+        <v>146.8</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>94.20999999999999</v>
+        <v>139.33</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>104.68</v>
+        <v>99.2</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>110.75</v>
+        <v>139.78</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>120.01</v>
+        <v>143.74</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>116.66</v>
+        <v>143.87</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>106.87</v>
+        <v>143.46</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>104.06</v>
+        <v>143.7</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>65.19</v>
+        <v>141.22</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>75.05</v>
+        <v>101.4</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>127.46</v>
+        <v>90.64</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>141.33</v>
+        <v>165.85</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>126.26</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>125.22</v>
+        <v>53.02</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>123.9</v>
+        <v>84.03</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>136.2</v>
+        <v>41.44</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>73.61</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.42</v>
+        <v>1.72</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>2.57</v>
+        <v>1.65</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.18</v>
+        <v>1.69</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>3.46</v>
+        <v>4.32</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3.88</v>
+        <v>2.29</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>3.78</v>
+        <v>4.41</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>3.77</v>
+        <v>5.42</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>3.98</v>
+        <v>2.08</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>3.99</v>
+        <v>2.94</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>3.48</v>
+        <v>3.16</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.85</v>
+        <v>3.31</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>4.17</v>
+        <v>2.87</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>4.71</v>
+        <v>3.31</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>3.98</v>
+        <v>2.84</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>6.25</v>
+        <v>2.9</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>4.38</v>
+        <v>6.3</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>5.43</v>
+        <v>2.93</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>4.63</v>
+        <v>2.01</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>4.71</v>
+        <v>3.36</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>6.27</v>
+        <v>1.7</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>3.39</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="67">
@@ -6047,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6068,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>55.92</v>
+        <v>35.56</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>58.05</v>
+        <v>35.76</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>49.33</v>
+        <v>36.42</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>50.29</v>
+        <v>35.69</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>59.76</v>
+        <v>41.15</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>90</v>
+        <v>101.26</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>90</v>
+        <v>53.64</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>147.61</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>96.12</v>
+        <v>140.37</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>106</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>112.03</v>
+        <v>139.64</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>121.13</v>
+        <v>143.6</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>119</v>
+        <v>143.58</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>108.91</v>
+        <v>143.46</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>106</v>
+        <v>142.96</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>65.95</v>
+        <v>141.08</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>75.61</v>
+        <v>100.78</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>126</v>
+        <v>90.27</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>140.46</v>
+        <v>166.2</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>126</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>126</v>
+        <v>53.07</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>126</v>
+        <v>84.56</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>138.08</v>
+        <v>41.83</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>74.47</v>
+        <v>35.32</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3.24</v>
+        <v>2.24</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.43</v>
+        <v>2.22</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.86</v>
+        <v>2.26</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>3.53</v>
+        <v>2.43</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>4.6</v>
+        <v>5.06</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>5.11</v>
+        <v>2.68</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>5.67</v>
+        <v>6.46</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>5.3</v>
+        <v>1.98</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5.27</v>
+        <v>2.79</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>6.19</v>
+        <v>3.02</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>6.21</v>
+        <v>2.87</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>6.64</v>
+        <v>2.57</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>4.22</v>
+        <v>3.1</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>4.54</v>
+        <v>2.22</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>4.79</v>
+        <v>2.53</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.51</v>
+        <v>6.65</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>5.17</v>
+        <v>2.93</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>5.42</v>
+        <v>2.07</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>6.8</v>
+        <v>3.89</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>8.15</v>
+        <v>2.09</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>4.24</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="72">
@@ -6377,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11.97</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>0</v>
@@ -6467,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>54.48</v>
+        <v>34.64</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>56.55</v>
+        <v>34.8</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>48.01</v>
+        <v>35.47</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>48.99</v>
+        <v>34.76</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>58.22</v>
+        <v>40.21</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>76.01000000000001</v>
+        <v>99.58</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>81.54000000000001</v>
+        <v>52.75</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>145.56</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>93.43000000000001</v>
+        <v>137.72</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>103.71</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>109.95</v>
+        <v>138.65</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>119.52</v>
+        <v>142.72</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>116.78</v>
+        <v>142.56</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>106.21</v>
+        <v>142.44</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>103.28</v>
+        <v>141.67</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>64.3</v>
+        <v>139.51</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>73.95</v>
+        <v>100.27</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>124.7</v>
+        <v>89.53</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>139.89</v>
+        <v>163.81</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>124.57</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>124.31</v>
+        <v>52.47</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>123.39</v>
+        <v>83.16</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>134.65</v>
+        <v>41.01</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>72.77</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M76" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>3.19</v>
-      </c>
       <c r="N76" s="3" t="n">
-        <v>2.99</v>
+        <v>2.14</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.97</v>
+        <v>2</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>3.93</v>
+        <v>1.27</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>3.49</v>
+        <v>1.79</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.94</v>
+        <v>4.26</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.74</v>
+        <v>2.07</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>3.73</v>
+        <v>1.47</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>4.2</v>
+        <v>2.49</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>4.71</v>
+        <v>1.27</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>2.55</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="77">
@@ -6887,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6908,7 +6908,7 @@
         <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>52.68</v>
+        <v>33.32</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>54.63</v>
+        <v>33.54</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>46.47</v>
+        <v>34.16</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>47.37</v>
+        <v>33.48</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>56.24</v>
+        <v>38.72</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>73.43000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>50.96</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>80.27</v>
+        <v>142.4</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>90.44</v>
+        <v>133.91</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>100.7</v>
+        <v>97.12</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>106.76</v>
+        <v>136.85</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>116.53</v>
+        <v>140.58</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>112.81</v>
+        <v>140.57</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>102.7</v>
+        <v>140.59</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>99.34999999999999</v>
+        <v>140.39</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>61.73</v>
+        <v>137.97</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>71.06999999999999</v>
+        <v>98.56</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>121.21</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>136.95</v>
+        <v>159.55</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>120.83</v>
+        <v>80.83</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>120.58</v>
+        <v>51</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>119.2</v>
+        <v>80.67</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>129.93</v>
+        <v>39.74</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>70.22</v>
+        <v>33.52</v>
       </c>
     </row>
     <row r="80">
@@ -7307,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7328,7 +7328,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>54.99</v>
+        <v>34.17</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>58.12</v>
+        <v>34.72</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>49.28</v>
+        <v>35.04</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>50.4</v>
+        <v>34.58</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>59.89</v>
+        <v>40.25</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>77.79000000000001</v>
+        <v>99.17</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>49.86</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>84.67</v>
+        <v>128.5</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>95.3</v>
+        <v>90.36</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>105.89</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>111.79</v>
+        <v>134.43</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>121.89</v>
+        <v>130.05</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>116.78</v>
+        <v>124.56</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>105.23</v>
+        <v>129.7</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>99.87</v>
+        <v>129.97</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>61.98</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>66.86</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>112.44</v>
+        <v>75.48</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>126.69</v>
+        <v>90.09</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>119.05</v>
+        <v>72.95</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>121.92</v>
+        <v>47.71</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>122.88</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>134.51</v>
+        <v>41.35</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>73.84</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="85">
@@ -7475,10 +7475,10 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0</v>
+        <v>-33.63</v>
       </c>
       <c r="L85" s="3" t="n">
         <v>0</v>
@@ -7490,25 +7490,25 @@
         <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0</v>
+        <v>-6.81</v>
       </c>
       <c r="P85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>0</v>
+        <v>-6.47</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>0</v>
+        <v>-37.78</v>
       </c>
       <c r="S85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>0</v>
+        <v>-4.42</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>0</v>
+        <v>-55.36</v>
       </c>
       <c r="V85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>2.31</v>
+        <v>0.85</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>3.49</v>
+        <v>1.18</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2.81</v>
+        <v>0.88</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>3.02</v>
+        <v>1.11</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>3.65</v>
+        <v>1.53</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>4.36</v>
+        <v>2.98</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>4.05</v>
+        <v>-1.1</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>4.4</v>
+        <v>-5.89</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>4.86</v>
+        <v>-9.93</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>5.19</v>
+        <v>-1.44</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>5.03</v>
+        <v>-2.42</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>5.36</v>
+        <v>-10.53</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>3.97</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>2.53</v>
+        <v>-10.89</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0.51</v>
+        <v>-3.96</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0.25</v>
+        <v>-9.98</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-4.21</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-8.77</v>
+        <v>-7.83</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-10.26</v>
+        <v>-14.11</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-1.79</v>
+        <v>-7.88</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>1.34</v>
+        <v>-3.29</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>3.69</v>
+        <v>-1.27</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>4.57</v>
+        <v>1.61</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>3.62</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="87">
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
         <v>0</v>
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>51.09</v>
+        <v>32.51</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>53.14</v>
+        <v>33</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>45.43</v>
+        <v>33.33</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>46.35</v>
+        <v>32.69</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>54.7</v>
+        <v>37.48</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>71.56999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>79.12</v>
+        <v>48.81</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>75.76000000000001</v>
+        <v>109.86</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>65.23</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>66.20999999999999</v>
+        <v>63.14</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>68.31999999999999</v>
+        <v>78.52</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>75.8</v>
+        <v>84.61</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>73.65000000000001</v>
+        <v>84.08</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>66.73</v>
+        <v>83.87</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>67.25</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>60.03</v>
+        <v>83.31</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>87.93000000000001</v>
+        <v>78.12</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>198.24</v>
+        <v>80.11</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>222</v>
+        <v>105.1</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>222</v>
+        <v>75.2</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>92.98999999999999</v>
+        <v>48.25</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>82.31</v>
+        <v>59.17</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>84.98</v>
+        <v>37.88</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>51.34</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="90">
@@ -7889,61 +7889,61 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0</v>
+        <v>-21.74</v>
       </c>
       <c r="I90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>-1.2</v>
+        <v>-28.47</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-21.15</v>
+        <v>-48.79</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-29.33</v>
+        <v>-29.88</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-33.36</v>
+        <v>-52.94</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-34.03</v>
+        <v>-50.3</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-31.98</v>
+        <v>-50.43</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-30.9</v>
+        <v>-50.41</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-27.23</v>
+        <v>-50.18</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>0</v>
+        <v>-47.71</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>0</v>
+        <v>-15.74</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>0</v>
+        <v>-3.69</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>0</v>
+        <v>-46.13</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-23.52</v>
+        <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-32.31</v>
+        <v>-17.44</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-40.56</v>
+        <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-17.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-1.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-1.49</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.83</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.78</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.24</v>
       </c>
       <c r="H91" s="3" t="n">
+        <v>-3.97</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>-5.91</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>-4.09</v>
+      </c>
+      <c r="M91" s="3" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="Q91" s="3" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="R91" s="3" t="n">
+        <v>-6.94</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="Y91" s="3" t="n">
         <v>-1.86</v>
       </c>
-      <c r="I91" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>-3.31</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>-4.06</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="M91" s="3" t="n">
-        <v>-5.08</v>
-      </c>
-      <c r="N91" s="3" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>-7.18</v>
-      </c>
-      <c r="P91" s="3" t="n">
-        <v>-5.08</v>
-      </c>
-      <c r="Q91" s="3" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="R91" s="3" t="n">
-        <v>-2.71</v>
-      </c>
-      <c r="S91" s="3" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="U91" s="3" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="V91" s="3" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="W91" s="3" t="n">
-        <v>-4.08</v>
-      </c>
-      <c r="X91" s="3" t="n">
-        <v>-4.58</v>
-      </c>
-      <c r="Y91" s="3" t="n">
-        <v>-4.39</v>
-      </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.04</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="92">
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -8060,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -8087,19 +8087,19 @@
         <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>19.33</v>
+        <v>0</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>81.13</v>
+        <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>88.78</v>
+        <v>0</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>104.91</v>
+        <v>0</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>
@@ -8147,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0</v>
+        <v>36.64</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>-2.93</v>
+        <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-13T01:12:37</t>
+          <t>CreatedAt: 2026-10-13T09:10:14</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -659,67 +659,67 @@
         <v>33.62</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>32.85</v>
+        <v>30.36</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>37.85</v>
+        <v>33.94</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>71.75</v>
+        <v>68.61</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>49.52</v>
+        <v>81.23</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>110.85</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>80.22</v>
+        <v>48.71</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>63.68</v>
+        <v>66.87</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>78.77</v>
+        <v>65.45</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>85.26000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>84.98999999999999</v>
+        <v>61.48</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>84.64</v>
+        <v>47.47</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>84.55</v>
+        <v>52.03</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>84.7</v>
+        <v>60.73</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>79.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>81.09</v>
+        <v>101.49</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>106.84</v>
+        <v>77.58</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>76.3</v>
+        <v>84.45</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>48.9</v>
+        <v>49.62</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>59.83</v>
+        <v>40.34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>38.21</v>
+        <v>36.31</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.58</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="5">
@@ -749,55 +749,55 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-21.74</v>
+        <v>-22.71</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>-35.2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-28.47</v>
+        <v>-13.07</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-48.79</v>
+        <v>-45.44</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-29.88</v>
+        <v>-31.08</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-52.94</v>
+        <v>-32.1</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-50.3</v>
+        <v>-29.86</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-50.43</v>
+        <v>-16.34</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-50.41</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-50.18</v>
+        <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-47.71</v>
+        <v>-8.25</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-15.74</v>
+        <v>0</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-46.13</v>
+        <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-17.44</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -827,67 +827,67 @@
         <v>-0.54</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.55</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.71</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-2.71</v>
+        <v>-2.74</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-1.44</v>
+        <v>-3.14</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-3.08</v>
+        <v>-2.23</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-4.89</v>
+        <v>-4.23</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-3.56</v>
+        <v>-3.92</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-5.14</v>
+        <v>-4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-5.02</v>
+        <v>-4.67</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-5.15</v>
+        <v>-3.66</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-5.54</v>
+        <v>-2.42</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-5.66</v>
+        <v>-2.6</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.56</v>
+        <v>-3.52</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.42</v>
+        <v>-2.94</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-2.97</v>
+        <v>-3.65</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-6.58</v>
+        <v>-3.34</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.18</v>
+        <v>-3.29</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.18</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.4</v>
+        <v>-1.82</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.45</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="7">
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1079,67 +1079,67 @@
         <v>33.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>32.92</v>
+        <v>30.45</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>38.41</v>
+        <v>34.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>72.56999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>49.62</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>112.67</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>82.43000000000001</v>
+        <v>51.03</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>65.89</v>
+        <v>68.5</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>82.81999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>89.3</v>
+        <v>69.03</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>88.06</v>
+        <v>62.76</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>89.06999999999999</v>
+        <v>48.72</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>88.13</v>
+        <v>53.3</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>87.03</v>
+        <v>61.67</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>81.17</v>
+        <v>83.06</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>103.59</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>109.68</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>77.81999999999999</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>49.91</v>
+        <v>50.44</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>61.27</v>
+        <v>41.17</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>39.34</v>
+        <v>37.31</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.74</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="10">
@@ -1169,55 +1169,55 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-21.74</v>
+        <v>-22.71</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>-35.2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-28.47</v>
+        <v>-13.07</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-48.79</v>
+        <v>-45.44</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-29.88</v>
+        <v>-31.08</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-52.94</v>
+        <v>-32.1</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-50.3</v>
+        <v>-29.86</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-50.43</v>
+        <v>-16.34</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-50.41</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-50.18</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-47.71</v>
+        <v>-8.25</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-15.74</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-46.13</v>
+        <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-17.44</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>0</v>
@@ -1247,67 +1247,67 @@
         <v>-0.3</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.44</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="V11" s="3" t="n">
         <v>-1.89</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-3.23</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-1.66</v>
-      </c>
       <c r="W11" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.36</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.97</v>
+        <v>-0.99</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.45</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="12">
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1499,67 +1499,67 @@
         <v>33.86</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>32.95</v>
+        <v>30.45</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>38.41</v>
+        <v>34.2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>49.62</v>
+        <v>98.89</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>133.14</v>
+        <v>74.37</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>97.59</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>95.78</v>
+        <v>99.58</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>135.76</v>
+        <v>100.24</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>139.6</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>131.68</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>139.48</v>
+        <v>48.72</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>131.85</v>
+        <v>53.35</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>96.95999999999999</v>
+        <v>69.91</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>96.91</v>
+        <v>83.06</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>134.77</v>
+        <v>103.59</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>100.45</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>98.03</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>49.91</v>
+        <v>50.44</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>78.7</v>
+        <v>41.21</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>53.9</v>
+        <v>37.31</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>32.74</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="15">
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>-18.45</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-8</v>
+        <v>-15.69</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-33.63</v>
+        <v>-28.02</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
@@ -1610,28 +1610,28 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-6.81</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>-6.47</v>
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-37.78</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>48.16</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-55.36</v>
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>18.86</v>
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>14.56</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1667,67 +1667,67 @@
         <v>-0.3</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.53</v>
+        <v>-0.46</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.44</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-1.79</v>
+        <v>-2.29</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.34</v>
+        <v>-2.23</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.25</v>
+        <v>-0.95</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.69</v>
+        <v>-1.9</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.34</v>
+        <v>-2.29</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-1.09</v>
+        <v>-1.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-0.98</v>
+        <v>-2.97</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-2.08</v>
+        <v>-2.37</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-1.12</v>
+        <v>-1.17</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.07</v>
+        <v>-1.28</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-3.23</v>
+        <v>-2.59</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-1.65</v>
+        <v>-1.41</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.55</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-3.74</v>
+        <v>-2.13</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.66</v>
+        <v>-1.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-1.1</v>
+        <v>-1.36</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.97</v>
+        <v>-0.95</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.45</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1919,67 +1919,67 @@
         <v>33.49</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>32.79</v>
+        <v>30.27</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>37.7</v>
+        <v>34.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>48.41</v>
+        <v>87.25</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>49.23</v>
+        <v>121.09</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>80.69</v>
+        <v>61.79</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>28.66</v>
+        <v>0.8</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>32.24</v>
+        <v>37</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>23.37</v>
+        <v>31.59</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>32.35</v>
+        <v>35.63</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>31.81</v>
+        <v>43.96</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>31.62</v>
+        <v>47.29</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>31.63</v>
+        <v>51.78</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>34.12</v>
+        <v>51.75</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>62.41</v>
+        <v>81.22</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>76.89</v>
+        <v>101.1</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>57.71</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>74.44</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>48.62</v>
+        <v>49.38</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>41.25</v>
+        <v>40.19</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>38.1</v>
+        <v>36.17</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.61</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="20">
@@ -2009,55 +2009,55 @@
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-44.53</v>
+        <v>-46.52</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>-72.12</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-58.33</v>
+        <v>-26.79</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-99.97</v>
+        <v>-93.11</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-61.23</v>
+        <v>-63.68</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-108.47</v>
+        <v>-65.77</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-103.08</v>
+        <v>-61.2</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-103.35</v>
+        <v>-33.49</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-103.31</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-102.85</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-97.78</v>
+        <v>-16.9</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-32.27</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>-7.55</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-94.53</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-2.76</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-35.72</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>0</v>
@@ -2087,67 +2087,67 @@
         <v>-0.67</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.78</v>
       </c>
       <c r="H21" s="3" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="S21" s="3" t="n">
         <v>-3.25</v>
       </c>
-      <c r="I21" s="3" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>-5.15</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>-3.88</v>
-      </c>
       <c r="T21" s="3" t="n">
-        <v>-3.29</v>
+        <v>-4.04</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-7.31</v>
+        <v>-3.71</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.63</v>
+        <v>-3.78</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.38</v>
+        <v>-2.42</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-3.69</v>
+        <v>-1.97</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.59</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="22">
@@ -2174,13 +2174,13 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>42.81</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>77.34</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -2267,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2339,67 +2339,67 @@
         <v>33.49</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>32.79</v>
+        <v>30.27</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>37.7</v>
+        <v>33.87</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>71.20999999999999</v>
+        <v>68.25</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>49.23</v>
+        <v>80.67</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>110.55</v>
+        <v>75.5</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>79.84</v>
+        <v>48.47</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>63.59</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>85.13</v>
+        <v>66.97</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>84.73</v>
+        <v>61.11</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>84.51000000000001</v>
+        <v>47.29</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>84.29000000000001</v>
+        <v>51.78</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>84.19</v>
+        <v>60.41</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>78.94</v>
+        <v>81.22</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>80.76000000000001</v>
+        <v>101.1</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>106.11</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>75.86</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>48.62</v>
+        <v>49.38</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>59.54</v>
+        <v>40.19</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>38.1</v>
+        <v>36.17</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.61</v>
+        <v>32.29</v>
       </c>
     </row>
     <row r="25">
@@ -2429,55 +2429,55 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-21.74</v>
+        <v>-22.71</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>-35.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-28.47</v>
+        <v>-13.07</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-48.79</v>
+        <v>-45.44</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-29.88</v>
+        <v>-31.08</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-52.94</v>
+        <v>-32.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-50.3</v>
+        <v>-29.86</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-50.43</v>
+        <v>-16.34</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-50.41</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-50.18</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-47.71</v>
+        <v>-8.25</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-15.74</v>
+        <v>0</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-46.13</v>
+        <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-17.44</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>0</v>
@@ -2507,67 +2507,67 @@
         <v>-0.67</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-1.02</v>
+        <v>-0.78</v>
       </c>
       <c r="H26" s="3" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>-3.71</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>-4.11</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>-4.19</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>-5.04</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>-3.25</v>
       </c>
-      <c r="I26" s="3" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>-5.28</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>-5.15</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>-5.41</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>-5.67</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-5.92</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>-3.88</v>
-      </c>
       <c r="T26" s="3" t="n">
-        <v>-3.29</v>
+        <v>-4.04</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-7.31</v>
+        <v>-3.71</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.63</v>
+        <v>-3.78</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.38</v>
+        <v>-2.42</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-3.69</v>
+        <v>-1.97</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.59</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="27">
@@ -2687,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2759,67 +2759,67 @@
         <v>33.33</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>32.69</v>
+        <v>30.18</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>37.48</v>
+        <v>33.97</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>47.7</v>
+        <v>86.81</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>48.81</v>
+        <v>120.2</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>80</v>
+        <v>61.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>28.03</v>
+        <v>0.44</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>31.79</v>
+        <v>36.72</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>22.99</v>
+        <v>31.31</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>31.83</v>
+        <v>35.26</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>31.29</v>
+        <v>43.52</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>30.97</v>
+        <v>46.98</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>30.98</v>
+        <v>51.44</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>33.24</v>
+        <v>51.24</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>61.6</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>76.25</v>
+        <v>100.52</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>56.7</v>
+        <v>76.77</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>73.79000000000001</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>48.25</v>
+        <v>49.01</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>40.88</v>
+        <v>39.92</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>37.88</v>
+        <v>36</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.67</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="30">
@@ -2849,55 +2849,55 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-44.53</v>
+        <v>-46.52</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0</v>
+        <v>-72.12</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-58.33</v>
+        <v>-26.79</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-99.97</v>
+        <v>-93.11</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-61.23</v>
+        <v>-63.68</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-108.47</v>
+        <v>-65.77</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-103.08</v>
+        <v>-61.2</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-103.35</v>
+        <v>-33.49</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-103.31</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-102.85</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-97.78</v>
+        <v>-16.9</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-32.27</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-7.55</v>
+        <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-94.53</v>
+        <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-2.76</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-35.72</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>0</v>
@@ -2927,67 +2927,67 @@
         <v>-0.83</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.72</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.91</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-3.97</v>
+        <v>-3.53</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-2.15</v>
+        <v>-4.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-4.07</v>
+        <v>-2.92</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-5.91</v>
+        <v>-4.83</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-4.09</v>
+        <v>-4.39</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-5.39</v>
+        <v>-4.47</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-5.67</v>
+        <v>-5.4</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-5.92</v>
+        <v>-4.47</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-6.31</v>
+        <v>-2.91</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-6.56</v>
+        <v>-3.19</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.94</v>
+        <v>-4.36</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-4.69</v>
+        <v>-3.71</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-3.94</v>
+        <v>-4.62</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-8.32</v>
+        <v>-4.15</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4.29</v>
+        <v>-4.42</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-2.75</v>
+        <v>-2.79</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-4.06</v>
+        <v>-2.24</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.76</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3014,13 +3014,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>42.81</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>77.34</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3179,67 +3179,67 @@
         <v>34.51</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>33.34</v>
+        <v>30.91</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>39.23</v>
+        <v>65.52</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>96.39</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>50.21</v>
+        <v>100.76</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>135.14</v>
+        <v>75.77</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>100.15</v>
+        <v>70.36</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>97.8</v>
+        <v>101.36</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>139.07</v>
+        <v>102.68</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>143.3</v>
+        <v>100.66</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>134.46</v>
+        <v>80.59</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>143.31</v>
+        <v>50.04</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>135.63</v>
+        <v>54.74</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>99.64</v>
+        <v>71.22</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>99.36</v>
+        <v>84.98</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>136.87</v>
+        <v>105.99</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>103.88</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>100.01</v>
+        <v>87.91</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>51.05</v>
+        <v>51.44</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>80.27</v>
+        <v>41.99</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>54.86</v>
+        <v>38.22</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>33.12</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="35">
@@ -3272,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0</v>
+        <v>-18.45</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-8</v>
+        <v>-15.69</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-33.63</v>
+        <v>-28.02</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>0</v>
@@ -3290,28 +3290,28 @@
         <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-6.81</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>-6.47</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-37.78</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>48.16</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-55.36</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>18.86</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>14.56</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3347,67 +3347,67 @@
         <v>0.35</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="G36" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="S36" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>0.79</v>
-      </c>
       <c r="T36" s="3" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.48</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.05</v>
+        <v>-0.36</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.17</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="37">
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>30.63</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3599,67 +3599,67 @@
         <v>33.62</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>32.85</v>
+        <v>30.36</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>37.85</v>
+        <v>33.94</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>71.75</v>
+        <v>68.61</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>49.52</v>
+        <v>81.23</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>110.85</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>80.22</v>
+        <v>48.71</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>63.68</v>
+        <v>66.87</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>78.77</v>
+        <v>65.45</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>85.26000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>84.98999999999999</v>
+        <v>61.48</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>84.64</v>
+        <v>47.47</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>84.55</v>
+        <v>52.03</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>84.7</v>
+        <v>60.73</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>79.39</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>81.09</v>
+        <v>101.49</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>106.84</v>
+        <v>77.58</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>76.3</v>
+        <v>84.45</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>48.9</v>
+        <v>49.62</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>59.83</v>
+        <v>40.34</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>38.21</v>
+        <v>36.31</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.58</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="40">
@@ -3689,55 +3689,55 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-21.74</v>
+        <v>-22.71</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>-35.2</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-28.47</v>
+        <v>-13.07</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-48.79</v>
+        <v>-45.44</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-29.88</v>
+        <v>-31.08</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-52.94</v>
+        <v>-32.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-50.3</v>
+        <v>-29.86</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-50.43</v>
+        <v>-16.34</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-50.41</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-50.18</v>
+        <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-47.71</v>
+        <v>-8.25</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-15.74</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-46.13</v>
+        <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-17.44</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
@@ -3767,67 +3767,67 @@
         <v>-0.54</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.55</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.71</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-2.71</v>
+        <v>-2.74</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-1.44</v>
+        <v>-3.14</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-3.08</v>
+        <v>-2.23</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-4.89</v>
+        <v>-4.23</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-3.56</v>
+        <v>-3.92</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-5.14</v>
+        <v>-4</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-5.02</v>
+        <v>-4.67</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-5.15</v>
+        <v>-3.66</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-5.54</v>
+        <v>-2.42</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-5.66</v>
+        <v>-2.6</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.56</v>
+        <v>-3.52</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-3.42</v>
+        <v>-2.94</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-2.97</v>
+        <v>-3.65</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-6.58</v>
+        <v>-3.34</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.18</v>
+        <v>-3.29</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.1</v>
+        <v>-2.18</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.4</v>
+        <v>-1.82</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.45</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="42">
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -4019,67 +4019,67 @@
         <v>34.33</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>33.65</v>
+        <v>31.13</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>38.84</v>
+        <v>34.86</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>93.87</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>50.91</v>
+        <v>119.69</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>141.66</v>
+        <v>90.86</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>132.28</v>
+        <v>97.61</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>94.75</v>
+        <v>100.56</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>133.51</v>
+        <v>100.34</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>137.82</v>
+        <v>100.36</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>137.81</v>
+        <v>79.72</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>137.03</v>
+        <v>48.48</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>136.7</v>
+        <v>53.2</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>135</v>
+        <v>70.94</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>97.3</v>
+        <v>83.06</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>86.95999999999999</v>
+        <v>104</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>158.44</v>
+        <v>80.27</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>80.11</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>50.55</v>
+        <v>51.39</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>80.11</v>
+        <v>41.91</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>39.54</v>
+        <v>37.57</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>33.42</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="45">
@@ -4187,67 +4187,67 @@
         <v>0.17</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="G46" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="J46" s="3" t="n">
-        <v>-0.74</v>
+        <v>-0.15</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-1.63</v>
+        <v>-0.77</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-2.37</v>
+        <v>-1.31</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-3.34</v>
+        <v>-1.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-2.76</v>
+        <v>-1.51</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-2.76</v>
+        <v>-1.75</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-3.56</v>
+        <v>-1.41</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-3.69</v>
+        <v>-1.44</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-2.97</v>
+        <v>-1.56</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.41</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-0.78</v>
+        <v>-1.14</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.11</v>
+        <v>-0.64</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.41</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4439,67 +4439,67 @@
         <v>34.82</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>34.27</v>
+        <v>31.57</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>39.92</v>
+        <v>35.61</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>100.21</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>52.59</v>
+        <v>123.15</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>145.44</v>
+        <v>93.31</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>137.43</v>
+        <v>102.08</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>100.12</v>
+        <v>106</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>140.5</v>
+        <v>105.34</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>144.33</v>
+        <v>105.02</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>144.02</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>144.05</v>
+        <v>51.17</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>144.14</v>
+        <v>56.21</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>134.74</v>
+        <v>75.13</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>97.59</v>
+        <v>83.72</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>87.04000000000001</v>
+        <v>104.62</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>156.27</v>
+        <v>79.56</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>82.98999999999999</v>
+        <v>90.36</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>52.04</v>
+        <v>52.97</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>83.16</v>
+        <v>43.46</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>40.8</v>
+        <v>38.77</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>34.21</v>
+        <v>33.84</v>
       </c>
     </row>
     <row r="50">
@@ -4607,64 +4607,64 @@
         <v>0.66</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>4.01</v>
+        <v>3.21</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>1.63</v>
+        <v>3.57</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>3.05</v>
+        <v>2.29</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>3</v>
+        <v>4.13</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>3.65</v>
+        <v>3.79</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.46</v>
+        <v>2.17</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>3.46</v>
+        <v>1.28</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>3.75</v>
+        <v>1.57</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.23</v>
+        <v>2.63</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.98</v>
+        <v>-0.75</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.52</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.28</v>
+        <v>-1.35</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.49</v>
+        <v>1.3</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>0.68</v>
@@ -4787,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4859,67 +4859,67 @@
         <v>35.59</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>35.02</v>
+        <v>32.16</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>40.59</v>
+        <v>36.24</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>100.41</v>
+        <v>98.38</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>51.37</v>
+        <v>101.36</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>132.22</v>
+        <v>74.81</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>68.33</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>102.69</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>137.54</v>
+        <v>103.51</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>137.15</v>
+        <v>103.21</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>131.27</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>137.56</v>
+        <v>50.5</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>134.06</v>
+        <v>54.85</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>95.91</v>
+        <v>72.28</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>93.06999999999999</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>77.5</v>
+        <v>99.28</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>93.06</v>
+        <v>76.69</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>74.84</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>47.85</v>
+        <v>50.54</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>81.31999999999999</v>
+        <v>42.54</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>41.61</v>
+        <v>39.5</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>34.99</v>
+        <v>34.62</v>
       </c>
     </row>
     <row r="55">
@@ -4952,13 +4952,13 @@
         <v>0</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0</v>
+        <v>-18.45</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-8</v>
+        <v>-15.69</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>-33.63</v>
+        <v>-28.02</v>
       </c>
       <c r="L55" s="3" t="n">
         <v>0</v>
@@ -4970,25 +4970,25 @@
         <v>0</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>-6.81</v>
+        <v>0</v>
       </c>
       <c r="P55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>-6.47</v>
+        <v>0</v>
       </c>
       <c r="R55" s="3" t="n">
-        <v>-37.78</v>
+        <v>0</v>
       </c>
       <c r="S55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="3" t="n">
-        <v>-4.42</v>
+        <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>-55.36</v>
+        <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>0</v>
@@ -5027,67 +5027,67 @@
         <v>1.42</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.41</v>
+        <v>0.24</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-2.18</v>
+        <v>-0.52</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-4.38</v>
+        <v>-2.03</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.97</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-3.43</v>
+        <v>1.34</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-2.49</v>
+        <v>2.26</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-3.03</v>
+        <v>0.61</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-4.28</v>
+        <v>-0.22</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-5.49</v>
+        <v>-2.94</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-5.82</v>
+        <v>-5.86</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-11.13</v>
+        <v>-4.22</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-5.99</v>
+        <v>-4.81</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-3.16</v>
+        <v>-1.26</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.65</v>
+        <v>0.38</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="57">
@@ -5207,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5279,67 +5279,67 @@
         <v>35.44</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>34.73</v>
+        <v>32.16</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>40.12</v>
+        <v>36.02</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>99.06999999999999</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>52.53</v>
+        <v>123.4</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>145.22</v>
+        <v>93.31</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>137.14</v>
+        <v>101.94</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>97.8</v>
+        <v>103.94</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>137.81</v>
+        <v>103.83</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>141.86</v>
+        <v>103.84</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>141.7</v>
+        <v>82.13</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>141.58</v>
+        <v>50.19</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>141.1</v>
+        <v>54.96</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>139.23</v>
+        <v>73.23</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>99.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>89.26000000000001</v>
+        <v>106.63</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>163.14</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>89.62</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>52.2</v>
+        <v>53.02</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>43.33</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>40.84</v>
+        <v>38.85</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>34.49</v>
+        <v>34.16</v>
       </c>
     </row>
     <row r="60">
@@ -5450,64 +5450,64 @@
         <v>1.25</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1.58</v>
+        <v>3.83</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2.82</v>
+        <v>2.29</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>3.23</v>
+        <v>3.57</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.68</v>
+        <v>2.08</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.96</v>
+        <v>2.28</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.13</v>
+        <v>0.66</v>
       </c>
       <c r="P61" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z61" s="3" t="n">
         <v>0.99</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X61" s="3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y61" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z61" s="3" t="n">
-        <v>0.97</v>
       </c>
     </row>
     <row r="62">
@@ -5627,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5699,67 +5699,67 @@
         <v>35.88</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>35.17</v>
+        <v>32.57</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>40.63</v>
+        <v>36.51</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>100.52</v>
+        <v>98.08</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>53.25</v>
+        <v>124.69</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>146.8</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>139.33</v>
+        <v>103.32</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>99.2</v>
+        <v>104.48</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>139.78</v>
+        <v>105.23</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>143.74</v>
+        <v>104.37</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>143.87</v>
+        <v>83.31</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>143.46</v>
+        <v>50.91</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>143.7</v>
+        <v>55.75</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>141.22</v>
+        <v>74.44</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>101.4</v>
+        <v>86.55</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>90.64</v>
+        <v>108.39</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>165.85</v>
+        <v>84.02</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>53.02</v>
+        <v>53.85</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>84.03</v>
+        <v>43.96</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>41.44</v>
+        <v>39.42</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>34.88</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="65">
@@ -5867,67 +5867,67 @@
         <v>1.72</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>4.32</v>
+        <v>4.02</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2.29</v>
+        <v>5.11</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>4.41</v>
+        <v>3.33</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>5.42</v>
+        <v>4.94</v>
       </c>
       <c r="L66" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S66" s="3" t="n">
         <v>2.08</v>
       </c>
-      <c r="M66" s="3" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Q66" s="3" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="R66" s="3" t="n">
+      <c r="T66" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="S66" s="3" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U66" s="3" t="n">
-        <v>6.3</v>
+        <v>3.11</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>2.93</v>
+        <v>3.37</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>3.36</v>
+        <v>1.8</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="67">
@@ -6047,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6119,67 +6119,67 @@
         <v>36.42</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>35.69</v>
+        <v>33.02</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>41.15</v>
+        <v>37.02</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>101.26</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>53.64</v>
+        <v>126</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>147.61</v>
+        <v>95</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>140.37</v>
+        <v>105</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>106</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>139.64</v>
+        <v>106</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>143.6</v>
+        <v>106</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>143.58</v>
+        <v>83.23</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>143.46</v>
+        <v>50.86</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>142.96</v>
+        <v>55.75</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>141.08</v>
+        <v>74.28</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>100.78</v>
+        <v>86.02</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>90.27</v>
+        <v>107.95</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>166.2</v>
+        <v>84.11</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>91.02</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>53.07</v>
+        <v>53.91</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>84.56</v>
+        <v>44.29</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>41.83</v>
+        <v>39.75</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>35.32</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="70">
@@ -6287,67 +6287,67 @@
         <v>2.26</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>5.06</v>
+        <v>4.85</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>2.68</v>
+        <v>6.43</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>5.22</v>
+        <v>3.99</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>6.46</v>
+        <v>6.63</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1.98</v>
+        <v>4.13</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>2.79</v>
+        <v>4.45</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>3.02</v>
+        <v>4.13</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.02</v>
+        <v>1.75</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2.87</v>
+        <v>0.97</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>2.57</v>
+        <v>1.11</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>6.65</v>
+        <v>3.2</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>2.93</v>
+        <v>3.28</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>3.89</v>
+        <v>2.13</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="72">
@@ -6467,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6539,67 +6539,67 @@
         <v>35.47</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>34.76</v>
+        <v>32.16</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>40.21</v>
+        <v>36.09</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>99.58</v>
+        <v>97.16</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>52.75</v>
+        <v>123.91</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>145.56</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>137.72</v>
+        <v>102.35</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>104.59</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>138.65</v>
+        <v>104.47</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>142.72</v>
+        <v>104.59</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>142.56</v>
+        <v>82.72</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>142.44</v>
+        <v>50.55</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>141.67</v>
+        <v>55.3</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>139.51</v>
+        <v>73.61</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>100.27</v>
+        <v>85.58</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>89.53</v>
+        <v>107.18</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>163.81</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>90.17</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>52.47</v>
+        <v>53.3</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>83.16</v>
+        <v>43.55</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>41.01</v>
+        <v>39.01</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>34.59</v>
+        <v>34.23</v>
       </c>
     </row>
     <row r="75">
@@ -6707,67 +6707,67 @@
         <v>1.31</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G76" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="W76" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="H76" s="3" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X76" s="3" t="n">
-        <v>2.49</v>
+        <v>1.39</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="77">
@@ -6887,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6959,67 +6959,67 @@
         <v>34.16</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>33.48</v>
+        <v>30.91</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>38.72</v>
+        <v>34.65</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>96.2</v>
+        <v>94.05</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>50.96</v>
+        <v>119.57</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>142.4</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>133.91</v>
+        <v>98.37</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>97.12</v>
+        <v>101.87</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>136.85</v>
+        <v>101.55</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>140.58</v>
+        <v>101.87</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>140.57</v>
+        <v>81.48</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>140.59</v>
+        <v>49.89</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>140.39</v>
+        <v>54.63</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>137.97</v>
+        <v>72.5</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>98.56</v>
+        <v>84.47</v>
       </c>
       <c r="T79" s="3" t="n">
+        <v>105.14</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="V79" s="3" t="n">
         <v>87.73999999999999</v>
       </c>
-      <c r="U79" s="3" t="n">
-        <v>159.55</v>
-      </c>
-      <c r="V79" s="3" t="n">
-        <v>80.83</v>
-      </c>
       <c r="W79" s="3" t="n">
-        <v>51</v>
+        <v>51.8</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>80.67</v>
+        <v>42.16</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>39.74</v>
+        <v>37.76</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>33.52</v>
+        <v>33.17</v>
       </c>
     </row>
     <row r="80">
@@ -7307,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7379,67 +7379,67 @@
         <v>35.04</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>34.58</v>
+        <v>31.7</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>40.25</v>
+        <v>35.94</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>99.17</v>
+        <v>97.16</v>
       </c>
       <c r="I84" s="3" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>63.77</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="M84" s="3" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>82.05</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="Q84" s="3" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>79.69</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>81.77</v>
+      </c>
+      <c r="W84" s="3" t="n">
         <v>49.86</v>
       </c>
-      <c r="J84" s="3" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>90.36</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>95.68000000000001</v>
-      </c>
-      <c r="M84" s="3" t="n">
-        <v>134.43</v>
-      </c>
-      <c r="N84" s="3" t="n">
-        <v>130.05</v>
-      </c>
-      <c r="O84" s="3" t="n">
-        <v>124.56</v>
-      </c>
-      <c r="P84" s="3" t="n">
-        <v>129.7</v>
-      </c>
-      <c r="Q84" s="3" t="n">
-        <v>129.97</v>
-      </c>
-      <c r="R84" s="3" t="n">
-        <v>90.20999999999999</v>
-      </c>
-      <c r="S84" s="3" t="n">
-        <v>89.93000000000001</v>
-      </c>
-      <c r="T84" s="3" t="n">
-        <v>75.48</v>
-      </c>
-      <c r="U84" s="3" t="n">
-        <v>90.09</v>
-      </c>
-      <c r="V84" s="3" t="n">
-        <v>72.95</v>
-      </c>
-      <c r="W84" s="3" t="n">
-        <v>47.71</v>
-      </c>
       <c r="X84" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>41.5</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>41.35</v>
+        <v>39.29</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>34.85</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="85">
@@ -7472,13 +7472,13 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0</v>
+        <v>-18.45</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>-8</v>
+        <v>-15.69</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>-33.63</v>
+        <v>-28.02</v>
       </c>
       <c r="L85" s="3" t="n">
         <v>0</v>
@@ -7490,25 +7490,25 @@
         <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>-6.81</v>
+        <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>-6.47</v>
+        <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>-37.78</v>
+        <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>-4.42</v>
+        <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-55.36</v>
+        <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
         <v>0</v>
@@ -7547,67 +7547,67 @@
         <v>0.88</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.11</v>
+        <v>0.79</v>
       </c>
       <c r="G86" s="3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="M86" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="Q86" s="3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>-7.43</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="Y86" s="3" t="n">
         <v>1.53</v>
       </c>
-      <c r="H86" s="3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>-5.89</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>-9.93</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="M86" s="3" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="N86" s="3" t="n">
-        <v>-10.53</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="P86" s="3" t="n">
-        <v>-10.89</v>
-      </c>
-      <c r="Q86" s="3" t="n">
-        <v>-3.96</v>
-      </c>
-      <c r="R86" s="3" t="n">
-        <v>-9.98</v>
-      </c>
-      <c r="S86" s="3" t="n">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>-7.83</v>
-      </c>
-      <c r="U86" s="3" t="n">
-        <v>-14.11</v>
-      </c>
-      <c r="V86" s="3" t="n">
-        <v>-7.88</v>
-      </c>
-      <c r="W86" s="3" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="X86" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="Y86" s="3" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Z86" s="3" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="87">
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7799,67 +7799,67 @@
         <v>33.33</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>32.69</v>
+        <v>30.18</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>37.48</v>
+        <v>33.97</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>70.5</v>
+        <v>110.63</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>48.81</v>
+        <v>157.12</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>109.86</v>
+        <v>75.02</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>79.20999999999999</v>
+        <v>48.11</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>63.14</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>78.52</v>
+        <v>64.98</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>84.61</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>84.08</v>
+        <v>60.6</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>83.87</v>
+        <v>46.98</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>83.65000000000001</v>
+        <v>51.44</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>83.31</v>
+        <v>59.89</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>78.12</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>80.11</v>
+        <v>100.52</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>105.1</v>
+        <v>76.77</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>75.2</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>48.25</v>
+        <v>49.01</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>59.17</v>
+        <v>39.92</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>37.88</v>
+        <v>36</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.67</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="90">
@@ -7889,55 +7889,55 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>-21.74</v>
+        <v>-22.71</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0</v>
+        <v>-35.2</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>-28.47</v>
+        <v>-13.07</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-48.79</v>
+        <v>-45.44</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-29.88</v>
+        <v>-31.08</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-52.94</v>
+        <v>-32.1</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-50.3</v>
+        <v>-29.86</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-50.43</v>
+        <v>-16.34</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-50.41</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-50.18</v>
+        <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-47.71</v>
+        <v>-8.25</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-15.74</v>
+        <v>0</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>-3.69</v>
+        <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>-46.13</v>
+        <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-17.44</v>
+        <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
         <v>0</v>
@@ -7967,67 +7967,67 @@
         <v>-0.83</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.72</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.91</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-3.97</v>
+        <v>-3.53</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-2.15</v>
+        <v>-4.6</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-4.07</v>
+        <v>-2.92</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-5.91</v>
+        <v>-4.83</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-4.09</v>
+        <v>-4.39</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-5.39</v>
+        <v>-4.47</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-5.67</v>
+        <v>-5.4</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-6.05</v>
+        <v>-4.54</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-6.31</v>
+        <v>-2.91</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-6.56</v>
+        <v>-3.19</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.94</v>
+        <v>-4.36</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-4.69</v>
+        <v>-3.71</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-3.94</v>
+        <v>-4.62</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-8.32</v>
+        <v>-4.15</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4.29</v>
+        <v>-4.42</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-2.75</v>
+        <v>-2.79</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-4.06</v>
+        <v>-2.24</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.76</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -8054,13 +8054,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>42.81</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>77.34</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -8147,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>36.64</v>
+        <v>16.81</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>-3.26</v>
+        <v>-30.21</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-13T09:10:14</t>
+          <t>CreatedAt: 2026-10-13T15:08:48</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -683,43 +683,43 @@
         <v>65.45</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>67.34</v>
+        <v>68.08</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>61.48</v>
+        <v>75.94</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>47.47</v>
+        <v>77.42</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>52.03</v>
+        <v>121.65</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>60.73</v>
+        <v>121.73</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>81.54000000000001</v>
+        <v>212.04</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>101.49</v>
+        <v>333.33</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>77.58</v>
+        <v>492.41</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>84.45</v>
+        <v>237.13</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>49.62</v>
+        <v>100.14</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>40.34</v>
+        <v>60.11</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>36.31</v>
+        <v>37.06</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.23</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="5">
@@ -767,19 +767,19 @@
         <v>-32.1</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-29.86</v>
+        <v>-29.39</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-16.34</v>
+        <v>-41.62</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
+        <v>-39.7</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-8.25</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-111.41</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0</v>
+        <v>-24.15</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0</v>
+        <v>-14.87</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -851,43 +851,43 @@
         <v>-4</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-4.67</v>
+        <v>-4.19</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-3.66</v>
+        <v>-5.29</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-2.42</v>
+        <v>-5.86</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-2.6</v>
+        <v>-5.11</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-3.52</v>
+        <v>-5.55</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-2.94</v>
+        <v>-8.06</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.65</v>
+        <v>-10.33</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.34</v>
+        <v>-17.73</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.29</v>
+        <v>-14.29</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.18</v>
+        <v>-5.84</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.82</v>
+        <v>-3.37</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.52</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="7">
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>0</v>
@@ -1103,43 +1103,43 @@
         <v>68.05</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>69.03</v>
+        <v>69.98</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>62.76</v>
+        <v>78.12</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.72</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>53.3</v>
+        <v>126.38</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>61.67</v>
+        <v>128.19</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>83.06</v>
+        <v>219.65</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>103.59</v>
+        <v>344.01</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>78.79000000000001</v>
+        <v>501.11</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>85.84999999999999</v>
+        <v>245.01</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>50.44</v>
+        <v>103.05</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>41.17</v>
+        <v>61.88</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>37.31</v>
+        <v>38.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>32.26</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="10">
@@ -1187,19 +1187,19 @@
         <v>-32.1</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-29.86</v>
+        <v>-29.39</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-16.34</v>
+        <v>-41.62</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>-39.7</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-8.25</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0</v>
@@ -1211,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0</v>
+        <v>-111.41</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0</v>
+        <v>-24.15</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0</v>
+        <v>-14.87</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>0</v>
@@ -1271,43 +1271,43 @@
         <v>-1.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-2.97</v>
+        <v>-2.29</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-2.37</v>
+        <v>-3.11</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-1.17</v>
+        <v>-2.88</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.38</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-2.59</v>
+        <v>0.91</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-1.41</v>
+        <v>-0.44</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.55</v>
+        <v>0.34</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-2.13</v>
+        <v>-9.02</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.89</v>
+        <v>-6.42</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-1.36</v>
+        <v>-2.93</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.61</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.38</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="12">
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>0</v>
@@ -1523,43 +1523,43 @@
         <v>100.24</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>99.47</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>105.27</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>48.72</v>
+        <v>120.09</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>53.35</v>
+        <v>126.38</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>69.91</v>
+        <v>195.33</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>83.06</v>
+        <v>836.75</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>103.59</v>
+        <v>647.8200000000001</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>78.79000000000001</v>
+        <v>501.27</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>85.93000000000001</v>
+        <v>356.51</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>50.44</v>
+        <v>148.73</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>41.21</v>
+        <v>1620.43</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>37.31</v>
+        <v>1395.16</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>32.26</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="15">
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0</v>
+        <v>-14.47</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1619,28 +1619,28 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>67.14</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0</v>
+        <v>617.1</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>303.81</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>0</v>
+        <v>21.53</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>0</v>
+        <v>1543.61</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>1356.92</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1691,43 +1691,43 @@
         <v>-1.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-2.97</v>
+        <v>-2.19</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-2.37</v>
+        <v>-3.11</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-1.17</v>
+        <v>-2.88</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-1.28</v>
+        <v>-0.38</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-2.59</v>
+        <v>0.91</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-1.41</v>
+        <v>-0.44</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.55</v>
+        <v>0.34</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-2.13</v>
+        <v>-9.02</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.8</v>
+        <v>-6.42</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-1.36</v>
+        <v>-2.93</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.54</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.34</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="17">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>0</v>
@@ -1943,43 +1943,43 @@
         <v>31.59</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>35.63</v>
+        <v>36.87</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>43.96</v>
+        <v>31.93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>47.29</v>
+        <v>36.42</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>51.78</v>
+        <v>122.23</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>51.75</v>
+        <v>122.32</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>81.22</v>
+        <v>727.49</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>101.1</v>
+        <v>1612.05</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>77.20999999999999</v>
+        <v>491.46</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>83.95999999999999</v>
+        <v>118.25</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>49.38</v>
+        <v>74.22</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>40.19</v>
+        <v>44.16</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>36.17</v>
+        <v>36.92</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.29</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="20">
@@ -2027,19 +2027,19 @@
         <v>-65.77</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-61.2</v>
+        <v>-60.22</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-33.49</v>
+        <v>-85.29000000000001</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>-81.36</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-16.9</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0</v>
+        <v>-228.3</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>0</v>
+        <v>-49.48</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0</v>
+        <v>-30.46</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>0</v>
@@ -2111,43 +2111,43 @@
         <v>-4.19</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-5.04</v>
+        <v>-4.56</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-4.03</v>
+        <v>-5.63</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-2.6</v>
+        <v>-6.08</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-2.85</v>
+        <v>-4.52</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-3.84</v>
+        <v>-4.96</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-3.25</v>
+        <v>-7.24</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-4.04</v>
+        <v>-9.69</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.71</v>
+        <v>-18.68</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.78</v>
+        <v>-16.29</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.42</v>
+        <v>-6.43</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.97</v>
+        <v>-3.73</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.59</v>
+        <v>-1.66</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="22">
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
@@ -2210,10 +2210,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0</v>
+        <v>514.63</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0</v>
+        <v>1278.07</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>0</v>
@@ -2363,43 +2363,43 @@
         <v>65.26000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>66.97</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>61.11</v>
+        <v>75.61</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>47.29</v>
+        <v>77.2</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>51.78</v>
+        <v>122.23</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>60.41</v>
+        <v>122.32</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>81.22</v>
+        <v>212.86</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>101.1</v>
+        <v>333.98</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>77.20999999999999</v>
+        <v>491.46</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>83.95999999999999</v>
+        <v>235.14</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>49.38</v>
+        <v>99.55</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>40.19</v>
+        <v>59.76</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>36.17</v>
+        <v>36.92</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.29</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="25">
@@ -2447,19 +2447,19 @@
         <v>-32.1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-29.86</v>
+        <v>-29.39</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-16.34</v>
+        <v>-41.62</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
+        <v>-39.7</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-8.25</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>0</v>
@@ -2471,13 +2471,13 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>-111.41</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0</v>
+        <v>-24.15</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>0</v>
+        <v>-14.87</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>0</v>
@@ -2531,43 +2531,43 @@
         <v>-4.19</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-5.04</v>
+        <v>-4.56</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-4.03</v>
+        <v>-5.63</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-2.6</v>
+        <v>-6.08</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-2.85</v>
+        <v>-4.52</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-3.84</v>
+        <v>-4.96</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-3.25</v>
+        <v>-7.24</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-4.04</v>
+        <v>-9.69</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.71</v>
+        <v>-18.68</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.78</v>
+        <v>-16.29</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.42</v>
+        <v>-6.43</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.97</v>
+        <v>-3.73</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.59</v>
+        <v>-1.66</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.87</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="27">
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>0</v>
@@ -2783,43 +2783,43 @@
         <v>31.31</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>35.26</v>
+        <v>36.41</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>43.52</v>
+        <v>31.38</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>46.98</v>
+        <v>35.87</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>51.44</v>
+        <v>122.71</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>51.24</v>
+        <v>122.8</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>80.76000000000001</v>
+        <v>727.9</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>100.52</v>
+        <v>1612.05</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>76.77</v>
+        <v>490.04</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>83.31999999999999</v>
+        <v>115.3</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>49.01</v>
+        <v>73.17</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>39.92</v>
+        <v>43.67</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>36</v>
+        <v>36.71</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.36</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="30">
@@ -2867,19 +2867,19 @@
         <v>-65.77</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-61.2</v>
+        <v>-60.22</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-33.49</v>
+        <v>-85.29000000000001</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>-81.36</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-16.9</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>0</v>
@@ -2891,13 +2891,13 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>0</v>
+        <v>-228.3</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>0</v>
+        <v>-49.48</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0</v>
+        <v>-30.46</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>0</v>
@@ -2951,43 +2951,43 @@
         <v>-4.47</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-5.4</v>
+        <v>-5.02</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-4.47</v>
+        <v>-6.18</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-2.91</v>
+        <v>-6.63</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-3.19</v>
+        <v>-4.05</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.48</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-3.71</v>
+        <v>-6.82</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-4.62</v>
+        <v>-9.69</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.15</v>
+        <v>-20.09</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4.42</v>
+        <v>-19.24</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-2.79</v>
+        <v>-7.48</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-2.24</v>
+        <v>-4.23</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.87</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="32">
@@ -3041,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>0</v>
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0</v>
+        <v>514.63</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>0</v>
+        <v>1278.07</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>0</v>
@@ -3203,43 +3203,43 @@
         <v>102.68</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>100.66</v>
+        <v>101.35</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>80.59</v>
+        <v>107.17</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>50.04</v>
+        <v>122.61</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>54.74</v>
+        <v>127.27</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>71.22</v>
+        <v>198.68</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>84.98</v>
+        <v>841</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>105.99</v>
+        <v>652</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>510.8</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>87.91</v>
+        <v>366.22</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>51.44</v>
+        <v>151.91</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>41.99</v>
+        <v>1622.12</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>38.22</v>
+        <v>1396.05</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>32.55</v>
+        <v>33.76</v>
       </c>
     </row>
     <row r="35">
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0</v>
+        <v>-14.47</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3299,28 +3299,28 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>67.14</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0</v>
+        <v>617.1</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>303.81</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>21.53</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>0</v>
+        <v>1543.61</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>1356.92</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3371,43 +3371,43 @@
         <v>1.13</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-1.21</v>
+        <v>-0.3</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.22</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.15</v>
+        <v>-0.37</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.11</v>
+        <v>0.51</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-1.28</v>
+        <v>4.26</v>
       </c>
       <c r="S36" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>0.51</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>-0.48</v>
-      </c>
       <c r="V36" s="3" t="n">
-        <v>0.18</v>
+        <v>3.3</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>-0.36</v>
+        <v>0.26</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>-0.17</v>
+        <v>0.16</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>-0.62</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>0</v>
@@ -3623,43 +3623,43 @@
         <v>65.45</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>67.34</v>
+        <v>68.08</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>61.48</v>
+        <v>75.94</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>47.47</v>
+        <v>77.42</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>52.03</v>
+        <v>121.65</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>60.73</v>
+        <v>121.73</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>81.54000000000001</v>
+        <v>212.04</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>101.49</v>
+        <v>333.33</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>77.58</v>
+        <v>492.41</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>84.45</v>
+        <v>237.13</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>49.62</v>
+        <v>100.14</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>40.34</v>
+        <v>60.11</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>36.31</v>
+        <v>37.06</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.23</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="40">
@@ -3707,19 +3707,19 @@
         <v>-32.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-29.86</v>
+        <v>-29.39</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-16.34</v>
+        <v>-41.62</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>-39.7</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-8.25</v>
+        <v>0</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>-111.41</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>0</v>
+        <v>-24.15</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>0</v>
+        <v>-14.87</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
@@ -3791,43 +3791,43 @@
         <v>-4</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-4.67</v>
+        <v>-4.19</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-3.66</v>
+        <v>-5.29</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-2.42</v>
+        <v>-5.86</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-2.6</v>
+        <v>-5.11</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-3.52</v>
+        <v>-5.55</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-2.94</v>
+        <v>-8.06</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.65</v>
+        <v>-10.33</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.34</v>
+        <v>-17.73</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.29</v>
+        <v>-14.29</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.18</v>
+        <v>-5.84</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.82</v>
+        <v>-3.37</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.52</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.93</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="42">
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>0</v>
@@ -4043,43 +4043,43 @@
         <v>100.34</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>100.36</v>
+        <v>100.95</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>79.72</v>
+        <v>121.04</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>48.48</v>
+        <v>120.33</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>53.2</v>
+        <v>122.59</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>70.94</v>
+        <v>122.92</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>83.06</v>
+        <v>212.65</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>104</v>
+        <v>335.28</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>80.27</v>
+        <v>508.1</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>87.04000000000001</v>
+        <v>360.32</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>51.39</v>
+        <v>128.84</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>41.91</v>
+        <v>77.81</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>37.57</v>
+        <v>38.39</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>33.1</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="45">
@@ -4211,43 +4211,43 @@
         <v>-1.2</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-1.51</v>
+        <v>-0.71</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1.75</v>
+        <v>-1.82</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.41</v>
+        <v>-2.65</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.44</v>
+        <v>-4.17</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.56</v>
+        <v>-4.36</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-1.41</v>
+        <v>-7.44</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.14</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-0.64</v>
+        <v>-2.03</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.7</v>
+        <v>-2.52</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.41</v>
+        <v>-1.29</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.25</v>
+        <v>-0.54</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>-0.19</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="47">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0</v>
@@ -4463,43 +4463,43 @@
         <v>105.34</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>105.02</v>
+        <v>105.56</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>83.65000000000001</v>
+        <v>126.91</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>51.17</v>
+        <v>126.91</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>56.21</v>
+        <v>130.01</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>75.13</v>
+        <v>123.77</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>83.72</v>
+        <v>215.57</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>104.62</v>
+        <v>339.25</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>79.56</v>
+        <v>499.64</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>90.36</v>
+        <v>355.38</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>52.97</v>
+        <v>133.19</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>43.46</v>
+        <v>80.86</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>38.77</v>
+        <v>39.65</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>33.84</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="50">
@@ -4631,43 +4631,43 @@
         <v>3.79</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.15</v>
+        <v>3.91</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>2.17</v>
+        <v>4.06</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.28</v>
+        <v>3.93</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>2.63</v>
+        <v>-3.51</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-0.75</v>
+        <v>-4.53</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-0.52</v>
+        <v>-4.41</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-1.35</v>
+        <v>-10.49</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.62</v>
+        <v>-7.46</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.17</v>
+        <v>3.06</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.3</v>
+        <v>2.51</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="52">
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="R53" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S53" s="3" t="n">
         <v>0</v>
@@ -4883,43 +4883,43 @@
         <v>103.51</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>103.21</v>
+        <v>100.75</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>83.73999999999999</v>
+        <v>107.29</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>50.5</v>
+        <v>122.36</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>54.85</v>
+        <v>122.59</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>72.28</v>
+        <v>123.89</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>81.54000000000001</v>
+        <v>205.89</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>99.28</v>
+        <v>322.99</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>76.69</v>
+        <v>481.71</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>349.55</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>50.54</v>
+        <v>128.97</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>42.54</v>
+        <v>79.23</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>39.5</v>
+        <v>40.23</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>34.62</v>
+        <v>34.74</v>
       </c>
     </row>
     <row r="55">
@@ -4970,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>0</v>
+        <v>-14.47</v>
       </c>
       <c r="P55" s="3" t="n">
         <v>0</v>
@@ -5051,43 +5051,43 @@
         <v>1.97</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>1.34</v>
+        <v>-0.91</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>2.26</v>
+        <v>-1.1</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.61</v>
+        <v>-0.61</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0.22</v>
+        <v>-4.17</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-0.22</v>
+        <v>-3.39</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-2.94</v>
+        <v>-14.21</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-5.86</v>
+        <v>-20.67</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-4.22</v>
+        <v>-28.42</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-4.81</v>
+        <v>-13.28</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.16</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.38</v>
+        <v>0.87</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="57">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S58" s="3" t="n">
         <v>0</v>
@@ -5303,43 +5303,43 @@
         <v>103.83</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>103.84</v>
+        <v>104.05</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>82.13</v>
+        <v>124.34</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>50.19</v>
+        <v>124.22</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>54.96</v>
+        <v>125.75</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>73.23</v>
+        <v>126</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>85.23999999999999</v>
+        <v>216.63</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>106.63</v>
+        <v>340.94</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>82.65000000000001</v>
+        <v>523.22</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>89.62</v>
+        <v>371</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>53.02</v>
+        <v>132.92</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>43.33</v>
+        <v>80.36</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>38.85</v>
+        <v>39.65</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>34.16</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="60">
@@ -5471,43 +5471,43 @@
         <v>2.28</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.66</v>
+        <v>1.49</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>0.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0.33</v>
+        <v>-1.01</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>0.73</v>
+        <v>-1.28</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0.77</v>
+        <v>-3.47</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.49</v>
+        <v>-2.73</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.74</v>
+        <v>13.08</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.88</v>
+        <v>8.16</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.22</v>
+        <v>2.79</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.17</v>
+        <v>2.01</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="62">
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S63" s="3" t="n">
         <v>0</v>
@@ -5723,43 +5723,43 @@
         <v>105.23</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>104.37</v>
+        <v>104.69</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>83.31</v>
+        <v>124.6</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>50.91</v>
+        <v>124.98</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>55.75</v>
+        <v>127.52</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>74.44</v>
+        <v>128.19</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>86.55</v>
+        <v>219.87</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>108.39</v>
+        <v>346.44</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>84.02</v>
+        <v>532.5</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>91.11</v>
+        <v>377.96</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>53.85</v>
+        <v>134.99</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>43.96</v>
+        <v>81.62</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>39.42</v>
+        <v>40.23</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>34.58</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="65">
@@ -5891,43 +5891,43 @@
         <v>3.68</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>1.94</v>
+        <v>0.91</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>2.08</v>
+        <v>-0.22</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.11</v>
+        <v>22.36</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.37</v>
+        <v>15.12</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.05</v>
+        <v>4.86</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.8</v>
+        <v>3.26</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="67">
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S68" s="3" t="n">
         <v>0</v>
@@ -6146,40 +6146,40 @@
         <v>106</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>83.23</v>
+        <v>126</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>50.86</v>
+        <v>126</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>55.75</v>
+        <v>126</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>74.28</v>
+        <v>126</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>86.02</v>
+        <v>214.72</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>107.95</v>
+        <v>339.25</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>84.11</v>
+        <v>531.9400000000001</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>91.02</v>
+        <v>377.17</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>53.91</v>
+        <v>135.27</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>44.29</v>
+        <v>82.13</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>39.75</v>
+        <v>40.61</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>34.95</v>
+        <v>35.22</v>
       </c>
     </row>
     <row r="70">
@@ -6311,43 +6311,43 @@
         <v>4.45</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.13</v>
+        <v>4.35</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0.97</v>
+        <v>3.02</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>1.11</v>
+        <v>-0.76</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>1.78</v>
+        <v>-1.28</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>1.55</v>
+        <v>-5.37</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>2.81</v>
+        <v>-4.41</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>3.2</v>
+        <v>21.81</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.28</v>
+        <v>14.33</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.1</v>
+        <v>5.14</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>2.13</v>
+        <v>3.78</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="72">
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S73" s="3" t="n">
         <v>0</v>
@@ -6563,43 +6563,43 @@
         <v>104.47</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>104.59</v>
+        <v>104.69</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>82.72</v>
+        <v>125.23</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>50.55</v>
+        <v>125.1</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>55.3</v>
+        <v>126.38</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>73.61</v>
+        <v>126.38</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>85.58</v>
+        <v>217.7</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>107.18</v>
+        <v>342.98</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>83.06999999999999</v>
+        <v>523.75</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>90.17</v>
+        <v>371.76</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>53.3</v>
+        <v>133.74</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>43.55</v>
+        <v>80.78</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>39.01</v>
+        <v>39.82</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>34.23</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="75">
@@ -6731,43 +6731,43 @@
         <v>2.93</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.72</v>
+        <v>3.04</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>0.66</v>
+        <v>2.13</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0.66</v>
+        <v>-0.38</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>1.11</v>
+        <v>-2.39</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.04</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.16</v>
+        <v>13.62</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.43</v>
+        <v>8.92</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.49</v>
+        <v>3.61</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="77">
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S78" s="3" t="n">
         <v>0</v>
@@ -6983,43 +6983,43 @@
         <v>101.55</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>101.87</v>
+        <v>101.65</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>81.48</v>
+        <v>122.85</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>49.89</v>
+        <v>122.98</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>54.63</v>
+        <v>126.76</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>72.5</v>
+        <v>127.28</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>84.47</v>
+        <v>220.09</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>105.14</v>
+        <v>343.66</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>80.91</v>
+        <v>510.14</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>87.73999999999999</v>
+        <v>362.84</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>51.8</v>
+        <v>130.13</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>42.16</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>37.76</v>
+        <v>38.58</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>33.17</v>
+        <v>33.46</v>
       </c>
     </row>
     <row r="80">
@@ -7331,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S83" s="3" t="n">
         <v>0</v>
@@ -7403,43 +7403,43 @@
         <v>101.65</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>101.26</v>
+        <v>95.36</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>82.05</v>
+        <v>101.1</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>48.53</v>
+        <v>116.79</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>52.63</v>
+        <v>116.72</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>69.91</v>
+        <v>118.17</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>79.69</v>
+        <v>199.36</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>97.70999999999999</v>
+        <v>312.42</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>75.55</v>
+        <v>466.3</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>81.77</v>
+        <v>341.01</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>49.86</v>
+        <v>123.58</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>41.5</v>
+        <v>75.7</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>39.29</v>
+        <v>39.9</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>34.44</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="85">
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0</v>
+        <v>-14.47</v>
       </c>
       <c r="P85" s="3" t="n">
         <v>0</v>
@@ -7571,43 +7571,43 @@
         <v>0.1</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-0.61</v>
+        <v>-6.29</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.57</v>
+        <v>-7.28</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-1.36</v>
+        <v>-6.19</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-2</v>
+        <v>-10.04</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-2.59</v>
+        <v>-9.1</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-4.78</v>
+        <v>-20.73</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-7.43</v>
+        <v>-31.24</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-5.36</v>
+        <v>-43.83</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-5.97</v>
+        <v>-21.82</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-1.94</v>
+        <v>-6.55</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.66</v>
+        <v>-2.65</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.27</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="87">
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S88" s="3" t="n">
         <v>0</v>
@@ -7823,43 +7823,43 @@
         <v>64.98</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>66.59999999999999</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>60.6</v>
+        <v>75.05</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>46.98</v>
+        <v>77.53</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>51.44</v>
+        <v>122.71</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>59.89</v>
+        <v>122.8</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>80.76000000000001</v>
+        <v>727.9</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>100.52</v>
+        <v>1612.05</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>76.77</v>
+        <v>490.04</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>83.31999999999999</v>
+        <v>232.18</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>49.01</v>
+        <v>98.5</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>39.92</v>
+        <v>59.26</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>36</v>
+        <v>36.71</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.36</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="90">
@@ -7907,19 +7907,19 @@
         <v>-32.1</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-29.86</v>
+        <v>-29.39</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-16.34</v>
+        <v>-41.62</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>0</v>
+        <v>-39.7</v>
       </c>
       <c r="Q90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-8.25</v>
+        <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>0</v>
+        <v>-111.41</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>0</v>
+        <v>-24.15</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>0</v>
+        <v>-14.87</v>
       </c>
       <c r="Y90" s="3" t="n">
         <v>0</v>
@@ -7991,43 +7991,43 @@
         <v>-4.47</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-5.4</v>
+        <v>-5.02</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-4.54</v>
+        <v>-6.18</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-2.91</v>
+        <v>-6.63</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-3.19</v>
+        <v>-4.05</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.48</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-3.71</v>
+        <v>-6.82</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-4.62</v>
+        <v>-9.69</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.15</v>
+        <v>-20.09</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4.42</v>
+        <v>-19.24</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-2.79</v>
+        <v>-7.48</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-2.24</v>
+        <v>-4.23</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.87</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="92">
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="Q92" s="3" t="n">
         <v>0</v>
@@ -8090,10 +8090,10 @@
         <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>514.63</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>1278.07</v>
       </c>
       <c r="U92" s="3" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="S93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-13T15:08:48</t>
+          <t>CreatedAt: 2026-10-13T18:07:54</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -701,25 +701,25 @@
         <v>212.04</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>333.33</v>
+        <v>201.6</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>492.41</v>
+        <v>854.24</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>237.13</v>
+        <v>552.47</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>100.14</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>60.11</v>
+        <v>85.11</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>37.06</v>
+        <v>57</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.61</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="5">
@@ -791,16 +791,16 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-111.41</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-24.15</v>
+        <v>-38.42</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-14.87</v>
+        <v>-46.6</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-19.84</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
@@ -869,25 +869,25 @@
         <v>-8.06</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-10.33</v>
+        <v>-7.86</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-17.73</v>
+        <v>-17</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-14.29</v>
+        <v>-2.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-5.84</v>
+        <v>-5.95</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.37</v>
+        <v>-5.66</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.52</v>
+        <v>-3.15</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>0</v>
@@ -1121,25 +1121,25 @@
         <v>219.65</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>344.01</v>
+        <v>208</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>501.11</v>
+        <v>865.04</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>245.01</v>
+        <v>554.51</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>103.05</v>
+        <v>92.53</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>61.88</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>38.2</v>
+        <v>59.52</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>33.26</v>
+        <v>36.82</v>
       </c>
     </row>
     <row r="10">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-111.41</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-24.15</v>
+        <v>-38.42</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-14.87</v>
+        <v>-46.6</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-19.84</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>0</v>
@@ -1289,25 +1289,25 @@
         <v>-0.44</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0.34</v>
+        <v>-1.46</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-9.02</v>
+        <v>-6.21</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-6.42</v>
+        <v>-0.16</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-2.93</v>
+        <v>-1.57</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.61</v>
+        <v>-2.43</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.38</v>
+        <v>-0.63</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="12">
@@ -1460,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>0</v>
@@ -1541,25 +1541,25 @@
         <v>836.75</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>647.8200000000001</v>
+        <v>1747.27</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>501.27</v>
+        <v>1996.73</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>356.51</v>
+        <v>2000</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>148.73</v>
+        <v>1777</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>1620.43</v>
+        <v>1629.38</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1395.16</v>
+        <v>159.52</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>33.26</v>
+        <v>36.86</v>
       </c>
     </row>
     <row r="15">
@@ -1625,22 +1625,22 @@
         <v>617.1</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>303.81</v>
+        <v>1539.06</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0.15</v>
+        <v>1131.34</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0.08</v>
+        <v>1445.49</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>21.53</v>
+        <v>1645.92</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>1543.61</v>
+        <v>1494.43</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1356.92</v>
+        <v>80.17</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1709,25 +1709,25 @@
         <v>-0.44</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>0.34</v>
+        <v>-1.25</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-9.02</v>
+        <v>-5.85</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-6.42</v>
+        <v>-0.16</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-2.93</v>
+        <v>-1.44</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.54</v>
+        <v>-2.43</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.34</v>
+        <v>-0.63</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="17">
@@ -1880,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>0</v>
@@ -1961,25 +1961,25 @@
         <v>727.49</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>1612.05</v>
+        <v>1613.2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>491.46</v>
+        <v>1602.01</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>118.25</v>
+        <v>552.62</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>74.22</v>
+        <v>255.12</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>44.16</v>
+        <v>35.72</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>36.92</v>
+        <v>35.98</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>32.67</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="20">
@@ -2051,16 +2051,16 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-228.3</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-49.48</v>
+        <v>-78.72</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-30.46</v>
+        <v>-95.48</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0</v>
+        <v>-40.64</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>0</v>
@@ -2129,25 +2129,25 @@
         <v>-7.24</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-9.69</v>
+        <v>-8.06</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-18.68</v>
+        <v>-17.68</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-16.29</v>
+        <v>-2.05</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-6.43</v>
+        <v>-5.83</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-3.73</v>
+        <v>-6.17</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.66</v>
+        <v>-3.37</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="22">
@@ -2213,16 +2213,16 @@
         <v>514.63</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>1278.07</v>
+        <v>1411.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0</v>
+        <v>748.45</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>0</v>
+        <v>207.15</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>0</v>
@@ -2300,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>0</v>
@@ -2381,25 +2381,25 @@
         <v>212.86</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>333.98</v>
+        <v>201.4</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>491.46</v>
+        <v>853.5599999999999</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>235.14</v>
+        <v>552.62</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>99.55</v>
+        <v>88.27</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>59.76</v>
+        <v>84.61</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>36.92</v>
+        <v>56.78</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>32.67</v>
+        <v>36.17</v>
       </c>
     </row>
     <row r="25">
@@ -2471,16 +2471,16 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-111.41</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-24.15</v>
+        <v>-38.42</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-14.87</v>
+        <v>-46.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-19.84</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -2549,25 +2549,25 @@
         <v>-7.24</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-9.69</v>
+        <v>-8.06</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-18.68</v>
+        <v>-17.68</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-16.29</v>
+        <v>-2.05</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-6.43</v>
+        <v>-5.83</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-3.73</v>
+        <v>-6.17</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.66</v>
+        <v>-3.37</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.78</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="27">
@@ -2720,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
@@ -2804,22 +2804,22 @@
         <v>1612.05</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>490.04</v>
+        <v>1600</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>115.3</v>
+        <v>552.62</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>73.17</v>
+        <v>255</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>43.67</v>
+        <v>34.98</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>36.71</v>
+        <v>35.68</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>32.74</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="30">
@@ -2891,16 +2891,16 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-228.3</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-49.48</v>
+        <v>-78.72</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-30.46</v>
+        <v>-95.48</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>-40.64</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>0</v>
@@ -2969,25 +2969,25 @@
         <v>-6.82</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-9.69</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-20.09</v>
+        <v>-19.69</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-19.24</v>
+        <v>-2.05</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-7.48</v>
+        <v>-5.95</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-4.23</v>
+        <v>-6.91</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.87</v>
+        <v>-3.66</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="32">
@@ -3053,16 +3053,16 @@
         <v>514.63</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1278.07</v>
+        <v>1411.8</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>0</v>
+        <v>748.45</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>0</v>
+        <v>207.15</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>0</v>
@@ -3140,10 +3140,10 @@
         <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>0</v>
@@ -3221,25 +3221,25 @@
         <v>841</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>652</v>
+        <v>1750</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>510.8</v>
+        <v>2000</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>366.22</v>
+        <v>2000</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>151.91</v>
+        <v>1780.32</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>1622.12</v>
+        <v>1632.22</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>1396.05</v>
+        <v>161.38</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>33.76</v>
+        <v>37.42</v>
       </c>
     </row>
     <row r="35">
@@ -3305,22 +3305,22 @@
         <v>617.1</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>303.81</v>
+        <v>1539.06</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>0.15</v>
+        <v>1131.34</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0.08</v>
+        <v>1445.49</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>21.53</v>
+        <v>1645.92</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1543.61</v>
+        <v>1494.43</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1356.92</v>
+        <v>80.17</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3389,25 +3389,25 @@
         <v>3.81</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.53</v>
+        <v>1.48</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.51</v>
+        <v>-2.58</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>3.3</v>
+        <v>0.44</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>0.26</v>
+        <v>1.88</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.16</v>
+        <v>0.41</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.55</v>
+        <v>1.22</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="37">
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
@@ -3641,25 +3641,25 @@
         <v>212.04</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>333.33</v>
+        <v>201.6</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>492.41</v>
+        <v>854.24</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>237.13</v>
+        <v>552.47</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>100.14</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>60.11</v>
+        <v>85.11</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>37.06</v>
+        <v>57</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>32.61</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="40">
@@ -3731,16 +3731,16 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-111.41</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-24.15</v>
+        <v>-38.42</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-14.87</v>
+        <v>-46.6</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-19.84</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>0</v>
@@ -3809,25 +3809,25 @@
         <v>-8.06</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-10.33</v>
+        <v>-7.86</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-17.73</v>
+        <v>-17</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-14.29</v>
+        <v>-2.2</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-5.84</v>
+        <v>-5.95</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.37</v>
+        <v>-5.66</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.52</v>
+        <v>-3.15</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.85</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -3980,10 +3980,10 @@
         <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0</v>
@@ -4061,25 +4061,25 @@
         <v>212.65</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>335.28</v>
+        <v>203.56</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>508.1</v>
+        <v>858.34</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>360.32</v>
+        <v>551.92</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>128.84</v>
+        <v>128.78</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>77.81</v>
+        <v>136.56</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>38.39</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>33.36</v>
+        <v>36.93</v>
       </c>
     </row>
     <row r="45">
@@ -4229,25 +4229,25 @@
         <v>-7.44</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-8.380000000000001</v>
+        <v>-5.9</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-2.03</v>
+        <v>-12.9</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-2.52</v>
+        <v>-2.75</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-1.29</v>
+        <v>-3.73</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.82</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="47">
@@ -4400,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W48" s="3" t="n">
         <v>0</v>
@@ -4481,25 +4481,25 @@
         <v>215.57</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>339.25</v>
+        <v>205.96</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>499.64</v>
+        <v>861.48</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>355.38</v>
+        <v>552.62</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>133.19</v>
+        <v>134.81</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>80.86</v>
+        <v>141.92</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>39.65</v>
+        <v>82.12</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>34.1</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="50">
@@ -4649,25 +4649,25 @@
         <v>-4.53</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-4.41</v>
+        <v>-3.5</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-10.49</v>
+        <v>-9.76</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-7.46</v>
+        <v>-2.05</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.51</v>
+        <v>4.54</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.07</v>
+        <v>2.14</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="52">
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W53" s="3" t="n">
         <v>0</v>
@@ -4901,25 +4901,25 @@
         <v>205.89</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>322.99</v>
+        <v>197.79</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>481.71</v>
+        <v>859.73</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>349.55</v>
+        <v>553.65</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>128.97</v>
+        <v>134.67</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>79.23</v>
+        <v>136.83</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>40.23</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>34.74</v>
+        <v>38.62</v>
       </c>
     </row>
     <row r="55">
@@ -5069,25 +5069,25 @@
         <v>-14.21</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-20.67</v>
+        <v>-11.67</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-28.42</v>
+        <v>-11.51</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-13.28</v>
+        <v>-1.02</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-1.16</v>
+        <v>2.15</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.87</v>
+        <v>-0.55</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.65</v>
+        <v>3.16</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="57">
@@ -5240,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W58" s="3" t="n">
         <v>0</v>
@@ -5321,25 +5321,25 @@
         <v>216.63</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>340.94</v>
+        <v>207.39</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>523.22</v>
+        <v>864.6799999999999</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>371</v>
+        <v>552.42</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>132.92</v>
+        <v>131.73</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>80.36</v>
+        <v>141.04</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>39.65</v>
+        <v>82.12</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>34.42</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="60">
@@ -5489,25 +5489,25 @@
         <v>-3.47</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>-2.73</v>
+        <v>-2.07</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>13.08</v>
+        <v>-6.56</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>8.16</v>
+        <v>-2.25</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>2.79</v>
+        <v>-0.79</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.01</v>
+        <v>3.67</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.07</v>
+        <v>2.14</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="62">
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W63" s="3" t="n">
         <v>0</v>
@@ -5741,25 +5741,25 @@
         <v>219.87</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>346.44</v>
+        <v>210.51</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>532.5</v>
+        <v>873.86</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>377.96</v>
+        <v>554.46</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>134.99</v>
+        <v>133.72</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>81.62</v>
+        <v>143.1</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>40.23</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>34.85</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="65">
@@ -5909,25 +5909,25 @@
         <v>-0.22</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.77</v>
+        <v>1.05</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>22.36</v>
+        <v>2.62</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>15.12</v>
+        <v>-0.22</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>4.86</v>
+        <v>1.2</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>3.26</v>
+        <v>5.72</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.65</v>
+        <v>3.33</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="67">
@@ -6080,10 +6080,10 @@
         <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W68" s="3" t="n">
         <v>0</v>
@@ -6161,25 +6161,25 @@
         <v>214.72</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>339.25</v>
+        <v>206.16</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>531.9400000000001</v>
+        <v>861.48</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>377.17</v>
+        <v>551</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>135.27</v>
+        <v>131.73</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>82.13</v>
+        <v>144.15</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>40.61</v>
+        <v>84.11</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>35.22</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="70">
@@ -6329,25 +6329,25 @@
         <v>-5.37</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>-4.41</v>
+        <v>-3.3</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>21.81</v>
+        <v>-9.76</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>14.33</v>
+        <v>-3.67</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>5.14</v>
+        <v>-0.79</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>3.78</v>
+        <v>6.78</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.03</v>
+        <v>4.12</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="72">
@@ -6500,10 +6500,10 @@
         <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W73" s="3" t="n">
         <v>0</v>
@@ -6581,25 +6581,25 @@
         <v>217.7</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>342.98</v>
+        <v>208.42</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>523.75</v>
+        <v>867.2</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>371.76</v>
+        <v>552.77</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>133.74</v>
+        <v>132.65</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>80.78</v>
+        <v>141.77</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>39.82</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>34.49</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="75">
@@ -6749,25 +6749,25 @@
         <v>-2.39</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>13.62</v>
+        <v>-4.04</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>8.92</v>
+        <v>-1.9</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>3.61</v>
+        <v>0.13</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.42</v>
+        <v>4.39</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.23</v>
+        <v>2.47</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="77">
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W78" s="3" t="n">
         <v>0</v>
@@ -7001,25 +7001,25 @@
         <v>220.09</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>343.66</v>
+        <v>209.46</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>510.14</v>
+        <v>871.24</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>362.84</v>
+        <v>554.67</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>130.13</v>
+        <v>132.52</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>78.34999999999999</v>
+        <v>137.38</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>38.58</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>33.46</v>
+        <v>37.08</v>
       </c>
     </row>
     <row r="80">
@@ -7340,10 +7340,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W83" s="3" t="n">
         <v>0</v>
@@ -7421,25 +7421,25 @@
         <v>199.36</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>312.42</v>
+        <v>191.29</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>466.3</v>
+        <v>849.24</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>341.01</v>
+        <v>552.37</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>123.58</v>
+        <v>134.54</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>75.7</v>
+        <v>129.72</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>39.9</v>
+        <v>81.37</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>34.42</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="85">
@@ -7589,25 +7589,25 @@
         <v>-20.73</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-31.24</v>
+        <v>-18.17</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-43.83</v>
+        <v>-22</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-21.82</v>
+        <v>-2.3</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-6.55</v>
+        <v>2.02</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-2.65</v>
+        <v>-7.65</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>0.96</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="87">
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W88" s="3" t="n">
         <v>0</v>
@@ -7844,22 +7844,22 @@
         <v>1612.05</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>490.04</v>
+        <v>1600</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>232.18</v>
+        <v>552.62</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>98.5</v>
+        <v>295.3</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>59.26</v>
+        <v>83.86</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>36.71</v>
+        <v>56.42</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>32.74</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="90">
@@ -7931,16 +7931,16 @@
         <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-111.41</v>
+        <v>0</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-24.15</v>
+        <v>-38.42</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-14.87</v>
+        <v>-46.6</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>0</v>
+        <v>-19.84</v>
       </c>
       <c r="Z90" s="3" t="n">
         <v>0</v>
@@ -8009,25 +8009,25 @@
         <v>-6.82</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-9.69</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-20.09</v>
+        <v>-19.69</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-19.24</v>
+        <v>-2.05</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-7.48</v>
+        <v>-5.95</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-4.23</v>
+        <v>-6.91</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-1.87</v>
+        <v>-3.74</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.72</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="92">
@@ -8093,16 +8093,16 @@
         <v>514.63</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>1278.07</v>
+        <v>1411.8</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>0</v>
+        <v>748.45</v>
       </c>
       <c r="V92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>0</v>
+        <v>207.15</v>
       </c>
       <c r="X92" s="3" t="n">
         <v>0</v>
@@ -8180,10 +8180,10 @@
         <v>0</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-13T18:07:54</t>
+          <t>CreatedAt: 2026-10-13T23:14:07</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32.8</v>
+        <v>44.62</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>33.11</v>
+        <v>37.48</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>33.62</v>
+        <v>33.29</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>30.36</v>
+        <v>38.22</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>33.94</v>
+        <v>76.52</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>68.61</v>
+        <v>194.01</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>81.23</v>
+        <v>91.11</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>75.70999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>48.71</v>
+        <v>72.88</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>66.87</v>
+        <v>93.95</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>65.45</v>
+        <v>91.89</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>68.08</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>75.94</v>
+        <v>89.62</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>77.42</v>
+        <v>79.59</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>121.65</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>121.73</v>
+        <v>101.6</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>212.04</v>
+        <v>226.72</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>201.6</v>
+        <v>122.31</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>854.24</v>
+        <v>110</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>552.47</v>
+        <v>102.12</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>88.15000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>85.11</v>
+        <v>52.2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>57</v>
+        <v>48.2</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>36.14</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="5">
@@ -749,40 +749,40 @@
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-22.71</v>
+        <v>0</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-35.2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-13.07</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-45.44</v>
+        <v>-22.27</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-31.08</v>
+        <v>-49.9</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-32.1</v>
+        <v>-49.2</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-29.39</v>
+        <v>-48.29</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-41.62</v>
+        <v>-38.23</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-39.7</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>-16.73</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>-25.93</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0</v>
+        <v>-95.63</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>0</v>
@@ -794,13 +794,13 @@
         <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-38.42</v>
+        <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-46.6</v>
+        <v>-2.12</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-19.84</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-0.52</v>
+        <v>-1.07</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.82</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.96</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-0.71</v>
+        <v>-2.45</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-2.74</v>
+        <v>-6.79</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-3.14</v>
+        <v>-3.37</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.36</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-4.23</v>
+        <v>-4.76</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-3.92</v>
+        <v>-8.06</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-4</v>
+        <v>-7.62</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-4.19</v>
+        <v>-7.94</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-5.29</v>
+        <v>-7.29</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-5.86</v>
+        <v>-4.3</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-5.11</v>
+        <v>-5.27</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.55</v>
+        <v>-7.14</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-8.06</v>
+        <v>-14.83</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-7.86</v>
+        <v>-5.5</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-17</v>
+        <v>-5.06</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-5.95</v>
+        <v>-2.4</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-5.66</v>
+        <v>-2.39</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-3.15</v>
+        <v>-1.98</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -1007,10 +1007,10 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>0</v>
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>33.39</v>
+        <v>44.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>33.99</v>
+        <v>37.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>33.86</v>
+        <v>33.59</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>30.45</v>
+        <v>38.14</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>34.2</v>
+        <v>76.38</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>69.05</v>
+        <v>192.52</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>82.15000000000001</v>
+        <v>92.45</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>76.98999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>51.03</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>68.5</v>
+        <v>95.75</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>68.05</v>
+        <v>94.34</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>69.98</v>
+        <v>95.78</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>78.12</v>
+        <v>91.09</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>81.05</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>126.38</v>
+        <v>80.67</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>128.19</v>
+        <v>102.57</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>219.65</v>
+        <v>226.72</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>208</v>
+        <v>124.57</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>865.04</v>
+        <v>112.25</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>554.51</v>
+        <v>104.01</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>92.53</v>
+        <v>54.88</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>88.34999999999999</v>
+        <v>53.75</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>59.52</v>
+        <v>49.87</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>36.82</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="10">
@@ -1169,40 +1169,40 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-22.71</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-35.2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-13.07</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-45.44</v>
+        <v>-22.27</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-31.08</v>
+        <v>-49.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-32.1</v>
+        <v>-49.2</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-29.39</v>
+        <v>-48.29</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-41.62</v>
+        <v>-38.23</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-39.7</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>-16.73</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>-25.93</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>-95.63</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>0</v>
@@ -1214,13 +1214,13 @@
         <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>-38.42</v>
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-46.6</v>
+        <v>-2.12</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-19.84</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>0</v>
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.44</v>
+        <v>-0.6</v>
       </c>
       <c r="E11" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>-14.83</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-3.24</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="Y11" s="3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>-6.21</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-0.63</v>
-      </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.26</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="12">
@@ -1427,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>0</v>
@@ -1460,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>33.42</v>
+        <v>44.66</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>33.99</v>
+        <v>37.7</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>33.86</v>
+        <v>33.59</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>30.45</v>
+        <v>38.14</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>34.2</v>
+        <v>76.38</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>91.76000000000001</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>98.89</v>
+        <v>94.73</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>74.37</v>
+        <v>71.16</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>68.45999999999999</v>
+        <v>96.63</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>99.58</v>
+        <v>145.64</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>100.24</v>
+        <v>143.54</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>99.47</v>
+        <v>144.08</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>105.27</v>
+        <v>129.32</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>120.09</v>
+        <v>81.05</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>126.38</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>195.33</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>836.75</v>
+        <v>207.59</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>1747.27</v>
+        <v>136.97</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1996.73</v>
+        <v>135.28</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>2000</v>
+        <v>104.11</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>1777</v>
+        <v>132.16</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>1629.38</v>
+        <v>74.27</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>159.52</v>
+        <v>49.87</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>36.86</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="15">
@@ -1589,16 +1589,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>-93.23</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-18.45</v>
+        <v>2.28</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-15.69</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>-28.02</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>-14.47</v>
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0</v>
@@ -1619,28 +1619,28 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>67.14</v>
+        <v>-30.44</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>617.1</v>
+        <v>-114.76</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>1539.06</v>
+        <v>12.27</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>1131.34</v>
+        <v>23.03</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>1445.49</v>
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>1645.92</v>
+        <v>77.28</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>1494.43</v>
+        <v>18.35</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>80.17</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.1</v>
+        <v>-1.03</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.44</v>
+        <v>-0.6</v>
       </c>
       <c r="E16" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>-5.17</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>-6.17</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>-14.83</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="Y16" s="3" t="n">
         <v>-0.3</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>-2.19</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>-3.11</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>-2.88</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>-0.63</v>
-      </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="17">
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>0</v>
@@ -1880,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.7</v>
+        <v>44.53</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>33.19</v>
+        <v>37.44</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33.49</v>
+        <v>33.23</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>30.27</v>
+        <v>38.18</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>34.1</v>
+        <v>76.23</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>87.25</v>
+        <v>193.08</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>121.09</v>
+        <v>91.11</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>61.79</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>48.9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>37</v>
+        <v>40.95</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>31.59</v>
+        <v>39.76</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>36.87</v>
+        <v>42.15</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>31.93</v>
+        <v>48.82</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>36.42</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>122.23</v>
+        <v>61.01</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>122.32</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>727.49</v>
+        <v>124.27</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>1613.2</v>
+        <v>121.72</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>1602.01</v>
+        <v>109.48</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>552.62</v>
+        <v>101.44</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>255.12</v>
+        <v>53.1</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>35.72</v>
+        <v>49.72</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>35.98</v>
+        <v>48.01</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>36.17</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="20">
@@ -2009,40 +2009,40 @@
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-46.52</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-72.12</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-26.79</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-93.11</v>
+        <v>-45.63</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-63.68</v>
+        <v>-102.22</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-65.77</v>
+        <v>-100.79</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-60.22</v>
+        <v>-98.94</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-85.29000000000001</v>
+        <v>-78.31</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-81.36</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0</v>
+        <v>-34.27</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0</v>
+        <v>-53.13</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0</v>
+        <v>-195.93</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>0</v>
@@ -2054,13 +2054,13 @@
         <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-78.72</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-95.48</v>
+        <v>-4.34</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-40.64</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>0</v>
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-0.62</v>
+        <v>-1.16</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.86</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.86</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.99</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-0.78</v>
+        <v>-2.74</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-3.09</v>
+        <v>-7.72</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.37</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-2.44</v>
+        <v>-3.76</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-4.47</v>
+        <v>-5.39</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-4.11</v>
+        <v>-8.73</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-4.19</v>
+        <v>-8.15</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-4.56</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-5.63</v>
+        <v>-8.01</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-6.08</v>
+        <v>-4.67</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-4.52</v>
+        <v>-5.81</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-4.96</v>
+        <v>-7.86</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-7.24</v>
+        <v>-16.97</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-8.06</v>
+        <v>-6.09</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-17.68</v>
+        <v>-5.58</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-2.05</v>
+        <v>-5.38</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-5.83</v>
+        <v>-2.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-6.17</v>
+        <v>-2.65</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-3.37</v>
+        <v>-2.16</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -2174,13 +2174,13 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>42.81</v>
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>77.34</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -2201,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
@@ -2210,19 +2210,19 @@
         <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>514.63</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>1411.8</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>748.45</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>207.15</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>0</v>
@@ -2267,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>0</v>
@@ -2300,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>32.7</v>
+        <v>44.53</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>33.05</v>
+        <v>37.44</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>33.49</v>
+        <v>33.23</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>30.27</v>
+        <v>38.18</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>33.87</v>
+        <v>76.23</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>68.25</v>
+        <v>193.08</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>80.67</v>
+        <v>91.11</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>75.5</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>48.47</v>
+        <v>72.25</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>66.68000000000001</v>
+        <v>93.27</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>65.26000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>67.70999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>75.61</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>77.2</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>122.23</v>
+        <v>78.56</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>122.32</v>
+        <v>100.88</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>212.86</v>
+        <v>224.57</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>201.4</v>
+        <v>121.72</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>853.5599999999999</v>
+        <v>109.48</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>552.62</v>
+        <v>101.44</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>88.27</v>
+        <v>53.1</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>84.61</v>
+        <v>51.94</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>56.78</v>
+        <v>48.01</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>36.17</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="25">
@@ -2429,40 +2429,40 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-22.71</v>
+        <v>0</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-35.2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-13.07</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-45.44</v>
+        <v>-22.27</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-31.08</v>
+        <v>-49.9</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-32.1</v>
+        <v>-49.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-29.39</v>
+        <v>-48.29</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-41.62</v>
+        <v>-38.23</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-39.7</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0</v>
+        <v>-16.73</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0</v>
+        <v>-25.93</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0</v>
+        <v>-95.63</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-38.42</v>
+        <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-46.6</v>
+        <v>-2.12</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-19.84</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.62</v>
+        <v>-1.16</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.86</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.67</v>
+        <v>-0.86</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.64</v>
+        <v>-0.99</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-0.78</v>
+        <v>-2.74</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-3.09</v>
+        <v>-7.72</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-3.71</v>
+        <v>-3.37</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-2.44</v>
+        <v>-3.76</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-4.47</v>
+        <v>-5.39</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-4.11</v>
+        <v>-8.73</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-4.19</v>
+        <v>-8.15</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-4.56</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-5.63</v>
+        <v>-8.01</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-6.08</v>
+        <v>-4.67</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-4.52</v>
+        <v>-5.81</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-4.96</v>
+        <v>-7.86</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-7.24</v>
+        <v>-16.97</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-8.06</v>
+        <v>-6.09</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-17.68</v>
+        <v>-5.58</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-2.05</v>
+        <v>-5.38</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-5.83</v>
+        <v>-2.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-6.17</v>
+        <v>-2.65</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-3.37</v>
+        <v>-2.16</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.9</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="27">
@@ -2687,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>0</v>
@@ -2720,10 +2720,10 @@
         <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>32.51</v>
+        <v>44.4</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>33</v>
+        <v>37.33</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>33.33</v>
+        <v>33.16</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.18</v>
+        <v>38.14</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>33.97</v>
+        <v>75.94</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>86.81</v>
+        <v>192.34</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>120.2</v>
+        <v>91.03</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>61.3</v>
+        <v>69.02</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.44</v>
+        <v>48.01</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>36.72</v>
+        <v>39.88</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>31.31</v>
+        <v>38.97</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>36.41</v>
+        <v>41.22</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>31.38</v>
+        <v>47.87</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>35.87</v>
+        <v>78.69</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>122.71</v>
+        <v>60.21</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>122.8</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>727.9</v>
+        <v>121.56</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>1612.05</v>
+        <v>120.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>1600</v>
+        <v>108.65</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>552.62</v>
+        <v>100.3</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>255</v>
+        <v>52.7</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>34.98</v>
+        <v>49.31</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>35.68</v>
+        <v>47.65</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>36.21</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="30">
@@ -2849,40 +2849,40 @@
         <v>0</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-46.52</v>
+        <v>0</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-72.12</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-26.79</v>
+        <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-93.11</v>
+        <v>-45.63</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-63.68</v>
+        <v>-102.22</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-65.77</v>
+        <v>-100.79</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-60.22</v>
+        <v>-98.94</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-85.29000000000001</v>
+        <v>-78.31</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-81.36</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0</v>
+        <v>-34.27</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0</v>
+        <v>-53.13</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0</v>
+        <v>-195.93</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>-78.72</v>
+        <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-95.48</v>
+        <v>-4.34</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-40.64</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>0</v>
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.29</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.97</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.03</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0.91</v>
+        <v>-3.04</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-3.53</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-4.6</v>
+        <v>-3.46</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-2.92</v>
+        <v>-4.28</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-4.83</v>
+        <v>-6.27</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-4.39</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-4.47</v>
+        <v>-8.94</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-5.02</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-6.18</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-6.63</v>
+        <v>-5.19</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-4.05</v>
+        <v>-6.61</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-4.48</v>
+        <v>-8.81</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-6.82</v>
+        <v>-19.68</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-9.210000000000001</v>
+        <v>-7.01</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-19.69</v>
+        <v>-6.41</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-2.05</v>
+        <v>-6.52</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-5.95</v>
+        <v>-3</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-6.91</v>
+        <v>-3.06</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-3.66</v>
+        <v>-2.53</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="32">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>0</v>
@@ -3014,13 +3014,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>42.81</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>77.34</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>0</v>
@@ -3041,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>0</v>
@@ -3050,19 +3050,19 @@
         <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>514.63</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1411.8</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>748.45</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>207.15</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>0</v>
@@ -3140,10 +3140,10 @@
         <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>34.28</v>
+        <v>45.23</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>35.01</v>
+        <v>38.22</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>34.51</v>
+        <v>34.09</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>30.91</v>
+        <v>38.52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>65.52</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>93.68000000000001</v>
+        <v>111.23</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>100.76</v>
+        <v>95.83</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>75.77</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>70.36</v>
+        <v>98.53</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>101.36</v>
+        <v>148.06</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>102.68</v>
+        <v>146.36</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>101.35</v>
+        <v>146.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>107.17</v>
+        <v>131.57</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>122.61</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>127.27</v>
+        <v>99.73</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>198.68</v>
+        <v>100.26</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>841</v>
+        <v>212.73</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>1750</v>
+        <v>139.96</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2000</v>
+        <v>137.86</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>2000</v>
+        <v>107.36</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>1780.32</v>
+        <v>134.01</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>1632.22</v>
+        <v>75.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>161.38</v>
+        <v>51.67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>37.42</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="35">
@@ -3269,16 +3269,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>-83.91</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-18.45</v>
+        <v>2.28</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-15.69</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>-28.02</v>
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>0</v>
@@ -3290,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-14.47</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
@@ -3299,28 +3299,28 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>67.14</v>
+        <v>-30.44</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>617.1</v>
+        <v>-114.76</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1539.06</v>
+        <v>12.27</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1131.34</v>
+        <v>23.03</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>1445.49</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>1645.92</v>
+        <v>77.28</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1494.43</v>
+        <v>18.35</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>80.17</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.96</v>
+        <v>-0.45</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.47</v>
+        <v>-0.08</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.24</v>
+        <v>-1.62</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-0.37</v>
+        <v>-5.66</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.45</v>
+        <v>-0.58</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>-1.38</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.51</v>
+        <v>-3.85</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1.13</v>
+        <v>-2.34</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-0.3</v>
+        <v>-2.79</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-1.22</v>
+        <v>-3.68</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.37</v>
+        <v>-1.16</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.51</v>
+        <v>-1.59</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>4.26</v>
+        <v>-4.18</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>3.81</v>
+        <v>-9.82</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.48</v>
+        <v>-0.13</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-2.58</v>
+        <v>-0.23</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.88</v>
+        <v>1.02</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="37">
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>30.63</v>
+        <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0</v>
@@ -3458,19 +3458,19 @@
         <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.8</v>
+        <v>44.62</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>33.11</v>
+        <v>37.48</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>33.62</v>
+        <v>33.29</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>30.36</v>
+        <v>38.22</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>33.94</v>
+        <v>76.52</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>68.61</v>
+        <v>194.01</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>81.23</v>
+        <v>91.11</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>75.70999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>48.71</v>
+        <v>72.88</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>66.87</v>
+        <v>93.95</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>65.45</v>
+        <v>91.89</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>68.08</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>75.94</v>
+        <v>89.62</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>77.42</v>
+        <v>79.59</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>121.65</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>121.73</v>
+        <v>101.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>212.04</v>
+        <v>226.72</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>201.6</v>
+        <v>122.31</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>854.24</v>
+        <v>110</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>552.47</v>
+        <v>102.12</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>88.15000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>85.11</v>
+        <v>52.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>57</v>
+        <v>48.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>36.14</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="40">
@@ -3689,40 +3689,40 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-22.71</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>-35.2</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-13.07</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-45.44</v>
+        <v>-22.27</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-31.08</v>
+        <v>-49.9</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-32.1</v>
+        <v>-49.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-29.39</v>
+        <v>-48.29</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-41.62</v>
+        <v>-38.23</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-39.7</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>-16.73</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>-25.93</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>-95.63</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>0</v>
@@ -3734,13 +3734,13 @@
         <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>-38.42</v>
+        <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-46.6</v>
+        <v>-2.12</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-19.84</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>0</v>
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-0.52</v>
+        <v>-1.07</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.82</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.54</v>
+        <v>-0.8</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.96</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-0.71</v>
+        <v>-2.45</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-2.74</v>
+        <v>-6.79</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-3.14</v>
+        <v>-3.37</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-2.23</v>
+        <v>-3.36</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-4.23</v>
+        <v>-4.76</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-3.92</v>
+        <v>-8.06</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-4</v>
+        <v>-7.62</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-4.19</v>
+        <v>-7.94</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-5.29</v>
+        <v>-7.29</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-5.86</v>
+        <v>-4.3</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-5.11</v>
+        <v>-5.27</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.55</v>
+        <v>-7.14</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-8.06</v>
+        <v>-14.83</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-7.86</v>
+        <v>-5.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-17</v>
+        <v>-5.06</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.2</v>
+        <v>-4.7</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-5.95</v>
+        <v>-2.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-5.66</v>
+        <v>-2.39</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-3.15</v>
+        <v>-1.98</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="42">
@@ -3947,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>0</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="n">
         <v>0</v>
@@ -3980,10 +3980,10 @@
         <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0</v>
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>33.49</v>
+        <v>45.82</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>33.68</v>
+        <v>38.42</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>34.33</v>
+        <v>34.23</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>31.13</v>
+        <v>39.37</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>34.86</v>
+        <v>79.05</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>93.87</v>
+        <v>202.01</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>119.69</v>
+        <v>94.2</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>90.86</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>97.61</v>
+        <v>99.02</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>100.56</v>
+        <v>148.64</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>100.34</v>
+        <v>145.79</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>100.95</v>
+        <v>146.33</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>121.04</v>
+        <v>131.84</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>120.33</v>
+        <v>81.92</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>122.59</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>122.92</v>
+        <v>132.81</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>212.65</v>
+        <v>335.17</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>203.56</v>
+        <v>125.8</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>858.34</v>
+        <v>112.91</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>551.92</v>
+        <v>105.87</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>128.78</v>
+        <v>55.31</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>136.56</v>
+        <v>56.54</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>79.51000000000001</v>
+        <v>49.97</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>36.93</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-0.19</v>
+        <v>1.21</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.15</v>
+        <v>-0.51</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.77</v>
+        <v>-0.89</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-1.31</v>
+        <v>-3.27</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-1.2</v>
+        <v>-2.92</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-0.71</v>
+        <v>-3.37</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-1.82</v>
+        <v>-3.3</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-2.65</v>
+        <v>-1.97</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-4.17</v>
+        <v>-1.89</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-4.36</v>
+        <v>-1.86</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-7.44</v>
+        <v>-2.01</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-5.9</v>
+        <v>-2.01</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-12.9</v>
+        <v>-2.15</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-2.75</v>
+        <v>-0.95</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-3.73</v>
+        <v>-0.39</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.17</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.2</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47">
@@ -4367,10 +4367,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0</v>
@@ -4400,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W48" s="3" t="n">
         <v>0</v>
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>33.93</v>
+        <v>46.62</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>34.12</v>
+        <v>38.96</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.82</v>
+        <v>34.75</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>31.57</v>
+        <v>39.93</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>35.61</v>
+        <v>81.08</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>97.26000000000001</v>
+        <v>209.17</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>123.15</v>
+        <v>97.11</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>93.31</v>
+        <v>75.41</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>102.08</v>
+        <v>103</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>106</v>
+        <v>155.96</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>105.34</v>
+        <v>152.05</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>105.56</v>
+        <v>155.12</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>126.91</v>
+        <v>139.03</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>126.91</v>
+        <v>86.13</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>130.01</v>
+        <v>104.33</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>123.77</v>
+        <v>131.64</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>215.57</v>
+        <v>334.17</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>205.96</v>
+        <v>124.33</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>861.48</v>
+        <v>111.93</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>552.62</v>
+        <v>109.45</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>134.81</v>
+        <v>57.6</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>141.92</v>
+        <v>58.7</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>82.12</v>
+        <v>51.46</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>37.76</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.58</v>
+        <v>0.66</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>0.66</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.96</v>
+        <v>2.11</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>3.21</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>3.57</v>
+        <v>2.62</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>4.13</v>
+        <v>4.05</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>3.79</v>
+        <v>3.35</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.91</v>
+        <v>5.43</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>3.93</v>
+        <v>2.24</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.51</v>
+        <v>-3.03</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-4.53</v>
+        <v>-3.01</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.5</v>
+        <v>-3.48</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-9.76</v>
+        <v>-3.13</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-2.05</v>
+        <v>2.63</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>4.54</v>
+        <v>2</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="52">
@@ -4787,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>0</v>
@@ -4811,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="R53" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S53" s="3" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W53" s="3" t="n">
         <v>0</v>
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>34.71</v>
+        <v>47.64</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>35.09</v>
+        <v>39.81</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>35.59</v>
+        <v>35.47</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>32.16</v>
+        <v>40.72</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>36.24</v>
+        <v>82.44</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>98.38</v>
+        <v>200.8</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>101.36</v>
+        <v>92.36</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>74.81</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>68.33</v>
+        <v>100.21</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>102.69</v>
+        <v>152.06</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>103.51</v>
+        <v>147.23</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>100.75</v>
+        <v>144.77</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>107.29</v>
+        <v>131.84</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>122.36</v>
+        <v>84.14</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>122.59</v>
+        <v>100.39</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>123.89</v>
+        <v>101.47</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>205.89</v>
+        <v>201.25</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>197.79</v>
+        <v>118.78</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>859.73</v>
+        <v>106.44</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>553.65</v>
+        <v>99.09</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>134.67</v>
+        <v>52.55</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>136.83</v>
+        <v>55.92</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>83.15000000000001</v>
+        <v>52.21</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>38.62</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="55">
@@ -4952,13 +4952,13 @@
         <v>0</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>-18.45</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-15.69</v>
+        <v>0</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>-28.02</v>
+        <v>0</v>
       </c>
       <c r="L55" s="3" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="O55" s="3" t="n">
-        <v>-14.47</v>
+        <v>0</v>
       </c>
       <c r="P55" s="3" t="n">
         <v>0</v>
@@ -4979,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="R55" s="3" t="n">
-        <v>0</v>
+        <v>-30.44</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>0</v>
+        <v>-114.76</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>0</v>
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>1.59</v>
+        <v>3.46</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.24</v>
+        <v>-2.12</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.52</v>
+        <v>0.67</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-2.03</v>
+        <v>0.3</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.82</v>
+        <v>0.15</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>1.97</v>
+        <v>-1.47</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.91</v>
+        <v>-4.92</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.61</v>
+        <v>0.25</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-4.17</v>
+        <v>-0.7</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-3.39</v>
+        <v>-2.77</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-14.21</v>
+        <v>-21.17</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-11.67</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-11.51</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-1.02</v>
+        <v>-7.73</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>2.15</v>
+        <v>-3.15</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.55</v>
+        <v>-0.78</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.16</v>
+        <v>2.04</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="57">
@@ -5207,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>0</v>
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
         <v>0</v>
@@ -5240,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3" t="n">
         <v>0</v>
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>34.6</v>
+        <v>47.15</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>34.8</v>
+        <v>39.57</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>35.44</v>
+        <v>35.33</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>32.16</v>
+        <v>40.59</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>36.02</v>
+        <v>81.42</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>96.76000000000001</v>
+        <v>208.3</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>123.4</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>93.31</v>
+        <v>75.33</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>101.94</v>
+        <v>102.68</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>103.94</v>
+        <v>154.06</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>103.83</v>
+        <v>151.28</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>104.05</v>
+        <v>152.28</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>124.34</v>
+        <v>137.34</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>124.22</v>
+        <v>85.16</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>125.75</v>
+        <v>103.27</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>126</v>
+        <v>138.55</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>216.63</v>
+        <v>348.68</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>207.39</v>
+        <v>130.42</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>864.6799999999999</v>
+        <v>116.93</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>552.42</v>
+        <v>109.56</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>131.73</v>
+        <v>57.19</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>141.04</v>
+        <v>58.58</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>82.12</v>
+        <v>51.56</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>38.07</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P61" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O61" s="3" t="n">
+      <c r="Q61" s="3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="W61" s="3" t="n">
         <v>1.49</v>
       </c>
-      <c r="P61" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>-3.47</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>-6.56</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>-0.79</v>
-      </c>
       <c r="X61" s="3" t="n">
-        <v>3.67</v>
+        <v>1.87</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>0.99</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="62">
@@ -5627,10 +5627,10 @@
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L63" s="3" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S63" s="3" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W63" s="3" t="n">
         <v>0</v>
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>35.04</v>
+        <v>47.74</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>35.2</v>
+        <v>40.02</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>35.88</v>
+        <v>35.77</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>32.57</v>
+        <v>41.1</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>36.51</v>
+        <v>82.44</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>98.08</v>
+        <v>211.37</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>124.69</v>
+        <v>98.52</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>94.34999999999999</v>
+        <v>76.59</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>103.32</v>
+        <v>104.4</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>104.48</v>
+        <v>156.6</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>105.23</v>
+        <v>153.78</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>104.69</v>
+        <v>154.8</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>124.6</v>
+        <v>139.46</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>124.98</v>
+        <v>86.48</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>127.52</v>
+        <v>104.87</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>128.19</v>
+        <v>140.87</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>219.87</v>
+        <v>354.18</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>210.51</v>
+        <v>132.45</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>873.86</v>
+        <v>119.11</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>554.46</v>
+        <v>111.27</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>133.72</v>
+        <v>58.02</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>143.1</v>
+        <v>59.44</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>83.31999999999999</v>
+        <v>52.26</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>38.54</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D66" s="3" t="n">
         <v>1.72</v>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>1.65</v>
-      </c>
       <c r="E66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>1.86</v>
+        <v>3.46</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>4.02</v>
+        <v>10.57</v>
       </c>
       <c r="I66" s="3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="N66" s="3" t="n">
         <v>5.11</v>
       </c>
-      <c r="J66" s="3" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>3.04</v>
-      </c>
       <c r="O66" s="3" t="n">
-        <v>1.74</v>
+        <v>4.32</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0.77</v>
+        <v>3.78</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>0.91</v>
+        <v>6.2</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>-0.22</v>
+        <v>17</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>1.05</v>
+        <v>4.64</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.62</v>
+        <v>4.05</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>-0.22</v>
+        <v>4.45</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.2</v>
+        <v>2.32</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>5.72</v>
+        <v>2.73</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>3.33</v>
+        <v>2.09</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="67">
@@ -6047,10 +6047,10 @@
         <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S68" s="3" t="n">
         <v>0</v>
@@ -6080,10 +6080,10 @@
         <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W68" s="3" t="n">
         <v>0</v>
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>35.56</v>
+        <v>48.29</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>35.76</v>
+        <v>40.53</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>36.42</v>
+        <v>36.31</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>33.02</v>
+        <v>41.72</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>37.02</v>
+        <v>83.31</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>213.84</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>126</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>95</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>105</v>
+        <v>105.17</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>106</v>
+        <v>156.77</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>106</v>
+        <v>154.42</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>106</v>
+        <v>155.61</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>126</v>
+        <v>140.48</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>126</v>
+        <v>87.11</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>126</v>
+        <v>105.97</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>126</v>
+        <v>142.51</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>214.72</v>
+        <v>358.7</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>206.16</v>
+        <v>133.14</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>861.48</v>
+        <v>119.36</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>551</v>
+        <v>112.09</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>131.73</v>
+        <v>58.57</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>144.15</v>
+        <v>60.13</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>84.11</v>
+        <v>52.87</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>38.95</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.24</v>
+        <v>2.61</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>2.37</v>
+        <v>4.33</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>4.85</v>
+        <v>13.04</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>6.43</v>
+        <v>4.56</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>3.99</v>
+        <v>3.78</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>6.63</v>
+        <v>5.26</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4.13</v>
+        <v>4.86</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4.45</v>
+        <v>5.71</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.35</v>
+        <v>5.91</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>3.15</v>
+        <v>5.34</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>-0.76</v>
+        <v>4.87</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>-1.28</v>
+        <v>7.84</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>-5.37</v>
+        <v>21.52</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>-3.3</v>
+        <v>5.33</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>-9.76</v>
+        <v>4.3</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>-3.67</v>
+        <v>5.27</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>-0.79</v>
+        <v>2.87</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>6.78</v>
+        <v>3.43</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>4.12</v>
+        <v>2.7</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="72">
@@ -6467,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S73" s="3" t="n">
         <v>0</v>
@@ -6500,10 +6500,10 @@
         <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W73" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>34.64</v>
+        <v>47.2</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>34.8</v>
+        <v>39.57</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>35.47</v>
+        <v>35.36</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>32.16</v>
+        <v>40.63</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>36.09</v>
+        <v>81.42</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>97.16</v>
+        <v>208.95</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>123.91</v>
+        <v>97.31</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>93.45999999999999</v>
+        <v>75.64</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>102.35</v>
+        <v>103.32</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>104.59</v>
+        <v>155.16</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>104.47</v>
+        <v>152.36</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>104.69</v>
+        <v>153.38</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>125.23</v>
+        <v>138.18</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>125.1</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>126.38</v>
+        <v>103.69</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>126.38</v>
+        <v>138.84</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>217.7</v>
+        <v>349.41</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>208.42</v>
+        <v>130.82</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>867.2</v>
+        <v>117.41</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>552.77</v>
+        <v>109.9</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>132.65</v>
+        <v>57.42</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>141.77</v>
+        <v>58.82</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>82.45999999999999</v>
+        <v>51.78</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>38.15</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>1.44</v>
+        <v>2.44</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>3.11</v>
+        <v>8.15</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>4.34</v>
+        <v>2.82</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>3.98</v>
+        <v>3.41</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>2.72</v>
+        <v>3.26</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="N76" s="3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O76" s="3" t="n">
         <v>3.04</v>
       </c>
-      <c r="O76" s="3" t="n">
-        <v>2.38</v>
-      </c>
       <c r="P76" s="3" t="n">
-        <v>2.13</v>
+        <v>1.62</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>-0.38</v>
+        <v>2.59</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>-0.9</v>
+        <v>4.17</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>-2.39</v>
+        <v>12.23</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>-1.04</v>
+        <v>3.01</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>-4.04</v>
+        <v>2.35</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>-1.9</v>
+        <v>3.08</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>0.13</v>
+        <v>1.72</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>4.39</v>
+        <v>2.12</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.47</v>
+        <v>1.61</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="77">
@@ -6887,10 +6887,10 @@
         <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L78" s="3" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
         <v>0</v>
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W78" s="3" t="n">
         <v>0</v>
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>33.32</v>
+        <v>45.69</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>33.54</v>
+        <v>38.3</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>34.16</v>
+        <v>34.09</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>30.91</v>
+        <v>39.17</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>34.65</v>
+        <v>78.97</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>94.05</v>
+        <v>200.8</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>119.57</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>91.01000000000001</v>
+        <v>73.29000000000001</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>98.37</v>
+        <v>99.91</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>101.87</v>
+        <v>151.91</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>101.55</v>
+        <v>148.71</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>101.65</v>
+        <v>149.7</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>122.85</v>
+        <v>135.14</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>122.98</v>
+        <v>83.89</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>126.76</v>
+        <v>101.1</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>127.28</v>
+        <v>134.67</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>220.09</v>
+        <v>337.18</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>209.46</v>
+        <v>127.81</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>871.24</v>
+        <v>115.06</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>554.67</v>
+        <v>106.82</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>132.52</v>
+        <v>55.7</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>137.38</v>
+        <v>56.71</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>50.17</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>37.08</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="80">
@@ -7307,10 +7307,10 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="n">
         <v>0</v>
@@ -7331,7 +7331,7 @@
         <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="n">
         <v>0</v>
@@ -7340,10 +7340,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="n">
         <v>0</v>
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>34.17</v>
+        <v>47.49</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>34.72</v>
+        <v>39.49</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>35.04</v>
+        <v>35.18</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>31.7</v>
+        <v>40.3</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>35.94</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>97.16</v>
+        <v>196.48</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>97.08</v>
+        <v>89.81</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>72.33</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>63.77</v>
+        <v>100.01</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>100.76</v>
+        <v>151.45</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>101.65</v>
+        <v>146.94</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>95.36</v>
+        <v>139.9</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>101.1</v>
+        <v>126.3</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>116.79</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>116.72</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>118.17</v>
+        <v>96.25</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>199.36</v>
+        <v>195.15</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>191.29</v>
+        <v>116.19</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>849.24</v>
+        <v>104.22</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>552.37</v>
+        <v>97.73</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>134.54</v>
+        <v>52.25</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>129.72</v>
+        <v>54.89</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>81.37</v>
+        <v>52.15</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>38.26</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="85">
@@ -7472,13 +7472,13 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>-18.45</v>
+        <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>-15.69</v>
+        <v>0</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>-28.02</v>
+        <v>0</v>
       </c>
       <c r="L85" s="3" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>-14.47</v>
+        <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
         <v>0</v>
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>0</v>
+        <v>-30.44</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>0</v>
+        <v>-114.76</v>
       </c>
       <c r="T85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.85</v>
+        <v>1.8</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>1.18</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.88</v>
+        <v>1.09</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>3.11</v>
+        <v>-4.32</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-4.04</v>
+        <v>-4.67</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-2.99</v>
+        <v>0.67</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-6.59</v>
+        <v>0.1</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-1.11</v>
+        <v>-0.45</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.1</v>
+        <v>-1.76</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-6.29</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-7.28</v>
+        <v>-8.84</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-6.19</v>
+        <v>-3.46</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-10.04</v>
+        <v>-5</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-9.1</v>
+        <v>-7.98</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-20.73</v>
+        <v>-27.27</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-18.17</v>
+        <v>-11.62</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-22</v>
+        <v>-10.84</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-2.3</v>
+        <v>-9.09</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>2.02</v>
+        <v>-3.45</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-7.65</v>
+        <v>-1.81</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.38</v>
+        <v>1.98</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="87">
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
         <v>0</v>
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
         <v>0</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W88" s="3" t="n">
         <v>0</v>
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>32.51</v>
+        <v>44.4</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>33</v>
+        <v>37.33</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>33.33</v>
+        <v>33.16</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>30.18</v>
+        <v>38.14</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>33.97</v>
+        <v>75.94</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>110.63</v>
+        <v>192.34</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>157.12</v>
+        <v>91.03</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>75.02</v>
+        <v>69.02</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>48.11</v>
+        <v>71.37</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>69.31999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>64.98</v>
+        <v>90.56</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>67.23999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>75.05</v>
+        <v>87.95</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>77.53</v>
+        <v>78.69</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>122.71</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>122.8</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>727.9</v>
+        <v>221.86</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>1612.05</v>
+        <v>120.8</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>1600</v>
+        <v>108.65</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>552.62</v>
+        <v>100.3</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>295.3</v>
+        <v>52.7</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>83.86</v>
+        <v>51.53</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>56.42</v>
+        <v>47.65</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>36.21</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="90">
@@ -7889,40 +7889,40 @@
         <v>0</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>-22.71</v>
+        <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-35.2</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>-13.07</v>
+        <v>0</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-45.44</v>
+        <v>-22.27</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-31.08</v>
+        <v>-49.9</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-32.1</v>
+        <v>-49.2</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-29.39</v>
+        <v>-48.29</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-41.62</v>
+        <v>-38.23</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-39.7</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0</v>
+        <v>-16.73</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>0</v>
+        <v>-25.93</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>0</v>
+        <v>-95.63</v>
       </c>
       <c r="T90" s="3" t="n">
         <v>0</v>
@@ -7934,13 +7934,13 @@
         <v>0</v>
       </c>
       <c r="W90" s="3" t="n">
-        <v>-38.42</v>
+        <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-46.6</v>
+        <v>-2.12</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-19.84</v>
+        <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
         <v>0</v>
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.29</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.97</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.83</v>
+        <v>-0.93</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-0.72</v>
+        <v>-1.03</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-0.91</v>
+        <v>-3.04</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-3.53</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-4.6</v>
+        <v>-3.46</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-2.92</v>
+        <v>-4.28</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-4.83</v>
+        <v>-6.27</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-4.39</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-4.47</v>
+        <v>-8.94</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-5.02</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-6.18</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-6.63</v>
+        <v>-5.19</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-4.05</v>
+        <v>-6.61</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-4.48</v>
+        <v>-8.81</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-6.82</v>
+        <v>-19.68</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-9.210000000000001</v>
+        <v>-7.01</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-19.69</v>
+        <v>-6.41</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-2.05</v>
+        <v>-6.52</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-5.95</v>
+        <v>-3</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-6.91</v>
+        <v>-3.06</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-3.74</v>
+        <v>-2.53</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-0.87</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="92">
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -8054,13 +8054,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>42.81</v>
+        <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>77.34</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
         <v>0</v>
@@ -8090,19 +8090,19 @@
         <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>514.63</v>
+        <v>0</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>1411.8</v>
+        <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>748.45</v>
+        <v>0</v>
       </c>
       <c r="V92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W92" s="3" t="n">
-        <v>207.15</v>
+        <v>0</v>
       </c>
       <c r="X92" s="3" t="n">
         <v>0</v>
@@ -8147,10 +8147,10 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>16.81</v>
+        <v>0</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>-30.21</v>
+        <v>0</v>
       </c>
       <c r="L93" s="3" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="S93" s="3" t="n">
         <v>0</v>
@@ -8180,10 +8180,10 @@
         <v>0</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="W93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-13T23:14:07</t>
+          <t>CreatedAt: 2026-10-14T04:11:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -653,73 +653,73 @@
         <v>44.62</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>37.48</v>
+        <v>43.6</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>33.29</v>
+        <v>41.33</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>38.22</v>
+        <v>45.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>76.52</v>
+        <v>77.77</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>194.01</v>
+        <v>115.9</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>91.11</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>69.94</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>72.88</v>
+        <v>76.33</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>93.95</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>91.89</v>
+        <v>90.27</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>93.45999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>89.62</v>
+        <v>85.69</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>79.59</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>101.6</v>
+        <v>91.06</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>226.72</v>
+        <v>138.63</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>122.31</v>
+        <v>102.72</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>110</v>
+        <v>101.19</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>102.12</v>
+        <v>90</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>53.3</v>
+        <v>54.57</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>52.2</v>
+        <v>61.82</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>48.2</v>
+        <v>43.37</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>41.9</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="5">
@@ -755,34 +755,34 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>-12.75</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-22.27</v>
+        <v>-25.16</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-49.9</v>
+        <v>-49.13</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-49.2</v>
+        <v>-45.38</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-48.29</v>
+        <v>-42.03</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-38.23</v>
+        <v>-34.8</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
+        <v>-6.09</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-16.73</v>
+        <v>-15.76</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-25.93</v>
+        <v>-35.49</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-95.63</v>
+        <v>-28.4</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-2.12</v>
+        <v>-12.44</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -821,73 +821,73 @@
         <v>-1.07</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.82</v>
+        <v>-1.13</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.22</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-2.45</v>
+        <v>-2.72</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-6.79</v>
+        <v>-4.06</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.22</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-3.36</v>
+        <v>-4.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-4.76</v>
+        <v>-5.28</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-8.06</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-7.62</v>
+        <v>-7.33</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-7.94</v>
+        <v>-6.95</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-7.29</v>
+        <v>-6.63</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-4.3</v>
+        <v>-4.97</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-5.27</v>
+        <v>-4.81</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-7.14</v>
+        <v>-6.45</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-14.83</v>
+        <v>-7.18</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-5.5</v>
+        <v>-4.21</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-5.06</v>
+        <v>-4.15</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-4.7</v>
+        <v>-3.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.4</v>
+        <v>-2.51</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-2.39</v>
+        <v>-3.27</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.98</v>
+        <v>-1.69</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="7">
@@ -1004,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1073,73 +1073,73 @@
         <v>44.66</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>37.7</v>
+        <v>43.94</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>33.59</v>
+        <v>41.57</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>38.14</v>
+        <v>44.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>76.38</v>
+        <v>77.47</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>192.52</v>
+        <v>115.34</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>92.45</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>71.16</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>74.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>95.75</v>
+        <v>94.08</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>94.34</v>
+        <v>91.97</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>95.78</v>
+        <v>88.55</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>91.09</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>81.05</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>80.67</v>
+        <v>80.03</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>102.57</v>
+        <v>92.03</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>226.72</v>
+        <v>139.11</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>124.57</v>
+        <v>105.24</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>112.25</v>
+        <v>103.07</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>104.01</v>
+        <v>92.41</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>54.88</v>
+        <v>56.24</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>53.75</v>
+        <v>63.94</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>49.87</v>
+        <v>45.06</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>42.44</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="10">
@@ -1175,34 +1175,34 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>-12.75</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-22.27</v>
+        <v>-25.16</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-49.9</v>
+        <v>-49.13</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-49.2</v>
+        <v>-45.38</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-48.29</v>
+        <v>-42.03</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-38.23</v>
+        <v>-34.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>-6.09</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-16.73</v>
+        <v>-15.76</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-25.93</v>
+        <v>-35.49</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-95.63</v>
+        <v>-28.4</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>0</v>
@@ -1211,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-2.12</v>
+        <v>-12.44</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>0</v>
@@ -1241,73 +1241,73 @@
         <v>-1.03</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.79</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.52</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-2.6</v>
+        <v>-3.02</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-8.279999999999999</v>
+        <v>-4.61</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-2.03</v>
+        <v>-1.73</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.81</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-3.29</v>
+        <v>-4.2</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-6.26</v>
+        <v>-7.45</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-5.17</v>
+        <v>-5.63</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-5.62</v>
+        <v>-5.09</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-5.82</v>
+        <v>-5.36</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.84</v>
+        <v>-3.46</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.7</v>
+        <v>-3.35</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-6.17</v>
+        <v>-5.48</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-14.83</v>
+        <v>-6.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-3.24</v>
+        <v>-1.68</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-2.81</v>
+        <v>-2.27</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2.81</v>
+        <v>-1.39</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.84</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.84</v>
+        <v>-1.15</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="12">
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1493,73 +1493,73 @@
         <v>44.66</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>37.7</v>
+        <v>43.94</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>33.59</v>
+        <v>41.57</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>38.14</v>
+        <v>44.8</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>76.38</v>
+        <v>77.47</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>99.29000000000001</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>94.73</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>71.16</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>96.63</v>
+        <v>102.56</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>145.64</v>
+        <v>143.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>143.54</v>
+        <v>137.34</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>144.08</v>
+        <v>130.58</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>129.32</v>
+        <v>121.75</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>81.05</v>
+        <v>93.58</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>98.06999999999999</v>
+        <v>97.87</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>207.59</v>
+        <v>133.43</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>136.97</v>
+        <v>134.36</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>135.28</v>
+        <v>134.41</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>104.11</v>
+        <v>92.84</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>132.16</v>
+        <v>131.86</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>74.27</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>49.87</v>
+        <v>45.06</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>42.44</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="15">
@@ -1589,10 +1589,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-93.23</v>
+        <v>-26.54</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1619,25 +1619,25 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-30.44</v>
+        <v>-29.77</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-114.76</v>
+        <v>-34.08</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>12.27</v>
+        <v>29.11</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>23.03</v>
+        <v>31.33</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>77.28</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.35</v>
+        <v>16.65</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>0</v>
@@ -1661,73 +1661,73 @@
         <v>-1.03</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.79</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.52</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.6</v>
+        <v>-3.02</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-8.279999999999999</v>
+        <v>-4.61</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-2.03</v>
+        <v>-1.64</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-2.13</v>
+        <v>-2.81</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-3.29</v>
+        <v>-4.2</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-6.26</v>
+        <v>-7.45</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-5.17</v>
+        <v>-5.63</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-5.62</v>
+        <v>-5.09</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-5.82</v>
+        <v>-5.36</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.84</v>
+        <v>-3.46</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-3.7</v>
+        <v>-3.35</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-6.17</v>
+        <v>-5.36</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-14.83</v>
+        <v>-6.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-3.12</v>
+        <v>-1.68</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-2.81</v>
+        <v>-2.27</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-2.71</v>
+        <v>-1.39</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.79</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.78</v>
+        <v>-1.15</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.59</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="17">
@@ -1844,10 +1844,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1913,73 +1913,73 @@
         <v>44.53</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>37.44</v>
+        <v>43.47</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>33.23</v>
+        <v>41.17</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>38.18</v>
+        <v>44.93</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>76.23</v>
+        <v>77.55</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>193.08</v>
+        <v>115.67</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>91.11</v>
+        <v>93.73</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>69.54000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>48.9</v>
+        <v>49.18</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>40.95</v>
+        <v>41.07</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>39.76</v>
+        <v>42.17</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>42.15</v>
+        <v>42.12</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>48.82</v>
+        <v>48.74</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>79.20999999999999</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>61.01</v>
+        <v>61.51</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>73.68000000000001</v>
+        <v>53.12</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>124.27</v>
+        <v>107.72</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>121.72</v>
+        <v>102.22</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>109.48</v>
+        <v>100.61</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>101.44</v>
+        <v>88.84</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>53.1</v>
+        <v>54.36</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>49.72</v>
+        <v>48.49</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>48.01</v>
+        <v>43.21</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>41.9</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="20">
@@ -2015,34 +2015,34 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0</v>
+        <v>-26.12</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-45.63</v>
+        <v>-51.54</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-102.22</v>
+        <v>-100.65</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-100.79</v>
+        <v>-92.97</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-98.94</v>
+        <v>-86.11</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-78.31</v>
+        <v>-71.28</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>-12.47</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-34.27</v>
+        <v>-32.29</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-53.13</v>
+        <v>-72.70999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-195.93</v>
+        <v>-58.19</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-4.34</v>
+        <v>-25.49</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>0</v>
@@ -2081,73 +2081,73 @@
         <v>-1.16</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.26</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.36</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.39</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-2.74</v>
+        <v>-2.95</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-7.72</v>
+        <v>-4.28</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.31</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-3.76</v>
+        <v>-4.94</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-5.39</v>
+        <v>-6.04</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-8.73</v>
+        <v>-8.93</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-8.15</v>
+        <v>-7.84</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.44</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-8.01</v>
+        <v>-7.08</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-4.67</v>
+        <v>-5.32</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-5.81</v>
+        <v>-5.35</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-7.86</v>
+        <v>-7.17</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-16.97</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-6.09</v>
+        <v>-4.7</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-5.58</v>
+        <v>-4.73</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-5.38</v>
+        <v>-4.49</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.6</v>
+        <v>-2.72</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-2.65</v>
+        <v>-3.55</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.16</v>
+        <v>-1.86</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="22">
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
@@ -2333,73 +2333,73 @@
         <v>44.53</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>37.44</v>
+        <v>43.47</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>33.23</v>
+        <v>41.17</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>38.18</v>
+        <v>44.93</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>76.23</v>
+        <v>77.55</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>193.08</v>
+        <v>115.67</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>91.11</v>
+        <v>93.73</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>69.54000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>72.25</v>
+        <v>75.56</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>93.27</v>
+        <v>92.59</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>91.36</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>92.8</v>
+        <v>86.2</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>85.23</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>79.20999999999999</v>
+        <v>85.64</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>78.56</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>100.88</v>
+        <v>90.34</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>224.57</v>
+        <v>137.51</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>121.72</v>
+        <v>102.22</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>109.48</v>
+        <v>100.61</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>101.44</v>
+        <v>89.31</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>53.1</v>
+        <v>54.36</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>51.94</v>
+        <v>61.54</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>48.01</v>
+        <v>43.21</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>41.9</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="25">
@@ -2435,34 +2435,34 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>-12.75</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-22.27</v>
+        <v>-25.16</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-49.9</v>
+        <v>-49.13</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-49.2</v>
+        <v>-45.38</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-48.29</v>
+        <v>-42.03</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-38.23</v>
+        <v>-34.8</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
+        <v>-6.09</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-16.73</v>
+        <v>-15.76</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-25.93</v>
+        <v>-35.49</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-95.63</v>
+        <v>-28.4</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>0</v>
@@ -2471,13 +2471,13 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-2.12</v>
+        <v>-12.44</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>0</v>
@@ -2501,73 +2501,73 @@
         <v>-1.16</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.26</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.36</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-0.99</v>
+        <v>-1.39</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-2.74</v>
+        <v>-2.95</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-7.72</v>
+        <v>-4.28</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.31</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-3.76</v>
+        <v>-4.94</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-5.39</v>
+        <v>-6.04</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-8.73</v>
+        <v>-8.93</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-8.15</v>
+        <v>-7.84</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-8.609999999999999</v>
+        <v>-7.44</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-8.01</v>
+        <v>-7.08</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-4.67</v>
+        <v>-5.32</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-5.81</v>
+        <v>-5.35</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-7.86</v>
+        <v>-7.17</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-16.97</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-6.09</v>
+        <v>-4.7</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-5.58</v>
+        <v>-4.73</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-5.38</v>
+        <v>-4.49</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.6</v>
+        <v>-2.72</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-2.65</v>
+        <v>-3.55</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.16</v>
+        <v>-1.86</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="27">
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2753,73 +2753,73 @@
         <v>44.4</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>37.33</v>
+        <v>43.34</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>33.16</v>
+        <v>40.97</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>38.14</v>
+        <v>44.75</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>75.94</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>192.34</v>
+        <v>115.45</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>91.03</v>
+        <v>93.73</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>69.02</v>
+        <v>64.38</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>48.01</v>
+        <v>48.14</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>39.88</v>
+        <v>40.02</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>38.97</v>
+        <v>41.28</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>41.22</v>
+        <v>41.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>47.87</v>
+        <v>47.84</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>78.69</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>60.21</v>
+        <v>60.71</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>72.73999999999999</v>
+        <v>52.18</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>121.56</v>
+        <v>106.47</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>120.8</v>
+        <v>101.35</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>108.65</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>100.3</v>
+        <v>87.91</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>52.7</v>
+        <v>53.95</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>49.31</v>
+        <v>48</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>47.65</v>
+        <v>42.92</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>41.9</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="30">
@@ -2855,34 +2855,34 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0</v>
+        <v>-26.12</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-45.63</v>
+        <v>-51.54</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-102.22</v>
+        <v>-100.65</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-100.79</v>
+        <v>-92.97</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-98.94</v>
+        <v>-86.11</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-78.31</v>
+        <v>-71.28</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>-12.47</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-34.27</v>
+        <v>-32.29</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-53.13</v>
+        <v>-72.70999999999999</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-195.93</v>
+        <v>-58.19</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>0</v>
@@ -2891,13 +2891,13 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-4.34</v>
+        <v>-25.49</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>0</v>
@@ -2921,73 +2921,73 @@
         <v>-1.29</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.39</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.93</v>
+        <v>-1.56</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.57</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-3.04</v>
+        <v>-3.17</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.31</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-4.28</v>
+        <v>-5.71</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-6.27</v>
+        <v>-7.08</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.99</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-8.94</v>
+        <v>-8.73</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-9.529999999999999</v>
+        <v>-8.16</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-8.960000000000001</v>
+        <v>-7.98</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-5.19</v>
+        <v>-6.01</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-6.61</v>
+        <v>-6.14</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-8.81</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-19.68</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-7.01</v>
+        <v>-5.57</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-6.41</v>
+        <v>-5.49</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-6.52</v>
+        <v>-5.42</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3</v>
+        <v>-3.13</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-3.06</v>
+        <v>-4.04</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.15</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="32">
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3173,73 +3173,73 @@
         <v>45.23</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>38.22</v>
+        <v>44.73</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>34.09</v>
+        <v>42.31</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>38.52</v>
+        <v>45.23</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>77.34999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>111.23</v>
+        <v>92.91</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>95.83</v>
+        <v>99.98</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>72.70999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>98.53</v>
+        <v>104.26</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>148.06</v>
+        <v>144.72</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>146.36</v>
+        <v>139.35</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>146.9</v>
+        <v>132.62</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>131.57</v>
+        <v>123.59</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>82.84999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>99.73</v>
+        <v>97.98</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>100.26</v>
+        <v>99.87</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>212.73</v>
+        <v>136.44</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>139.96</v>
+        <v>137.12</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>137.86</v>
+        <v>136.46</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>107.36</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>134.01</v>
+        <v>133.82</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>75.8</v>
+        <v>94.97</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>51.67</v>
+        <v>46.65</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>43.25</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="35">
@@ -3269,10 +3269,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-83.91</v>
+        <v>-23.89</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -3299,25 +3299,25 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-30.44</v>
+        <v>-29.77</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-114.76</v>
+        <v>-34.08</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>12.27</v>
+        <v>29.11</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>23.03</v>
+        <v>31.33</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>77.28</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>18.35</v>
+        <v>16.65</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0</v>
@@ -3341,73 +3341,73 @@
         <v>-0.45</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-0.65</v>
+        <v>-1.09</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-1.62</v>
+        <v>-2.19</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-5.66</v>
+        <v>-3.15</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.37</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.86</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-1.38</v>
+        <v>-2.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-3.85</v>
+        <v>-5.93</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-2.34</v>
+        <v>-3.62</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-2.79</v>
+        <v>-3.05</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-3.68</v>
+        <v>-3.7</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-1.16</v>
+        <v>-1.72</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-1.59</v>
+        <v>-1.37</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-4.18</v>
+        <v>-3.62</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-9.82</v>
+        <v>-3.92</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>-0.13</v>
+        <v>1.08</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>0.54</v>
+        <v>1.73</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.22</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="37">
@@ -3458,19 +3458,19 @@
         <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3593,73 +3593,73 @@
         <v>44.62</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>37.48</v>
+        <v>43.6</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>33.29</v>
+        <v>41.33</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>38.22</v>
+        <v>45.1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>76.52</v>
+        <v>77.77</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>194.01</v>
+        <v>115.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>91.11</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>69.94</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>72.88</v>
+        <v>76.33</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>93.95</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>91.89</v>
+        <v>90.27</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>93.45999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>89.62</v>
+        <v>85.69</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>79.59</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>101.6</v>
+        <v>91.06</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>226.72</v>
+        <v>138.63</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>122.31</v>
+        <v>102.72</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>110</v>
+        <v>101.19</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>102.12</v>
+        <v>90</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>53.3</v>
+        <v>54.57</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>52.2</v>
+        <v>61.82</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>48.2</v>
+        <v>43.37</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>41.9</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="40">
@@ -3695,34 +3695,34 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>-12.75</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-22.27</v>
+        <v>-25.16</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-49.9</v>
+        <v>-49.13</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-49.2</v>
+        <v>-45.38</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-48.29</v>
+        <v>-42.03</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-38.23</v>
+        <v>-34.8</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>-6.09</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-16.73</v>
+        <v>-15.76</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-25.93</v>
+        <v>-35.49</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-95.63</v>
+        <v>-28.4</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-2.12</v>
+        <v>-12.44</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
@@ -3761,73 +3761,73 @@
         <v>-1.07</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-0.82</v>
+        <v>-1.13</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-0.96</v>
+        <v>-1.22</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-2.45</v>
+        <v>-2.72</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-6.79</v>
+        <v>-4.06</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.22</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-3.36</v>
+        <v>-4.5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-4.76</v>
+        <v>-5.28</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-8.06</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-7.62</v>
+        <v>-7.33</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-7.94</v>
+        <v>-6.95</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-7.29</v>
+        <v>-6.63</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-4.3</v>
+        <v>-4.97</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-5.27</v>
+        <v>-4.81</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-7.14</v>
+        <v>-6.45</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-14.83</v>
+        <v>-7.18</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-5.5</v>
+        <v>-4.21</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-5.06</v>
+        <v>-4.15</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-4.7</v>
+        <v>-3.8</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.4</v>
+        <v>-2.51</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-2.39</v>
+        <v>-3.27</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.98</v>
+        <v>-1.69</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="42">
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4013,73 +4013,73 @@
         <v>45.82</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>38.42</v>
+        <v>44.82</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>34.23</v>
+        <v>42.61</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>39.37</v>
+        <v>46.46</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>79.05</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>202.01</v>
+        <v>119.71</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>94.2</v>
+        <v>96.77</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>72.79000000000001</v>
+        <v>95.44</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>99.02</v>
+        <v>105.7</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>148.64</v>
+        <v>147.26</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>145.79</v>
+        <v>139.9</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>146.33</v>
+        <v>132.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>131.84</v>
+        <v>123.89</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>81.92</v>
+        <v>94.77</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>99.20999999999999</v>
+        <v>97.78</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>132.81</v>
+        <v>131.94</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>335.17</v>
+        <v>173.51</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>125.8</v>
+        <v>105.66</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>112.91</v>
+        <v>104.09</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>105.87</v>
+        <v>93.59</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>55.31</v>
+        <v>56.69</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>56.54</v>
+        <v>77.3</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>49.97</v>
+        <v>44.84</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>43.08</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="45">
@@ -4181,73 +4181,73 @@
         <v>0.14</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E46" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>0.14</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>0.2</v>
-      </c>
       <c r="G46" s="3" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.21</v>
+        <v>-0.24</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>-0.28</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.76</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.06</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.39</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-2.92</v>
+        <v>-3.08</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-3.37</v>
+        <v>-3.57</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-3.3</v>
+        <v>-3.22</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-1.97</v>
+        <v>-2.27</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.89</v>
+        <v>-1.37</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.06</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-2.01</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-2.01</v>
+        <v>-1.27</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-2.15</v>
+        <v>-1.25</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.95</v>
+        <v>-0.66</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.17</v>
+        <v>-0.23</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.22</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4364,10 +4364,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -4433,73 +4433,73 @@
         <v>46.62</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>38.96</v>
+        <v>45.5</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>34.75</v>
+        <v>43.39</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>39.93</v>
+        <v>47.27</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>81.08</v>
+        <v>82.47</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>209.17</v>
+        <v>124.3</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>97.11</v>
+        <v>99.23</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>75.41</v>
+        <v>98.48</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>103</v>
+        <v>110.86</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>155.96</v>
+        <v>155.79</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>152.05</v>
+        <v>147.4</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>155.12</v>
+        <v>141.92</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>139.03</v>
+        <v>131.99</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>86.13</v>
+        <v>99.23</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>104.33</v>
+        <v>101.79</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>131.64</v>
+        <v>129.88</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>334.17</v>
+        <v>172.66</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>124.33</v>
+        <v>104.22</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>111.93</v>
+        <v>102.37</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>109.45</v>
+        <v>96.56</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>57.6</v>
+        <v>59.09</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>58.7</v>
+        <v>80.09</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>51.46</v>
+        <v>46.08</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>43.91</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="50">
@@ -4601,73 +4601,73 @@
         <v>0.93</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.66</v>
+        <v>0.87</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>8.369999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>3.09</v>
+        <v>4.1</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>4.05</v>
+        <v>5.14</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>3.35</v>
+        <v>4.42</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>5.43</v>
+        <v>6.24</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.89</v>
+        <v>4.88</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.03</v>
+        <v>-3.12</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.01</v>
+        <v>-1.55</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.48</v>
+        <v>-2.71</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.13</v>
+        <v>-2.97</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="52">
@@ -4784,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>0</v>
@@ -4853,73 +4853,73 @@
         <v>47.64</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>39.81</v>
+        <v>46.59</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>35.47</v>
+        <v>44.39</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>40.72</v>
+        <v>48.3</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>82.44</v>
+        <v>83.94</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>200.8</v>
+        <v>118.53</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>92.36</v>
+        <v>98.17</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>73.95999999999999</v>
+        <v>97.48</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>100.21</v>
+        <v>105.6</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>152.06</v>
+        <v>146.55</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>147.23</v>
+        <v>140.45</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>144.77</v>
+        <v>134.86</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>131.84</v>
+        <v>125.85</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>84.14</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>100.39</v>
+        <v>98.36</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>101.47</v>
+        <v>100.49</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>201.25</v>
+        <v>130.89</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>118.78</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>106.44</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>99.09</v>
+        <v>87.05</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>52.55</v>
+        <v>53.9</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>55.92</v>
+        <v>78.23</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>52.21</v>
+        <v>46.84</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>44.97</v>
+        <v>45.24</v>
       </c>
     </row>
     <row r="55">
@@ -4979,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="R55" s="3" t="n">
-        <v>-30.44</v>
+        <v>-29.77</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>-114.76</v>
+        <v>-34.08</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5021,73 +5021,73 @@
         <v>1.95</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>-1.42</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-2.12</v>
+        <v>1.13</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.67</v>
+        <v>1.27</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.3</v>
+        <v>-1.16</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.15</v>
+        <v>-4.1</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-1.47</v>
+        <v>-2.53</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-4.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-3.3</v>
+        <v>-1.26</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.79</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-2.77</v>
+        <v>-2.74</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-21.17</v>
+        <v>-9.24</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-9.029999999999999</v>
+        <v>-7.27</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-8.619999999999999</v>
+        <v>-7.35</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-7.73</v>
+        <v>-6.66</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-3.15</v>
+        <v>-3.18</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.78</v>
+        <v>0.7</v>
       </c>
       <c r="Y56" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z56" s="3" t="n">
         <v>2.04</v>
-      </c>
-      <c r="Z56" s="3" t="n">
-        <v>1.93</v>
       </c>
     </row>
     <row r="57">
@@ -5204,10 +5204,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>0</v>
@@ -5273,73 +5273,73 @@
         <v>47.15</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>39.57</v>
+        <v>46.16</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>35.33</v>
+        <v>43.93</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>40.59</v>
+        <v>47.85</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>81.42</v>
+        <v>82.98</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>208.3</v>
+        <v>123.28</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>97.01000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>75.33</v>
+        <v>98.78</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>102.68</v>
+        <v>109.5</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>154.06</v>
+        <v>152.32</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>151.28</v>
+        <v>144.86</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>152.28</v>
+        <v>137.18</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>137.34</v>
+        <v>128.65</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>85.16</v>
+        <v>98.62</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>103.27</v>
+        <v>101.59</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>138.55</v>
+        <v>137.11</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>348.68</v>
+        <v>180.15</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>130.42</v>
+        <v>109.22</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>116.93</v>
+        <v>107.49</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>109.56</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>57.19</v>
+        <v>58.73</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>58.58</v>
+        <v>80.09</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>51.56</v>
+        <v>46.36</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>44.46</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="60">
@@ -5441,73 +5441,73 @@
         <v>1.46</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="G61" s="3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q61" s="3" t="n">
         <v>2.44</v>
       </c>
-      <c r="H61" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I61" s="3" t="n">
+      <c r="R61" s="3" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V61" s="3" t="n">
         <v>2.52</v>
       </c>
-      <c r="J61" s="3" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>11.51</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>2.74</v>
-      </c>
       <c r="W61" s="3" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>1.87</v>
+        <v>2.56</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="62">
@@ -5624,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>0</v>
@@ -5693,73 +5693,73 @@
         <v>47.74</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>40.02</v>
+        <v>46.69</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>35.77</v>
+        <v>44.48</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>41.1</v>
+        <v>48.45</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>82.44</v>
+        <v>84.02</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>211.37</v>
+        <v>125.08</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>98.52</v>
+        <v>101.01</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>76.59</v>
+        <v>100.43</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>104.4</v>
+        <v>111.09</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>156.6</v>
+        <v>154.67</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>153.78</v>
+        <v>147.09</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>154.8</v>
+        <v>139.29</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>139.46</v>
+        <v>130.5</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>86.48</v>
+        <v>100.15</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>104.87</v>
+        <v>103.17</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>140.87</v>
+        <v>139.41</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>354.18</v>
+        <v>182.99</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>132.45</v>
+        <v>110.92</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>119.11</v>
+        <v>109.16</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>111.27</v>
+        <v>98.28</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>58.02</v>
+        <v>59.59</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>59.44</v>
+        <v>81.27</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>52.26</v>
+        <v>46.99</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>45.06</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="65">
@@ -5861,73 +5861,73 @@
         <v>2.05</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="F66" s="3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y66" s="3" t="n">
         <v>1.93</v>
       </c>
-      <c r="G66" s="3" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M66" s="3" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="N66" s="3" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="P66" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Q66" s="3" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="R66" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S66" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="T66" s="3" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="U66" s="3" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="V66" s="3" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W66" s="3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X66" s="3" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y66" s="3" t="n">
-        <v>2.09</v>
-      </c>
       <c r="Z66" s="3" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="67">
@@ -6044,10 +6044,10 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0</v>
@@ -6113,73 +6113,73 @@
         <v>48.29</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>40.53</v>
+        <v>47.28</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>36.31</v>
+        <v>45.05</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>41.72</v>
+        <v>49.07</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>83.31</v>
+        <v>85</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>213.84</v>
+        <v>126</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>99.04000000000001</v>
+        <v>101.52</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>77.06999999999999</v>
+        <v>101.07</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>105.17</v>
+        <v>112.14</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>156.77</v>
+        <v>155.15</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>154.42</v>
+        <v>147.85</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>155.61</v>
+        <v>140.16</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>140.48</v>
+        <v>131.72</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>87.11</v>
+        <v>100.88</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>105.97</v>
+        <v>104.15</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>142.51</v>
+        <v>141.04</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>358.7</v>
+        <v>185.13</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>133.14</v>
+        <v>111.38</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>119.36</v>
+        <v>109.62</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>112.09</v>
+        <v>99</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>58.57</v>
+        <v>60.09</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>60.13</v>
+        <v>82.3</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>52.87</v>
+        <v>47.49</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>45.64</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="70">
@@ -6281,73 +6281,73 @@
         <v>2.61</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.21</v>
+        <v>2.52</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>13.04</v>
+        <v>6.05</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>3.78</v>
+        <v>4.86</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>5.26</v>
+        <v>5.38</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5.71</v>
+        <v>4.88</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>5.91</v>
+        <v>4.48</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>5.34</v>
+        <v>4.61</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.22</v>
+        <v>3.83</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>7.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>21.52</v>
+        <v>10.92</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>5.33</v>
+        <v>4.46</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>5.27</v>
+        <v>4.75</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>3.43</v>
+        <v>4.77</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="72">
@@ -6464,10 +6464,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
@@ -6533,73 +6533,73 @@
         <v>47.2</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>39.57</v>
+        <v>46.21</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>35.36</v>
+        <v>43.97</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>40.63</v>
+        <v>47.9</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>81.42</v>
+        <v>82.98</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>208.95</v>
+        <v>123.53</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>97.31</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>75.64</v>
+        <v>99.19</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>103.32</v>
+        <v>110.18</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>155.16</v>
+        <v>153.41</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>152.36</v>
+        <v>145.89</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>153.38</v>
+        <v>138.16</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>138.18</v>
+        <v>129.57</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>85.51000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>103.69</v>
+        <v>101.9</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>138.84</v>
+        <v>137.25</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>349.41</v>
+        <v>180.9</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>130.82</v>
+        <v>109.56</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>117.41</v>
+        <v>107.82</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>109.9</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>57.42</v>
+        <v>59.03</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>58.82</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>51.78</v>
+        <v>46.51</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>44.55</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="75">
@@ -6701,73 +6701,73 @@
         <v>1.51</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>8.15</v>
+        <v>3.58</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>3.26</v>
+        <v>2.76</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>3.66</v>
+        <v>2.92</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>3.68</v>
+        <v>2.49</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>3.04</v>
+        <v>2.46</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>12.23</v>
+        <v>6.69</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>3.01</v>
+        <v>2.63</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.12</v>
+        <v>2.98</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="77">
@@ -6884,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K78" s="3" t="n">
         <v>0</v>
@@ -6953,73 +6953,73 @@
         <v>45.69</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>38.3</v>
+        <v>44.73</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>34.09</v>
+        <v>42.52</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>39.17</v>
+        <v>46.32</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>78.97</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>200.8</v>
+        <v>119.95</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>94.48999999999999</v>
+        <v>97.05</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>73.29000000000001</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>99.91</v>
+        <v>106.76</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>151.91</v>
+        <v>150.65</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>148.71</v>
+        <v>142.98</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>149.7</v>
+        <v>135.67</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>135.14</v>
+        <v>127.11</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>83.89</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>101.1</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>134.67</v>
+        <v>133</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>337.18</v>
+        <v>174.21</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>127.81</v>
+        <v>106.93</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>115.06</v>
+        <v>105.34</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>106.82</v>
+        <v>94.25</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>55.7</v>
+        <v>57.08</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>56.71</v>
+        <v>77.53</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>50.17</v>
+        <v>45.06</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>43.04</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="80">
@@ -7304,10 +7304,10 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
@@ -7373,73 +7373,73 @@
         <v>47.49</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>39.49</v>
+        <v>46.21</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>35.18</v>
+        <v>44.25</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>40.3</v>
+        <v>48.1</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>82.18000000000001</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>196.48</v>
+        <v>116.57</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>89.81</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>73.95999999999999</v>
+        <v>97.58</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>100.01</v>
+        <v>105.81</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>151.45</v>
+        <v>147.26</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>146.94</v>
+        <v>136.04</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>139.9</v>
+        <v>130.08</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>126.3</v>
+        <v>120.14</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>93.58</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>96.25</v>
+        <v>95.47</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>195.15</v>
+        <v>127.67</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>116.19</v>
+        <v>97.47</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>104.22</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>97.73</v>
+        <v>85.61</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>52.25</v>
+        <v>53.65</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>54.89</v>
+        <v>79.11</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>52.15</v>
+        <v>46.65</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>44.69</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="85">
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>-30.44</v>
+        <v>-29.77</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>-114.76</v>
+        <v>-34.08</v>
       </c>
       <c r="T85" s="3" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7541,73 +7541,73 @@
         <v>1.8</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1.18</v>
+        <v>1.48</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.13</v>
+        <v>1.78</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-4.32</v>
+        <v>-3.38</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-4.67</v>
+        <v>1.41</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.67</v>
+        <v>1.37</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-0.45</v>
+        <v>-3.39</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-1.76</v>
+        <v>-6.94</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-9.789999999999999</v>
+        <v>-5.59</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-8.84</v>
+        <v>-6.97</v>
       </c>
       <c r="P86" s="3" t="n">
         <v>-3.46</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-5</v>
+        <v>-5.96</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-7.98</v>
+        <v>-7.76</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-27.27</v>
+        <v>-12.46</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-11.62</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-10.84</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-9.09</v>
+        <v>-8.1</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.45</v>
+        <v>-3.43</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-1.81</v>
+        <v>1.58</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.98</v>
+        <v>1.59</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="87">
@@ -7724,10 +7724,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>0</v>
@@ -7793,73 +7793,73 @@
         <v>44.4</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>37.33</v>
+        <v>43.34</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>33.16</v>
+        <v>40.97</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>38.14</v>
+        <v>44.71</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>75.94</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>192.34</v>
+        <v>115.45</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>91.03</v>
+        <v>93.73</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>69.02</v>
+        <v>77.75</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>71.37</v>
+        <v>74.53</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>92.2</v>
+        <v>91.53</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>90.56</v>
+        <v>88.87</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>91.87</v>
+        <v>85.48</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>87.95</v>
+        <v>84.33</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>78.69</v>
+        <v>84.95</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>77.76000000000001</v>
+        <v>77.25</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>99.93000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>221.86</v>
+        <v>136.26</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>120.8</v>
+        <v>101.35</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>108.65</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>100.3</v>
+        <v>88.38</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>52.7</v>
+        <v>53.95</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>51.53</v>
+        <v>60.98</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>47.65</v>
+        <v>42.92</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>41.9</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="90">
@@ -7895,34 +7895,34 @@
         <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0</v>
+        <v>-12.75</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-22.27</v>
+        <v>-25.16</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-49.9</v>
+        <v>-49.13</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-49.2</v>
+        <v>-45.38</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-48.29</v>
+        <v>-42.03</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-38.23</v>
+        <v>-34.8</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>0</v>
+        <v>-6.09</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-16.73</v>
+        <v>-15.76</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-25.93</v>
+        <v>-35.49</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-95.63</v>
+        <v>-28.4</v>
       </c>
       <c r="T90" s="3" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-2.12</v>
+        <v>-12.44</v>
       </c>
       <c r="Y90" s="3" t="n">
         <v>0</v>
@@ -7961,73 +7961,73 @@
         <v>-1.29</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.39</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.93</v>
+        <v>-1.56</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.61</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-3.04</v>
+        <v>-3.17</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-8.460000000000001</v>
+        <v>-4.5</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.31</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-4.28</v>
+        <v>-5.71</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-6.27</v>
+        <v>-7.08</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.99</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-8.94</v>
+        <v>-8.73</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-9.529999999999999</v>
+        <v>-8.16</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-8.960000000000001</v>
+        <v>-7.98</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-5.19</v>
+        <v>-6.01</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-6.61</v>
+        <v>-6.14</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-8.81</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-19.68</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-7.01</v>
+        <v>-5.57</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-6.41</v>
+        <v>-5.49</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-6.52</v>
+        <v>-5.42</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3</v>
+        <v>-3.13</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-3.06</v>
+        <v>-4.11</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.53</v>
+        <v>-2.15</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.13</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="92">
@@ -8144,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="K93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-14T04:11:43</t>
+          <t>CreatedAt: 2026-10-14T09:11:55</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -671,55 +671,55 @@
         <v>93.81999999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>78.95999999999999</v>
+        <v>96.41</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>76.33</v>
+        <v>80.83</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>90.27</v>
+        <v>95.75</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>86.69</v>
+        <v>98.12</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>85.69</v>
+        <v>86.59</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>85.98999999999999</v>
+        <v>92.87</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>78.56999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>91.06</v>
+        <v>103.98</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>138.63</v>
+        <v>146.12</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>102.72</v>
+        <v>144</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>101.19</v>
+        <v>144</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>90</v>
+        <v>101.1</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>54.57</v>
+        <v>69.66</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>61.82</v>
+        <v>62.05</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>43.37</v>
+        <v>42.46</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>42.07</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="5">
@@ -755,34 +755,34 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-12.75</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>-25.16</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-49.13</v>
+        <v>-29.84</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-45.38</v>
+        <v>-0.28</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-42.03</v>
+        <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-34.8</v>
+        <v>-36.49</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-6.09</v>
+        <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-15.76</v>
+        <v>-20.91</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-35.49</v>
+        <v>-4.73</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-28.4</v>
+        <v>-23.5</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-12.44</v>
+        <v>-12.43</v>
       </c>
       <c r="Y5" s="3" t="n">
         <v>0</v>
@@ -836,58 +836,58 @@
         <v>-4.06</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-4.5</v>
+        <v>-4.24</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-5.28</v>
+        <v>-4.04</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-8.119999999999999</v>
+        <v>-6.75</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-7.33</v>
+        <v>-5.38</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-6.95</v>
+        <v>-5.49</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-6.63</v>
+        <v>-6.65</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-4.97</v>
+        <v>-5.01</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>-4.81</v>
       </c>
       <c r="R6" s="3" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>-6.45</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>-7.18</v>
-      </c>
       <c r="T6" s="3" t="n">
-        <v>-4.21</v>
+        <v>-5.18</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-4.15</v>
+        <v>-5.47</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.8</v>
+        <v>-4.25</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.51</v>
+        <v>-3.06</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.13</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.61</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="7">
@@ -1004,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1088,58 +1088,58 @@
         <v>115.34</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>95.31999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>80.65000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>282.11</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>94.08</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>91.97</v>
+        <v>155.66</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>88.55</v>
+        <v>100.77</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>86.95999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>87.48999999999999</v>
+        <v>94.94</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>80.03</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>92.03</v>
+        <v>105.02</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>139.11</v>
+        <v>146.78</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>105.24</v>
+        <v>147.42</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>103.07</v>
+        <v>146.97</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>92.41</v>
+        <v>103.58</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>56.24</v>
+        <v>71.86</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>63.94</v>
+        <v>64.41</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>45.06</v>
+        <v>44.34</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>42.77</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="10">
@@ -1175,34 +1175,34 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-12.75</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>-25.16</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-49.13</v>
+        <v>-29.84</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-45.38</v>
+        <v>-0.28</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-42.03</v>
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-34.8</v>
+        <v>-36.49</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-6.09</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-15.76</v>
+        <v>-20.91</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-35.49</v>
+        <v>-4.73</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-28.4</v>
+        <v>-23.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>0</v>
@@ -1211,13 +1211,13 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-12.44</v>
+        <v>-12.43</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>0</v>
@@ -1256,58 +1256,58 @@
         <v>-4.61</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.73</v>
+        <v>-1.52</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.81</v>
+        <v>-2.45</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-4.2</v>
+        <v>-2.87</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-7.45</v>
+        <v>-5.41</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-5.63</v>
+        <v>-3.33</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-5.09</v>
+        <v>-3.31</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-5.36</v>
+        <v>-4.87</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-3.46</v>
+        <v>-2.94</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.35</v>
+        <v>-2.85</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-5.48</v>
+        <v>-4.06</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-6.7</v>
+        <v>-5.79</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.77</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.5</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.39</v>
+        <v>-1.76</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.84</v>
+        <v>-0.86</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.77</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="12">
@@ -1346,16 +1346,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>200.11</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>57.86</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1424,10 +1424,10 @@
         <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1508,58 +1508,58 @@
         <v>88.79000000000001</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>98.70999999999999</v>
+        <v>95.39</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>102.56</v>
+        <v>282.11</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>143.2</v>
+        <v>117.8</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>137.34</v>
+        <v>155.94</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>130.58</v>
+        <v>100.87</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>121.75</v>
+        <v>124.86</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>93.58</v>
+        <v>94.94</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>95.79000000000001</v>
+        <v>98.17</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>97.87</v>
+        <v>104.18</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>133.43</v>
+        <v>142.08</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>134.36</v>
+        <v>500</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>134.41</v>
+        <v>500</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>92.84</v>
+        <v>135.11</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>131.86</v>
+        <v>271.75</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>93.04000000000001</v>
+        <v>131.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>45.06</v>
+        <v>100.42</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>42.77</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="15">
@@ -1592,7 +1592,7 @@
         <v>-26.54</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
@@ -1619,28 +1619,28 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-29.77</v>
+        <v>-5.68</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-34.08</v>
+        <v>-28.19</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>29.11</v>
+        <v>352.58</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>31.33</v>
+        <v>353.03</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>-0.02</v>
+        <v>31.52</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>75.56999999999999</v>
+        <v>199.9</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>16.65</v>
+        <v>54.38</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>56.04</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1676,58 +1676,58 @@
         <v>-4.61</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.64</v>
+        <v>-1.43</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-2.81</v>
+        <v>-2.45</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-4.2</v>
+        <v>-2.87</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-7.45</v>
+        <v>-5.3</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-5.63</v>
+        <v>-3.33</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-5.09</v>
+        <v>-3.21</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-5.36</v>
+        <v>-4.87</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-3.46</v>
+        <v>-2.94</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-3.35</v>
+        <v>-2.85</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-5.36</v>
+        <v>-3.96</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-6.7</v>
+        <v>-5.79</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.68</v>
+        <v>-1.77</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.5</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.39</v>
+        <v>-1.76</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.86</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.43</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="17">
@@ -1766,16 +1766,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>200.11</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0</v>
+        <v>57.86</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>0</v>
@@ -1844,10 +1844,10 @@
         <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1928,58 +1928,58 @@
         <v>115.67</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>93.73</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>65.15000000000001</v>
+        <v>96.22</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>49.18</v>
+        <v>80.44</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>41.07</v>
+        <v>54.67</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>42.17</v>
+        <v>95.27</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>42.12</v>
+        <v>98.12</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>48.74</v>
+        <v>47.97</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>79.26000000000001</v>
+        <v>92.61</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>61.51</v>
+        <v>52.91</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>53.12</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>107.72</v>
+        <v>120.51</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>102.22</v>
+        <v>143.45</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>100.61</v>
+        <v>143.58</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>88.84</v>
+        <v>100.52</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>54.36</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>48.49</v>
+        <v>48.67</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>43.21</v>
+        <v>42.34</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>42.07</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="20">
@@ -2015,34 +2015,34 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-26.12</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-51.54</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-100.65</v>
+        <v>-61.14</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-92.97</v>
+        <v>-0.58</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-86.11</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-71.28</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-12.47</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-32.29</v>
+        <v>-42.85</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-72.70999999999999</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-58.19</v>
+        <v>-48.14</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-25.49</v>
+        <v>-25.46</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>0</v>
@@ -2096,58 +2096,58 @@
         <v>-4.28</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-4.94</v>
+        <v>-4.43</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-6.04</v>
+        <v>-4.42</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-8.93</v>
+        <v>-7.3</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-7.84</v>
+        <v>-5.56</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-7.44</v>
+        <v>-5.49</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-7.08</v>
+        <v>-7</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-5.32</v>
+        <v>-5.28</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-5.35</v>
+        <v>-5.27</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-7.17</v>
+        <v>-5.63</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.42</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-4.7</v>
+        <v>-5.74</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-4.73</v>
+        <v>-5.89</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-4.49</v>
+        <v>-4.82</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.72</v>
+        <v>-3.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-3.55</v>
+        <v>-3.48</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.74</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="22">
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
@@ -2348,58 +2348,58 @@
         <v>115.67</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>93.73</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>78.52</v>
+        <v>96.22</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>75.56</v>
+        <v>80.44</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>92.59</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>89.76000000000001</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>86.2</v>
+        <v>98.12</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.23</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>85.64</v>
+        <v>92.61</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>90.34</v>
+        <v>103.46</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>137.51</v>
+        <v>145.15</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>102.22</v>
+        <v>143.45</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>100.61</v>
+        <v>143.58</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>89.31</v>
+        <v>100.52</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>54.36</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>61.54</v>
+        <v>61.7</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>43.21</v>
+        <v>42.34</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>42.07</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="25">
@@ -2435,34 +2435,34 @@
         <v>0</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-12.75</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>-25.16</v>
+        <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-49.13</v>
+        <v>-29.84</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-45.38</v>
+        <v>-0.28</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-42.03</v>
+        <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-34.8</v>
+        <v>-36.49</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-6.09</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-15.76</v>
+        <v>-20.91</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-35.49</v>
+        <v>-4.73</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-28.4</v>
+        <v>-23.5</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>0</v>
@@ -2471,13 +2471,13 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-12.44</v>
+        <v>-12.43</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>0</v>
@@ -2516,58 +2516,58 @@
         <v>-4.28</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-4.94</v>
+        <v>-4.43</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-6.04</v>
+        <v>-4.42</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-8.93</v>
+        <v>-7.3</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-7.84</v>
+        <v>-5.56</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-7.44</v>
+        <v>-5.49</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-7.08</v>
+        <v>-7</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-5.32</v>
+        <v>-5.28</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-5.35</v>
+        <v>-5.27</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-7.17</v>
+        <v>-5.63</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.42</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-4.7</v>
+        <v>-5.74</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-4.73</v>
+        <v>-5.89</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-4.49</v>
+        <v>-4.82</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.72</v>
+        <v>-3.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-3.55</v>
+        <v>-3.48</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.74</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="27">
@@ -2684,10 +2684,10 @@
         <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2768,58 +2768,58 @@
         <v>115.45</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>93.73</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>64.38</v>
+        <v>95.95</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>48.14</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>40.02</v>
+        <v>54.02</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>41.28</v>
+        <v>95</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>41.4</v>
+        <v>98.03</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>47.84</v>
+        <v>47.4</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>78.56999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>60.71</v>
+        <v>52.28</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>52.18</v>
+        <v>97.98</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>106.47</v>
+        <v>119.54</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>101.35</v>
+        <v>142.62</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>99.84999999999999</v>
+        <v>142.9</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>87.91</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>53.95</v>
+        <v>68.86</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>48</v>
+        <v>48.17</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>42.92</v>
+        <v>42.05</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>41.98</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="30">
@@ -2855,34 +2855,34 @@
         <v>0</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-26.12</v>
+        <v>0</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-51.54</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-100.65</v>
+        <v>-61.14</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-92.97</v>
+        <v>-0.58</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-86.11</v>
+        <v>0</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-71.28</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-12.47</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-32.29</v>
+        <v>-42.85</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-72.70999999999999</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-58.19</v>
+        <v>-48.14</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>0</v>
@@ -2891,13 +2891,13 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-25.49</v>
+        <v>-25.46</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>0</v>
@@ -2936,58 +2936,58 @@
         <v>-4.5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-5.71</v>
+        <v>-4.7</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-7.08</v>
+        <v>-4.88</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-9.99</v>
+        <v>-7.95</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-8.73</v>
+        <v>-5.83</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-8.16</v>
+        <v>-5.59</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-7.98</v>
+        <v>-7.57</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-6.01</v>
+        <v>-5.8</v>
       </c>
       <c r="Q31" s="3" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>-6.14</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>-8.119999999999999</v>
-      </c>
       <c r="S31" s="3" t="n">
-        <v>-9.550000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-5.57</v>
+        <v>-6.56</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-5.49</v>
+        <v>-6.57</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-5.42</v>
+        <v>-5.77</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.86</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-4.04</v>
+        <v>-3.98</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.15</v>
+        <v>-2.02</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
@@ -3104,10 +3104,10 @@
         <v>0</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -3188,58 +3188,58 @@
         <v>92.91</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>99.98</v>
+        <v>96.53</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>95.34999999999999</v>
+        <v>100.25</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>104.26</v>
+        <v>103.08</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>144.72</v>
+        <v>119.52</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>139.35</v>
+        <v>105.78</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>132.62</v>
+        <v>102.42</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>123.59</v>
+        <v>126.8</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>95.48999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>97.98</v>
+        <v>100.61</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>99.87</v>
+        <v>105.77</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>136.44</v>
+        <v>144.81</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>137.12</v>
+        <v>503.58</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>136.46</v>
+        <v>502.95</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>95.95999999999999</v>
+        <v>138.69</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>133.82</v>
+        <v>274.33</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>94.97</v>
+        <v>133.49</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>46.65</v>
+        <v>102.09</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>43.81</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="35">
@@ -3272,7 +3272,7 @@
         <v>-23.89</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
         <v>0</v>
@@ -3299,28 +3299,28 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-29.77</v>
+        <v>-5.68</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-34.08</v>
+        <v>-28.19</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>29.11</v>
+        <v>352.58</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>31.33</v>
+        <v>353.03</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>-0.02</v>
+        <v>31.52</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>75.56999999999999</v>
+        <v>199.9</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>16.65</v>
+        <v>54.38</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>56.04</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3356,58 +3356,58 @@
         <v>-3.15</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-0.86</v>
+        <v>-0.4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-2.5</v>
+        <v>-1.42</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-5.93</v>
+        <v>-3.59</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-3.62</v>
+        <v>-1.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-3.05</v>
+        <v>-1.53</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-3.7</v>
+        <v>-3.04</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-1.72</v>
+        <v>-0.97</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-1.37</v>
+        <v>-0.7</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-3.62</v>
+        <v>-2.56</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-3.92</v>
+        <v>-3.28</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.08</v>
+        <v>1.81</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>-0.21</v>
+        <v>0.45</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.78</v>
+        <v>1.5</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="37">
@@ -3446,31 +3446,31 @@
         <v>0</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0</v>
+        <v>19.63</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>0</v>
@@ -3524,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3611,55 +3611,55 @@
         <v>93.81999999999999</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>78.95999999999999</v>
+        <v>96.41</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>76.33</v>
+        <v>80.83</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>90.27</v>
+        <v>95.75</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>86.69</v>
+        <v>98.12</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>85.69</v>
+        <v>86.59</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>85.98999999999999</v>
+        <v>92.87</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>78.56999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>91.06</v>
+        <v>103.98</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>138.63</v>
+        <v>146.12</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>102.72</v>
+        <v>144</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>101.19</v>
+        <v>144</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>90</v>
+        <v>101.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>54.57</v>
+        <v>69.66</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>61.82</v>
+        <v>62.05</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>43.37</v>
+        <v>42.46</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>42.07</v>
+        <v>37.26</v>
       </c>
     </row>
     <row r="40">
@@ -3695,34 +3695,34 @@
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-12.75</v>
+        <v>0</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-25.16</v>
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-49.13</v>
+        <v>-29.84</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-45.38</v>
+        <v>-0.28</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-42.03</v>
+        <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-34.8</v>
+        <v>-36.49</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-6.09</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-15.76</v>
+        <v>-20.91</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-35.49</v>
+        <v>-4.73</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-28.4</v>
+        <v>-23.5</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-12.44</v>
+        <v>-12.43</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>0</v>
@@ -3776,58 +3776,58 @@
         <v>-4.06</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-4.5</v>
+        <v>-4.24</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-5.28</v>
+        <v>-4.04</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-8.119999999999999</v>
+        <v>-6.75</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-7.33</v>
+        <v>-5.38</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-6.95</v>
+        <v>-5.49</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-6.63</v>
+        <v>-6.65</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-4.97</v>
+        <v>-5.01</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>-4.81</v>
       </c>
       <c r="R41" s="3" t="n">
+        <v>-5.11</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>-6.45</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>-7.18</v>
-      </c>
       <c r="T41" s="3" t="n">
-        <v>-4.21</v>
+        <v>-5.18</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-4.15</v>
+        <v>-5.47</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.8</v>
+        <v>-4.25</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.51</v>
+        <v>-3.06</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.27</v>
+        <v>-3.13</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.61</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.14</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="42">
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="n">
         <v>0</v>
@@ -4028,58 +4028,58 @@
         <v>119.71</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>96.77</v>
+        <v>96.73</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>95.44</v>
+        <v>100.15</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>105.7</v>
+        <v>84.36</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>147.26</v>
+        <v>120.22</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>139.9</v>
+        <v>99.42</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>132.1</v>
+        <v>100.89</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>123.89</v>
+        <v>126.32</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>94.77</v>
+        <v>95.59</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>97.78</v>
+        <v>99.73</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>131.94</v>
+        <v>113.14</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>173.51</v>
+        <v>175.89</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>105.66</v>
+        <v>148</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>104.09</v>
+        <v>147.55</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>93.59</v>
+        <v>104.51</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>56.69</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>77.3</v>
+        <v>77.38</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>44.84</v>
+        <v>43.9</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>43.2</v>
+        <v>38.23</v>
       </c>
     </row>
     <row r="45">
@@ -4196,55 +4196,55 @@
         <v>-0.24</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.76</v>
+        <v>-0.5</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.51</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-3.39</v>
+        <v>-2.89</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-3.08</v>
+        <v>-1.99</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-3.57</v>
+        <v>-2.72</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3.41</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-2.27</v>
+        <v>-2.29</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.06</v>
+        <v>-0.68</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.18</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.18</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.25</v>
+        <v>-1.92</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.84</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.51</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>-0.23</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>0</v>
@@ -4364,10 +4364,10 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
@@ -4448,58 +4448,58 @@
         <v>124.3</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>99.23</v>
+        <v>99.41</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>98.48</v>
+        <v>103.66</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>110.86</v>
+        <v>88.13</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>155.79</v>
+        <v>127.17</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>147.4</v>
+        <v>104.76</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>141.92</v>
+        <v>107.04</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>131.99</v>
+        <v>132.92</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>99.23</v>
+        <v>98.77</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>101.79</v>
+        <v>103.93</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>129.88</v>
+        <v>113.48</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>172.66</v>
+        <v>174.5</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>104.22</v>
+        <v>147.71</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>102.37</v>
+        <v>147.26</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>96.56</v>
+        <v>109.28</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>59.09</v>
+        <v>75.2</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>80.09</v>
+        <v>80.17</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>46.08</v>
+        <v>45.02</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>44.26</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="50">
@@ -4616,58 +4616,58 @@
         <v>4.35</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2.27</v>
+        <v>3.01</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>4.1</v>
+        <v>3.26</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>5.14</v>
+        <v>4.07</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4.42</v>
+        <v>3.35</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>6.24</v>
+        <v>3.43</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>4.88</v>
+        <v>3.19</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>2.18</v>
+        <v>0.89</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.12</v>
+        <v>-0.34</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.55</v>
+        <v>-1.57</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-2.71</v>
+        <v>-1.48</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.97</v>
+        <v>-2.21</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.32</v>
+        <v>3.93</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.01</v>
+        <v>0.95</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4784,10 +4784,10 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>0</v>
@@ -4868,58 +4868,58 @@
         <v>118.53</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>98.17</v>
+        <v>95.86</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>97.48</v>
+        <v>100.55</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>105.6</v>
+        <v>85.73</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>146.55</v>
+        <v>125.23</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>140.45</v>
+        <v>101.1</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>134.86</v>
+        <v>103.1</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>125.85</v>
+        <v>128.32</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>97.81999999999999</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>98.36</v>
+        <v>99.53</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>100.49</v>
+        <v>103.76</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>130.89</v>
+        <v>138.06</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>99.65000000000001</v>
+        <v>139.69</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>97.98999999999999</v>
+        <v>139.56</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>87.05</v>
+        <v>98.45</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>53.9</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>78.23</v>
+        <v>78.31</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>46.84</v>
+        <v>45.81</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>45.24</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="55">
@@ -4979,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="R55" s="3" t="n">
-        <v>-29.77</v>
+        <v>-5.68</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>-34.08</v>
+        <v>-28.19</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5036,58 +5036,58 @@
         <v>-1.42</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>1.13</v>
+        <v>-0.96</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>1.27</v>
+        <v>-0.1</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-1.16</v>
+        <v>0.86</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-4.1</v>
+        <v>2.13</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-2.53</v>
+        <v>-0.3</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.52</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-1.26</v>
+        <v>-1.41</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0.78</v>
+        <v>-0.1</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-0.79</v>
+        <v>-1.49</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-2.74</v>
+        <v>-4.38</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-9.24</v>
+        <v>-9.81</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-7.27</v>
+        <v>-9.5</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-7.35</v>
+        <v>-9.91</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-6.66</v>
+        <v>-6.89</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-3.18</v>
+        <v>-3.46</v>
       </c>
       <c r="X56" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="57">
@@ -5204,10 +5204,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>0</v>
@@ -5288,58 +5288,58 @@
         <v>123.28</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>99.52</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>98.78</v>
+        <v>103.55</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>109.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>152.32</v>
+        <v>124.22</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>144.86</v>
+        <v>102.95</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>137.18</v>
+        <v>104.87</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>128.65</v>
+        <v>131.31</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>98.62</v>
+        <v>99.48</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>101.59</v>
+        <v>103.51</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>137.11</v>
+        <v>117.46</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>180.15</v>
+        <v>182.26</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>109.22</v>
+        <v>152.7</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>107.49</v>
+        <v>152.21</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>96.76000000000001</v>
+        <v>108.04</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>58.73</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>80.09</v>
+        <v>80.17</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>46.36</v>
+        <v>45.34</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>44.58</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="60">
@@ -5456,58 +5456,58 @@
         <v>3.33</v>
       </c>
       <c r="I61" s="3" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q61" s="3" t="n">
         <v>2.48</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="R61" s="3" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X61" s="3" t="n">
         <v>2.57</v>
       </c>
-      <c r="K61" s="3" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="M61" s="3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="N61" s="3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P61" s="3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q61" s="3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R61" s="3" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S61" s="3" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="T61" s="3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U61" s="3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V61" s="3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W61" s="3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X61" s="3" t="n">
-        <v>2.56</v>
-      </c>
       <c r="Y61" s="3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="62">
@@ -5624,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>0</v>
@@ -5708,58 +5708,58 @@
         <v>125.08</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>101.01</v>
+        <v>100.96</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>100.43</v>
+        <v>105.17</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>111.09</v>
+        <v>88.77</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>154.67</v>
+        <v>126</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>147.09</v>
+        <v>104.54</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>139.29</v>
+        <v>106.49</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>130.5</v>
+        <v>133.2</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>100.15</v>
+        <v>101.12</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>103.17</v>
+        <v>105.12</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>139.41</v>
+        <v>119.43</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>182.99</v>
+        <v>185.33</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>110.92</v>
+        <v>155.24</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>109.16</v>
+        <v>154.57</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>98.28</v>
+        <v>109.73</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>59.59</v>
+        <v>75.83</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>81.27</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>46.99</v>
+        <v>45.95</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>45.14</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="65">
@@ -5876,58 +5876,58 @@
         <v>5.13</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3.97</v>
+        <v>4.14</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>4.23</v>
+        <v>4.52</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>4.33</v>
+        <v>3.91</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>4.02</v>
+        <v>2.9</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>4.12</v>
+        <v>3.14</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>3.62</v>
+        <v>2.88</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.39</v>
+        <v>3.46</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>6.41</v>
+        <v>5.61</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.99</v>
+        <v>6.05</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.03</v>
+        <v>4.39</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="X66" s="3" t="n">
         <v>3.74</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="67">
@@ -6044,10 +6044,10 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0</v>
@@ -6128,58 +6128,58 @@
         <v>126</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>101.52</v>
+        <v>101.49</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>101.07</v>
+        <v>105.95</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>112.14</v>
+        <v>89.62</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>155.15</v>
+        <v>126</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>147.85</v>
+        <v>105.09</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>140.16</v>
+        <v>107.26</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>131.72</v>
+        <v>134.3</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>100.88</v>
+        <v>101.75</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>104.15</v>
+        <v>106.12</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>141.04</v>
+        <v>120.83</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>185.13</v>
+        <v>187.5</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>111.38</v>
+        <v>155.89</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>109.62</v>
+        <v>155.21</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>99</v>
+        <v>110.54</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>60.09</v>
+        <v>76.55</v>
       </c>
       <c r="X69" s="3" t="n">
         <v>82.3</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>47.49</v>
+        <v>46.44</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>45.76</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="70">
@@ -6296,58 +6296,58 @@
         <v>6.05</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>4.47</v>
+        <v>4.67</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>4.86</v>
+        <v>5.3</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>5.38</v>
+        <v>4.75</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>4.88</v>
+        <v>3.68</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.48</v>
+        <v>3.65</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="P71" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W71" s="3" t="n">
         <v>3.83</v>
       </c>
-      <c r="Q71" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="S71" s="3" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="T71" s="3" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="U71" s="3" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="V71" s="3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W71" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="X71" s="3" t="n">
-        <v>4.77</v>
+        <v>4.69</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="72">
@@ -6464,10 +6464,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
@@ -6548,58 +6548,58 @@
         <v>123.53</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>99.81999999999999</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>99.19</v>
+        <v>103.98</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>110.18</v>
+        <v>87.95</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>153.41</v>
+        <v>125.23</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>145.89</v>
+        <v>103.69</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>138.16</v>
+        <v>105.73</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>129.57</v>
+        <v>131.84</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>99.02</v>
+        <v>99.88</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>101.9</v>
+        <v>103.83</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>137.25</v>
+        <v>117.7</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>180.9</v>
+        <v>183.02</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>109.56</v>
+        <v>153.32</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>107.82</v>
+        <v>152.68</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>97.26000000000001</v>
+        <v>108.6</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>59.03</v>
+        <v>75.12</v>
       </c>
       <c r="X74" s="3" t="n">
         <v>80.51000000000001</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>46.51</v>
+        <v>45.48</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>44.68</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="75">
@@ -6716,58 +6716,58 @@
         <v>3.58</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2.98</v>
+        <v>3.33</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>2.92</v>
+        <v>2.28</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>2.46</v>
+        <v>2.11</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>6.69</v>
+        <v>6.95</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>2.63</v>
+        <v>4.14</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>2.48</v>
+        <v>3.21</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.47</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="77">
@@ -6884,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K78" s="3" t="n">
         <v>0</v>
@@ -6968,58 +6968,58 @@
         <v>119.95</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>97.05</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>96.20999999999999</v>
+        <v>100.65</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>106.76</v>
+        <v>84.87</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>150.65</v>
+        <v>123.1</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>142.98</v>
+        <v>101.41</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>135.67</v>
+        <v>103.61</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>127.11</v>
+        <v>129.73</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>97.04000000000001</v>
+        <v>97.88</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>99.15000000000001</v>
+        <v>101.02</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>133</v>
+        <v>113.82</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>174.21</v>
+        <v>176.07</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>106.93</v>
+        <v>149.18</v>
       </c>
       <c r="U79" s="3" t="n">
+        <v>149.47</v>
+      </c>
+      <c r="V79" s="3" t="n">
         <v>105.34</v>
       </c>
-      <c r="V79" s="3" t="n">
-        <v>94.25</v>
-      </c>
       <c r="W79" s="3" t="n">
-        <v>57.08</v>
+        <v>72.72</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>77.53</v>
+        <v>77.61</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>45.06</v>
+        <v>44.07</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>43.2</v>
+        <v>38.23</v>
       </c>
     </row>
     <row r="80">
@@ -7304,10 +7304,10 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
@@ -7388,58 +7388,58 @@
         <v>116.57</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>98.45999999999999</v>
+        <v>94.19</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>97.58</v>
+        <v>100.75</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>105.81</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>147.26</v>
+        <v>124.22</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>136.04</v>
+        <v>97.7</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>130.08</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>120.14</v>
+        <v>122.74</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>93.58</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>93.18000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>95.47</v>
+        <v>99.03</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>127.67</v>
+        <v>134.53</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>97.47</v>
+        <v>135.99</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>96.29000000000001</v>
+        <v>136.13</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>85.61</v>
+        <v>96.47</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>53.65</v>
+        <v>68.73</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>79.11</v>
+        <v>79.03</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>46.65</v>
+        <v>45.57</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>45.19</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="85">
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>-29.77</v>
+        <v>-5.68</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>-34.08</v>
+        <v>-28.19</v>
       </c>
       <c r="T85" s="3" t="n">
         <v>0</v>
@@ -7511,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7556,58 +7556,58 @@
         <v>-3.38</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>1.41</v>
+        <v>-2.64</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>1.37</v>
+        <v>0.1</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-0.95</v>
+        <v>1.12</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>-3.39</v>
+        <v>1.12</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-6.94</v>
+        <v>-3.71</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-5.59</v>
+        <v>-3.79</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-6.97</v>
+        <v>-7</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-3.46</v>
+        <v>-3.67</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-5.96</v>
+        <v>-6.52</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-7.76</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-12.46</v>
+        <v>-13.34</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-9.449999999999999</v>
+        <v>-13.19</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-9.050000000000001</v>
+        <v>-13.34</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-8.1</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.43</v>
+        <v>-3.99</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="87">
@@ -7724,10 +7724,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>0</v>
@@ -7808,58 +7808,58 @@
         <v>115.45</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>93.73</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>77.75</v>
+        <v>95.95</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>74.53</v>
+        <v>79.91</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>91.53</v>
+        <v>85.31</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>88.87</v>
+        <v>95.3</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>85.48</v>
+        <v>98.03</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>84.33</v>
+        <v>85.67</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>84.95</v>
+        <v>92.08</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>77.25</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>102.95</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>136.26</v>
+        <v>144.19</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>101.35</v>
+        <v>142.62</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>99.84999999999999</v>
+        <v>142.9</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>88.38</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>53.95</v>
+        <v>68.86</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>60.98</v>
+        <v>61.2</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>42.92</v>
+        <v>42.05</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>41.98</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="90">
@@ -7895,34 +7895,34 @@
         <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>-12.75</v>
+        <v>0</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>-25.16</v>
+        <v>0</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-49.13</v>
+        <v>-29.84</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-45.38</v>
+        <v>-0.28</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-42.03</v>
+        <v>0</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-34.8</v>
+        <v>-36.49</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-6.09</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-15.76</v>
+        <v>-20.91</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-35.49</v>
+        <v>-4.73</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-28.4</v>
+        <v>-23.5</v>
       </c>
       <c r="T90" s="3" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-12.44</v>
+        <v>-12.43</v>
       </c>
       <c r="Y90" s="3" t="n">
         <v>0</v>
@@ -7976,58 +7976,58 @@
         <v>-4.5</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-5.71</v>
+        <v>-4.7</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-7.08</v>
+        <v>-4.95</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-9.99</v>
+        <v>-7.95</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-8.73</v>
+        <v>-5.83</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-8.16</v>
+        <v>-5.59</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-7.98</v>
+        <v>-7.57</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-6.01</v>
+        <v>-5.8</v>
       </c>
       <c r="Q91" s="3" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="R91" s="3" t="n">
         <v>-6.14</v>
       </c>
-      <c r="R91" s="3" t="n">
-        <v>-8.119999999999999</v>
-      </c>
       <c r="S91" s="3" t="n">
-        <v>-9.550000000000001</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-5.57</v>
+        <v>-6.56</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-5.49</v>
+        <v>-6.57</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-5.42</v>
+        <v>-5.77</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.13</v>
+        <v>-3.86</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-4.11</v>
+        <v>-3.98</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.15</v>
+        <v>-2.02</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="92">
@@ -8144,10 +8144,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-14T09:11:55</t>
+          <t>CreatedAt: 2026-10-14T13:09:26</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -683,43 +683,43 @@
         <v>95.75</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>98.12</v>
+        <v>100.82</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>86.59</v>
+        <v>117.26</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>92.87</v>
+        <v>100.59</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>75.3</v>
+        <v>103.25</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>103.98</v>
+        <v>116.81</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>146.12</v>
+        <v>317.61</v>
       </c>
       <c r="T4" s="3" t="n">
+        <v>320.66</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>203.93</v>
+      </c>
+      <c r="V4" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>101.1</v>
-      </c>
       <c r="W4" s="3" t="n">
-        <v>69.66</v>
+        <v>90.97</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>62.05</v>
+        <v>75.03</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>42.46</v>
+        <v>62</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>37.26</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="5">
@@ -770,19 +770,19 @@
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-36.49</v>
+        <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-20.91</v>
+        <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-4.73</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>-23.5</v>
+        <v>0</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>0</v>
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-12.43</v>
+        <v>-23.34</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-17.38</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
@@ -851,43 +851,43 @@
         <v>-5.38</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-5.49</v>
+        <v>-5.55</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-6.65</v>
+        <v>-6.1</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-5.01</v>
+        <v>-5.23</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-4.81</v>
+        <v>-4.75</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.11</v>
+        <v>-5.77</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-6.45</v>
+        <v>-12.7</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-5.18</v>
+        <v>-11.86</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-5.47</v>
+        <v>-8.16</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-4.25</v>
+        <v>-6.34</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-3.06</v>
+        <v>-4.09</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.13</v>
+        <v>-4.23</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.61</v>
+        <v>-3.18</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="7">
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>0</v>
@@ -1103,43 +1103,43 @@
         <v>155.66</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>100.77</v>
+        <v>103.65</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>88.37</v>
+        <v>119.88</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>94.94</v>
+        <v>101.55</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>77.26000000000001</v>
+        <v>104.96</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>105.02</v>
+        <v>116.56</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>146.78</v>
+        <v>319.14</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>147.42</v>
+        <v>328.58</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>146.97</v>
+        <v>207.92</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>103.58</v>
+        <v>147.53</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>71.86</v>
+        <v>93.84</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>64.41</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>44.34</v>
+        <v>65.67</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>37.96</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="10">
@@ -1190,19 +1190,19 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-36.49</v>
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-20.91</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-4.73</v>
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>-23.5</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>0</v>
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-12.43</v>
+        <v>-23.34</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-17.38</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>0</v>
@@ -1271,43 +1271,43 @@
         <v>-3.33</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-4.87</v>
+        <v>-3.48</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.94</v>
+        <v>-4.27</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3.04</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-4.06</v>
+        <v>-6.01</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-5.79</v>
+        <v>-11.17</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-1.77</v>
+        <v>-3.94</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-2.5</v>
+        <v>-4.16</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.76</v>
+        <v>-2.8</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.22</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.77</v>
+        <v>-1.22</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
@@ -1355,7 +1355,7 @@
         <v>57.86</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1451,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>0</v>
@@ -1523,43 +1523,43 @@
         <v>155.94</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>100.87</v>
+        <v>103.75</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>124.86</v>
+        <v>119.88</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>94.94</v>
+        <v>101.55</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>98.17</v>
+        <v>104.96</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>104.18</v>
+        <v>116.56</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>142.08</v>
+        <v>319.14</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>500</v>
+        <v>1985.76</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>500</v>
+        <v>1992.15</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>135.11</v>
+        <v>483.08</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>271.75</v>
+        <v>270.87</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>131.3</v>
+        <v>1997</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>100.42</v>
+        <v>99.64</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>37.96</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="15">
@@ -1619,28 +1619,28 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-5.68</v>
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>-28.19</v>
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>352.58</v>
+        <v>1657.18</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>353.03</v>
+        <v>1784.02</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>31.52</v>
+        <v>335.55</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>199.9</v>
+        <v>177.03</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>54.38</v>
+        <v>1895.52</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>56.04</v>
+        <v>16.5</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1691,43 +1691,43 @@
         <v>-3.33</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-4.87</v>
+        <v>-3.48</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.94</v>
+        <v>-4.27</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.85</v>
+        <v>-3.04</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-3.96</v>
+        <v>-6.01</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-5.79</v>
+        <v>-11.17</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-1.77</v>
+        <v>-3.94</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-2.5</v>
+        <v>-3.95</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.76</v>
+        <v>-2.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.22</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.12</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.31</v>
+        <v>0.58</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.27</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17">
@@ -1775,7 +1775,7 @@
         <v>57.86</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>0</v>
@@ -1871,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>0</v>
@@ -1943,43 +1943,43 @@
         <v>95.27</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>98.12</v>
+        <v>100.82</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>47.97</v>
+        <v>139.6</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>92.61</v>
+        <v>154.9</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>52.91</v>
+        <v>187.57</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>98.48999999999999</v>
+        <v>230.6</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>120.51</v>
+        <v>315.79</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>143.45</v>
+        <v>319.73</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>143.58</v>
+        <v>203.14</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>100.52</v>
+        <v>143.18</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>69.31999999999999</v>
+        <v>90.53</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>48.67</v>
+        <v>50.09</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>42.34</v>
+        <v>43.55</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>37.26</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="20">
@@ -2030,19 +2030,19 @@
         <v>0</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-74.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-42.85</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>-48.14</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>0</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-25.46</v>
+        <v>-47.81</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0</v>
+        <v>-35.6</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>0</v>
@@ -2111,43 +2111,43 @@
         <v>-5.56</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-5.49</v>
+        <v>-5.55</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-7</v>
+        <v>-5.87</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-5.28</v>
+        <v>-5.33</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-5.27</v>
+        <v>-4.85</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-5.63</v>
+        <v>-6.25</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-7.42</v>
+        <v>-14.52</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-5.74</v>
+        <v>-12.79</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-5.89</v>
+        <v>-8.94</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-4.82</v>
+        <v>-7.16</v>
       </c>
       <c r="W21" s="3" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="Y21" s="3" t="n">
         <v>-3.4</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>-3.48</v>
-      </c>
-      <c r="Y21" s="3" t="n">
-        <v>-1.74</v>
-      </c>
       <c r="Z21" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="22">
@@ -2198,16 +2198,16 @@
         <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0</v>
+        <v>22.12</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0</v>
+        <v>54.41</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0</v>
+        <v>84.41</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>0</v>
+        <v>114.28</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>0</v>
@@ -2363,43 +2363,43 @@
         <v>95.56999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>98.12</v>
+        <v>100.82</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>86.23999999999999</v>
+        <v>117.48</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>92.61</v>
+        <v>100.49</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>74.84</v>
+        <v>103.15</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>103.46</v>
+        <v>116.32</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>145.15</v>
+        <v>315.79</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>143.45</v>
+        <v>319.73</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>143.58</v>
+        <v>203.14</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>100.52</v>
+        <v>143.18</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>69.31999999999999</v>
+        <v>90.53</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>61.7</v>
+        <v>74.56</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>42.34</v>
+        <v>61.77</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>37.26</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="25">
@@ -2450,19 +2450,19 @@
         <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-36.49</v>
+        <v>0</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-20.91</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>-4.73</v>
+        <v>0</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>-23.5</v>
+        <v>0</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-12.43</v>
+        <v>-23.34</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-17.38</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -2531,43 +2531,43 @@
         <v>-5.56</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-5.49</v>
+        <v>-5.55</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-7</v>
+        <v>-5.87</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-5.28</v>
+        <v>-5.33</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-5.27</v>
+        <v>-4.85</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-5.63</v>
+        <v>-6.25</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-7.42</v>
+        <v>-14.52</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-5.74</v>
+        <v>-12.79</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-5.89</v>
+        <v>-8.94</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-4.82</v>
+        <v>-7.16</v>
       </c>
       <c r="W26" s="3" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="Y26" s="3" t="n">
         <v>-3.4</v>
       </c>
-      <c r="X26" s="3" t="n">
-        <v>-3.48</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>-1.74</v>
-      </c>
       <c r="Z26" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="27">
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>0</v>
@@ -2783,43 +2783,43 @@
         <v>95</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>98.03</v>
+        <v>100.73</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>47.4</v>
+        <v>139.71</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>92.08</v>
+        <v>154.71</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>52.28</v>
+        <v>187.18</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>97.98</v>
+        <v>229.99</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>119.54</v>
+        <v>313.09</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>142.62</v>
+        <v>317.9</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>142.9</v>
+        <v>201.79</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>99.56999999999999</v>
+        <v>141.69</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>68.86</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>48.17</v>
+        <v>49.34</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>42.05</v>
+        <v>43.17</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>37.22</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="30">
@@ -2870,19 +2870,19 @@
         <v>0</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-74.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-42.85</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-48.14</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>0</v>
@@ -2897,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-25.46</v>
+        <v>-47.81</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>-35.6</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>0</v>
@@ -2951,43 +2951,43 @@
         <v>-5.83</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-5.59</v>
+        <v>-5.64</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-7.57</v>
+        <v>-5.76</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.52</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-5.9</v>
+        <v>-5.24</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.14</v>
+        <v>-6.86</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-8.380000000000001</v>
+        <v>-17.21</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-6.56</v>
+        <v>-14.62</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-6.57</v>
+        <v>-10.29</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-5.77</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.86</v>
+        <v>-5.13</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-3.98</v>
+        <v>-5.44</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.02</v>
+        <v>-3.78</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="32">
@@ -3038,16 +3038,16 @@
         <v>0</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>0</v>
+        <v>22.12</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>54.41</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0</v>
+        <v>84.41</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>0</v>
+        <v>114.28</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>0</v>
@@ -3203,43 +3203,43 @@
         <v>105.78</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>102.42</v>
+        <v>105.57</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>126.8</v>
+        <v>121.53</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>97.09999999999999</v>
+        <v>103.44</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>100.61</v>
+        <v>107.04</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>105.77</v>
+        <v>117.67</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>144.81</v>
+        <v>324.15</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>503.58</v>
+        <v>1993.74</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>502.95</v>
+        <v>1996.31</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>138.69</v>
+        <v>488.33</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>274.33</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>133.49</v>
+        <v>2000</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>102.09</v>
+        <v>102.86</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>38.93</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="35">
@@ -3299,28 +3299,28 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>-5.68</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>-28.19</v>
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>352.58</v>
+        <v>1657.18</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>353.03</v>
+        <v>1784.02</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>31.52</v>
+        <v>335.55</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>199.9</v>
+        <v>177.03</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>54.38</v>
+        <v>1895.52</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>56.04</v>
+        <v>16.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3371,43 +3371,43 @@
         <v>-1.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-1.53</v>
+        <v>-1.05</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-3.04</v>
+        <v>-1.82</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>-0.97</v>
+        <v>-2.38</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.7</v>
+        <v>-0.96</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-2.56</v>
+        <v>-4.9</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-3.28</v>
+        <v>-6.16</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>1.81</v>
+        <v>4.04</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.98</v>
+        <v>3.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="37">
@@ -3455,22 +3455,22 @@
         <v>5.87</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>0</v>
@@ -3623,43 +3623,43 @@
         <v>95.75</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>98.12</v>
+        <v>100.82</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>86.59</v>
+        <v>117.26</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>92.87</v>
+        <v>100.59</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>75.3</v>
+        <v>103.25</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>103.98</v>
+        <v>116.81</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>146.12</v>
+        <v>317.61</v>
       </c>
       <c r="T39" s="3" t="n">
+        <v>320.66</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>203.93</v>
+      </c>
+      <c r="V39" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="U39" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>101.1</v>
-      </c>
       <c r="W39" s="3" t="n">
-        <v>69.66</v>
+        <v>90.97</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>62.05</v>
+        <v>75.03</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>42.46</v>
+        <v>62</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>37.26</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="40">
@@ -3710,19 +3710,19 @@
         <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-36.49</v>
+        <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-20.91</v>
+        <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>-4.73</v>
+        <v>0</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>-23.5</v>
+        <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>0</v>
@@ -3737,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-12.43</v>
+        <v>-23.34</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-17.38</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>0</v>
@@ -3791,43 +3791,43 @@
         <v>-5.38</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-5.49</v>
+        <v>-5.55</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-6.65</v>
+        <v>-6.1</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-5.01</v>
+        <v>-5.23</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-4.81</v>
+        <v>-4.75</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.11</v>
+        <v>-5.77</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-6.45</v>
+        <v>-12.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-5.18</v>
+        <v>-11.86</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-5.47</v>
+        <v>-8.16</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-4.25</v>
+        <v>-6.34</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-3.06</v>
+        <v>-4.09</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.13</v>
+        <v>-4.23</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.61</v>
+        <v>-3.18</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-0.97</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="42">
@@ -3971,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>0</v>
@@ -4043,43 +4043,43 @@
         <v>99.42</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>100.89</v>
+        <v>103.88</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>126.32</v>
+        <v>119.53</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>95.59</v>
+        <v>103.54</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>99.73</v>
+        <v>106.2</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>113.14</v>
+        <v>120.47</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>175.89</v>
+        <v>329.65</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>148</v>
+        <v>328.58</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>147.55</v>
+        <v>209.57</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>104.51</v>
+        <v>149.14</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>72.20999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>77.38</v>
+        <v>102.29</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>43.9</v>
+        <v>82.14</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>38.23</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="45">
@@ -4211,40 +4211,40 @@
         <v>-1.99</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-2.72</v>
+        <v>-2.49</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-3.41</v>
+        <v>-3.82</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-2.29</v>
+        <v>-2.28</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.81</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-0.68</v>
+        <v>-2.11</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.66</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.18</v>
+        <v>-3.94</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.51</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-0.84</v>
+        <v>-1.19</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.66</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.18</v>
+        <v>-0.41</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>0</v>
@@ -4463,43 +4463,43 @@
         <v>104.76</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>107.04</v>
+        <v>109.43</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>132.92</v>
+        <v>126.39</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>98.77</v>
+        <v>107.65</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>103.93</v>
+        <v>111.57</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>113.48</v>
+        <v>119.18</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>174.5</v>
+        <v>322.89</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>147.71</v>
+        <v>324.1</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>147.26</v>
+        <v>206.31</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>109.28</v>
+        <v>148.55</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>75.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>80.17</v>
+        <v>106.1</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>45.02</v>
+        <v>84.41</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>39.17</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="50">
@@ -4631,43 +4631,43 @@
         <v>3.35</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.43</v>
+        <v>3.06</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.19</v>
+        <v>3.03</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>0.89</v>
+        <v>1.83</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.91</v>
+        <v>3.57</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-0.34</v>
+        <v>-3.39</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.57</v>
+        <v>-7.42</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-1.48</v>
+        <v>-8.43</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-2.21</v>
+        <v>-5.78</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>3.93</v>
+        <v>-1.78</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>2.48</v>
+        <v>3.35</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>0.95</v>
+        <v>1.86</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="52">
@@ -4811,10 +4811,10 @@
         <v>0</v>
       </c>
       <c r="R53" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>0</v>
@@ -4883,43 +4883,43 @@
         <v>101.1</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>103.1</v>
+        <v>106.05</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>128.32</v>
+        <v>122.37</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>97.79000000000001</v>
+        <v>104.46</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>99.53</v>
+        <v>106.09</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>103.76</v>
+        <v>116.56</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>138.06</v>
+        <v>310.45</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>139.69</v>
+        <v>310.48</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>139.56</v>
+        <v>197.65</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>98.45</v>
+        <v>140.63</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>69.26000000000001</v>
+        <v>90.62</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>78.31</v>
+        <v>100.98</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>45.81</v>
+        <v>85.81</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>39.99</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="55">
@@ -4979,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="R55" s="3" t="n">
-        <v>-5.68</v>
+        <v>0</v>
       </c>
       <c r="S55" s="3" t="n">
-        <v>-28.19</v>
+        <v>0</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>0</v>
@@ -5051,43 +5051,43 @@
         <v>-0.3</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.52</v>
+        <v>-0.32</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-1.41</v>
+        <v>-0.98</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-0.1</v>
+        <v>-1.36</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-1.49</v>
+        <v>-1.91</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-4.38</v>
+        <v>-6.01</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-9.81</v>
+        <v>-19.86</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-9.5</v>
+        <v>-22.04</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-9.91</v>
+        <v>-14.43</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-6.89</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-3.46</v>
+        <v>-4.44</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.7</v>
+        <v>-1.62</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.74</v>
+        <v>3.26</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="57">
@@ -5231,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>0</v>
@@ -5303,43 +5303,43 @@
         <v>102.95</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>104.87</v>
+        <v>107.77</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>131.31</v>
+        <v>123.85</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>99.48</v>
+        <v>107.54</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>103.51</v>
+        <v>110.09</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>117.46</v>
+        <v>124.61</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>182.26</v>
+        <v>341.23</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>152.7</v>
+        <v>338.96</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>152.21</v>
+        <v>216.19</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>108.04</v>
+        <v>154.35</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>74.73999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>80.17</v>
+        <v>106.1</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>45.34</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>39.45</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="60">
@@ -5471,43 +5471,43 @@
         <v>1.54</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.58</v>
+        <v>0.5</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>2.48</v>
+        <v>2.09</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>3.64</v>
+        <v>2.04</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>6.2</v>
+        <v>10.92</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>3.51</v>
+        <v>6.44</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>2.74</v>
+        <v>4.11</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.7</v>
+        <v>4.01</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.57</v>
+        <v>3.5</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.27</v>
+        <v>2.38</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="62">
@@ -5651,10 +5651,10 @@
         <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T63" s="3" t="n">
         <v>0</v>
@@ -5723,43 +5723,43 @@
         <v>104.54</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>106.49</v>
+        <v>109.43</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>133.2</v>
+        <v>126</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>101.12</v>
+        <v>109.32</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>105.12</v>
+        <v>111.8</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>119.43</v>
+        <v>126.86</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>185.33</v>
+        <v>346.96</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>155.24</v>
+        <v>344.23</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>154.57</v>
+        <v>219.55</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>109.73</v>
+        <v>156.93</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>75.83</v>
+        <v>99.23</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>81.34999999999999</v>
+        <v>107.66</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>45.95</v>
+        <v>86.08</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>39.94</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="65">
@@ -5891,43 +5891,43 @@
         <v>3.14</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.46</v>
+        <v>2.65</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>5.61</v>
+        <v>4.28</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>9.27</v>
+        <v>16.65</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>6.05</v>
+        <v>11.7</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>5.1</v>
+        <v>7.46</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.39</v>
+        <v>6.59</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>3.11</v>
+        <v>4.17</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>3.74</v>
+        <v>5.06</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>1.88</v>
+        <v>3.53</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="67">
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T68" s="3" t="n">
         <v>0</v>
@@ -6143,43 +6143,43 @@
         <v>105.09</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>107.26</v>
+        <v>110</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>134.3</v>
+        <v>126</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>101.75</v>
+        <v>110</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>106.12</v>
+        <v>112.5</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>120.83</v>
+        <v>127</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>187.5</v>
+        <v>350.64</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>155.89</v>
+        <v>345.66</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>155.21</v>
+        <v>220.46</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>110.54</v>
+        <v>157.91</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>76.55</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>82.3</v>
+        <v>108.91</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>46.44</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>40.5</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="70">
@@ -6311,43 +6311,43 @@
         <v>3.68</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>4.57</v>
+        <v>2.65</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>3.87</v>
+        <v>4.18</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>5.09</v>
+        <v>4.5</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>7.01</v>
+        <v>4.43</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>11.44</v>
+        <v>20.33</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>6.7</v>
+        <v>13.14</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>5.74</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>5.2</v>
+        <v>7.58</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.83</v>
+        <v>4.9</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>4.69</v>
+        <v>6.32</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.37</v>
+        <v>4.44</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.27</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="72">
@@ -6491,10 +6491,10 @@
         <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T73" s="3" t="n">
         <v>0</v>
@@ -6563,43 +6563,43 @@
         <v>103.69</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>105.73</v>
+        <v>108.65</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>131.84</v>
+        <v>124.47</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>99.88</v>
+        <v>108.09</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>103.83</v>
+        <v>110.55</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>117.7</v>
+        <v>124.89</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>183.02</v>
+        <v>341.93</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>153.32</v>
+        <v>339.31</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>152.68</v>
+        <v>216.85</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>108.6</v>
+        <v>154.98</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>75.12</v>
+        <v>98.2</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>80.51000000000001</v>
+        <v>106.65</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>45.48</v>
+        <v>85.28</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>39.49</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="75">
@@ -6731,43 +6731,43 @@
         <v>2.28</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="O76" s="3" t="n">
-        <v>2.11</v>
+        <v>1.12</v>
       </c>
       <c r="P76" s="3" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>3.88</v>
+        <v>2.32</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>6.95</v>
+        <v>11.62</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>4.14</v>
+        <v>6.79</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>3.21</v>
+        <v>4.77</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>3.26</v>
+        <v>4.65</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.41</v>
+        <v>2.73</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="77">
@@ -6911,10 +6911,10 @@
         <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>0</v>
@@ -6983,43 +6983,43 @@
         <v>101.41</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>103.61</v>
+        <v>106.37</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>129.73</v>
+        <v>123.35</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>97.88</v>
+        <v>105.82</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>101.02</v>
+        <v>108</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>113.82</v>
+        <v>122.57</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>176.07</v>
+        <v>330.31</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>149.18</v>
+        <v>332.52</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>149.47</v>
+        <v>212.08</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>105.34</v>
+        <v>150.34</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>72.72</v>
+        <v>95.06</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>77.61</v>
+        <v>102.6</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>44.07</v>
+        <v>82.55</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>38.23</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="80">
@@ -7331,10 +7331,10 @@
         <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T83" s="3" t="n">
         <v>0</v>
@@ -7403,43 +7403,43 @@
         <v>97.7</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>99.81999999999999</v>
+        <v>102.57</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>122.74</v>
+        <v>117.26</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>94.20999999999999</v>
+        <v>99.92</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>94.5</v>
+        <v>100.66</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>99.03</v>
+        <v>111.41</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>134.53</v>
+        <v>302.21</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>135.99</v>
+        <v>302.84</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>136.13</v>
+        <v>192.8</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>96.47</v>
+        <v>138.05</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>68.73</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>79.03</v>
+        <v>98.27</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>45.57</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>39.94</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="85">
@@ -7499,10 +7499,10 @@
         <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>-5.68</v>
+        <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>-28.19</v>
+        <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
         <v>0</v>
@@ -7571,43 +7571,43 @@
         <v>-3.71</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-3.79</v>
+        <v>-3.8</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-7</v>
+        <v>-6.1</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-3.67</v>
+        <v>-5.9</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-6.52</v>
+        <v>-7.35</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-9.109999999999999</v>
+        <v>-11.17</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-13.34</v>
+        <v>-28.1</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-13.19</v>
+        <v>-29.68</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-13.34</v>
+        <v>-19.28</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-12.29</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.99</v>
+        <v>-6.63</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.42</v>
+        <v>-4.32</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.5</v>
+        <v>2.91</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="87">
@@ -7751,10 +7751,10 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T88" s="3" t="n">
         <v>0</v>
@@ -7823,43 +7823,43 @@
         <v>95.3</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>98.03</v>
+        <v>100.73</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>85.67</v>
+        <v>139.71</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>92.08</v>
+        <v>154.71</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>74.20999999999999</v>
+        <v>187.18</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>102.95</v>
+        <v>229.99</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>144.19</v>
+        <v>313.09</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>142.62</v>
+        <v>317.9</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>142.9</v>
+        <v>201.79</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>99.56999999999999</v>
+        <v>141.69</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>68.86</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>61.2</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>42.05</v>
+        <v>61.39</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>37.22</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="90">
@@ -7910,19 +7910,19 @@
         <v>0</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>-36.49</v>
+        <v>0</v>
       </c>
       <c r="P90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-20.91</v>
+        <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>-4.73</v>
+        <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>-23.5</v>
+        <v>0</v>
       </c>
       <c r="T90" s="3" t="n">
         <v>0</v>
@@ -7937,10 +7937,10 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-12.43</v>
+        <v>-23.34</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>0</v>
+        <v>-17.38</v>
       </c>
       <c r="Z90" s="3" t="n">
         <v>0</v>
@@ -7991,43 +7991,43 @@
         <v>-5.83</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-5.59</v>
+        <v>-5.64</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-7.57</v>
+        <v>-5.76</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.52</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-5.9</v>
+        <v>-5.24</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.14</v>
+        <v>-6.86</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-8.380000000000001</v>
+        <v>-17.21</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-6.56</v>
+        <v>-14.62</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-6.57</v>
+        <v>-10.29</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-5.77</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.86</v>
+        <v>-5.13</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-3.98</v>
+        <v>-5.44</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.02</v>
+        <v>-3.78</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="92">
@@ -8078,16 +8078,16 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>22.12</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>54.41</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>84.41</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>114.28</v>
       </c>
       <c r="S92" s="3" t="n">
         <v>0</v>
@@ -8171,10 +8171,10 @@
         <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>0</v>
+        <v>-11.32</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-14T13:09:26</t>
+          <t>CreatedAt: 2026-10-14T17:09:27</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -695,31 +695,31 @@
         <v>103.25</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>116.81</v>
+        <v>117.02</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>317.61</v>
+        <v>119.88</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>320.66</v>
+        <v>119.84</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>203.93</v>
+        <v>119.16</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>144</v>
+        <v>101.49</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>90.97</v>
+        <v>58.1</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>75.03</v>
+        <v>62.78</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>62</v>
+        <v>49.19</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>47.11</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="5">
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-23.34</v>
+        <v>-11.79</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-17.38</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
@@ -863,28 +863,28 @@
         <v>-4.75</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.77</v>
+        <v>-5.03</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-12.7</v>
+        <v>-4.2</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-11.86</v>
+        <v>-3.48</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-8.16</v>
+        <v>-3.69</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-6.34</v>
+        <v>-3.65</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-4.09</v>
+        <v>-2.56</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-4.23</v>
+        <v>-3.21</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-3.18</v>
+        <v>-1.77</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>-1.27</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>0</v>
@@ -1115,31 +1115,31 @@
         <v>104.96</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>116.56</v>
+        <v>116.57</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>319.14</v>
+        <v>121.05</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>328.58</v>
+        <v>122.83</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>207.92</v>
+        <v>124.82</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>147.53</v>
+        <v>104.41</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>93.84</v>
+        <v>60.06</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>78.04000000000001</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>65.67</v>
+        <v>51.22</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>48.53</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="10">
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-23.34</v>
+        <v>-11.79</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-17.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>0</v>
@@ -1283,31 +1283,31 @@
         <v>-3.04</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-6.01</v>
+        <v>-5.48</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-11.17</v>
+        <v>-3.03</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-3.94</v>
+        <v>-0.49</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-4.16</v>
+        <v>-1.22</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.73</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-1.22</v>
+        <v>-0.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.22</v>
+        <v>-0.92</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.5</v>
+        <v>0.26</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>0</v>
@@ -1451,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>0</v>
@@ -1535,31 +1535,31 @@
         <v>104.96</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>116.56</v>
+        <v>116.57</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>319.14</v>
+        <v>121.05</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>1985.76</v>
+        <v>137.96</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1992.15</v>
+        <v>140.54</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>483.08</v>
+        <v>272.82</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>270.87</v>
+        <v>272.24</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>1997</v>
+        <v>133.48</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>99.64</v>
+        <v>100.85</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>48.53</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="15">
@@ -1625,22 +1625,22 @@
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>1657.18</v>
+        <v>15.01</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>1784.02</v>
+        <v>15.72</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>335.55</v>
+        <v>168.41</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>177.03</v>
+        <v>212.18</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>1895.52</v>
+        <v>56.54</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>16.5</v>
+        <v>49.63</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1703,31 +1703,31 @@
         <v>-3.04</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-6.01</v>
+        <v>-5.48</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-11.17</v>
+        <v>-3.03</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-3.94</v>
+        <v>-0.37</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-3.95</v>
+        <v>-1.22</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.73</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-1.22</v>
+        <v>-0.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.12</v>
+        <v>-0.85</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>0</v>
@@ -1871,10 +1871,10 @@
         <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>0</v>
@@ -1955,31 +1955,31 @@
         <v>187.57</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>230.6</v>
+        <v>230.54</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>315.79</v>
+        <v>750.36</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>319.73</v>
+        <v>750</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>203.14</v>
+        <v>401.22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>143.18</v>
+        <v>188.58</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>90.53</v>
+        <v>57.88</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>50.09</v>
+        <v>50.13</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>43.55</v>
+        <v>48.96</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>47.11</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="20">
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-47.81</v>
+        <v>-24.16</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-35.6</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>0</v>
@@ -2123,31 +2123,31 @@
         <v>-4.85</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-6.25</v>
+        <v>-5.48</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-14.52</v>
+        <v>-4.43</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-12.79</v>
+        <v>-3.82</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-8.94</v>
+        <v>-4.04</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-7.16</v>
+        <v>-3.95</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-4.53</v>
+        <v>-2.78</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-4.7</v>
+        <v>-3.49</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-3.4</v>
+        <v>-2.01</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="22">
@@ -2207,19 +2207,19 @@
         <v>84.41</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>114.28</v>
+        <v>113.97</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0</v>
+        <v>630.71</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0</v>
+        <v>630.51</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0</v>
+        <v>282.41</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>0</v>
+        <v>87.39</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2291,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>0</v>
@@ -2375,31 +2375,31 @@
         <v>103.15</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>116.32</v>
+        <v>116.57</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>315.79</v>
+        <v>119.65</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>319.73</v>
+        <v>119.49</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>203.14</v>
+        <v>118.81</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>143.18</v>
+        <v>101.19</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>90.53</v>
+        <v>57.88</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>74.56</v>
+        <v>62.5</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61.77</v>
+        <v>48.96</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>47.11</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="25">
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-23.34</v>
+        <v>-11.79</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-17.38</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -2543,31 +2543,31 @@
         <v>-4.85</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-6.25</v>
+        <v>-5.48</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-14.52</v>
+        <v>-4.43</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-12.79</v>
+        <v>-3.82</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-8.94</v>
+        <v>-4.04</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-7.16</v>
+        <v>-3.95</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-4.53</v>
+        <v>-2.78</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-4.7</v>
+        <v>-3.49</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-3.4</v>
+        <v>-2.01</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="27">
@@ -2711,10 +2711,10 @@
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>0</v>
@@ -2798,28 +2798,28 @@
         <v>229.99</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>313.09</v>
+        <v>749.6799999999999</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>317.9</v>
+        <v>749.1900000000001</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>201.79</v>
+        <v>400.42</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>141.69</v>
+        <v>188</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>89.93000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>49.34</v>
+        <v>49.57</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>43.17</v>
+        <v>48.59</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>47.02</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="30">
@@ -2897,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-47.81</v>
+        <v>-24.16</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-35.6</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>0</v>
@@ -2963,31 +2963,31 @@
         <v>-5.24</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.86</v>
+        <v>-6.03</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-17.21</v>
+        <v>-5.12</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-14.62</v>
+        <v>-4.63</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-10.29</v>
+        <v>-4.84</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-8.640000000000001</v>
+        <v>-4.53</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-5.13</v>
+        <v>-3.16</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-5.44</v>
+        <v>-4.06</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-3.78</v>
+        <v>-2.38</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="32">
@@ -3047,19 +3047,19 @@
         <v>84.41</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>114.28</v>
+        <v>113.98</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0</v>
+        <v>630.71</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>0</v>
+        <v>630.51</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>0</v>
+        <v>282.41</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>0</v>
+        <v>87.39</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>0</v>
@@ -3215,31 +3215,31 @@
         <v>107.04</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>117.67</v>
+        <v>117.58</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>324.15</v>
+        <v>123.22</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>1993.74</v>
+        <v>140.97</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1996.31</v>
+        <v>139.44</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>488.33</v>
+        <v>276.24</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>274.33</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>2000</v>
+        <v>135.75</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>102.86</v>
+        <v>102.77</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>49.98</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="35">
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>1657.18</v>
+        <v>15.01</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1784.02</v>
+        <v>15.72</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>335.55</v>
+        <v>168.41</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>177.03</v>
+        <v>212.18</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1895.52</v>
+        <v>56.54</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>16.5</v>
+        <v>49.63</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3383,31 +3383,31 @@
         <v>-0.96</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-4.9</v>
+        <v>-4.47</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-6.16</v>
+        <v>-0.86</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>4.04</v>
+        <v>2.65</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.21</v>
+        <v>0.87</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.24</v>
+        <v>1.49</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="37">
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>0</v>
@@ -3635,31 +3635,31 @@
         <v>103.25</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>116.81</v>
+        <v>117.02</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>317.61</v>
+        <v>119.88</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>320.66</v>
+        <v>119.84</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>203.93</v>
+        <v>119.16</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>144</v>
+        <v>101.49</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>90.97</v>
+        <v>58.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>75.03</v>
+        <v>62.78</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>62</v>
+        <v>49.19</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>47.11</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="40">
@@ -3737,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-23.34</v>
+        <v>-11.79</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-17.38</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>0</v>
@@ -3803,28 +3803,28 @@
         <v>-4.75</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.77</v>
+        <v>-5.03</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-12.7</v>
+        <v>-4.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-11.86</v>
+        <v>-3.48</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-8.16</v>
+        <v>-3.69</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-6.34</v>
+        <v>-3.65</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-4.09</v>
+        <v>-2.56</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-4.23</v>
+        <v>-3.21</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-3.18</v>
+        <v>-1.77</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>-1.27</v>
@@ -3971,10 +3971,10 @@
         <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>0</v>
@@ -4055,31 +4055,31 @@
         <v>106.2</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>120.47</v>
+        <v>120.48</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>329.65</v>
+        <v>121.89</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>328.58</v>
+        <v>121.61</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>209.57</v>
+        <v>121.03</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>149.14</v>
+        <v>104.1</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>60.24</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>102.29</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>82.14</v>
+        <v>50.76</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>48.38</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="45">
@@ -4223,28 +4223,28 @@
         <v>-1.81</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-2.11</v>
+        <v>-1.57</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-0.66</v>
+        <v>-2.19</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-3.94</v>
+        <v>-1.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-2.51</v>
+        <v>-1.82</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.19</v>
+        <v>-1.04</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.66</v>
+        <v>-0.42</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.31</v>
+        <v>-0.39</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.41</v>
+        <v>-0.2</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>0</v>
@@ -4475,31 +4475,31 @@
         <v>111.57</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>119.18</v>
+        <v>126.34</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>322.89</v>
+        <v>120.35</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>324.1</v>
+        <v>119.96</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>206.31</v>
+        <v>119.74</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>148.55</v>
+        <v>101.98</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>61.83</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>106.1</v>
+        <v>80.27</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>84.41</v>
+        <v>52.06</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>49.62</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="50">
@@ -4643,28 +4643,28 @@
         <v>3.57</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>-3.39</v>
+        <v>4.3</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-7.42</v>
+        <v>-3.73</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-8.43</v>
+        <v>-3.36</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-5.78</v>
+        <v>-3.11</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-1.78</v>
+        <v>-3.16</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>3.35</v>
+        <v>1.17</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.86</v>
+        <v>1.09</v>
       </c>
       <c r="Z51" s="3" t="n">
         <v>1.24</v>
@@ -4811,10 +4811,10 @@
         <v>0</v>
       </c>
       <c r="R53" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S53" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>0</v>
@@ -4895,31 +4895,31 @@
         <v>106.09</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>116.56</v>
+        <v>116.46</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>310.45</v>
+        <v>116.73</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>310.48</v>
+        <v>115.36</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>197.65</v>
+        <v>115.03</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>140.63</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>90.62</v>
+        <v>58.1</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>100.98</v>
+        <v>78.89</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>85.81</v>
+        <v>52.81</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>50.66</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="55">
@@ -5063,31 +5063,31 @@
         <v>-1.91</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-6.01</v>
+        <v>-5.59</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-19.86</v>
+        <v>-7.35</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-22.04</v>
+        <v>-7.96</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-14.43</v>
+        <v>-7.82</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-9.699999999999999</v>
+        <v>-6.79</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-4.44</v>
+        <v>-2.56</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-1.62</v>
+        <v>1.1</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.26</v>
+        <v>1.85</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="57">
@@ -5231,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>0</v>
@@ -5315,31 +5315,31 @@
         <v>110.09</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>124.61</v>
+        <v>124.54</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>341.23</v>
+        <v>125.21</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>338.96</v>
+        <v>125.07</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>216.19</v>
+        <v>124.22</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>154.35</v>
+        <v>107.51</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>97.7</v>
+        <v>62.28</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>106.1</v>
+        <v>80.11</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>84.93000000000001</v>
+        <v>52.38</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>49.93</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="60">
@@ -5483,31 +5483,31 @@
         <v>2.09</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2.04</v>
+        <v>2.49</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>10.92</v>
+        <v>1.13</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>6.44</v>
+        <v>1.75</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>4.11</v>
+        <v>1.37</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>4.01</v>
+        <v>2.37</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>2.64</v>
+        <v>1.62</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="62">
@@ -5651,10 +5651,10 @@
         <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S63" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T63" s="3" t="n">
         <v>0</v>
@@ -5735,31 +5735,31 @@
         <v>111.8</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>126.86</v>
+        <v>126.34</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>346.96</v>
+        <v>127.13</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>344.23</v>
+        <v>125.71</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>219.55</v>
+        <v>126.13</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>156.93</v>
+        <v>109.18</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>99.23</v>
+        <v>63.25</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>107.66</v>
+        <v>81.28</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>86.08</v>
+        <v>53.03</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>50.56</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="65">
@@ -5903,31 +5903,31 @@
         <v>3.8</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>16.65</v>
+        <v>3.05</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>11.7</v>
+        <v>2.39</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>7.46</v>
+        <v>3.28</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>6.59</v>
+        <v>4.04</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>4.17</v>
+        <v>2.59</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>5.06</v>
+        <v>3.49</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>3.53</v>
+        <v>2.07</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="67">
@@ -6071,10 +6071,10 @@
         <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T68" s="3" t="n">
         <v>0</v>
@@ -6158,28 +6158,28 @@
         <v>127</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>350.64</v>
+        <v>127</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>345.66</v>
+        <v>127</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>220.46</v>
+        <v>126</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>157.91</v>
+        <v>109.86</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>99.95999999999999</v>
+        <v>63.79</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>108.91</v>
+        <v>82.31</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>86.98999999999999</v>
+        <v>53.65</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>51.25</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="70">
@@ -6323,31 +6323,31 @@
         <v>4.5</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>4.43</v>
+        <v>4.95</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>20.33</v>
+        <v>2.92</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>13.14</v>
+        <v>3.68</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>8.380000000000001</v>
+        <v>3.15</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>7.58</v>
+        <v>4.72</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>4.9</v>
+        <v>3.13</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>6.32</v>
+        <v>4.53</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>4.44</v>
+        <v>2.68</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="72">
@@ -6491,10 +6491,10 @@
         <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S73" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T73" s="3" t="n">
         <v>0</v>
@@ -6575,31 +6575,31 @@
         <v>110.55</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>124.89</v>
+        <v>124.92</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>341.93</v>
+        <v>125.46</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>339.31</v>
+        <v>125.07</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>216.85</v>
+        <v>124.34</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>154.98</v>
+        <v>107.62</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>98.2</v>
+        <v>62.47</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>106.65</v>
+        <v>80.52</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>85.28</v>
+        <v>52.54</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>50.03</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="75">
@@ -6743,31 +6743,31 @@
         <v>2.54</v>
       </c>
       <c r="R76" s="3" t="n">
-        <v>2.32</v>
+        <v>2.87</v>
       </c>
       <c r="S76" s="3" t="n">
-        <v>11.62</v>
+        <v>1.38</v>
       </c>
       <c r="T76" s="3" t="n">
-        <v>6.79</v>
+        <v>1.75</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>4.77</v>
+        <v>1.49</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>4.65</v>
+        <v>2.48</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>3.14</v>
+        <v>1.81</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>4.05</v>
+        <v>2.74</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.73</v>
+        <v>1.58</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="77">
@@ -6911,10 +6911,10 @@
         <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>0</v>
@@ -6995,31 +6995,31 @@
         <v>108</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>122.57</v>
+        <v>122.05</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>330.31</v>
+        <v>124.08</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>332.52</v>
+        <v>123.32</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>212.08</v>
+        <v>122.85</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>150.34</v>
+        <v>105.14</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>95.06</v>
+        <v>60.66</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>102.6</v>
+        <v>77.78</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>82.55</v>
+        <v>50.97</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>48.38</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="80">
@@ -7331,10 +7331,10 @@
         <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="n">
         <v>0</v>
@@ -7415,31 +7415,31 @@
         <v>100.66</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>111.41</v>
+        <v>111.76</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>302.21</v>
+        <v>112.9</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>302.84</v>
+        <v>111.8</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>192.8</v>
+        <v>112.6</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>138.05</v>
+        <v>96.28</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>88.43000000000001</v>
+        <v>57.44</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>98.27</v>
+        <v>79.37</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>85.45999999999999</v>
+        <v>52.54</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>50.66</v>
+        <v>52.34</v>
       </c>
     </row>
     <row r="85">
@@ -7583,31 +7583,31 @@
         <v>-7.35</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-11.17</v>
+        <v>-10.28</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-28.1</v>
+        <v>-11.18</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-29.68</v>
+        <v>-11.52</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-19.28</v>
+        <v>-10.25</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-12.29</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-6.63</v>
+        <v>-3.22</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-4.32</v>
+        <v>1.59</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.91</v>
+        <v>1.58</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="87">
@@ -7751,10 +7751,10 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T88" s="3" t="n">
         <v>0</v>
@@ -7838,28 +7838,28 @@
         <v>229.99</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>313.09</v>
+        <v>749.6799999999999</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>317.9</v>
+        <v>749.1900000000001</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>201.79</v>
+        <v>400.42</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>141.69</v>
+        <v>188</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>89.93000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>73.81999999999999</v>
+        <v>61.94</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>61.39</v>
+        <v>48.59</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>47.02</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="90">
@@ -7937,10 +7937,10 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-23.34</v>
+        <v>-11.79</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-17.38</v>
+        <v>0</v>
       </c>
       <c r="Z90" s="3" t="n">
         <v>0</v>
@@ -8003,31 +8003,31 @@
         <v>-5.24</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.86</v>
+        <v>-6.03</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-17.21</v>
+        <v>-5.12</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-14.62</v>
+        <v>-4.63</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-10.29</v>
+        <v>-4.84</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-8.640000000000001</v>
+        <v>-4.53</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-5.13</v>
+        <v>-3.16</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-5.44</v>
+        <v>-4.06</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-3.78</v>
+        <v>-2.38</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="92">
@@ -8087,19 +8087,19 @@
         <v>84.41</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>114.28</v>
+        <v>113.98</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>630.71</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>630.51</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>0</v>
+        <v>282.41</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>0</v>
+        <v>87.39</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>
@@ -8171,10 +8171,10 @@
         <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>-11.32</v>
+        <v>0</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T93" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-14T17:09:27</t>
+          <t>CreatedAt: 2026-10-14T19:09:45</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -707,19 +707,19 @@
         <v>119.16</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>101.49</v>
+        <v>117.96</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>58.1</v>
+        <v>99.34</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>62.78</v>
+        <v>80.55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>49.19</v>
+        <v>62</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>48.98</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="5">
@@ -797,10 +797,10 @@
         <v>0</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-11.79</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-11.41</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>0</v>
@@ -875,19 +875,19 @@
         <v>-3.69</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.01</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.56</v>
+        <v>-4.17</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.62</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.77</v>
+        <v>-2.94</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="7">
@@ -1127,19 +1127,19 @@
         <v>124.82</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>104.41</v>
+        <v>121.97</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>60.06</v>
+        <v>102.69</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>65.06999999999999</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>51.22</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>50.15</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="10">
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>-11.79</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>0</v>
+        <v>-11.41</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>0</v>
@@ -1295,19 +1295,19 @@
         <v>-1.22</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.82</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.92</v>
+        <v>-1.33</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="12">
@@ -1547,19 +1547,19 @@
         <v>140.54</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>272.82</v>
+        <v>212.23</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>272.24</v>
+        <v>133.38</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>133.48</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>100.85</v>
+        <v>1996.98</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>50.15</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="15">
@@ -1631,16 +1631,16 @@
         <v>15.72</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>168.41</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>212.18</v>
+        <v>30.69</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>56.54</v>
+        <v>12.61</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>49.63</v>
+        <v>1920.55</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1715,19 +1715,19 @@
         <v>-1.22</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-0.73</v>
+        <v>0</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.6</v>
+        <v>-0.82</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.85</v>
+        <v>-1.24</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="17">
@@ -1967,19 +1967,19 @@
         <v>401.22</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>188.58</v>
+        <v>188.57</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>57.88</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>50.13</v>
+        <v>80.09</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>48.96</v>
+        <v>49.75</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>48.93</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="20">
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>-24.16</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>0</v>
+        <v>-23.38</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>0</v>
@@ -2135,19 +2135,19 @@
         <v>-4.04</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.95</v>
+        <v>-4.24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.78</v>
+        <v>-4.55</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-3.49</v>
+        <v>-4.08</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-2.01</v>
+        <v>-3.22</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="22">
@@ -2219,7 +2219,7 @@
         <v>282.41</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>87.39</v>
+        <v>70.83</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2387,19 +2387,19 @@
         <v>118.81</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>101.19</v>
+        <v>117.73</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>57.88</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>62.5</v>
+        <v>80.09</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>48.96</v>
+        <v>61.72</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>48.93</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="25">
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>-11.79</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0</v>
+        <v>-11.41</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>0</v>
@@ -2555,19 +2555,19 @@
         <v>-4.04</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.95</v>
+        <v>-4.24</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.78</v>
+        <v>-4.55</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-3.49</v>
+        <v>-4.08</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-2.01</v>
+        <v>-3.22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.32</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="27">
@@ -2810,16 +2810,16 @@
         <v>188</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>57.5</v>
+        <v>98.39</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>49.57</v>
+        <v>79.41</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>48.59</v>
+        <v>49.06</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>48.79</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="30">
@@ -2897,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>-24.16</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>-23.38</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>0</v>
@@ -2975,19 +2975,19 @@
         <v>-4.84</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4.53</v>
+        <v>-4.8</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-3.16</v>
+        <v>-5.12</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-4.06</v>
+        <v>-4.76</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-2.38</v>
+        <v>-3.91</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.46</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="32">
@@ -3059,7 +3059,7 @@
         <v>282.41</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>87.39</v>
+        <v>70.83</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
@@ -3227,19 +3227,19 @@
         <v>139.44</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>276.24</v>
+        <v>312.46</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>274.33</v>
+        <v>191.09</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>135.75</v>
+        <v>97.98</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>102.77</v>
+        <v>2000</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>51.54</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="35">
@@ -3311,16 +3311,16 @@
         <v>15.72</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>168.41</v>
+        <v>90.26000000000001</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>212.18</v>
+        <v>30.69</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>56.54</v>
+        <v>12.61</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>49.63</v>
+        <v>1920.55</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3395,19 +3395,19 @@
         <v>0.87</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>2.7</v>
+        <v>3.77</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>1.49</v>
+        <v>2.76</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="37">
@@ -3479,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>0</v>
+        <v>96.45</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>0</v>
+        <v>54.13</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>0</v>
@@ -3647,19 +3647,19 @@
         <v>119.16</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>101.49</v>
+        <v>117.96</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>58.1</v>
+        <v>99.34</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>62.78</v>
+        <v>80.55</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>49.19</v>
+        <v>62</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>48.98</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="40">
@@ -3737,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>-11.79</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0</v>
+        <v>-11.41</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>0</v>
@@ -3815,19 +3815,19 @@
         <v>-3.69</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.01</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.56</v>
+        <v>-4.17</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.62</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.77</v>
+        <v>-2.94</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.27</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="42">
@@ -4067,19 +4067,19 @@
         <v>121.03</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>104.1</v>
+        <v>120.4</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>60.24</v>
+        <v>103.41</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>83.67</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>50.76</v>
+        <v>75.89</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>50.25</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="45">
@@ -4235,16 +4235,16 @@
         <v>-1.82</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.04</v>
+        <v>-1.57</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.42</v>
+        <v>-0.1</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.39</v>
+        <v>-0.5</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.2</v>
+        <v>-0.46</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>0</v>
@@ -4487,19 +4487,19 @@
         <v>119.74</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>101.98</v>
+        <v>118.88</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>61.83</v>
+        <v>106.38</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>80.27</v>
+        <v>86.87</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>52.06</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>51.49</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="50">
@@ -4655,19 +4655,19 @@
         <v>-3.11</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.16</v>
+        <v>-3.09</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.17</v>
+        <v>2.87</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="52">
@@ -4907,19 +4907,19 @@
         <v>115.03</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>98.34999999999999</v>
+        <v>114.2</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>58.1</v>
+        <v>98.58</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>78.89</v>
+        <v>85.02</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>52.81</v>
+        <v>79.2</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>52.45</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="55">
@@ -5075,19 +5075,19 @@
         <v>-7.82</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-6.79</v>
+        <v>-7.77</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-2.56</v>
+        <v>-4.93</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="57">
@@ -5327,19 +5327,19 @@
         <v>124.22</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>107.51</v>
+        <v>123.83</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>62.28</v>
+        <v>107.04</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>80.11</v>
+        <v>86.69</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>52.38</v>
+        <v>78.39</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>51.75</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="60">
@@ -5495,19 +5495,19 @@
         <v>1.37</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2.37</v>
+        <v>1.86</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.62</v>
+        <v>3.53</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="62">
@@ -5747,19 +5747,19 @@
         <v>126.13</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>109.18</v>
+        <v>125.74</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>63.25</v>
+        <v>108.61</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>81.28</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>53.03</v>
+        <v>79.45</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>52.4</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="65">
@@ -5915,19 +5915,19 @@
         <v>3.28</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>4.04</v>
+        <v>3.77</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>2.59</v>
+        <v>5.1</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>3.49</v>
+        <v>3.78</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="67">
@@ -6167,19 +6167,19 @@
         <v>126</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>109.86</v>
+        <v>126</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>63.79</v>
+        <v>110</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>82.31</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>53.65</v>
+        <v>80.37</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>53.17</v>
+        <v>54.68</v>
       </c>
     </row>
     <row r="70">
@@ -6335,19 +6335,19 @@
         <v>3.15</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>4.72</v>
+        <v>4.03</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>3.13</v>
+        <v>6.49</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>4.53</v>
+        <v>4.99</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>2.68</v>
+        <v>4.02</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="72">
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="Y72" s="3" t="n">
         <v>0</v>
@@ -6587,19 +6587,19 @@
         <v>124.34</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>107.62</v>
+        <v>124.08</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>62.47</v>
+        <v>107.37</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>80.52</v>
+        <v>87.14</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>52.54</v>
+        <v>78.63</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>51.86</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="75">
@@ -6755,19 +6755,19 @@
         <v>1.49</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>1.81</v>
+        <v>3.87</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="77">
@@ -7007,19 +7007,19 @@
         <v>122.85</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>105.14</v>
+        <v>121.97</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>60.66</v>
+        <v>103.51</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>77.78</v>
+        <v>84.17</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>50.97</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>50.25</v>
+        <v>51.67</v>
       </c>
     </row>
     <row r="80">
@@ -7427,19 +7427,19 @@
         <v>112.6</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>96.28</v>
+        <v>111.29</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>57.44</v>
+        <v>95.84</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>79.37</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>52.54</v>
+        <v>78.87</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>52.34</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="85">
@@ -7595,19 +7595,19 @@
         <v>-10.25</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-8.859999999999999</v>
+        <v>-10.68</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-3.22</v>
+        <v>-7.67</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>1.59</v>
+        <v>0.34</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>1.58</v>
+        <v>2.52</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="87">
@@ -7850,16 +7850,16 @@
         <v>188</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>57.5</v>
+        <v>98.3</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>61.94</v>
+        <v>79.41</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>48.59</v>
+        <v>61.02</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>48.79</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="90">
@@ -7937,10 +7937,10 @@
         <v>0</v>
       </c>
       <c r="X90" s="3" t="n">
-        <v>-11.79</v>
+        <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>0</v>
+        <v>-11.41</v>
       </c>
       <c r="Z90" s="3" t="n">
         <v>0</v>
@@ -8015,19 +8015,19 @@
         <v>-4.84</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4.53</v>
+        <v>-4.8</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-3.16</v>
+        <v>-5.21</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-4.06</v>
+        <v>-4.76</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-2.38</v>
+        <v>-3.91</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.46</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="92">
@@ -8099,7 +8099,7 @@
         <v>282.41</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>87.39</v>
+        <v>70.83</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-14T19:09:45</t>
+          <t>CreatedAt: 2026-10-14T23:18:30</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -650,76 +650,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>44.62</v>
+        <v>59.35</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>43.6</v>
+        <v>66.42</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>41.33</v>
+        <v>66.94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>45.1</v>
+        <v>66.47</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>77.77</v>
+        <v>122.47</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>115.9</v>
+        <v>126.86</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>126.1</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>96.41</v>
+        <v>122.26</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>80.83</v>
+        <v>107.75</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>86.51000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>95.75</v>
+        <v>81.06</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>100.82</v>
+        <v>79.34</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>117.26</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>100.59</v>
+        <v>80.91</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>103.25</v>
+        <v>82.22</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>117.02</v>
+        <v>101.96</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>119.88</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>119.84</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>119.16</v>
+        <v>57.06</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>117.96</v>
+        <v>54.01</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>99.34</v>
+        <v>38.36</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>80.55</v>
+        <v>35.16</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>62</v>
+        <v>54.82</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>50.31</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="5">
@@ -761,22 +761,22 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-29.84</v>
+        <v>-20.48</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-0.28</v>
+        <v>-24.79</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-30.24</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0</v>
+        <v>-27.41</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>-31.54</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>-10.02</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
@@ -800,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-11.41</v>
+        <v>-21.95</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-30.56</v>
       </c>
     </row>
     <row r="6">
@@ -818,76 +818,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-1.07</v>
+        <v>-2.02</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-1.13</v>
+        <v>-2.19</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.81</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.86</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-2.72</v>
+        <v>-3.31</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-4.06</v>
+        <v>-5.07</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-3</v>
+        <v>-5.3</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-4.24</v>
+        <v>-5.38</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-4.04</v>
+        <v>-5.17</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-6.75</v>
+        <v>-4.71</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-5.38</v>
+        <v>-5.72</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.59</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-6.1</v>
+        <v>-4.75</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-5.23</v>
+        <v>-5.74</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-4.75</v>
+        <v>-6.37</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.03</v>
+        <v>-5.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-4.2</v>
+        <v>-3.81</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.48</v>
+        <v>-3.21</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.69</v>
+        <v>-2.94</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-4.01</v>
+        <v>-2.82</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-4.17</v>
+        <v>-1.53</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-3.62</v>
+        <v>-1.3</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.92</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-1.36</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="7">
@@ -1070,76 +1070,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>44.66</v>
+        <v>59.41</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>43.94</v>
+        <v>67.8</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>41.57</v>
+        <v>68.2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>44.8</v>
+        <v>67.66</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>77.47</v>
+        <v>122.71</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>115.34</v>
+        <v>127.23</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>95.3</v>
+        <v>129.71</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>98.2</v>
+        <v>125.88</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>282.11</v>
+        <v>110.49</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>87.84999999999999</v>
+        <v>73.06</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>155.66</v>
+        <v>83.42</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>103.65</v>
+        <v>81.25</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>119.88</v>
+        <v>95.33</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>101.55</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>104.96</v>
+        <v>85.77</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>116.57</v>
+        <v>104.04</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>121.05</v>
+        <v>89.62</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>122.83</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>124.82</v>
+        <v>58.05</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>121.97</v>
+        <v>55.2</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>102.69</v>
+        <v>39.46</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>82.84999999999999</v>
+        <v>36.07</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>65.01000000000001</v>
+        <v>58.06</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>51.36</v>
+        <v>59.95</v>
       </c>
     </row>
     <row r="10">
@@ -1181,22 +1181,22 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-29.84</v>
+        <v>-20.48</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-0.28</v>
+        <v>-24.79</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>-30.24</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>-27.41</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>-31.54</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>0</v>
+        <v>-10.02</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-11.41</v>
+        <v>-21.95</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>0</v>
+        <v>-30.56</v>
       </c>
     </row>
     <row r="11">
@@ -1238,76 +1238,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.96</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.55</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.52</v>
+        <v>-0.68</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-3.02</v>
+        <v>-3.07</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-4.61</v>
+        <v>-4.71</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.69</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-2.45</v>
+        <v>-1.76</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.87</v>
+        <v>-2.43</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-5.41</v>
+        <v>-1.78</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-3.33</v>
+        <v>-3.35</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-3.1</v>
+        <v>-3.68</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-3.48</v>
+        <v>-2.57</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-4.27</v>
+        <v>-2.89</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-3.04</v>
+        <v>-2.82</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-5.48</v>
+        <v>-3.12</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-3.03</v>
+        <v>-2.69</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-0.49</v>
+        <v>-2.54</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.95</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.43</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-1.33</v>
+        <v>-0.4</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-0.31</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="12">
@@ -1346,16 +1346,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>200.11</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>57.86</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>0</v>
@@ -1490,76 +1490,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>44.66</v>
+        <v>54.28</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>43.94</v>
+        <v>67.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>41.57</v>
+        <v>68.27</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>44.8</v>
+        <v>67.73</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>77.47</v>
+        <v>122.71</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>88.79000000000001</v>
+        <v>127.23</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>95.39</v>
+        <v>129.84</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>98.2</v>
+        <v>125.88</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>282.11</v>
+        <v>110.49</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>117.8</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>155.94</v>
+        <v>108.21</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>103.75</v>
+        <v>111.49</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>119.88</v>
+        <v>95.33</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>101.55</v>
+        <v>111.17</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>104.96</v>
+        <v>117.31</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>116.57</v>
+        <v>104.04</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>121.05</v>
+        <v>89.62</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>137.96</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>140.54</v>
+        <v>56.69</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>212.23</v>
+        <v>53.26</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>133.38</v>
+        <v>39.46</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>95.54000000000001</v>
+        <v>36.07</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1996.98</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>51.36</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>-5.12</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-26.54</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0</v>
@@ -1625,22 +1625,22 @@
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>15.72</v>
+        <v>-8.15</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>90.26000000000001</v>
+        <v>-12.03</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>30.69</v>
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>12.61</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>1920.55</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1658,76 +1658,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.03</v>
+        <v>-1.96</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-0.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.48</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.52</v>
+        <v>-0.61</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-3.02</v>
+        <v>-3.07</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.61</v>
+        <v>-4.71</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.43</v>
+        <v>-1.56</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-2.45</v>
+        <v>-1.76</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.87</v>
+        <v>-2.43</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-5.3</v>
+        <v>-1.78</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.33</v>
+        <v>-3.35</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-3</v>
+        <v>-3.68</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-3.48</v>
+        <v>-2.57</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-4.27</v>
+        <v>-2.89</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-3.04</v>
+        <v>-2.82</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-5.48</v>
+        <v>-3.12</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-3.03</v>
+        <v>-2.69</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-0.37</v>
+        <v>-2.54</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.95</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>0</v>
+        <v>-1.57</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.43</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-1.24</v>
+        <v>-0.4</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-0.31</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="17">
@@ -1766,16 +1766,16 @@
         <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>200.11</v>
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>57.86</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>0</v>
@@ -1910,76 +1910,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>44.53</v>
+        <v>59.01</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>43.47</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>41.17</v>
+        <v>66.75</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>44.93</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>77.55</v>
+        <v>121.88</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>115.67</v>
+        <v>126.5</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>126.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>96.22</v>
+        <v>121.91</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>80.44</v>
+        <v>107.34</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>54.67</v>
+        <v>48.57</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>95.27</v>
+        <v>54.77</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>100.82</v>
+        <v>47.42</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>139.6</v>
+        <v>92.88</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>154.9</v>
+        <v>51.65</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>187.57</v>
+        <v>48.72</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>230.54</v>
+        <v>101.38</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>750.36</v>
+        <v>88</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>750</v>
+        <v>75.89</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>401.22</v>
+        <v>49.51</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>188.57</v>
+        <v>43.07</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>98.95999999999999</v>
+        <v>38.25</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>80.09</v>
+        <v>35.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>49.75</v>
+        <v>31.65</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>50.26</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="20">
@@ -2021,22 +2021,22 @@
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-61.14</v>
+        <v>-41.95</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-0.58</v>
+        <v>-50.78</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0</v>
+        <v>-61.96</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0</v>
+        <v>-56.16</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0</v>
+        <v>-64.61</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0</v>
+        <v>-13.91</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>0</v>
+        <v>-20.53</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
@@ -2060,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-23.38</v>
+        <v>-44.97</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>0</v>
+        <v>-62.61</v>
       </c>
     </row>
     <row r="21">
@@ -2078,76 +2078,76 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>-1.16</v>
+        <v>-2.36</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-1.26</v>
+        <v>-2.32</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-1.36</v>
+        <v>-2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-1.39</v>
+        <v>-1.99</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-2.95</v>
+        <v>-3.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-4.28</v>
+        <v>-5.44</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-3</v>
+        <v>-5.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-4.43</v>
+        <v>-5.73</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-4.42</v>
+        <v>-5.58</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-7.3</v>
+        <v>-4.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-5.56</v>
+        <v>-6.02</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-5.87</v>
+        <v>-5.02</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-5.33</v>
+        <v>-6.25</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-4.85</v>
+        <v>-6.8</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-5.48</v>
+        <v>-5.78</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-4.43</v>
+        <v>-4.31</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-3.82</v>
+        <v>-3.72</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-4.04</v>
+        <v>-3.36</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-4.24</v>
+        <v>-3.24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-4.55</v>
+        <v>-1.64</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-4.08</v>
+        <v>-1.37</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3.07</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-1.41</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="22">
@@ -2198,28 +2198,28 @@
         <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>22.12</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>54.41</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>84.41</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>113.97</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>630.71</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>630.51</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>282.41</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>70.83</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2330,76 +2330,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>44.53</v>
+        <v>59.01</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>43.47</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>41.17</v>
+        <v>66.75</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>44.93</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>77.55</v>
+        <v>121.88</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>115.67</v>
+        <v>126.5</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>126.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>96.22</v>
+        <v>121.91</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>80.44</v>
+        <v>107.34</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>85.95999999999999</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>95.56999999999999</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>100.82</v>
+        <v>79.13</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>117.48</v>
+        <v>92.88</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>100.49</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>103.15</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>116.57</v>
+        <v>101.38</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>119.65</v>
+        <v>88</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>119.49</v>
+        <v>75.89</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>118.81</v>
+        <v>56.63</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>117.73</v>
+        <v>53.59</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>98.95999999999999</v>
+        <v>38.25</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>80.09</v>
+        <v>35.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>61.72</v>
+        <v>54.67</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>50.26</v>
+        <v>58.56</v>
       </c>
     </row>
     <row r="25">
@@ -2441,22 +2441,22 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-29.84</v>
+        <v>-20.48</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-0.28</v>
+        <v>-24.79</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0</v>
+        <v>-30.24</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
+        <v>-27.41</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0</v>
+        <v>-31.54</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>-10.02</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
@@ -2480,10 +2480,10 @@
         <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-11.41</v>
+        <v>-21.95</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>0</v>
+        <v>-30.56</v>
       </c>
     </row>
     <row r="26">
@@ -2498,76 +2498,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-1.16</v>
+        <v>-2.36</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-1.26</v>
+        <v>-2.32</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-1.36</v>
+        <v>-2</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-1.39</v>
+        <v>-1.99</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-2.95</v>
+        <v>-3.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-4.28</v>
+        <v>-5.44</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-3</v>
+        <v>-5.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-4.43</v>
+        <v>-5.73</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-4.42</v>
+        <v>-5.58</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-7.3</v>
+        <v>-4.8</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-5.56</v>
+        <v>-6.02</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-5.87</v>
+        <v>-5.02</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-5.33</v>
+        <v>-6.25</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-4.85</v>
+        <v>-6.8</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-5.48</v>
+        <v>-5.78</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-4.43</v>
+        <v>-4.31</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-3.82</v>
+        <v>-3.72</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-4.04</v>
+        <v>-3.36</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-4.24</v>
+        <v>-3.24</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-4.55</v>
+        <v>-1.64</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-4.08</v>
+        <v>-1.37</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3.07</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-1.41</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="27">
@@ -2750,76 +2750,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>44.4</v>
+        <v>58.5</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>43.34</v>
+        <v>65.97</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>40.97</v>
+        <v>66.42</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>44.75</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>77.31999999999999</v>
+        <v>121.18</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>115.45</v>
+        <v>126.02</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>125.86</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>95.95</v>
+        <v>121.45</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>106.73</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>54.02</v>
+        <v>48.31</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>95</v>
+        <v>54.37</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>100.73</v>
+        <v>47</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>139.71</v>
+        <v>92.36</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>154.71</v>
+        <v>50.84</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>187.18</v>
+        <v>47.98</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>229.99</v>
+        <v>100.53</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>749.6799999999999</v>
+        <v>87.25</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>749.1900000000001</v>
+        <v>75.25</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>400.42</v>
+        <v>48.86</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>188</v>
+        <v>42.53</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>98.39</v>
+        <v>38.03</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>79.41</v>
+        <v>34.99</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>49.06</v>
+        <v>31.29</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>50.07</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -2861,22 +2861,22 @@
         <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-61.14</v>
+        <v>-41.95</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-0.58</v>
+        <v>-50.78</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0</v>
+        <v>-61.96</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>-56.16</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0</v>
+        <v>-64.61</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>0</v>
+        <v>-13.91</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>0</v>
+        <v>-20.53</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
@@ -2900,10 +2900,10 @@
         <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-23.38</v>
+        <v>-44.97</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0</v>
+        <v>-62.61</v>
       </c>
     </row>
     <row r="31">
@@ -2918,76 +2918,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-1.29</v>
+        <v>-2.87</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-1.39</v>
+        <v>-2.64</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-1.56</v>
+        <v>-2.32</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-1.57</v>
+        <v>-2.37</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-3.17</v>
+        <v>-4.6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-4.5</v>
+        <v>-5.92</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-3</v>
+        <v>-5.54</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-4.7</v>
+        <v>-6.19</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-4.88</v>
+        <v>-6.19</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-7.95</v>
+        <v>-5.05</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-5.83</v>
+        <v>-6.41</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-5.64</v>
+        <v>-6.21</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-5.76</v>
+        <v>-5.54</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-5.52</v>
+        <v>-7.06</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-5.24</v>
+        <v>-7.54</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.03</v>
+        <v>-6.63</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-5.12</v>
+        <v>-5.06</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-4.63</v>
+        <v>-4.36</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.84</v>
+        <v>-4.02</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-4.8</v>
+        <v>-3.78</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-5.12</v>
+        <v>-1.86</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-4.76</v>
+        <v>-1.47</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-3.91</v>
+        <v>-3.43</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-1.6</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="32">
@@ -3038,28 +3038,28 @@
         <v>0</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>22.12</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>54.41</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>84.41</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>113.98</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>630.71</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>630.51</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>282.41</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>70.83</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
@@ -3170,76 +3170,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>45.23</v>
+        <v>56.15</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>44.73</v>
+        <v>69.87</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>42.31</v>
+        <v>70.08</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>45.23</v>
+        <v>69.52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>78.3</v>
+        <v>125.53</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>92.91</v>
+        <v>130.5</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>96.53</v>
+        <v>133.27</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>100.25</v>
+        <v>129.45</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>103.08</v>
+        <v>113.26</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>119.52</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>105.78</v>
+        <v>110.68</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>105.57</v>
+        <v>113.58</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>121.53</v>
+        <v>97.61</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>103.44</v>
+        <v>114.29</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>107.04</v>
+        <v>120.97</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>117.58</v>
+        <v>106.63</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>123.22</v>
+        <v>91.31</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>140.97</v>
+        <v>78.59</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>139.44</v>
+        <v>58.37</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>312.46</v>
+        <v>54.96</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>191.09</v>
+        <v>40.26</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>97.98</v>
+        <v>36.87</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>2000</v>
+        <v>82.67</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>52.73</v>
+        <v>92.68000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0</v>
+        <v>-4.61</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-23.89</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0</v>
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>15.01</v>
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>15.72</v>
+        <v>-8.15</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>90.26000000000001</v>
+        <v>-12.03</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>30.69</v>
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>12.61</v>
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1920.55</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3338,76 +3338,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-0.45</v>
+        <v>-0.61</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.21</v>
+        <v>1.33</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-1.09</v>
+        <v>1.18</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-2.19</v>
+        <v>-0.25</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-3.15</v>
+        <v>-1.44</v>
       </c>
       <c r="I36" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="O36" s="3" t="n">
         <v>-0.29</v>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>-3.59</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>-1.82</v>
-      </c>
       <c r="P36" s="3" t="n">
-        <v>-2.38</v>
+        <v>0.23</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>-0.96</v>
+        <v>0.85</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-4.47</v>
+        <v>-0.53</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>2.65</v>
+        <v>-1.02</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.87</v>
+        <v>-0.27</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>3.77</v>
+        <v>0.13</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>2.76</v>
+        <v>0.36</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.2</v>
+        <v>0.41</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.05</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="37">
@@ -3446,16 +3446,16 @@
         <v>0</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>19.63</v>
+        <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>5.87</v>
+        <v>0</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>0</v>
@@ -3479,10 +3479,10 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>96.45</v>
+        <v>0</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>54.13</v>
+        <v>0</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>0</v>
@@ -3590,76 +3590,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>44.62</v>
+        <v>59.35</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>43.6</v>
+        <v>66.42</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>41.33</v>
+        <v>66.94</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>45.1</v>
+        <v>66.47</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>77.77</v>
+        <v>122.47</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>115.9</v>
+        <v>126.86</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>126.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>96.41</v>
+        <v>122.26</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>80.83</v>
+        <v>107.75</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>86.51000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>95.75</v>
+        <v>81.06</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>100.82</v>
+        <v>79.34</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>117.26</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>100.59</v>
+        <v>80.91</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>103.25</v>
+        <v>82.22</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>117.02</v>
+        <v>101.96</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>119.88</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>119.84</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>119.16</v>
+        <v>57.06</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>117.96</v>
+        <v>54.01</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>99.34</v>
+        <v>38.36</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>80.55</v>
+        <v>35.16</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>62</v>
+        <v>54.82</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>50.31</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="40">
@@ -3701,22 +3701,22 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-29.84</v>
+        <v>-20.48</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-0.28</v>
+        <v>-24.79</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>-30.24</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>-27.41</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>-31.54</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>0</v>
+        <v>-10.02</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
@@ -3740,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-11.41</v>
+        <v>-21.95</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>0</v>
+        <v>-30.56</v>
       </c>
     </row>
     <row r="41">
@@ -3758,76 +3758,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-1.07</v>
+        <v>-2.02</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-1.13</v>
+        <v>-2.19</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-1.2</v>
+        <v>-1.81</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-1.22</v>
+        <v>-1.86</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-2.72</v>
+        <v>-3.31</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-4.06</v>
+        <v>-5.07</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-3</v>
+        <v>-5.3</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-4.24</v>
+        <v>-5.38</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-4.04</v>
+        <v>-5.17</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-6.75</v>
+        <v>-4.71</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-5.38</v>
+        <v>-5.72</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-5.55</v>
+        <v>-5.59</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-6.1</v>
+        <v>-4.75</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-5.23</v>
+        <v>-5.74</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-4.75</v>
+        <v>-6.37</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.03</v>
+        <v>-5.2</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-4.2</v>
+        <v>-3.81</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.48</v>
+        <v>-3.21</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.69</v>
+        <v>-2.94</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-4.01</v>
+        <v>-2.82</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-4.17</v>
+        <v>-1.53</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-3.62</v>
+        <v>-1.3</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.94</v>
+        <v>-2.92</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-1.36</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="42">
@@ -4010,76 +4010,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>45.82</v>
+        <v>61.24</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>44.82</v>
+        <v>68.47</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>42.61</v>
+        <v>68.41</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>46.46</v>
+        <v>68.06</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>80.48999999999999</v>
+        <v>126.03</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>119.71</v>
+        <v>131.54</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>96.73</v>
+        <v>130.36</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>100.15</v>
+        <v>126.63</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>84.36</v>
+        <v>112.02</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>120.22</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>99.42</v>
+        <v>109.06</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>103.88</v>
+        <v>113.14</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>119.53</v>
+        <v>96.36</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>103.54</v>
+        <v>112.49</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>106.2</v>
+        <v>117.77</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>120.48</v>
+        <v>105.89</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>121.89</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>121.61</v>
+        <v>79.14</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>121.03</v>
+        <v>66.19</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>120.4</v>
+        <v>66.52</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>103.41</v>
+        <v>39.74</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>83.67</v>
+        <v>36.21</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>75.89</v>
+        <v>79.14</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>51.67</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="45">
@@ -4178,76 +4178,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.34</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-0.24</v>
+        <v>-0.39</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-1.04</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-0.5</v>
+        <v>-1.01</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>-0.51</v>
+        <v>-0.9</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-2.89</v>
+        <v>-1.96</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.51</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>-2.49</v>
+        <v>-2.04</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>-3.82</v>
+        <v>-1.54</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>-2.28</v>
+        <v>-1.57</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>-1.81</v>
+        <v>-2.36</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>-1.57</v>
+        <v>-1.27</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>-2.19</v>
+        <v>-0.46</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>-1.7</v>
+        <v>-0.47</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>-1.82</v>
+        <v>-0.6</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>-1.57</v>
+        <v>-0.33</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>-0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>-0.46</v>
+        <v>-0.55</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="47">
@@ -4430,76 +4430,76 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>46.62</v>
+        <v>62.87</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>45.5</v>
+        <v>70.08</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>43.39</v>
+        <v>69.94</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>47.27</v>
+        <v>69.8</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>82.47</v>
+        <v>130.07</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>124.3</v>
+        <v>133.81</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>99.41</v>
+        <v>135.6</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>103.66</v>
+        <v>131.59</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>88.13</v>
+        <v>116.65</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>127.17</v>
+        <v>97.06</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>104.76</v>
+        <v>114.31</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>109.43</v>
+        <v>117.88</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>126.39</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>107.65</v>
+        <v>116.63</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>111.57</v>
+        <v>122.58</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>126.34</v>
+        <v>109.46</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>120.35</v>
+        <v>91.13</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>119.96</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>119.74</v>
+        <v>65.61</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>118.88</v>
+        <v>69.13</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>106.38</v>
+        <v>41.04</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>86.87</v>
+        <v>37.83</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>77.98999999999999</v>
+        <v>82.33</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>52.94</v>
+        <v>94.95999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4598,76 +4598,76 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.93</v>
+        <v>1.51</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.77</v>
+        <v>1.47</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.87</v>
+        <v>1.19</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.95</v>
+        <v>1.47</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1.98</v>
+        <v>4.29</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>4.35</v>
+        <v>1.87</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2.58</v>
+        <v>4.2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>3.01</v>
+        <v>3.95</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>3.26</v>
+        <v>3.73</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>4.07</v>
+        <v>1.75</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>3.35</v>
+        <v>2.74</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>3.06</v>
+        <v>2.71</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>3.03</v>
+        <v>2</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>1.83</v>
+        <v>2.57</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>3.57</v>
+        <v>2.45</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-3.73</v>
+        <v>-1.18</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-3.36</v>
+        <v>-1.1</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-3.11</v>
+        <v>-1.18</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>-3.09</v>
+        <v>2.28</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>2.87</v>
+        <v>1.15</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>2.69</v>
+        <v>1.36</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>1.27</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="52">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>47.64</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>46.59</v>
+        <v>71.84</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>44.39</v>
+        <v>71.91</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>48.3</v>
+        <v>71.33</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>83.94</v>
+        <v>126.03</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>118.53</v>
+        <v>130.63</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>95.86</v>
+        <v>127.33</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>100.55</v>
+        <v>124.04</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>85.73</v>
+        <v>111.58</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>125.23</v>
+        <v>97.06</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>101.1</v>
+        <v>113.85</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>106.05</v>
+        <v>114.94</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>122.37</v>
+        <v>100.31</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>104.46</v>
+        <v>116.15</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>106.09</v>
+        <v>122.83</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>116.46</v>
+        <v>106</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>116.73</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>115.36</v>
+        <v>74.33</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>115.03</v>
+        <v>54.44</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>114.2</v>
+        <v>50.69</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>98.58</v>
+        <v>37.46</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>85.02</v>
+        <v>36.1</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>79.2</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>53.99</v>
+        <v>96.94</v>
       </c>
     </row>
     <row r="55">
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>0</v>
+        <v>-8.15</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>0</v>
+        <v>-12.03</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5018,76 +5018,76 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.95</v>
+        <v>2.96</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.86</v>
+        <v>3.23</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>1.86</v>
+        <v>3.16</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.98</v>
+        <v>3</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>3.44</v>
+        <v>0.25</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-1.42</v>
+        <v>-1.31</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.96</v>
+        <v>-4.07</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-0.1</v>
+        <v>-3.6</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.86</v>
+        <v>-1.34</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>-0.3</v>
+        <v>2.28</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>-0.98</v>
+        <v>2.41</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>-1.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>-1.91</v>
+        <v>2.7</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-5.59</v>
+        <v>-1.17</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-7.35</v>
+        <v>-3.64</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-7.96</v>
+        <v>-5.28</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-7.82</v>
+        <v>-4.19</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-7.77</v>
+        <v>-4.14</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-4.93</v>
+        <v>-2.43</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>0.85</v>
+        <v>-0.36</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>2.32</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="57">
@@ -5270,76 +5270,76 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>47.15</v>
+        <v>63.2</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>46.16</v>
+        <v>70.66</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>43.93</v>
+        <v>70.37</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>47.85</v>
+        <v>70.02</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>82.98</v>
+        <v>129.67</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>123.28</v>
+        <v>135.74</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>99.51000000000001</v>
+        <v>134.63</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>103.55</v>
+        <v>130.91</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>116.29</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>124.22</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>102.95</v>
+        <v>112.92</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>107.77</v>
+        <v>117.28</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>123.85</v>
+        <v>99.8</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>107.54</v>
+        <v>116.51</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>110.09</v>
+        <v>121.83</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>124.54</v>
+        <v>109.68</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>125.21</v>
+        <v>94.87</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>125.07</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>124.22</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>123.83</v>
+        <v>68.78</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>107.04</v>
+        <v>41.13</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>86.69</v>
+        <v>37.36</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>78.39</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>53.22</v>
+        <v>95.55</v>
       </c>
     </row>
     <row r="60">
@@ -5438,76 +5438,76 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.43</v>
+        <v>2.05</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>2.49</v>
+        <v>3.89</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2.69</v>
+        <v>3.23</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>2.53</v>
+        <v>3.37</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1.4</v>
+        <v>2.11</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>2.09</v>
+        <v>1.71</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1.13</v>
+        <v>2.56</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>3.53</v>
+        <v>1.23</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>2.51</v>
+        <v>0.9</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>1.54</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="62">
@@ -5690,76 +5690,76 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>47.74</v>
+        <v>63.99</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>46.69</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>44.48</v>
+        <v>71.17</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>48.45</v>
+        <v>70.89</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>84.02</v>
+        <v>131.43</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>125.08</v>
+        <v>137.72</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>100.96</v>
+        <v>136.59</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>105.17</v>
+        <v>132.96</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>88.77</v>
+        <v>118.12</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>126</v>
+        <v>98.06</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>104.54</v>
+        <v>114.55</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>109.43</v>
+        <v>118.98</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>126</v>
+        <v>101.35</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>109.32</v>
+        <v>118.32</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>111.8</v>
+        <v>123.84</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>126.34</v>
+        <v>111.51</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>127.13</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>125.71</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>126.13</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>125.74</v>
+        <v>69.86</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>108.61</v>
+        <v>41.73</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>87.95999999999999</v>
+        <v>37.87</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>79.45</v>
+        <v>82.41</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>53.88</v>
+        <v>96.73999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -5858,76 +5858,76 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.96</v>
+        <v>2.93</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>3.53</v>
+        <v>5.65</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>5.13</v>
+        <v>5.78</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>4.14</v>
+        <v>5.19</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>4.52</v>
+        <v>5.32</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>3.91</v>
+        <v>5.2</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>3.14</v>
+        <v>2.98</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>3.06</v>
+        <v>3.81</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>3.5</v>
+        <v>4.26</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>3.05</v>
+        <v>4.15</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>3.28</v>
+        <v>2.57</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3.77</v>
+        <v>3</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>5.1</v>
+        <v>1.84</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>3.78</v>
+        <v>1.4</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>2.21</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="67">
@@ -6110,76 +6110,76 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>48.29</v>
+        <v>64.87</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>47.28</v>
+        <v>72.53</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>45.05</v>
+        <v>71.91</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>49.07</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>85</v>
+        <v>132.82</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>126</v>
+        <v>138.88</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>101.49</v>
+        <v>137.45</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>105.95</v>
+        <v>134.07</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>89.62</v>
+        <v>119.49</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>126</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>105.09</v>
+        <v>115.02</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>110</v>
+        <v>119.85</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>126</v>
+        <v>101.98</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>110</v>
+        <v>118.94</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>112.5</v>
+        <v>124.1</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>127</v>
+        <v>112.09</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>127</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="T69" s="3" t="n">
-        <v>127</v>
+        <v>83.45</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>126</v>
+        <v>69.5</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>126</v>
+        <v>70.37</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>110</v>
+        <v>42.08</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>89.65000000000001</v>
+        <v>38.14</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>80.37</v>
+        <v>83.36</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>54.68</v>
+        <v>98.06999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -6278,76 +6278,76 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>2.55</v>
+        <v>3.92</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2.52</v>
+        <v>3.16</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.75</v>
+        <v>3.37</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>4.5</v>
+        <v>7.04</v>
       </c>
       <c r="H71" s="3" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="I71" s="3" t="n">
         <v>6.05</v>
       </c>
-      <c r="I71" s="3" t="n">
+      <c r="J71" s="3" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N71" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="J71" s="3" t="n">
+      <c r="O71" s="3" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="Z71" s="3" t="n">
         <v>5.3</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M71" s="3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P71" s="3" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="Q71" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R71" s="3" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="S71" s="3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T71" s="3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="U71" s="3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V71" s="3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="W71" s="3" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="X71" s="3" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="Y71" s="3" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="Z71" s="3" t="n">
-        <v>3.01</v>
       </c>
     </row>
     <row r="72">
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="X72" s="3" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="n">
         <v>0</v>
@@ -6530,76 +6530,76 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>47.2</v>
+        <v>63.33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>46.21</v>
+        <v>70.81</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>43.97</v>
+        <v>70.44</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>47.9</v>
+        <v>70.16</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>82.98</v>
+        <v>129.8</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>123.53</v>
+        <v>136.16</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>99.70999999999999</v>
+        <v>135.05</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>103.98</v>
+        <v>131.45</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>87.95</v>
+        <v>116.77</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>125.23</v>
+        <v>97.06</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>103.69</v>
+        <v>113.5</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>108.65</v>
+        <v>117.76</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>124.47</v>
+        <v>100.2</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>108.09</v>
+        <v>116.87</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>110.55</v>
+        <v>122.45</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>124.92</v>
+        <v>110.13</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>125.46</v>
+        <v>95.36</v>
       </c>
       <c r="T74" s="3" t="n">
-        <v>125.07</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>124.34</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>124.08</v>
+        <v>69.13</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>107.37</v>
+        <v>41.3</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>87.14</v>
+        <v>37.55</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>78.63</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>53.33</v>
+        <v>95.73999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -6698,76 +6698,76 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>1.48</v>
+        <v>2.19</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>2.49</v>
+        <v>4.02</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>3.58</v>
+        <v>4.22</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>2.89</v>
+        <v>3.65</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>3.33</v>
+        <v>3.81</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>3.08</v>
+        <v>3.85</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M76" s="3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V76" s="3" t="n">
         <v>2.28</v>
       </c>
-      <c r="N76" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>2.11</v>
-      </c>
       <c r="W76" s="3" t="n">
-        <v>3.87</v>
+        <v>1.4</v>
       </c>
       <c r="X76" s="3" t="n">
-        <v>2.96</v>
+        <v>1.09</v>
       </c>
       <c r="Y76" s="3" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="Z76" s="3" t="n">
-        <v>1.65</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="77">
@@ -6950,76 +6950,76 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>45.69</v>
+        <v>61.37</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>44.73</v>
+        <v>68.61</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>42.52</v>
+        <v>68.75</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>46.32</v>
+        <v>68.34</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>80.48999999999999</v>
+        <v>125.78</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>119.95</v>
+        <v>131.94</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>96.81999999999999</v>
+        <v>131.4</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>100.65</v>
+        <v>127.64</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>84.87</v>
+        <v>112.92</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>123.1</v>
+        <v>95.31</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>101.41</v>
+        <v>111.57</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>106.37</v>
+        <v>115.17</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>123.35</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>105.82</v>
+        <v>114.06</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>108</v>
+        <v>120.13</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>122.05</v>
+        <v>107.16</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>124.08</v>
+        <v>92.31</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>123.32</v>
+        <v>79.61</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>122.85</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>121.97</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>103.51</v>
+        <v>39.89</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>84.17</v>
+        <v>36.46</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>76.34999999999999</v>
+        <v>79.69</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>51.67</v>
+        <v>92.77</v>
       </c>
     </row>
     <row r="80">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>47.49</v>
+        <v>64.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>46.21</v>
+        <v>71.92</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>44.25</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>48.1</v>
+        <v>71.11</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>83.84999999999999</v>
+        <v>122.95</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>116.57</v>
+        <v>128.35</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>94.19</v>
+        <v>124.55</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>100.75</v>
+        <v>120.87</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>85.98999999999999</v>
+        <v>107.64</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>124.22</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>97.7</v>
+        <v>112.13</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>102.57</v>
+        <v>110</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>117.26</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>99.92</v>
+        <v>114.52</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>100.66</v>
+        <v>121.22</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>111.76</v>
+        <v>101.86</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>112.9</v>
+        <v>87.09</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>111.8</v>
+        <v>73.78</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>112.6</v>
+        <v>54.15</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>111.29</v>
+        <v>50.63</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>95.84</v>
+        <v>37.39</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>84.51000000000001</v>
+        <v>35.58</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>78.87</v>
+        <v>82.84</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>53.88</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -7508,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>0</v>
+        <v>-8.15</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>0</v>
+        <v>-12.03</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7538,76 +7538,76 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>1.48</v>
+        <v>3.31</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.73</v>
+        <v>3.24</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.78</v>
+        <v>2.77</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>3.35</v>
+        <v>-2.83</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-3.38</v>
+        <v>-3.59</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-2.64</v>
+        <v>-6.85</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.1</v>
+        <v>-6.77</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>1.12</v>
+        <v>-5.27</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>1.12</v>
+        <v>0.87</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>-3.71</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-3.8</v>
+        <v>-5.17</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>-6.1</v>
+        <v>0.59</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>-5.9</v>
+        <v>0.46</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>-7.35</v>
+        <v>1.09</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-10.28</v>
+        <v>-5.3</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-11.18</v>
+        <v>-5.23</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-11.52</v>
+        <v>-5.83</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-10.25</v>
+        <v>-4.49</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-10.68</v>
+        <v>-4.2</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-7.67</v>
+        <v>-2.51</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>0.34</v>
+        <v>-0.89</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>2.21</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="87">
@@ -7790,76 +7790,76 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>44.4</v>
+        <v>58.5</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>43.34</v>
+        <v>65.97</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>40.97</v>
+        <v>66.42</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>44.71</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>77.31999999999999</v>
+        <v>121.18</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>115.45</v>
+        <v>126.02</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>93.81999999999999</v>
+        <v>125.86</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>95.95</v>
+        <v>121.45</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>79.91</v>
+        <v>106.73</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>85.31</v>
+        <v>69.78</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>95.3</v>
+        <v>80.36</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>100.73</v>
+        <v>78.72</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>139.71</v>
+        <v>92.36</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>154.71</v>
+        <v>79.59</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>187.18</v>
+        <v>81.05</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>229.99</v>
+        <v>100.53</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>749.6799999999999</v>
+        <v>87.25</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>749.1900000000001</v>
+        <v>75.25</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>400.42</v>
+        <v>55.98</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>188</v>
+        <v>53.04</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>98.3</v>
+        <v>38.03</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>79.41</v>
+        <v>34.96</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>61.02</v>
+        <v>54.31</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>50.07</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="90">
@@ -7901,22 +7901,22 @@
         <v>0</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-29.84</v>
+        <v>-20.48</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-0.28</v>
+        <v>-24.79</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>0</v>
+        <v>-30.24</v>
       </c>
       <c r="O90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>0</v>
+        <v>-27.41</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0</v>
+        <v>-31.54</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0</v>
@@ -7928,10 +7928,10 @@
         <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>0</v>
+        <v>-6.79</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>0</v>
+        <v>-10.02</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
@@ -7940,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-11.41</v>
+        <v>-21.95</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>0</v>
+        <v>-30.56</v>
       </c>
     </row>
     <row r="91">
@@ -7958,76 +7958,76 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>-1.29</v>
+        <v>-2.87</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-1.39</v>
+        <v>-2.64</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-1.56</v>
+        <v>-2.32</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-1.61</v>
+        <v>-2.37</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-3.17</v>
+        <v>-4.6</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-4.5</v>
+        <v>-5.92</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-3</v>
+        <v>-5.54</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>-4.7</v>
+        <v>-6.19</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>-4.95</v>
+        <v>-6.19</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>-7.95</v>
+        <v>-5.05</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>-5.83</v>
+        <v>-6.41</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-5.64</v>
+        <v>-6.21</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-5.76</v>
+        <v>-5.54</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-5.52</v>
+        <v>-7.06</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-5.24</v>
+        <v>-7.54</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.03</v>
+        <v>-6.63</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-5.12</v>
+        <v>-5.06</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-4.63</v>
+        <v>-4.36</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.84</v>
+        <v>-4.02</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-4.8</v>
+        <v>-3.78</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-5.21</v>
+        <v>-1.86</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-4.76</v>
+        <v>-1.5</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-3.91</v>
+        <v>-3.43</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-1.6</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="92">
@@ -8078,28 +8078,28 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>22.12</v>
+        <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>54.41</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>84.41</v>
+        <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>113.98</v>
+        <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>630.71</v>
+        <v>0</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>630.51</v>
+        <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>282.41</v>
+        <v>0</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>70.83</v>
+        <v>0</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-14T23:18:30</t>
+          <t>CreatedAt: 2026-10-15T04:15:43</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -653,73 +653,73 @@
         <v>59.35</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>66.42</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>66.94</v>
+        <v>64.16</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>66.47</v>
+        <v>65.66</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>122.47</v>
+        <v>87</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>126.86</v>
+        <v>115.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>126.1</v>
+        <v>120.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>122.26</v>
+        <v>120.32</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>107.75</v>
+        <v>122.86</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>70.12</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>81.06</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>79.34</v>
+        <v>85.88</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>93.15000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>80.91</v>
+        <v>104.54</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>82.22</v>
+        <v>92.11</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>101.96</v>
+        <v>101.48</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>88.51000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>57.06</v>
+        <v>61.05</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>54.01</v>
+        <v>86.44</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>38.36</v>
+        <v>43.07</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>35.16</v>
+        <v>38.66</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>54.82</v>
+        <v>35.52</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>58.99</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="5">
@@ -761,22 +761,22 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-20.48</v>
+        <v>-3.04</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-24.79</v>
+        <v>-17.56</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-30.24</v>
+        <v>-7.16</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-7.18</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-27.41</v>
+        <v>-13.49</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>-31.54</v>
+        <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
@@ -788,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-6.79</v>
+        <v>-11.02</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-10.02</v>
+        <v>-50.74</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
@@ -800,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-21.95</v>
+        <v>-0.67</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-30.56</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="6">
@@ -824,70 +824,70 @@
         <v>-2.19</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-1.81</v>
+        <v>-1.92</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>-3.31</v>
+        <v>-2.96</v>
       </c>
       <c r="H6" s="3" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>-5.07</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>-5.72</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>-5.74</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>-6.37</v>
-      </c>
       <c r="R6" s="3" t="n">
-        <v>-5.2</v>
+        <v>-5.18</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.81</v>
+        <v>-3.99</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.14</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-2.94</v>
+        <v>-3.32</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-2.82</v>
+        <v>-6.17</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-1.53</v>
+        <v>-2.02</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.66</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-2.92</v>
+        <v>-1.41</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="7">
@@ -1073,73 +1073,73 @@
         <v>59.41</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>67.8</v>
+        <v>67.59</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>68.2</v>
+        <v>64.92</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>67.66</v>
+        <v>66.31</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>122.71</v>
+        <v>87.34</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>127.23</v>
+        <v>116.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>129.71</v>
+        <v>124.82</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>125.88</v>
+        <v>124.12</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>110.49</v>
+        <v>125.73</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>73.06</v>
+        <v>89.16</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>83.42</v>
+        <v>76.98</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>81.25</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>95.33</v>
+        <v>88.58</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>83.76000000000001</v>
+        <v>108.34</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>85.77</v>
+        <v>95.08</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>104.04</v>
+        <v>103.95</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>89.62</v>
+        <v>89.88</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>77.06999999999999</v>
+        <v>77.67</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>58.05</v>
+        <v>62.31</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>55.2</v>
+        <v>89.39</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>39.46</v>
+        <v>43.65</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>36.07</v>
+        <v>39.61</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>58.06</v>
+        <v>36.82</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>59.95</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="10">
@@ -1181,22 +1181,22 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-20.48</v>
+        <v>-3.04</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-24.79</v>
+        <v>-17.56</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-30.24</v>
+        <v>-7.16</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>-7.18</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-27.41</v>
+        <v>-13.49</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>-31.54</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-6.79</v>
+        <v>-11.02</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-10.02</v>
+        <v>-50.74</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-21.95</v>
+        <v>-0.67</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-30.56</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="11">
@@ -1241,73 +1241,73 @@
         <v>-1.96</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.88</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.55</v>
+        <v>-1.17</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.68</v>
+        <v>-1.26</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-3.07</v>
+        <v>-2.62</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-4.71</v>
+        <v>-4.08</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.69</v>
+        <v>-0.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.74</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.43</v>
+        <v>-3.52</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.78</v>
+        <v>-2.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-3.35</v>
+        <v>-3.31</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-3.68</v>
+        <v>-3.32</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.49</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-2.89</v>
+        <v>-2.8</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-2.82</v>
+        <v>-2.09</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-3.12</v>
+        <v>-2.7</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-2.69</v>
+        <v>-2.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.02</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>-1.95</v>
+        <v>-2.05</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>-1.63</v>
+        <v>-3.22</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-0.43</v>
+        <v>-1.44</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.71</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>-2.26</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="12">
@@ -1493,73 +1493,73 @@
         <v>54.28</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>67.8</v>
+        <v>67.66</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>68.27</v>
+        <v>54.28</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>67.73</v>
+        <v>56.89</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>122.71</v>
+        <v>83.88</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>127.23</v>
+        <v>105.23</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>129.84</v>
+        <v>124.82</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>125.88</v>
+        <v>124.12</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>110.49</v>
+        <v>125.73</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>93.54000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>108.21</v>
+        <v>94.63</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>111.49</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>95.33</v>
+        <v>133.03</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>111.17</v>
+        <v>133.79</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>117.31</v>
+        <v>97.42</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>104.04</v>
+        <v>104.2</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>89.62</v>
+        <v>96.41</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>77.06999999999999</v>
+        <v>77.67</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>56.69</v>
+        <v>60.11</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>53.26</v>
+        <v>79.25</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>39.46</v>
+        <v>43.65</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>36.07</v>
+        <v>39.61</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>80.01000000000001</v>
+        <v>37.49</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>90.51000000000001</v>
+        <v>111.15</v>
       </c>
     </row>
     <row r="15">
@@ -1580,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>-10.7</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>-9.42</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>-3.46</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
+        <v>-11.38</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>0</v>
@@ -1610,28 +1610,28 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0</v>
+        <v>37.27</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0</v>
+        <v>11.96</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-8.15</v>
+        <v>-13.23</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>-12.03</v>
+        <v>-60.89</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1664,70 +1664,70 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.48</v>
+        <v>-1.1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-0.61</v>
+        <v>-1.26</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-3.07</v>
+        <v>-2.62</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-4.71</v>
+        <v>-4.08</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-1.56</v>
+        <v>-0.5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.76</v>
+        <v>-1.74</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.43</v>
+        <v>-3.52</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-1.78</v>
+        <v>-2.4</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.35</v>
+        <v>-3.22</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-3.68</v>
+        <v>-3.32</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>-2.57</v>
+        <v>-2.49</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-2.89</v>
+        <v>-2.8</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>-2.82</v>
+        <v>-2</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-3.12</v>
+        <v>-2.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>-2.69</v>
+        <v>-2.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>-2.54</v>
+        <v>-2.02</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>-1.95</v>
+        <v>-2.05</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>-1.57</v>
+        <v>-3.22</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-0.43</v>
+        <v>-1.44</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>-0.4</v>
+        <v>-0.71</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>0.32</v>
+        <v>-0.11</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>-2.26</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="17">
@@ -1913,73 +1913,73 @@
         <v>59.01</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>66.29000000000001</v>
+        <v>66.09</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>66.75</v>
+        <v>63.91</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>66.34999999999999</v>
+        <v>65.41</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>121.88</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>126.5</v>
+        <v>115.49</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>126.1</v>
+        <v>131.12</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>121.91</v>
+        <v>120.21</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>107.34</v>
+        <v>122.39</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>48.57</v>
+        <v>82.77</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>54.77</v>
+        <v>56.25</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>47.42</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>92.88</v>
+        <v>78.16</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>51.65</v>
+        <v>89.95</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>48.72</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>101.38</v>
+        <v>101</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>75.89</v>
+        <v>76.11</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>49.51</v>
+        <v>49.08</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>43.07</v>
+        <v>32.59</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>38.25</v>
+        <v>42.86</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>35.1</v>
+        <v>38.58</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>31.65</v>
+        <v>34.71</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>26.52</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="20">
@@ -2021,22 +2021,22 @@
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-41.95</v>
+        <v>-6.23</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-50.78</v>
+        <v>-35.97</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-61.96</v>
+        <v>-14.68</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0</v>
+        <v>-14.71</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-56.16</v>
+        <v>-27.63</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-64.61</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-13.91</v>
+        <v>-22.58</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-20.53</v>
+        <v>-103.94</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
@@ -2060,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-44.97</v>
+        <v>-1.37</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-62.61</v>
+        <v>-110.62</v>
       </c>
     </row>
     <row r="21">
@@ -2081,73 +2081,73 @@
         <v>-2.36</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.38</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-2</v>
+        <v>-2.17</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.16</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-3.9</v>
+        <v>-2.96</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-5.44</v>
+        <v>-5.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-5.3</v>
+        <v>-4.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-5.73</v>
+        <v>-5.65</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-5.58</v>
+        <v>-6.85</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-4.8</v>
+        <v>-5.61</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-6.02</v>
+        <v>-5.63</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.56</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>-5.02</v>
+        <v>-5.39</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-6.25</v>
+        <v>-7.05</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-6.8</v>
+        <v>-5.41</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-5.78</v>
+        <v>-5.66</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-4.31</v>
+        <v>-4.58</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.58</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.36</v>
+        <v>-3.73</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-3.24</v>
+        <v>-6.83</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-1.64</v>
+        <v>-2.23</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.74</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-3.07</v>
+        <v>-1.52</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="22">
@@ -2174,13 +2174,13 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2333,73 +2333,73 @@
         <v>59.01</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>66.29000000000001</v>
+        <v>66.09</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>66.75</v>
+        <v>63.91</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>66.34999999999999</v>
+        <v>65.41</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>121.88</v>
+        <v>87</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>126.5</v>
+        <v>115.49</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>126.1</v>
+        <v>120.62</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>121.91</v>
+        <v>120.21</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>107.34</v>
+        <v>122.39</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>70.04000000000001</v>
+        <v>85.95</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>80.76000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>79.13</v>
+        <v>85.53</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.88</v>
+        <v>85.69</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>104.09</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>81.79000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>101.38</v>
+        <v>101</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>75.89</v>
+        <v>76.11</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>56.63</v>
+        <v>60.64</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>53.59</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>38.25</v>
+        <v>42.86</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>35.1</v>
+        <v>38.58</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>54.67</v>
+        <v>35.41</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>58.56</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="25">
@@ -2441,22 +2441,22 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-20.48</v>
+        <v>-3.04</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-24.79</v>
+        <v>-17.56</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-30.24</v>
+        <v>-7.16</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>0</v>
+        <v>-7.18</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-27.41</v>
+        <v>-13.49</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>-31.54</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-6.79</v>
+        <v>-11.02</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-10.02</v>
+        <v>-50.74</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
@@ -2480,10 +2480,10 @@
         <v>0</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-21.95</v>
+        <v>-0.67</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-30.56</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="26">
@@ -2501,73 +2501,73 @@
         <v>-2.36</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.38</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-2</v>
+        <v>-2.17</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-1.99</v>
+        <v>-2.16</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-3.9</v>
+        <v>-2.96</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-5.44</v>
+        <v>-5.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-5.3</v>
+        <v>-4.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-5.73</v>
+        <v>-5.65</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-5.58</v>
+        <v>-6.85</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-4.8</v>
+        <v>-5.61</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-6.02</v>
+        <v>-5.63</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-5.8</v>
+        <v>-5.56</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-5.02</v>
+        <v>-5.39</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-6.25</v>
+        <v>-7.05</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-6.8</v>
+        <v>-5.41</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-5.78</v>
+        <v>-5.66</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-4.31</v>
+        <v>-4.58</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-3.72</v>
+        <v>-3.58</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.36</v>
+        <v>-3.73</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-3.24</v>
+        <v>-6.83</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-1.64</v>
+        <v>-2.23</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.37</v>
+        <v>-1.74</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-3.07</v>
+        <v>-1.52</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-3.65</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="27">
@@ -2753,73 +2753,73 @@
         <v>58.5</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>65.97</v>
+        <v>65.78</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>66.42</v>
+        <v>63.54</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>65.95999999999999</v>
+        <v>64.97</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>121.18</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>126.02</v>
+        <v>115.38</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>125.86</v>
+        <v>131</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>121.45</v>
+        <v>119.86</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>106.73</v>
+        <v>121.7</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>48.31</v>
+        <v>82.19</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>54.37</v>
+        <v>55.56</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>47</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>92.36</v>
+        <v>77.55</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50.84</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>47.98</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>100.53</v>
+        <v>100.15</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>87.25</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>75.25</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>48.86</v>
+        <v>48.4</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>42.53</v>
+        <v>31.43</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>38.03</v>
+        <v>42.58</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>34.99</v>
+        <v>38.4</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>31.29</v>
+        <v>34.54</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>26</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="30">
@@ -2861,22 +2861,22 @@
         <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-41.95</v>
+        <v>-6.23</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-50.78</v>
+        <v>-35.97</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-61.96</v>
+        <v>-14.68</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0</v>
+        <v>-14.71</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-56.16</v>
+        <v>-27.63</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-64.61</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-13.91</v>
+        <v>-22.58</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-20.53</v>
+        <v>-103.94</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
@@ -2900,10 +2900,10 @@
         <v>0</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-44.97</v>
+        <v>-1.37</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-62.61</v>
+        <v>-110.62</v>
       </c>
     </row>
     <row r="31">
@@ -2921,73 +2921,73 @@
         <v>-2.87</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-2.64</v>
+        <v>-2.7</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.54</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.6</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-4.6</v>
+        <v>-2.96</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-5.92</v>
+        <v>-5.31</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-5.54</v>
+        <v>-4.82</v>
       </c>
       <c r="J31" s="3" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="L31" s="3" t="n">
         <v>-6.19</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>-6.19</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>-5.05</v>
-      </c>
       <c r="M31" s="3" t="n">
-        <v>-6.41</v>
+        <v>-6.32</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-6.21</v>
+        <v>-6.17</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-5.54</v>
+        <v>-6</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-7.06</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-7.54</v>
+        <v>-6.02</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.63</v>
+        <v>-6.51</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-5.06</v>
+        <v>-5.32</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.23</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.02</v>
+        <v>-4.4</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-3.78</v>
+        <v>-7.99</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-1.86</v>
+        <v>-2.51</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.47</v>
+        <v>-1.92</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-3.43</v>
+        <v>-1.69</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-4.16</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="32">
@@ -3014,13 +3014,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3173,73 +3173,73 @@
         <v>56.15</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>69.87</v>
+        <v>69.66</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>70.08</v>
+        <v>57.06</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>69.52</v>
+        <v>59.43</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>125.53</v>
+        <v>85.78</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>130.5</v>
+        <v>109.25</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>133.27</v>
+        <v>132.95</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>129.45</v>
+        <v>127.65</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>113.26</v>
+        <v>128.86</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>95.79000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>110.68</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>113.58</v>
+        <v>97.09</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>97.61</v>
+        <v>135.62</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>114.29</v>
+        <v>137.47</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>120.97</v>
+        <v>100.4</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>106.63</v>
+        <v>106.9</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>91.31</v>
+        <v>98.28</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>78.59</v>
+        <v>79.37</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>58.37</v>
+        <v>61.93</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>54.96</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>40.26</v>
+        <v>44.38</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>36.87</v>
+        <v>40.52</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82.67</v>
+        <v>38.56</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>92.68000000000001</v>
+        <v>113.24</v>
       </c>
     </row>
     <row r="35">
@@ -3260,16 +3260,16 @@
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0</v>
+        <v>-3.11</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0</v>
+        <v>-10.24</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>0</v>
@@ -3290,28 +3290,28 @@
         <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>0</v>
+        <v>37.27</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>11.96</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-8.15</v>
+        <v>-13.23</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>-12.03</v>
+        <v>-60.89</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3341,73 +3341,73 @@
         <v>-0.61</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.33</v>
+        <v>0.6</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.18</v>
+        <v>0.34</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-0.25</v>
+        <v>-1.07</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-1.44</v>
+        <v>-1.19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>1.87</v>
+        <v>3.21</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.34</v>
+        <v>-0.39</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.48</v>
+        <v>0.09</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.06</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-1.59</v>
+        <v>-1.17</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-0.29</v>
+        <v>0.1</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.23</v>
+        <v>0.88</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-1</v>
+        <v>-0.83</v>
       </c>
       <c r="T36" s="3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Z36" s="3" t="n">
         <v>-1.02</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>-0.09</v>
       </c>
     </row>
     <row r="37">
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>0</v>
@@ -3593,73 +3593,73 @@
         <v>59.35</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>66.42</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>66.94</v>
+        <v>64.16</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>66.47</v>
+        <v>65.66</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>122.47</v>
+        <v>87</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>126.86</v>
+        <v>115.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>126.1</v>
+        <v>120.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>122.26</v>
+        <v>120.32</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>107.75</v>
+        <v>122.86</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>70.12</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>81.06</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>79.34</v>
+        <v>85.88</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>93.15000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>80.91</v>
+        <v>104.54</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>82.22</v>
+        <v>92.11</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>101.96</v>
+        <v>101.48</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>88.51000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.55</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>57.06</v>
+        <v>61.05</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>54.01</v>
+        <v>86.44</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>38.36</v>
+        <v>43.07</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>35.16</v>
+        <v>38.66</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>54.82</v>
+        <v>35.52</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>58.99</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="40">
@@ -3701,22 +3701,22 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-20.48</v>
+        <v>-3.04</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-24.79</v>
+        <v>-17.56</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-30.24</v>
+        <v>-7.16</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>-7.18</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-27.41</v>
+        <v>-13.49</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>-31.54</v>
+        <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-6.79</v>
+        <v>-11.02</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-10.02</v>
+        <v>-50.74</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
@@ -3740,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-21.95</v>
+        <v>-0.67</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-30.56</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="41">
@@ -3764,70 +3764,70 @@
         <v>-2.19</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-1.81</v>
+        <v>-1.92</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.9</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-3.31</v>
+        <v>-2.96</v>
       </c>
       <c r="H41" s="3" t="n">
+        <v>-5.09</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>-5.53</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="Q41" s="3" t="n">
         <v>-5.07</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J41" s="3" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>-5.17</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>-5.72</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>-5.59</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>-5.74</v>
-      </c>
-      <c r="Q41" s="3" t="n">
-        <v>-6.37</v>
-      </c>
       <c r="R41" s="3" t="n">
-        <v>-5.2</v>
+        <v>-5.18</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-3.81</v>
+        <v>-3.99</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.21</v>
+        <v>-3.14</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-2.94</v>
+        <v>-3.32</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-2.82</v>
+        <v>-6.17</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-1.53</v>
+        <v>-2.02</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.3</v>
+        <v>-1.66</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-2.92</v>
+        <v>-1.41</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3.76</v>
       </c>
     </row>
     <row r="42">
@@ -4013,73 +4013,73 @@
         <v>61.24</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>68.47</v>
+        <v>68.34</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>68.41</v>
+        <v>65.95</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>68.06</v>
+        <v>67.56</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>126.03</v>
+        <v>90.05</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>131.54</v>
+        <v>120.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>130.36</v>
+        <v>123.96</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>126.63</v>
+        <v>124.24</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>112.02</v>
+        <v>127.34</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>93.34999999999999</v>
+        <v>92.02</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>109.06</v>
+        <v>95.28</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>113.14</v>
+        <v>95.86</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>96.36</v>
+        <v>96.14</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>112.49</v>
+        <v>121.95</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>117.77</v>
+        <v>94.8</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>105.89</v>
+        <v>104.98</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>91.84999999999999</v>
+        <v>91.75</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>79.14</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>66.19</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>66.52</v>
+        <v>142.36</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>39.74</v>
+        <v>44.73</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>36.21</v>
+        <v>39.88</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>79.14</v>
+        <v>37.26</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>92.5</v>
+        <v>114.14</v>
       </c>
     </row>
     <row r="45">
@@ -4184,70 +4184,70 @@
         <v>-0.14</v>
       </c>
       <c r="E46" s="3" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>-2.57</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="Y46" s="3" t="n">
         <v>-0.34</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>-1.96</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>-0.55</v>
-      </c>
       <c r="Z46" s="3" t="n">
-        <v>-0.28</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="47">
@@ -4433,73 +4433,73 @@
         <v>62.87</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>70.08</v>
+        <v>69.94</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>69.94</v>
+        <v>67.36</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>69.8</v>
+        <v>68.87</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>130.07</v>
+        <v>92.55</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>133.81</v>
+        <v>125.45</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>135.6</v>
+        <v>128.01</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>131.59</v>
+        <v>128.03</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>116.65</v>
+        <v>131.48</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>97.06</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>114.31</v>
+        <v>98.44</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>117.88</v>
+        <v>98.84</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="P49" s="3" t="n">
-        <v>116.63</v>
+        <v>126.27</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>122.58</v>
+        <v>98.55</v>
       </c>
       <c r="R49" s="3" t="n">
-        <v>109.46</v>
+        <v>108.83</v>
       </c>
       <c r="S49" s="3" t="n">
-        <v>91.13</v>
+        <v>90.14</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>78.51000000000001</v>
+        <v>77.52</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>65.61</v>
+        <v>73.55</v>
       </c>
       <c r="V49" s="3" t="n">
-        <v>69.13</v>
+        <v>147.03</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>41.04</v>
+        <v>46.15</v>
       </c>
       <c r="X49" s="3" t="n">
-        <v>37.83</v>
+        <v>41.57</v>
       </c>
       <c r="Y49" s="3" t="n">
-        <v>82.33</v>
+        <v>38.44</v>
       </c>
       <c r="Z49" s="3" t="n">
-        <v>94.95999999999999</v>
+        <v>117.91</v>
       </c>
     </row>
     <row r="50">
@@ -4604,70 +4604,70 @@
         <v>1.47</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>4.29</v>
+        <v>2.59</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>1.87</v>
+        <v>4.77</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>4.2</v>
+        <v>2.69</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>3.73</v>
+        <v>2.24</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>1.75</v>
+        <v>0.86</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>2.74</v>
+        <v>0.59</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>2.71</v>
+        <v>0.59</v>
       </c>
       <c r="O51" s="3" t="n">
-        <v>2</v>
+        <v>0.79</v>
       </c>
       <c r="P51" s="3" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>2.45</v>
+        <v>1.38</v>
       </c>
       <c r="R51" s="3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>-1.18</v>
+        <v>-2.43</v>
       </c>
       <c r="T51" s="3" t="n">
-        <v>-1.1</v>
+        <v>-2.17</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>-1.18</v>
+        <v>-1.84</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2.28</v>
+        <v>3.68</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X51" s="3" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Y51" s="3" t="n">
-        <v>2.63</v>
+        <v>0.85</v>
       </c>
       <c r="Z51" s="3" t="n">
-        <v>2.18</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="52">
@@ -4853,73 +4853,73 @@
         <v>64.31999999999999</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>71.84</v>
+        <v>71.7</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>71.91</v>
+        <v>69.13</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>71.33</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>126.03</v>
+        <v>90.5</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>130.63</v>
+        <v>120.44</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>127.33</v>
+        <v>122.26</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>124.04</v>
+        <v>122.67</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>111.58</v>
+        <v>126.71</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>97.06</v>
+        <v>96.83</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>113.85</v>
+        <v>99.95</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>114.94</v>
+        <v>100.05</v>
       </c>
       <c r="O54" s="3" t="n">
-        <v>100.31</v>
+        <v>100.05</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>116.15</v>
+        <v>124.38</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>122.83</v>
+        <v>99.97</v>
       </c>
       <c r="R54" s="3" t="n">
-        <v>106</v>
+        <v>105.7</v>
       </c>
       <c r="S54" s="3" t="n">
-        <v>88.68000000000001</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>74.33</v>
+        <v>74.2</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>54.44</v>
+        <v>57.43</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>50.69</v>
+        <v>73.22</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>37.46</v>
+        <v>42.58</v>
       </c>
       <c r="X54" s="3" t="n">
-        <v>36.1</v>
+        <v>40.04</v>
       </c>
       <c r="Y54" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>39.29</v>
       </c>
       <c r="Z54" s="3" t="n">
-        <v>96.94</v>
+        <v>120.15</v>
       </c>
     </row>
     <row r="55">
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>-8.15</v>
+        <v>-13.23</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>-12.03</v>
+        <v>-60.89</v>
       </c>
       <c r="W55" s="3" t="n">
         <v>0</v>
@@ -5024,70 +5024,70 @@
         <v>3.23</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.25</v>
+        <v>0.54</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>-1.31</v>
+        <v>-0.24</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-4.07</v>
+        <v>-3.06</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-3.6</v>
+        <v>-3.19</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>-1.34</v>
+        <v>-2.53</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>1.75</v>
+        <v>2.23</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>-0.23</v>
+        <v>1.8</v>
       </c>
       <c r="O56" s="3" t="n">
-        <v>2.41</v>
+        <v>1.8</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>2.09</v>
+        <v>-0.25</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>-1.17</v>
+        <v>-0.95</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>-3.64</v>
+        <v>-3.82</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>-5.28</v>
+        <v>-5.49</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>-4.19</v>
+        <v>-4.73</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>-4.14</v>
+        <v>-9.25</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>-2.43</v>
+        <v>-2.51</v>
       </c>
       <c r="X56" s="3" t="n">
-        <v>-0.36</v>
+        <v>-0.28</v>
       </c>
       <c r="Y56" s="3" t="n">
-        <v>3.23</v>
+        <v>1.69</v>
       </c>
       <c r="Z56" s="3" t="n">
-        <v>4.17</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="57">
@@ -5273,73 +5273,73 @@
         <v>63.2</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>70.66</v>
+        <v>70.52</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>70.37</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>70.02</v>
+        <v>69.73</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>129.67</v>
+        <v>93.03</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>135.74</v>
+        <v>124.16</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>134.63</v>
+        <v>127.75</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>130.91</v>
+        <v>128.69</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>116.29</v>
+        <v>132.43</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>96.56999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>112.92</v>
+        <v>98.84</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>117.28</v>
+        <v>99.55</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>99.8</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>116.51</v>
+        <v>126.66</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>121.83</v>
+        <v>98.25</v>
       </c>
       <c r="R59" s="3" t="n">
-        <v>109.68</v>
+        <v>108.83</v>
       </c>
       <c r="S59" s="3" t="n">
-        <v>94.87</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="T59" s="3" t="n">
-        <v>81.73999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>68.78</v>
+        <v>147.18</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>41.13</v>
+        <v>46.34</v>
       </c>
       <c r="X59" s="3" t="n">
-        <v>37.36</v>
+        <v>41.18</v>
       </c>
       <c r="Y59" s="3" t="n">
-        <v>81.56999999999999</v>
+        <v>38.41</v>
       </c>
       <c r="Z59" s="3" t="n">
-        <v>95.55</v>
+        <v>117.91</v>
       </c>
     </row>
     <row r="60">
@@ -5444,70 +5444,70 @@
         <v>2.05</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>3.89</v>
+        <v>3.07</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>3.8</v>
+        <v>3.48</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>3.23</v>
+        <v>2.43</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>3.27</v>
+        <v>2.83</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>1.26</v>
+        <v>0.86</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>1.36</v>
+        <v>0.99</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>2.11</v>
+        <v>1.29</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>1.71</v>
+        <v>1.08</v>
       </c>
       <c r="R61" s="3" t="n">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="T61" s="3" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>1.93</v>
+        <v>3.83</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X61" s="3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="Y61" s="3" t="n">
-        <v>1.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z61" s="3" t="n">
-        <v>2.77</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="62">
@@ -5693,73 +5693,73 @@
         <v>63.99</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>71.54000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>71.17</v>
+        <v>68.84</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>70.89</v>
+        <v>70.53</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>131.43</v>
+        <v>94.2</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>137.72</v>
+        <v>125.84</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>136.59</v>
+        <v>128.93</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>132.96</v>
+        <v>130.56</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>118.12</v>
+        <v>134.49</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>98.06</v>
+        <v>96.83</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>114.55</v>
+        <v>100.36</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>118.98</v>
+        <v>101.08</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>101.35</v>
+        <v>101.29</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>118.32</v>
+        <v>128.49</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>123.84</v>
+        <v>99.87</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>111.51</v>
+        <v>110.75</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>96.45999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>83.01000000000001</v>
+        <v>82.92</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>69.34999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>69.86</v>
+        <v>149.33</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>41.73</v>
+        <v>47.07</v>
       </c>
       <c r="X64" s="3" t="n">
-        <v>37.87</v>
+        <v>41.78</v>
       </c>
       <c r="Y64" s="3" t="n">
-        <v>82.41</v>
+        <v>38.92</v>
       </c>
       <c r="Z64" s="3" t="n">
-        <v>96.73999999999999</v>
+        <v>119.52</v>
       </c>
     </row>
     <row r="65">
@@ -5864,70 +5864,70 @@
         <v>2.93</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.55</v>
+        <v>2.96</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>5.65</v>
+        <v>4.24</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>5.78</v>
+        <v>5.16</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>5.19</v>
+        <v>3.61</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>5.32</v>
+        <v>4.7</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>2.98</v>
+        <v>2.51</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>3.81</v>
+        <v>2.83</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="P66" s="3" t="n">
-        <v>4.26</v>
+        <v>3.85</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>3.72</v>
+        <v>2.7</v>
       </c>
       <c r="R66" s="3" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="S66" s="3" t="n">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="T66" s="3" t="n">
-        <v>3.4</v>
+        <v>3.23</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>3</v>
+        <v>5.97</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="X66" s="3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Y66" s="3" t="n">
-        <v>2.72</v>
+        <v>1.32</v>
       </c>
       <c r="Z66" s="3" t="n">
-        <v>3.97</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="67">
@@ -6113,73 +6113,73 @@
         <v>64.87</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>72.53</v>
+        <v>72.38</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>71.91</v>
+        <v>69.78</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>71.70999999999999</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>132.82</v>
+        <v>105</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>138.88</v>
+        <v>127.3</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>137.45</v>
+        <v>130</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>134.07</v>
+        <v>131.79</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>119.49</v>
+        <v>136.19</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>98.45999999999999</v>
+        <v>97.33</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>115.02</v>
+        <v>100.77</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>119.85</v>
+        <v>101.82</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>101.98</v>
+        <v>102.03</v>
       </c>
       <c r="P69" s="3" t="n">
-        <v>118.94</v>
+        <v>129.56</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>124.1</v>
+        <v>100.07</v>
       </c>
       <c r="R69" s="3" t="n">
-        <v>112.09</v>
+        <v>111.33</v>
       </c>
       <c r="S69" s="3" t="n">
-        <v>97.06999999999999</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="T69" s="3" t="n">
         <v>83.45</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>69.5</v>
+        <v>78.36</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>70.37</v>
+        <v>150.58</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>42.08</v>
+        <v>47.41</v>
       </c>
       <c r="X69" s="3" t="n">
-        <v>38.14</v>
+        <v>42.09</v>
       </c>
       <c r="Y69" s="3" t="n">
-        <v>83.36</v>
+        <v>39.25</v>
       </c>
       <c r="Z69" s="3" t="n">
-        <v>98.06999999999999</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="70">
@@ -6281,73 +6281,73 @@
         <v>3.5</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>3.37</v>
+        <v>4.08</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>7.04</v>
+        <v>5.64</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>6.94</v>
+        <v>6.62</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>6.05</v>
+        <v>4.68</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>6.44</v>
+        <v>5.93</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>6.57</v>
+        <v>6.95</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>4.67</v>
+        <v>3.56</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>4.08</v>
+        <v>3.77</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>3.97</v>
+        <v>2.9</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>4.93</v>
+        <v>4.68</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>4.76</v>
+        <v>4.46</v>
       </c>
       <c r="T71" s="3" t="n">
-        <v>3.84</v>
+        <v>3.76</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>3.52</v>
+        <v>7.23</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="X71" s="3" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="Y71" s="3" t="n">
-        <v>3.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z71" s="3" t="n">
-        <v>5.3</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="72">
@@ -6374,7 +6374,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0</v>
@@ -6533,73 +6533,73 @@
         <v>63.33</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>70.81</v>
+        <v>70.66</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>70.44</v>
+        <v>68.13</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>70.16</v>
+        <v>69.8</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>129.8</v>
+        <v>93.03</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>136.16</v>
+        <v>124.67</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>135.05</v>
+        <v>128.14</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>131.45</v>
+        <v>129.22</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>116.77</v>
+        <v>132.97</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>97.06</v>
+        <v>95.94</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>113.5</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>117.76</v>
+        <v>99.95</v>
       </c>
       <c r="O74" s="3" t="n">
-        <v>100.2</v>
+        <v>100.15</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>116.87</v>
+        <v>127.31</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>122.45</v>
+        <v>98.75</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>110.13</v>
+        <v>109.39</v>
       </c>
       <c r="S74" s="3" t="n">
-        <v>95.36</v>
+        <v>95.34</v>
       </c>
       <c r="T74" s="3" t="n">
         <v>81.98999999999999</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>68.56999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>69.13</v>
+        <v>147.94</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>41.3</v>
+        <v>46.58</v>
       </c>
       <c r="X74" s="3" t="n">
-        <v>37.55</v>
+        <v>41.44</v>
       </c>
       <c r="Y74" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>38.56</v>
       </c>
       <c r="Z74" s="3" t="n">
-        <v>95.73999999999999</v>
+        <v>118.28</v>
       </c>
     </row>
     <row r="75">
@@ -6704,70 +6704,70 @@
         <v>2.19</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="G76" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M76" s="3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="Z76" s="3" t="n">
         <v>4.02</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M76" s="3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="N76" s="3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P76" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q76" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="R76" s="3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="S76" s="3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T76" s="3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U76" s="3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V76" s="3" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="W76" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X76" s="3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y76" s="3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Z76" s="3" t="n">
-        <v>2.97</v>
       </c>
     </row>
     <row r="77">
@@ -6953,73 +6953,73 @@
         <v>61.37</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>68.61</v>
+        <v>68.47</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>68.75</v>
+        <v>66.08</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>68.34</v>
+        <v>67.56</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>125.78</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>131.94</v>
+        <v>120.68</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>131.4</v>
+        <v>125.32</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>127.64</v>
+        <v>125.86</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>112.92</v>
+        <v>129.25</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>95.31</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>111.57</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>115.17</v>
+        <v>98.25</v>
       </c>
       <c r="O79" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>98.25</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>114.06</v>
+        <v>124.63</v>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>120.13</v>
+        <v>97.17</v>
       </c>
       <c r="R79" s="3" t="n">
-        <v>107.16</v>
+        <v>106.65</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>92.31</v>
+        <v>92.58</v>
       </c>
       <c r="T79" s="3" t="n">
-        <v>79.61</v>
+        <v>79.69</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>66.79000000000001</v>
+        <v>75.39</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>66.84999999999999</v>
+        <v>143.35</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>39.89</v>
+        <v>45.09</v>
       </c>
       <c r="X79" s="3" t="n">
-        <v>36.46</v>
+        <v>40.32</v>
       </c>
       <c r="Y79" s="3" t="n">
-        <v>79.69</v>
+        <v>37.6</v>
       </c>
       <c r="Z79" s="3" t="n">
-        <v>92.77</v>
+        <v>114.26</v>
       </c>
     </row>
     <row r="80">
@@ -7373,73 +7373,73 @@
         <v>64.39</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>71.92</v>
+        <v>71.77</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>71.98999999999999</v>
+        <v>68.91</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>71.11</v>
+        <v>70.31</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>122.95</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>128.35</v>
+        <v>117.74</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>124.55</v>
+        <v>118.56</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>120.87</v>
+        <v>119.64</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>107.64</v>
+        <v>122.16</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>96.18000000000001</v>
+        <v>96.14</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>112.13</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>110</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="O84" s="3" t="n">
-        <v>98.48999999999999</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>114.52</v>
+        <v>119.49</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>121.22</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>101.86</v>
+        <v>101.77</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>87.09</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>73.78</v>
+        <v>73.38</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>54.15</v>
+        <v>56.9</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>50.63</v>
+        <v>71.48</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>37.39</v>
+        <v>42.06</v>
       </c>
       <c r="X84" s="3" t="n">
-        <v>35.58</v>
+        <v>38.96</v>
       </c>
       <c r="Y84" s="3" t="n">
-        <v>82.84</v>
+        <v>39.25</v>
       </c>
       <c r="Z84" s="3" t="n">
-        <v>97.04000000000001</v>
+        <v>120.78</v>
       </c>
     </row>
     <row r="85">
@@ -7508,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>-8.15</v>
+        <v>-13.23</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>-12.03</v>
+        <v>-60.89</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -7541,73 +7541,73 @@
         <v>3.03</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>3.24</v>
+        <v>2.83</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>-2.83</v>
+        <v>-2.11</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-3.59</v>
+        <v>-2.94</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-6.85</v>
+        <v>-6.76</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>-6.77</v>
+        <v>-6.22</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>-5.27</v>
+        <v>-7.09</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.87</v>
+        <v>1.54</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>-5.17</v>
+        <v>0.1</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0.46</v>
+        <v>-5.14</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>-5.3</v>
+        <v>-4.88</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>-5.23</v>
+        <v>-5.65</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>-5.83</v>
+        <v>-6.31</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>-4.49</v>
+        <v>-5.26</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>-4.2</v>
+        <v>-10.99</v>
       </c>
       <c r="W86" s="3" t="n">
-        <v>-2.51</v>
+        <v>-3.03</v>
       </c>
       <c r="X86" s="3" t="n">
-        <v>-0.89</v>
+        <v>-1.36</v>
       </c>
       <c r="Y86" s="3" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="Z86" s="3" t="n">
-        <v>4.27</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="87">
@@ -7793,73 +7793,73 @@
         <v>58.5</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>65.97</v>
+        <v>65.78</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>66.42</v>
+        <v>63.54</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>65.95999999999999</v>
+        <v>64.97</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>121.18</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>126.02</v>
+        <v>115.38</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>125.86</v>
+        <v>131</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>121.45</v>
+        <v>119.86</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>106.73</v>
+        <v>121.7</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>69.78</v>
+        <v>85.37</v>
       </c>
       <c r="M89" s="3" t="n">
-        <v>80.36</v>
+        <v>73.97</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>78.72</v>
+        <v>84.92</v>
       </c>
       <c r="O89" s="3" t="n">
-        <v>92.36</v>
+        <v>85.08</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>79.59</v>
+        <v>103.1</v>
       </c>
       <c r="Q89" s="3" t="n">
-        <v>81.05</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>100.53</v>
+        <v>100.15</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>87.25</v>
+        <v>87.17</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>75.25</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>55.98</v>
+        <v>59.96</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>53.04</v>
+        <v>84.63</v>
       </c>
       <c r="W89" s="3" t="n">
-        <v>38.03</v>
+        <v>42.58</v>
       </c>
       <c r="X89" s="3" t="n">
-        <v>34.96</v>
+        <v>38.4</v>
       </c>
       <c r="Y89" s="3" t="n">
-        <v>54.31</v>
+        <v>35.24</v>
       </c>
       <c r="Z89" s="3" t="n">
-        <v>58.05</v>
+        <v>55.76</v>
       </c>
     </row>
     <row r="90">
@@ -7901,22 +7901,22 @@
         <v>0</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>-20.48</v>
+        <v>-3.04</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>-24.79</v>
+        <v>-17.56</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>-30.24</v>
+        <v>-7.16</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>0</v>
+        <v>-7.18</v>
       </c>
       <c r="P90" s="3" t="n">
-        <v>-27.41</v>
+        <v>-13.49</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>-31.54</v>
+        <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0</v>
@@ -7928,10 +7928,10 @@
         <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>-6.79</v>
+        <v>-11.02</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>-10.02</v>
+        <v>-50.74</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
@@ -7940,10 +7940,10 @@
         <v>0</v>
       </c>
       <c r="Y90" s="3" t="n">
-        <v>-21.95</v>
+        <v>-0.67</v>
       </c>
       <c r="Z90" s="3" t="n">
-        <v>-30.56</v>
+        <v>-54</v>
       </c>
     </row>
     <row r="91">
@@ -7961,73 +7961,73 @@
         <v>-2.87</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-2.64</v>
+        <v>-2.7</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-2.32</v>
+        <v>-2.54</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>-2.37</v>
+        <v>-2.6</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>-4.6</v>
+        <v>-2.96</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>-5.92</v>
+        <v>-5.31</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-5.54</v>
+        <v>-4.82</v>
       </c>
       <c r="J91" s="3" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>-7.55</v>
+      </c>
+      <c r="L91" s="3" t="n">
         <v>-6.19</v>
       </c>
-      <c r="K91" s="3" t="n">
-        <v>-6.19</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>-5.05</v>
-      </c>
       <c r="M91" s="3" t="n">
-        <v>-6.41</v>
+        <v>-6.32</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>-6.21</v>
+        <v>-6.17</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>-5.54</v>
+        <v>-6</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>-7.06</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>-7.54</v>
+        <v>-6.02</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>-6.63</v>
+        <v>-6.51</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>-5.06</v>
+        <v>-5.4</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>-4.36</v>
+        <v>-4.23</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>-4.02</v>
+        <v>-4.4</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>-3.78</v>
+        <v>-7.99</v>
       </c>
       <c r="W91" s="3" t="n">
-        <v>-1.86</v>
+        <v>-2.51</v>
       </c>
       <c r="X91" s="3" t="n">
-        <v>-1.5</v>
+        <v>-1.92</v>
       </c>
       <c r="Y91" s="3" t="n">
-        <v>-3.43</v>
+        <v>-1.69</v>
       </c>
       <c r="Z91" s="3" t="n">
-        <v>-4.16</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="92">
@@ -8054,13 +8054,13 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0</v>

--- a/output/latest.xlsx
+++ b/output/latest.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>CreatedAt: 2026-10-15T04:15:43</t>
+          <t>CreatedAt: 2026-10-15T09:14:44</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
@@ -668,58 +668,58 @@
         <v>115.6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>120.5</v>
+        <v>120.99</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>120.32</v>
+        <v>119.56</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>122.86</v>
+        <v>116.68</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>86.29000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>75.01000000000001</v>
+        <v>82.44</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>85.88</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>86.13</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>104.54</v>
+        <v>80.44</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>92.11</v>
+        <v>71.52</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>101.48</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>88.59</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>76.55</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>61.05</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>86.44</v>
+        <v>61.75</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>43.07</v>
+        <v>60</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>38.66</v>
+        <v>46.43</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>35.52</v>
+        <v>35.1</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>56.5</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="5">
@@ -761,19 +761,19 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-17.56</v>
+        <v>-17.89</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-7.16</v>
+        <v>-10.22</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-7.18</v>
+        <v>-8.16</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>-13.49</v>
+        <v>-11.53</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
@@ -785,25 +785,25 @@
         <v>0</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0</v>
+        <v>-2.95</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>-11.02</v>
+        <v>-7.11</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-50.74</v>
+        <v>-14.66</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0</v>
+        <v>-16.12</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0</v>
+        <v>-7.56</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-54</v>
+        <v>-45.5</v>
       </c>
     </row>
     <row r="6">
@@ -836,58 +836,58 @@
         <v>-5.09</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-4.82</v>
+        <v>-4.72</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-5.53</v>
+        <v>-5.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>-6.39</v>
+        <v>-6.3</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>-5.27</v>
+        <v>-5.93</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>-5.28</v>
+        <v>-6.12</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-5.21</v>
+        <v>-6.21</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-4.95</v>
+        <v>-5.08</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-6.61</v>
+        <v>-5.43</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-5.07</v>
+        <v>-4.08</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-5.18</v>
+        <v>-4.39</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.99</v>
+        <v>-4.14</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-3.14</v>
+        <v>-4</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>-3.32</v>
+        <v>-3.74</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-6.17</v>
+        <v>-3.59</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-2.02</v>
+        <v>-3.73</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-1.66</v>
+        <v>-2.48</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.44</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-3.76</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="7">
@@ -1088,58 +1088,58 @@
         <v>116.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>124.82</v>
+        <v>125.46</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>124.12</v>
+        <v>123.82</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>125.73</v>
+        <v>119.98</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>89.16</v>
+        <v>100.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>76.98</v>
+        <v>85.36</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>87.76000000000001</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>88.58</v>
+        <v>78.3</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>108.34</v>
+        <v>83.12</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>95.08</v>
+        <v>73.47</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>103.95</v>
+        <v>84.42</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>89.88</v>
+        <v>91.02</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>77.67</v>
+        <v>83.25</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>62.31</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>89.39</v>
+        <v>63.17</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>43.65</v>
+        <v>61.03</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>39.61</v>
+        <v>47.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>36.82</v>
+        <v>36.18</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>57.15</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="10">
@@ -1181,19 +1181,19 @@
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-17.56</v>
+        <v>-17.89</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-7.16</v>
+        <v>-10.22</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-7.18</v>
+        <v>-8.16</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>-13.49</v>
+        <v>-11.53</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
@@ -1205,25 +1205,25 @@
         <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>-2.95</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>-11.02</v>
+        <v>-7.11</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>-50.74</v>
+        <v>-14.66</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>0</v>
+        <v>-16.12</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0</v>
+        <v>-7.56</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-54</v>
+        <v>-45.5</v>
       </c>
     </row>
     <row r="11">
@@ -1256,58 +1256,58 @@
         <v>-4.08</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.74</v>
+        <v>-1.24</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-3.52</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-2.4</v>
+        <v>-4.13</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-3.31</v>
+        <v>-3.2</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-3.32</v>
+        <v>-5.65</v>
       </c>
       <c r="O11" s="3" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>-2.49</v>
       </c>
-      <c r="P11" s="3" t="n">
+      <c r="V11" s="3" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="Z11" s="3" t="n">
         <v>-2.8</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>-3.11</v>
       </c>
     </row>
     <row r="12">
@@ -1508,58 +1508,58 @@
         <v>105.23</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>124.82</v>
+        <v>125.59</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>124.12</v>
+        <v>123.82</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>125.73</v>
+        <v>119.98</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>92.2</v>
+        <v>100.7</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>94.63</v>
+        <v>103.25</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>94.93000000000001</v>
+        <v>85.69</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>133.03</v>
+        <v>131.92</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>133.79</v>
+        <v>131.62</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>97.42</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>104.2</v>
+        <v>98.09</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>96.41</v>
+        <v>133.23</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>77.67</v>
+        <v>94.94</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>60.11</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>79.25</v>
+        <v>95.53</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>43.65</v>
+        <v>77.22</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>39.61</v>
+        <v>55.37</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>37.49</v>
+        <v>36.22</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>111.15</v>
+        <v>93.20999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1607,31 +1607,31 @@
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0</v>
+        <v>-13.38</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>37.27</v>
+        <v>45.38</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>11.96</v>
+        <v>36.96</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>2.24</v>
+        <v>24.68</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0.24</v>
+        <v>13.67</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>6.53</v>
+        <v>42.21</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>-13.23</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>-60.89</v>
+        <v>17.7</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0</v>
@@ -1676,58 +1676,58 @@
         <v>-4.08</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.5</v>
+        <v>-0.13</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.74</v>
+        <v>-1.24</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-3.52</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-2.4</v>
+        <v>-4.13</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-3.22</v>
+        <v>-3.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>-3.32</v>
+        <v>-5.65</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>-2.79</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="U16" s="3" t="n">
         <v>-2.49</v>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="V16" s="3" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="Z16" s="3" t="n">
         <v>-2.8</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>-0.71</v>
-      </c>
-      <c r="Y16" s="3" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v>-3.11</v>
       </c>
     </row>
     <row r="17">
@@ -1928,58 +1928,58 @@
         <v>115.49</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>131.12</v>
+        <v>131</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>120.21</v>
+        <v>119.79</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>122.39</v>
+        <v>116.46</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>82.77</v>
+        <v>98.62</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>56.25</v>
+        <v>63.49</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>78.01000000000001</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>78.16</v>
+        <v>67.55</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>89.95</v>
+        <v>68.09</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>91.76000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>101</v>
+        <v>82.42</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>88</v>
+        <v>89.64</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>76.11</v>
+        <v>78.52</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>49.08</v>
+        <v>61.5</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>32.59</v>
+        <v>46.02</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>42.86</v>
+        <v>42.81</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>38.58</v>
+        <v>38.39</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>34.71</v>
+        <v>35.06</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>-0.44</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2021,19 +2021,19 @@
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-6.23</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-35.97</v>
+        <v>-36.65</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-14.68</v>
+        <v>-20.94</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-14.71</v>
+        <v>-16.71</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-27.63</v>
+        <v>-23.63</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
@@ -2045,25 +2045,25 @@
         <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>0</v>
+        <v>-6.05</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>-22.58</v>
+        <v>-14.56</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>-103.94</v>
+        <v>-30.04</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>0</v>
+        <v>-33.02</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0</v>
+        <v>-15.49</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>-1.37</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>-110.62</v>
+        <v>-93.22</v>
       </c>
     </row>
     <row r="21">
@@ -2096,58 +2096,58 @@
         <v>-5.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-4.7</v>
+        <v>-4.49</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-5.65</v>
+        <v>-5.27</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>-6.85</v>
+        <v>-6.52</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-5.61</v>
+        <v>-6.21</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>-5.63</v>
+        <v>-6.31</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>-5.56</v>
+        <v>-6.58</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>-5.39</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>-7.05</v>
+        <v>-5.69</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>-5.41</v>
+        <v>-4.35</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>-5.66</v>
+        <v>-4.78</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>-4.58</v>
+        <v>-4.57</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>-3.58</v>
+        <v>-4.48</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>-3.73</v>
+        <v>-4.11</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>-6.83</v>
+        <v>-3.95</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-2.23</v>
+        <v>-4.02</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.59</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.47</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>-4.08</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="22">
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>10.5</v>
+        <v>9.77</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>0</v>
@@ -2348,58 +2348,58 @@
         <v>115.49</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>120.62</v>
+        <v>121.23</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>120.21</v>
+        <v>119.79</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>122.39</v>
+        <v>116.46</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>85.95</v>
+        <v>98.62</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>74.66</v>
+        <v>82.25</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>85.53</v>
+        <v>87.92</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>85.69</v>
+        <v>76.11</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>104.09</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>91.76000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>101</v>
+        <v>82.42</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>88</v>
+        <v>89.64</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>76.11</v>
+        <v>81.62</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>60.64</v>
+        <v>68.95</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>85.79000000000001</v>
+        <v>61.39</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>42.86</v>
+        <v>59.71</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>38.58</v>
+        <v>46.32</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>35.41</v>
+        <v>35.06</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>56.18</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="25">
@@ -2441,19 +2441,19 @@
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-17.56</v>
+        <v>-17.89</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>-7.16</v>
+        <v>-10.22</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>-7.18</v>
+        <v>-8.16</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>-13.49</v>
+        <v>-11.53</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>0</v>
@@ -2465,25 +2465,25 @@
         <v>0</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>0</v>
+        <v>-2.95</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>-11.02</v>
+        <v>-7.11</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>-50.74</v>
+        <v>-14.66</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0</v>
+        <v>-16.12</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>0</v>
+        <v>-7.56</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>-54</v>
+        <v>-45.5</v>
       </c>
     </row>
     <row r="26">
@@ -2516,58 +2516,58 @@
         <v>-5.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-4.7</v>
+        <v>-4.49</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-5.65</v>
+        <v>-5.27</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-6.85</v>
+        <v>-6.52</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-5.61</v>
+        <v>-6.21</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-5.63</v>
+        <v>-6.31</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-5.56</v>
+        <v>-6.58</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>-5.39</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-7.05</v>
+        <v>-5.69</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-5.41</v>
+        <v>-4.35</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>-5.66</v>
+        <v>-4.78</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>-4.58</v>
+        <v>-4.57</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>-3.58</v>
+        <v>-4.48</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>-3.73</v>
+        <v>-4.11</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>-6.83</v>
+        <v>-3.95</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>-2.23</v>
+        <v>-4.02</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>-1.74</v>
+        <v>-2.59</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>-1.52</v>
+        <v>-1.47</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>-4.08</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="27">
@@ -2771,55 +2771,55 @@
         <v>131</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>119.86</v>
+        <v>119.79</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>121.7</v>
+        <v>116.13</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>82.19</v>
+        <v>98.34</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>55.56</v>
+        <v>63.21</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>77.55</v>
+        <v>67</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>88.95999999999999</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>91.15000000000001</v>
+        <v>70.92</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>100.15</v>
+        <v>81.88</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>87.25</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>75.45999999999999</v>
+        <v>77.88</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>48.4</v>
+        <v>60.85</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>31.43</v>
+        <v>45.52</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>42.58</v>
+        <v>42.45</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>38.4</v>
+        <v>38.14</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>34.54</v>
+        <v>35</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>-0.86</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="30">
@@ -2861,19 +2861,19 @@
         <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-6.23</v>
+        <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-35.97</v>
+        <v>-36.65</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-14.68</v>
+        <v>-20.94</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-14.71</v>
+        <v>-16.71</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-27.63</v>
+        <v>-23.63</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>0</v>
@@ -2885,25 +2885,25 @@
         <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>0</v>
+        <v>-6.05</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>-22.58</v>
+        <v>-14.56</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>-103.94</v>
+        <v>-30.04</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>0</v>
+        <v>-33.02</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>0</v>
+        <v>-15.49</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>-1.37</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>-110.62</v>
+        <v>-93.22</v>
       </c>
     </row>
     <row r="31">
@@ -2936,58 +2936,58 @@
         <v>-5.31</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-4.82</v>
+        <v>-4.49</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-5.99</v>
+        <v>-5.27</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-7.55</v>
+        <v>-6.85</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-6.19</v>
+        <v>-6.49</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-6.32</v>
+        <v>-6.59</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>-6.17</v>
+        <v>-6.85</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-6</v>
+        <v>-5.94</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-8.039999999999999</v>
+        <v>-6.2</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>-6.02</v>
+        <v>-4.68</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>-6.51</v>
+        <v>-5.32</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>-5.32</v>
+        <v>-5.16</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-4.23</v>
+        <v>-5.12</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>-4.4</v>
+        <v>-4.75</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>-7.99</v>
+        <v>-4.46</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>-2.51</v>
+        <v>-4.38</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>-1.92</v>
+        <v>-2.84</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>-1.69</v>
+        <v>-1.54</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>-4.5</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="32">
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>10.5</v>
+        <v>9.77</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>0</v>
@@ -3191,55 +3191,55 @@
         <v>132.95</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>127.65</v>
+        <v>127.22</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>128.86</v>
+        <v>123.1</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>94.7</v>
+        <v>101.58</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>96.79000000000001</v>
+        <v>105.29</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>97.09</v>
+        <v>89.13</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>135.62</v>
+        <v>134.06</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>137.47</v>
+        <v>134.26</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>100.4</v>
+        <v>100.28</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>106.9</v>
+        <v>100.01</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>98.28</v>
+        <v>134.75</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>79.37</v>
+        <v>96.81</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>61.93</v>
+        <v>71</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>97.39</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>44.38</v>
+        <v>78.36</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>40.52</v>
+        <v>56.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>38.56</v>
+        <v>37.1</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>113.24</v>
+        <v>94.87</v>
       </c>
     </row>
     <row r="35">
@@ -3287,31 +3287,31 @@
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0</v>
+        <v>-12.04</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>37.27</v>
+        <v>45.38</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>11.96</v>
+        <v>36.96</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>2.24</v>
+        <v>24.68</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>0.24</v>
+        <v>13.67</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>6.53</v>
+        <v>42.21</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0</v>
+        <v>8.73</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>-13.23</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>-60.89</v>
+        <v>17.7</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3320,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>0</v>
@@ -3356,58 +3356,58 @@
         <v>-1.19</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.21</v>
+        <v>3.62</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>-0.39</v>
+        <v>0.12</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.09</v>
+        <v>-3.25</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-1.06</v>
+        <v>-1.16</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-1.17</v>
+        <v>-3.54</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.1</v>
+        <v>-0.98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.88</v>
+        <v>-0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>-0.83</v>
+        <v>-1.67</v>
       </c>
       <c r="T36" s="3" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>0.43</v>
-      </c>
       <c r="W36" s="3" t="n">
-        <v>-0.71</v>
+        <v>-1.49</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>-1.02</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="37">
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>4.42</v>
+        <v>3.62</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>0</v>
@@ -3608,58 +3608,58 @@
         <v>115.6</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>120.5</v>
+        <v>120.99</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>120.32</v>
+        <v>119.56</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>122.86</v>
+        <v>116.68</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>86.29000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>75.01000000000001</v>
+        <v>82.44</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>85.88</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>86.13</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>104.54</v>
+        <v>80.44</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>92.11</v>
+        <v>71.52</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>101.48</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>88.59</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>76.55</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>61.05</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>86.44</v>
+        <v>61.75</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>43.07</v>
+        <v>60</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>38.66</v>
+        <v>46.43</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>35.52</v>
+        <v>35.1</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>56.5</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="40">
@@ -3701,19 +3701,19 @@
         <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-17.56</v>
+        <v>-17.89</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-7.16</v>
+        <v>-10.22</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-7.18</v>
+        <v>-8.16</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-13.49</v>
+        <v>-11.53</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>0</v>
@@ -3725,25 +3725,25 @@
         <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>-2.95</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>-11.02</v>
+        <v>-7.11</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>-50.74</v>
+        <v>-14.66</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>0</v>
+        <v>-16.12</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>0</v>
+        <v>-7.56</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>-54</v>
+        <v>-45.5</v>
       </c>
     </row>
     <row r="41">
@@ -3776,58 +3776,58 @@
         <v>-5.09</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-4.82</v>
+        <v>-4.72</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-5.53</v>
+        <v>-5.5</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-6.39</v>
+        <v>-6.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-5.27</v>
+        <v>-5.93</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>-5.28</v>
+        <v>-6.12</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-5.21</v>
+        <v>-6.21</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-4.95</v>
+        <v>-5.08</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-6.61</v>
+        <v>-5.43</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>-5.07</v>
+        <v>-4.08</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>-5.18</v>
+        <v>-4.39</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>-3.99</v>
+        <v>-4.14</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>-3.14</v>
+        <v>-4</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>-3.32</v>
+        <v>-3.74</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>-6.17</v>
+        <v>-3.59</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>-2.02</v>
+        <v>-3.73</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>-1.66</v>
+        <v>-2.48</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>-1.41</v>
+        <v>-1.44</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>-3.76</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="42">
@@ -4028,58 +4028,58 @@
         <v>120.2</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>123.96</v>
+        <v>124.34</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>124.24</v>
+        <v>123.46</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>127.34</v>
+        <v>121.76</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>92.02</v>
+        <v>102.88</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>95.28</v>
+        <v>104.16</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>95.86</v>
+        <v>102.57</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>96.14</v>
+        <v>87.39</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>121.95</v>
+        <v>95.02</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>94.8</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="R44" s="3" t="n">
-        <v>104.98</v>
+        <v>85.58</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>91.75</v>
+        <v>93.09</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>79.14</v>
+        <v>88</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>74.56999999999999</v>
+        <v>78.91</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>142.36</v>
+        <v>79.06</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>44.73</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>39.88</v>
+        <v>55.69</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>37.26</v>
+        <v>36.14</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>114.14</v>
+        <v>95.72</v>
       </c>
     </row>
     <row r="45">
@@ -4196,58 +4196,58 @@
         <v>-0.48</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>-1.36</v>
+        <v>-1.37</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>-1.62</v>
+        <v>-1.6</v>
       </c>
       <c r="K46" s="3" t="n">
